--- a/dados_formularios.xlsx
+++ b/dados_formularios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL7"/>
+  <dimension ref="A1:EL9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3503,47 +3503,33 @@
           <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0121000</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>01210000010</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C7" t="n">
+        <v>84</v>
+      </c>
+      <c r="D7" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>22133</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="L7" t="n">
+        <v>408</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -3555,25 +3541,19 @@
           <t>robo.relatorio@folhatech.com.br</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="O7" t="n">
+        <v>408</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Robo Cadastro Cliente</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1780628400</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>1780666934</t>
-        </is>
+      <c r="Q7" t="n">
+        <v>1780628400</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1780666934</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -3595,10 +3575,8 @@
           <t>03/06/2026 17:13</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="W7" t="n">
+        <v>22133</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -3610,35 +3588,27 @@
           <t>04/06/2026 17:25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="Z7" t="n">
+        <v>127857</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>08 - Confecção e assinatura (Contrato)</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>487</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
           <t>Pedro Santana</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>0121</t>
-        </is>
+      <c r="AE7" t="n">
+        <v>121</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -3655,10 +3625,8 @@
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>127857</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
@@ -3690,10 +3658,8 @@
           <t>Aumento de quadro</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>3500.00</t>
-        </is>
+      <c r="AT7" t="n">
+        <v>3500</v>
       </c>
       <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="inlineStr">
@@ -3821,10 +3787,8 @@
           <t>Pai</t>
         </is>
       </c>
-      <c r="DE7" t="inlineStr">
-        <is>
-          <t>1121029128</t>
-        </is>
+      <c r="DE7" t="n">
+        <v>1121029128</v>
       </c>
       <c r="DF7" t="inlineStr">
         <is>
@@ -3841,15 +3805,11 @@
           <t>Namorado(a)</t>
         </is>
       </c>
-      <c r="DI7" t="inlineStr">
-        <is>
-          <t>212122</t>
-        </is>
-      </c>
-      <c r="DJ7" t="inlineStr">
-        <is>
-          <t>12344</t>
-        </is>
+      <c r="DI7" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>12344</v>
       </c>
       <c r="DK7" t="inlineStr">
         <is>
@@ -3861,10 +3821,8 @@
           <t>pedro.santana@folhatech.com.br</t>
         </is>
       </c>
-      <c r="DM7" t="inlineStr">
-        <is>
-          <t>121212212112</t>
-        </is>
+      <c r="DM7" t="n">
+        <v>121212212112</v>
       </c>
       <c r="DN7" t="inlineStr"/>
       <c r="DO7" t="inlineStr">
@@ -3882,15 +3840,11 @@
           <t>Conta Corrente</t>
         </is>
       </c>
-      <c r="DR7" t="inlineStr">
-        <is>
-          <t>12121</t>
-        </is>
-      </c>
-      <c r="DS7" t="inlineStr">
-        <is>
-          <t>3144</t>
-        </is>
+      <c r="DR7" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>3144</v>
       </c>
       <c r="DT7" t="inlineStr">
         <is>
@@ -3907,10 +3861,8 @@
           <t>etetetet</t>
         </is>
       </c>
-      <c r="DW7" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="DW7" t="n">
+        <v>124</v>
       </c>
       <c r="DX7" t="inlineStr">
         <is>
@@ -3975,6 +3927,926 @@
         </is>
       </c>
       <c r="EL7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>05/06/2026, 10:56:41</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>84</v>
+      </c>
+      <c r="D8" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>408</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>408</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>1780628400</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1780667320</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>05/06/2026 10:48</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE8" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT8" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr"/>
+      <c r="CE8" t="inlineStr"/>
+      <c r="CF8" t="inlineStr"/>
+      <c r="CG8" t="inlineStr"/>
+      <c r="CH8" t="inlineStr"/>
+      <c r="CI8" t="inlineStr"/>
+      <c r="CJ8" t="inlineStr"/>
+      <c r="CK8" t="inlineStr"/>
+      <c r="CL8" t="inlineStr"/>
+      <c r="CM8" t="inlineStr"/>
+      <c r="CN8" t="inlineStr"/>
+      <c r="CO8" t="inlineStr"/>
+      <c r="CP8" t="inlineStr"/>
+      <c r="CQ8" t="inlineStr"/>
+      <c r="CR8" t="inlineStr"/>
+      <c r="CS8" t="inlineStr"/>
+      <c r="CT8" t="inlineStr"/>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC8" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD8" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE8" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF8" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG8" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH8" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI8" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK8" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL8" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM8" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN8" t="inlineStr"/>
+      <c r="DO8" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP8" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ8" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR8" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT8" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU8" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV8" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW8" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE8" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF8" t="inlineStr"/>
+      <c r="EG8" t="inlineStr"/>
+      <c r="EH8" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI8" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ8" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK8" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>05/06/2026, 10:58:51</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0121000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>01210000010</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1780628400</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1780667450</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>05/06/2026 10:50</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>3500.00</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="inlineStr"/>
+      <c r="CI9" t="inlineStr"/>
+      <c r="CJ9" t="inlineStr"/>
+      <c r="CK9" t="inlineStr"/>
+      <c r="CL9" t="inlineStr"/>
+      <c r="CM9" t="inlineStr"/>
+      <c r="CN9" t="inlineStr"/>
+      <c r="CO9" t="inlineStr"/>
+      <c r="CP9" t="inlineStr"/>
+      <c r="CQ9" t="inlineStr"/>
+      <c r="CR9" t="inlineStr"/>
+      <c r="CS9" t="inlineStr"/>
+      <c r="CT9" t="inlineStr"/>
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB9" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC9" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD9" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
+          <t>1121029128</t>
+        </is>
+      </c>
+      <c r="DF9" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG9" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI9" t="inlineStr">
+        <is>
+          <t>212122</t>
+        </is>
+      </c>
+      <c r="DJ9" t="inlineStr">
+        <is>
+          <t>12344</t>
+        </is>
+      </c>
+      <c r="DK9" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL9" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM9" t="inlineStr">
+        <is>
+          <t>121212212112</t>
+        </is>
+      </c>
+      <c r="DN9" t="inlineStr"/>
+      <c r="DO9" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR9" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
+          <t>3144</t>
+        </is>
+      </c>
+      <c r="DT9" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU9" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV9" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr"/>
+      <c r="EG9" t="inlineStr"/>
+      <c r="EH9" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI9" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ9" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK9" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4209,13 +5081,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974F33F7-5E24-44D5-91E3-C646EF4340AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08CAB4CC-F01A-4A7D-9B08-31B78D4FE740}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13C876D4-FB18-4A23-9087-8C0E0D8E7E2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D565463-EA89-4DEE-A91D-49D4A0C39119}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50CE03C6-A416-498C-B797-9A86597A19C1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1099D124-125E-45CF-9E63-66376AF57B53}"/>
 </file>
--- a/dados_formularios.xlsx
+++ b/dados_formularios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL9"/>
+  <dimension ref="A1:EL12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4375,47 +4375,33 @@
           <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0121000</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>01210000010</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C9" t="n">
+        <v>84</v>
+      </c>
+      <c r="D9" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22133</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="L9" t="n">
+        <v>408</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -4427,25 +4413,19 @@
           <t>robo.relatorio@folhatech.com.br</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="O9" t="n">
+        <v>408</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Robo Cadastro Cliente</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>1780628400</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>1780667450</t>
-        </is>
+      <c r="Q9" t="n">
+        <v>1780628400</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1780667450</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -4467,10 +4447,8 @@
           <t>03/06/2026 17:13</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="W9" t="n">
+        <v>22133</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -4482,35 +4460,27 @@
           <t>04/06/2026 17:25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="Z9" t="n">
+        <v>127857</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>08 - Confecção e assinatura (Contrato)</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
+      <c r="AB9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>487</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
           <t>Pedro Santana</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>0121</t>
-        </is>
+      <c r="AE9" t="n">
+        <v>121</v>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
@@ -4527,10 +4497,8 @@
       <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>127857</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -4562,10 +4530,8 @@
           <t>Aumento de quadro</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>3500.00</t>
-        </is>
+      <c r="AT9" t="n">
+        <v>3500</v>
       </c>
       <c r="AU9" t="inlineStr"/>
       <c r="AV9" t="inlineStr">
@@ -4693,10 +4659,8 @@
           <t>Pai</t>
         </is>
       </c>
-      <c r="DE9" t="inlineStr">
-        <is>
-          <t>1121029128</t>
-        </is>
+      <c r="DE9" t="n">
+        <v>1121029128</v>
       </c>
       <c r="DF9" t="inlineStr">
         <is>
@@ -4713,15 +4677,11 @@
           <t>Namorado(a)</t>
         </is>
       </c>
-      <c r="DI9" t="inlineStr">
-        <is>
-          <t>212122</t>
-        </is>
-      </c>
-      <c r="DJ9" t="inlineStr">
-        <is>
-          <t>12344</t>
-        </is>
+      <c r="DI9" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>12344</v>
       </c>
       <c r="DK9" t="inlineStr">
         <is>
@@ -4733,10 +4693,8 @@
           <t>pedro.santana@folhatech.com.br</t>
         </is>
       </c>
-      <c r="DM9" t="inlineStr">
-        <is>
-          <t>121212212112</t>
-        </is>
+      <c r="DM9" t="n">
+        <v>121212212112</v>
       </c>
       <c r="DN9" t="inlineStr"/>
       <c r="DO9" t="inlineStr">
@@ -4754,15 +4712,11 @@
           <t>Conta Corrente</t>
         </is>
       </c>
-      <c r="DR9" t="inlineStr">
-        <is>
-          <t>12121</t>
-        </is>
-      </c>
-      <c r="DS9" t="inlineStr">
-        <is>
-          <t>3144</t>
-        </is>
+      <c r="DR9" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>3144</v>
       </c>
       <c r="DT9" t="inlineStr">
         <is>
@@ -4779,10 +4733,8 @@
           <t>etetetet</t>
         </is>
       </c>
-      <c r="DW9" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="DW9" t="n">
+        <v>124</v>
       </c>
       <c r="DX9" t="inlineStr">
         <is>
@@ -4847,247 +4799,1364 @@
         </is>
       </c>
       <c r="EL9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>05/06/2026, 13:45:43</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>84</v>
+      </c>
+      <c r="D10" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>408</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>408</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>1780628400</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1780677461</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>05/06/2026 13:37</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE10" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT10" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="inlineStr"/>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="inlineStr"/>
+      <c r="CA10" t="inlineStr"/>
+      <c r="CB10" t="inlineStr"/>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr"/>
+      <c r="CE10" t="inlineStr"/>
+      <c r="CF10" t="inlineStr"/>
+      <c r="CG10" t="inlineStr"/>
+      <c r="CH10" t="inlineStr"/>
+      <c r="CI10" t="inlineStr"/>
+      <c r="CJ10" t="inlineStr"/>
+      <c r="CK10" t="inlineStr"/>
+      <c r="CL10" t="inlineStr"/>
+      <c r="CM10" t="inlineStr"/>
+      <c r="CN10" t="inlineStr"/>
+      <c r="CO10" t="inlineStr"/>
+      <c r="CP10" t="inlineStr"/>
+      <c r="CQ10" t="inlineStr"/>
+      <c r="CR10" t="inlineStr"/>
+      <c r="CS10" t="inlineStr"/>
+      <c r="CT10" t="inlineStr"/>
+      <c r="CU10" t="inlineStr"/>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB10" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC10" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD10" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE10" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF10" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG10" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH10" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI10" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK10" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL10" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM10" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN10" t="inlineStr"/>
+      <c r="DO10" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP10" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ10" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR10" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT10" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU10" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV10" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW10" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX10" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY10" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ10" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED10" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr"/>
+      <c r="EG10" t="inlineStr"/>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI10" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ10" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK10" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>05/06/2026, 13:52:22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>84</v>
+      </c>
+      <c r="D11" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>408</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>408</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>1780628400</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1780677859</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>05/06/2026 13:44</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT11" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr"/>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
+      <c r="CA11" t="inlineStr"/>
+      <c r="CB11" t="inlineStr"/>
+      <c r="CC11" t="inlineStr"/>
+      <c r="CD11" t="inlineStr"/>
+      <c r="CE11" t="inlineStr"/>
+      <c r="CF11" t="inlineStr"/>
+      <c r="CG11" t="inlineStr"/>
+      <c r="CH11" t="inlineStr"/>
+      <c r="CI11" t="inlineStr"/>
+      <c r="CJ11" t="inlineStr"/>
+      <c r="CK11" t="inlineStr"/>
+      <c r="CL11" t="inlineStr"/>
+      <c r="CM11" t="inlineStr"/>
+      <c r="CN11" t="inlineStr"/>
+      <c r="CO11" t="inlineStr"/>
+      <c r="CP11" t="inlineStr"/>
+      <c r="CQ11" t="inlineStr"/>
+      <c r="CR11" t="inlineStr"/>
+      <c r="CS11" t="inlineStr"/>
+      <c r="CT11" t="inlineStr"/>
+      <c r="CU11" t="inlineStr"/>
+      <c r="CV11" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW11" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX11" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY11" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ11" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA11" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB11" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC11" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD11" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE11" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF11" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG11" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH11" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI11" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK11" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL11" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM11" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN11" t="inlineStr"/>
+      <c r="DO11" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP11" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ11" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR11" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT11" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU11" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV11" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW11" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX11" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY11" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ11" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA11" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB11" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC11" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED11" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE11" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF11" t="inlineStr"/>
+      <c r="EG11" t="inlineStr"/>
+      <c r="EH11" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI11" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ11" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK11" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>05/06/2026, 13:53:11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0121000</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>01210000010</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1780628400</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1780677909</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>05/06/2026 13:45</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>3500.00</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
+      <c r="BQ12" t="inlineStr"/>
+      <c r="BR12" t="inlineStr"/>
+      <c r="BS12" t="inlineStr"/>
+      <c r="BT12" t="inlineStr"/>
+      <c r="BU12" t="inlineStr"/>
+      <c r="BV12" t="inlineStr"/>
+      <c r="BW12" t="inlineStr"/>
+      <c r="BX12" t="inlineStr"/>
+      <c r="BY12" t="inlineStr"/>
+      <c r="BZ12" t="inlineStr"/>
+      <c r="CA12" t="inlineStr"/>
+      <c r="CB12" t="inlineStr"/>
+      <c r="CC12" t="inlineStr"/>
+      <c r="CD12" t="inlineStr"/>
+      <c r="CE12" t="inlineStr"/>
+      <c r="CF12" t="inlineStr"/>
+      <c r="CG12" t="inlineStr"/>
+      <c r="CH12" t="inlineStr"/>
+      <c r="CI12" t="inlineStr"/>
+      <c r="CJ12" t="inlineStr"/>
+      <c r="CK12" t="inlineStr"/>
+      <c r="CL12" t="inlineStr"/>
+      <c r="CM12" t="inlineStr"/>
+      <c r="CN12" t="inlineStr"/>
+      <c r="CO12" t="inlineStr"/>
+      <c r="CP12" t="inlineStr"/>
+      <c r="CQ12" t="inlineStr"/>
+      <c r="CR12" t="inlineStr"/>
+      <c r="CS12" t="inlineStr"/>
+      <c r="CT12" t="inlineStr"/>
+      <c r="CU12" t="inlineStr"/>
+      <c r="CV12" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW12" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX12" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY12" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ12" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA12" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB12" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC12" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD12" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE12" t="inlineStr">
+        <is>
+          <t>1121029128</t>
+        </is>
+      </c>
+      <c r="DF12" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG12" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH12" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI12" t="inlineStr">
+        <is>
+          <t>212122</t>
+        </is>
+      </c>
+      <c r="DJ12" t="inlineStr">
+        <is>
+          <t>12344</t>
+        </is>
+      </c>
+      <c r="DK12" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL12" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM12" t="inlineStr">
+        <is>
+          <t>121212212112</t>
+        </is>
+      </c>
+      <c r="DN12" t="inlineStr"/>
+      <c r="DO12" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP12" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ12" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR12" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+      <c r="DS12" t="inlineStr">
+        <is>
+          <t>3144</t>
+        </is>
+      </c>
+      <c r="DT12" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU12" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV12" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW12" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="DX12" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY12" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ12" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA12" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB12" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC12" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED12" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE12" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF12" t="inlineStr"/>
+      <c r="EG12" t="inlineStr"/>
+      <c r="EH12" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI12" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ12" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK12" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B5FCC50092DEF84396333E47DAEFEB5E" ma:contentTypeVersion="13" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="3f5dff31fa7a2b799118bc7c00128ae3">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5df11fd7-6aff-4cc6-9d69-481ebafd3f51" xmlns:ns3="ba98ff8d-cf9c-4574-b9ff-8782fca0b7db" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5a22452f93ee1f3c8f432c572ea5d732" ns2:_="" ns3:_="">
-    <xsd:import namespace="5df11fd7-6aff-4cc6-9d69-481ebafd3f51"/>
-    <xsd:import namespace="ba98ff8d-cf9c-4574-b9ff-8782fca0b7db"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="5df11fd7-6aff-4cc6-9d69-481ebafd3f51" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4410abd1-e841-4d52-8c09-cc5936d54c0f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ba98ff8d-cf9c-4574-b9ff-8782fca0b7db" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{78d918e0-dd2a-4d55-9cd7-b9c5d47e1b97}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="ba98ff8d-cf9c-4574-b9ff-8782fca0b7db">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ba98ff8d-cf9c-4574-b9ff-8782fca0b7db" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5df11fd7-6aff-4cc6-9d69-481ebafd3f51">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08CAB4CC-F01A-4A7D-9B08-31B78D4FE740}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D565463-EA89-4DEE-A91D-49D4A0C39119}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1099D124-125E-45CF-9E63-66376AF57B53}"/>
 </file>
--- a/dados_formularios.xlsx
+++ b/dados_formularios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL12"/>
+  <dimension ref="A1:EL18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5683,47 +5683,33 @@
           <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0121000</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>01210000010</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C12" t="n">
+        <v>84</v>
+      </c>
+      <c r="D12" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>22133</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="L12" t="n">
+        <v>408</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -5735,25 +5721,19 @@
           <t>robo.relatorio@folhatech.com.br</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="O12" t="n">
+        <v>408</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Robo Cadastro Cliente</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1780628400</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1780677909</t>
-        </is>
+      <c r="Q12" t="n">
+        <v>1780628400</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1780677909</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -5775,10 +5755,8 @@
           <t>03/06/2026 17:13</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="W12" t="n">
+        <v>22133</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -5790,35 +5768,27 @@
           <t>04/06/2026 17:25</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="Z12" t="n">
+        <v>127857</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>08 - Confecção e assinatura (Contrato)</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>487</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
           <t>Pedro Santana</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>0121</t>
-        </is>
+      <c r="AE12" t="n">
+        <v>121</v>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
@@ -5835,10 +5805,8 @@
       <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr"/>
       <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>127857</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
@@ -5870,10 +5838,8 @@
           <t>Aumento de quadro</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>3500.00</t>
-        </is>
+      <c r="AT12" t="n">
+        <v>3500</v>
       </c>
       <c r="AU12" t="inlineStr"/>
       <c r="AV12" t="inlineStr">
@@ -6001,10 +5967,8 @@
           <t>Pai</t>
         </is>
       </c>
-      <c r="DE12" t="inlineStr">
-        <is>
-          <t>1121029128</t>
-        </is>
+      <c r="DE12" t="n">
+        <v>1121029128</v>
       </c>
       <c r="DF12" t="inlineStr">
         <is>
@@ -6021,15 +5985,11 @@
           <t>Namorado(a)</t>
         </is>
       </c>
-      <c r="DI12" t="inlineStr">
-        <is>
-          <t>212122</t>
-        </is>
-      </c>
-      <c r="DJ12" t="inlineStr">
-        <is>
-          <t>12344</t>
-        </is>
+      <c r="DI12" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>12344</v>
       </c>
       <c r="DK12" t="inlineStr">
         <is>
@@ -6041,10 +6001,8 @@
           <t>pedro.santana@folhatech.com.br</t>
         </is>
       </c>
-      <c r="DM12" t="inlineStr">
-        <is>
-          <t>121212212112</t>
-        </is>
+      <c r="DM12" t="n">
+        <v>121212212112</v>
       </c>
       <c r="DN12" t="inlineStr"/>
       <c r="DO12" t="inlineStr">
@@ -6062,15 +6020,11 @@
           <t>Conta Corrente</t>
         </is>
       </c>
-      <c r="DR12" t="inlineStr">
-        <is>
-          <t>12121</t>
-        </is>
-      </c>
-      <c r="DS12" t="inlineStr">
-        <is>
-          <t>3144</t>
-        </is>
+      <c r="DR12" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>3144</v>
       </c>
       <c r="DT12" t="inlineStr">
         <is>
@@ -6087,10 +6041,8 @@
           <t>etetetet</t>
         </is>
       </c>
-      <c r="DW12" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="DW12" t="n">
+        <v>124</v>
       </c>
       <c r="DX12" t="inlineStr">
         <is>
@@ -6155,8 +6107,2911 @@
         </is>
       </c>
       <c r="EL12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>05/06/2026, 15:12:41</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>84</v>
+      </c>
+      <c r="D13" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>408</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>408</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>1780628400</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1780682678</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>05/06/2026 15:04</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE13" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT13" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="inlineStr"/>
+      <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="inlineStr"/>
+      <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr"/>
+      <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="inlineStr"/>
+      <c r="CA13" t="inlineStr"/>
+      <c r="CB13" t="inlineStr"/>
+      <c r="CC13" t="inlineStr"/>
+      <c r="CD13" t="inlineStr"/>
+      <c r="CE13" t="inlineStr"/>
+      <c r="CF13" t="inlineStr"/>
+      <c r="CG13" t="inlineStr"/>
+      <c r="CH13" t="inlineStr"/>
+      <c r="CI13" t="inlineStr"/>
+      <c r="CJ13" t="inlineStr"/>
+      <c r="CK13" t="inlineStr"/>
+      <c r="CL13" t="inlineStr"/>
+      <c r="CM13" t="inlineStr"/>
+      <c r="CN13" t="inlineStr"/>
+      <c r="CO13" t="inlineStr"/>
+      <c r="CP13" t="inlineStr"/>
+      <c r="CQ13" t="inlineStr"/>
+      <c r="CR13" t="inlineStr"/>
+      <c r="CS13" t="inlineStr"/>
+      <c r="CT13" t="inlineStr"/>
+      <c r="CU13" t="inlineStr"/>
+      <c r="CV13" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW13" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX13" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY13" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ13" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA13" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB13" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC13" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD13" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE13" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF13" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG13" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH13" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI13" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK13" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL13" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM13" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN13" t="inlineStr"/>
+      <c r="DO13" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP13" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ13" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR13" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT13" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU13" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV13" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW13" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX13" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY13" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ13" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA13" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB13" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC13" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED13" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE13" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF13" t="inlineStr"/>
+      <c r="EG13" t="inlineStr"/>
+      <c r="EH13" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI13" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ13" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK13" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>05/06/2026, 16:03:47</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>84</v>
+      </c>
+      <c r="D14" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>408</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>408</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1780628400</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1780685744</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>05/06/2026 15:55</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z14" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE14" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr"/>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr"/>
+      <c r="BV14" t="inlineStr"/>
+      <c r="BW14" t="inlineStr"/>
+      <c r="BX14" t="inlineStr"/>
+      <c r="BY14" t="inlineStr"/>
+      <c r="BZ14" t="inlineStr"/>
+      <c r="CA14" t="inlineStr"/>
+      <c r="CB14" t="inlineStr"/>
+      <c r="CC14" t="inlineStr"/>
+      <c r="CD14" t="inlineStr"/>
+      <c r="CE14" t="inlineStr"/>
+      <c r="CF14" t="inlineStr"/>
+      <c r="CG14" t="inlineStr"/>
+      <c r="CH14" t="inlineStr"/>
+      <c r="CI14" t="inlineStr"/>
+      <c r="CJ14" t="inlineStr"/>
+      <c r="CK14" t="inlineStr"/>
+      <c r="CL14" t="inlineStr"/>
+      <c r="CM14" t="inlineStr"/>
+      <c r="CN14" t="inlineStr"/>
+      <c r="CO14" t="inlineStr"/>
+      <c r="CP14" t="inlineStr"/>
+      <c r="CQ14" t="inlineStr"/>
+      <c r="CR14" t="inlineStr"/>
+      <c r="CS14" t="inlineStr"/>
+      <c r="CT14" t="inlineStr"/>
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW14" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX14" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY14" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ14" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA14" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB14" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC14" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD14" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE14" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF14" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG14" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH14" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI14" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK14" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL14" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM14" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN14" t="inlineStr"/>
+      <c r="DO14" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP14" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ14" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR14" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT14" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU14" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV14" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW14" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX14" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY14" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ14" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA14" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB14" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC14" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED14" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE14" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF14" t="inlineStr"/>
+      <c r="EG14" t="inlineStr"/>
+      <c r="EH14" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI14" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ14" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK14" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>05/06/2026, 16:10:26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>84</v>
+      </c>
+      <c r="D15" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>408</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>408</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>1780628400</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1780686143</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>05/06/2026 16:02</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE15" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr"/>
+      <c r="BQ15" t="inlineStr"/>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="inlineStr"/>
+      <c r="BW15" t="inlineStr"/>
+      <c r="BX15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="inlineStr"/>
+      <c r="CA15" t="inlineStr"/>
+      <c r="CB15" t="inlineStr"/>
+      <c r="CC15" t="inlineStr"/>
+      <c r="CD15" t="inlineStr"/>
+      <c r="CE15" t="inlineStr"/>
+      <c r="CF15" t="inlineStr"/>
+      <c r="CG15" t="inlineStr"/>
+      <c r="CH15" t="inlineStr"/>
+      <c r="CI15" t="inlineStr"/>
+      <c r="CJ15" t="inlineStr"/>
+      <c r="CK15" t="inlineStr"/>
+      <c r="CL15" t="inlineStr"/>
+      <c r="CM15" t="inlineStr"/>
+      <c r="CN15" t="inlineStr"/>
+      <c r="CO15" t="inlineStr"/>
+      <c r="CP15" t="inlineStr"/>
+      <c r="CQ15" t="inlineStr"/>
+      <c r="CR15" t="inlineStr"/>
+      <c r="CS15" t="inlineStr"/>
+      <c r="CT15" t="inlineStr"/>
+      <c r="CU15" t="inlineStr"/>
+      <c r="CV15" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW15" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX15" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY15" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ15" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA15" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB15" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC15" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD15" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE15" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF15" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG15" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH15" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI15" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK15" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL15" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM15" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN15" t="inlineStr"/>
+      <c r="DO15" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP15" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ15" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR15" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT15" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU15" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV15" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW15" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX15" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY15" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ15" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA15" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB15" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC15" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED15" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE15" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF15" t="inlineStr"/>
+      <c r="EG15" t="inlineStr"/>
+      <c r="EH15" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI15" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ15" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK15" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>05/06/2026, 16:44:39</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>84</v>
+      </c>
+      <c r="D16" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>408</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>408</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>1780628400</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1780688196</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>05/06/2026 16:36</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE16" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT16" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr"/>
+      <c r="BQ16" t="inlineStr"/>
+      <c r="BR16" t="inlineStr"/>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="inlineStr"/>
+      <c r="BW16" t="inlineStr"/>
+      <c r="BX16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr"/>
+      <c r="BZ16" t="inlineStr"/>
+      <c r="CA16" t="inlineStr"/>
+      <c r="CB16" t="inlineStr"/>
+      <c r="CC16" t="inlineStr"/>
+      <c r="CD16" t="inlineStr"/>
+      <c r="CE16" t="inlineStr"/>
+      <c r="CF16" t="inlineStr"/>
+      <c r="CG16" t="inlineStr"/>
+      <c r="CH16" t="inlineStr"/>
+      <c r="CI16" t="inlineStr"/>
+      <c r="CJ16" t="inlineStr"/>
+      <c r="CK16" t="inlineStr"/>
+      <c r="CL16" t="inlineStr"/>
+      <c r="CM16" t="inlineStr"/>
+      <c r="CN16" t="inlineStr"/>
+      <c r="CO16" t="inlineStr"/>
+      <c r="CP16" t="inlineStr"/>
+      <c r="CQ16" t="inlineStr"/>
+      <c r="CR16" t="inlineStr"/>
+      <c r="CS16" t="inlineStr"/>
+      <c r="CT16" t="inlineStr"/>
+      <c r="CU16" t="inlineStr"/>
+      <c r="CV16" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW16" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX16" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY16" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ16" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA16" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB16" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC16" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD16" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE16" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF16" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG16" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH16" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI16" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK16" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL16" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM16" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN16" t="inlineStr"/>
+      <c r="DO16" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP16" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ16" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR16" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT16" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU16" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV16" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW16" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX16" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY16" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ16" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA16" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB16" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC16" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED16" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE16" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF16" t="inlineStr"/>
+      <c r="EG16" t="inlineStr"/>
+      <c r="EH16" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI16" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ16" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK16" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>05/06/2026, 17:04:12</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>84</v>
+      </c>
+      <c r="D17" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>408</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>408</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>1780628400</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1780689369</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>05/06/2026 16:56</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z17" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE17" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT17" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+      <c r="BO17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr"/>
+      <c r="BQ17" t="inlineStr"/>
+      <c r="BR17" t="inlineStr"/>
+      <c r="BS17" t="inlineStr"/>
+      <c r="BT17" t="inlineStr"/>
+      <c r="BU17" t="inlineStr"/>
+      <c r="BV17" t="inlineStr"/>
+      <c r="BW17" t="inlineStr"/>
+      <c r="BX17" t="inlineStr"/>
+      <c r="BY17" t="inlineStr"/>
+      <c r="BZ17" t="inlineStr"/>
+      <c r="CA17" t="inlineStr"/>
+      <c r="CB17" t="inlineStr"/>
+      <c r="CC17" t="inlineStr"/>
+      <c r="CD17" t="inlineStr"/>
+      <c r="CE17" t="inlineStr"/>
+      <c r="CF17" t="inlineStr"/>
+      <c r="CG17" t="inlineStr"/>
+      <c r="CH17" t="inlineStr"/>
+      <c r="CI17" t="inlineStr"/>
+      <c r="CJ17" t="inlineStr"/>
+      <c r="CK17" t="inlineStr"/>
+      <c r="CL17" t="inlineStr"/>
+      <c r="CM17" t="inlineStr"/>
+      <c r="CN17" t="inlineStr"/>
+      <c r="CO17" t="inlineStr"/>
+      <c r="CP17" t="inlineStr"/>
+      <c r="CQ17" t="inlineStr"/>
+      <c r="CR17" t="inlineStr"/>
+      <c r="CS17" t="inlineStr"/>
+      <c r="CT17" t="inlineStr"/>
+      <c r="CU17" t="inlineStr"/>
+      <c r="CV17" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW17" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX17" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY17" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ17" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA17" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB17" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC17" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD17" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE17" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF17" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG17" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH17" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI17" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK17" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL17" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM17" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN17" t="inlineStr"/>
+      <c r="DO17" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP17" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ17" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR17" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT17" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU17" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV17" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW17" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX17" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY17" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ17" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA17" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB17" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC17" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED17" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE17" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF17" t="inlineStr"/>
+      <c r="EG17" t="inlineStr"/>
+      <c r="EH17" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI17" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ17" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK17" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>05/06/2026, 17:17:06</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0121000</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>01210000010</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1780628400</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1780690142</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>05/06/2026 17:09</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>3500.00</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+      <c r="BO18" t="inlineStr"/>
+      <c r="BP18" t="inlineStr"/>
+      <c r="BQ18" t="inlineStr"/>
+      <c r="BR18" t="inlineStr"/>
+      <c r="BS18" t="inlineStr"/>
+      <c r="BT18" t="inlineStr"/>
+      <c r="BU18" t="inlineStr"/>
+      <c r="BV18" t="inlineStr"/>
+      <c r="BW18" t="inlineStr"/>
+      <c r="BX18" t="inlineStr"/>
+      <c r="BY18" t="inlineStr"/>
+      <c r="BZ18" t="inlineStr"/>
+      <c r="CA18" t="inlineStr"/>
+      <c r="CB18" t="inlineStr"/>
+      <c r="CC18" t="inlineStr"/>
+      <c r="CD18" t="inlineStr"/>
+      <c r="CE18" t="inlineStr"/>
+      <c r="CF18" t="inlineStr"/>
+      <c r="CG18" t="inlineStr"/>
+      <c r="CH18" t="inlineStr"/>
+      <c r="CI18" t="inlineStr"/>
+      <c r="CJ18" t="inlineStr"/>
+      <c r="CK18" t="inlineStr"/>
+      <c r="CL18" t="inlineStr"/>
+      <c r="CM18" t="inlineStr"/>
+      <c r="CN18" t="inlineStr"/>
+      <c r="CO18" t="inlineStr"/>
+      <c r="CP18" t="inlineStr"/>
+      <c r="CQ18" t="inlineStr"/>
+      <c r="CR18" t="inlineStr"/>
+      <c r="CS18" t="inlineStr"/>
+      <c r="CT18" t="inlineStr"/>
+      <c r="CU18" t="inlineStr"/>
+      <c r="CV18" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW18" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX18" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY18" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ18" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA18" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB18" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC18" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD18" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE18" t="inlineStr">
+        <is>
+          <t>1121029128</t>
+        </is>
+      </c>
+      <c r="DF18" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG18" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH18" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI18" t="inlineStr">
+        <is>
+          <t>212122</t>
+        </is>
+      </c>
+      <c r="DJ18" t="inlineStr">
+        <is>
+          <t>12344</t>
+        </is>
+      </c>
+      <c r="DK18" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL18" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM18" t="inlineStr">
+        <is>
+          <t>121212212112</t>
+        </is>
+      </c>
+      <c r="DN18" t="inlineStr"/>
+      <c r="DO18" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP18" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ18" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR18" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+      <c r="DS18" t="inlineStr">
+        <is>
+          <t>3144</t>
+        </is>
+      </c>
+      <c r="DT18" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU18" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV18" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW18" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="DX18" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY18" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ18" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA18" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB18" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC18" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED18" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE18" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF18" t="inlineStr"/>
+      <c r="EG18" t="inlineStr"/>
+      <c r="EH18" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI18" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ18" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK18" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B5FCC50092DEF84396333E47DAEFEB5E" ma:contentTypeVersion="13" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="3f5dff31fa7a2b799118bc7c00128ae3">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5df11fd7-6aff-4cc6-9d69-481ebafd3f51" xmlns:ns3="ba98ff8d-cf9c-4574-b9ff-8782fca0b7db" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5a22452f93ee1f3c8f432c572ea5d732" ns2:_="" ns3:_="">
+    <xsd:import namespace="5df11fd7-6aff-4cc6-9d69-481ebafd3f51"/>
+    <xsd:import namespace="ba98ff8d-cf9c-4574-b9ff-8782fca0b7db"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="5df11fd7-6aff-4cc6-9d69-481ebafd3f51" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4410abd1-e841-4d52-8c09-cc5936d54c0f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ba98ff8d-cf9c-4574-b9ff-8782fca0b7db" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{78d918e0-dd2a-4d55-9cd7-b9c5d47e1b97}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="ba98ff8d-cf9c-4574-b9ff-8782fca0b7db">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ba98ff8d-cf9c-4574-b9ff-8782fca0b7db" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5df11fd7-6aff-4cc6-9d69-481ebafd3f51">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E5362F9-87DC-4D00-AC6A-0D4FA0E11BC8}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60550303-CF0E-48C3-9117-6FA69E4BED68}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F51F449-F139-4018-8D77-64162D58004A}"/>
 </file>
--- a/dados_formularios.xlsx
+++ b/dados_formularios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL18"/>
+  <dimension ref="A1:EL26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8299,47 +8299,33 @@
           <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0121000</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>01210000010</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C18" t="n">
+        <v>84</v>
+      </c>
+      <c r="D18" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>22133</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="L18" t="n">
+        <v>408</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -8351,25 +8337,19 @@
           <t>robo.relatorio@folhatech.com.br</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="O18" t="n">
+        <v>408</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Robo Cadastro Cliente</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>1780628400</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>1780690142</t>
-        </is>
+      <c r="Q18" t="n">
+        <v>1780628400</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1780690142</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -8391,10 +8371,8 @@
           <t>03/06/2026 17:13</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="W18" t="n">
+        <v>22133</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -8406,35 +8384,27 @@
           <t>04/06/2026 17:25</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="Z18" t="n">
+        <v>127857</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>08 - Confecção e assinatura (Contrato)</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
+      <c r="AB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>487</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
           <t>Pedro Santana</t>
         </is>
       </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>0121</t>
-        </is>
+      <c r="AE18" t="n">
+        <v>121</v>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
@@ -8451,10 +8421,8 @@
       <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr"/>
       <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>127857</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
@@ -8486,10 +8454,8 @@
           <t>Aumento de quadro</t>
         </is>
       </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>3500.00</t>
-        </is>
+      <c r="AT18" t="n">
+        <v>3500</v>
       </c>
       <c r="AU18" t="inlineStr"/>
       <c r="AV18" t="inlineStr">
@@ -8617,10 +8583,8 @@
           <t>Pai</t>
         </is>
       </c>
-      <c r="DE18" t="inlineStr">
-        <is>
-          <t>1121029128</t>
-        </is>
+      <c r="DE18" t="n">
+        <v>1121029128</v>
       </c>
       <c r="DF18" t="inlineStr">
         <is>
@@ -8637,15 +8601,11 @@
           <t>Namorado(a)</t>
         </is>
       </c>
-      <c r="DI18" t="inlineStr">
-        <is>
-          <t>212122</t>
-        </is>
-      </c>
-      <c r="DJ18" t="inlineStr">
-        <is>
-          <t>12344</t>
-        </is>
+      <c r="DI18" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>12344</v>
       </c>
       <c r="DK18" t="inlineStr">
         <is>
@@ -8657,10 +8617,8 @@
           <t>pedro.santana@folhatech.com.br</t>
         </is>
       </c>
-      <c r="DM18" t="inlineStr">
-        <is>
-          <t>121212212112</t>
-        </is>
+      <c r="DM18" t="n">
+        <v>121212212112</v>
       </c>
       <c r="DN18" t="inlineStr"/>
       <c r="DO18" t="inlineStr">
@@ -8678,15 +8636,11 @@
           <t>Conta Corrente</t>
         </is>
       </c>
-      <c r="DR18" t="inlineStr">
-        <is>
-          <t>12121</t>
-        </is>
-      </c>
-      <c r="DS18" t="inlineStr">
-        <is>
-          <t>3144</t>
-        </is>
+      <c r="DR18" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>3144</v>
       </c>
       <c r="DT18" t="inlineStr">
         <is>
@@ -8703,10 +8657,8 @@
           <t>etetetet</t>
         </is>
       </c>
-      <c r="DW18" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="DW18" t="n">
+        <v>124</v>
       </c>
       <c r="DX18" t="inlineStr">
         <is>
@@ -8771,6 +8723,3542 @@
         </is>
       </c>
       <c r="EL18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>08/06/2026, 09:00:42</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>84</v>
+      </c>
+      <c r="D19" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>408</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>408</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1780919542</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>08/06/2026 08:52</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE19" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+      <c r="BO19" t="inlineStr"/>
+      <c r="BP19" t="inlineStr"/>
+      <c r="BQ19" t="inlineStr"/>
+      <c r="BR19" t="inlineStr"/>
+      <c r="BS19" t="inlineStr"/>
+      <c r="BT19" t="inlineStr"/>
+      <c r="BU19" t="inlineStr"/>
+      <c r="BV19" t="inlineStr"/>
+      <c r="BW19" t="inlineStr"/>
+      <c r="BX19" t="inlineStr"/>
+      <c r="BY19" t="inlineStr"/>
+      <c r="BZ19" t="inlineStr"/>
+      <c r="CA19" t="inlineStr"/>
+      <c r="CB19" t="inlineStr"/>
+      <c r="CC19" t="inlineStr"/>
+      <c r="CD19" t="inlineStr"/>
+      <c r="CE19" t="inlineStr"/>
+      <c r="CF19" t="inlineStr"/>
+      <c r="CG19" t="inlineStr"/>
+      <c r="CH19" t="inlineStr"/>
+      <c r="CI19" t="inlineStr"/>
+      <c r="CJ19" t="inlineStr"/>
+      <c r="CK19" t="inlineStr"/>
+      <c r="CL19" t="inlineStr"/>
+      <c r="CM19" t="inlineStr"/>
+      <c r="CN19" t="inlineStr"/>
+      <c r="CO19" t="inlineStr"/>
+      <c r="CP19" t="inlineStr"/>
+      <c r="CQ19" t="inlineStr"/>
+      <c r="CR19" t="inlineStr"/>
+      <c r="CS19" t="inlineStr"/>
+      <c r="CT19" t="inlineStr"/>
+      <c r="CU19" t="inlineStr"/>
+      <c r="CV19" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW19" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX19" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY19" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ19" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA19" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB19" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC19" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD19" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE19" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF19" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG19" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH19" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI19" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ19" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK19" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL19" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM19" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN19" t="inlineStr"/>
+      <c r="DO19" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP19" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ19" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR19" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS19" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT19" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU19" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV19" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW19" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX19" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY19" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ19" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA19" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB19" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC19" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED19" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE19" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF19" t="inlineStr"/>
+      <c r="EG19" t="inlineStr"/>
+      <c r="EH19" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI19" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ19" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK19" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>08/06/2026, 09:07:11</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>84</v>
+      </c>
+      <c r="D20" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>408</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>408</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1780919931</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>08/06/2026 08:58</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE20" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
+      <c r="BO20" t="inlineStr"/>
+      <c r="BP20" t="inlineStr"/>
+      <c r="BQ20" t="inlineStr"/>
+      <c r="BR20" t="inlineStr"/>
+      <c r="BS20" t="inlineStr"/>
+      <c r="BT20" t="inlineStr"/>
+      <c r="BU20" t="inlineStr"/>
+      <c r="BV20" t="inlineStr"/>
+      <c r="BW20" t="inlineStr"/>
+      <c r="BX20" t="inlineStr"/>
+      <c r="BY20" t="inlineStr"/>
+      <c r="BZ20" t="inlineStr"/>
+      <c r="CA20" t="inlineStr"/>
+      <c r="CB20" t="inlineStr"/>
+      <c r="CC20" t="inlineStr"/>
+      <c r="CD20" t="inlineStr"/>
+      <c r="CE20" t="inlineStr"/>
+      <c r="CF20" t="inlineStr"/>
+      <c r="CG20" t="inlineStr"/>
+      <c r="CH20" t="inlineStr"/>
+      <c r="CI20" t="inlineStr"/>
+      <c r="CJ20" t="inlineStr"/>
+      <c r="CK20" t="inlineStr"/>
+      <c r="CL20" t="inlineStr"/>
+      <c r="CM20" t="inlineStr"/>
+      <c r="CN20" t="inlineStr"/>
+      <c r="CO20" t="inlineStr"/>
+      <c r="CP20" t="inlineStr"/>
+      <c r="CQ20" t="inlineStr"/>
+      <c r="CR20" t="inlineStr"/>
+      <c r="CS20" t="inlineStr"/>
+      <c r="CT20" t="inlineStr"/>
+      <c r="CU20" t="inlineStr"/>
+      <c r="CV20" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW20" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX20" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY20" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ20" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA20" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB20" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC20" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD20" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE20" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF20" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG20" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH20" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI20" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ20" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK20" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL20" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM20" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN20" t="inlineStr"/>
+      <c r="DO20" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP20" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ20" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR20" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS20" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT20" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU20" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV20" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW20" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX20" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY20" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ20" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA20" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB20" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC20" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED20" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE20" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF20" t="inlineStr"/>
+      <c r="EG20" t="inlineStr"/>
+      <c r="EH20" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI20" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ20" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK20" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>08/06/2026, 12:16:38</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>84</v>
+      </c>
+      <c r="D21" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>408</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>408</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1780931293</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>08/06/2026 12:08</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE21" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+      <c r="BO21" t="inlineStr"/>
+      <c r="BP21" t="inlineStr"/>
+      <c r="BQ21" t="inlineStr"/>
+      <c r="BR21" t="inlineStr"/>
+      <c r="BS21" t="inlineStr"/>
+      <c r="BT21" t="inlineStr"/>
+      <c r="BU21" t="inlineStr"/>
+      <c r="BV21" t="inlineStr"/>
+      <c r="BW21" t="inlineStr"/>
+      <c r="BX21" t="inlineStr"/>
+      <c r="BY21" t="inlineStr"/>
+      <c r="BZ21" t="inlineStr"/>
+      <c r="CA21" t="inlineStr"/>
+      <c r="CB21" t="inlineStr"/>
+      <c r="CC21" t="inlineStr"/>
+      <c r="CD21" t="inlineStr"/>
+      <c r="CE21" t="inlineStr"/>
+      <c r="CF21" t="inlineStr"/>
+      <c r="CG21" t="inlineStr"/>
+      <c r="CH21" t="inlineStr"/>
+      <c r="CI21" t="inlineStr"/>
+      <c r="CJ21" t="inlineStr"/>
+      <c r="CK21" t="inlineStr"/>
+      <c r="CL21" t="inlineStr"/>
+      <c r="CM21" t="inlineStr"/>
+      <c r="CN21" t="inlineStr"/>
+      <c r="CO21" t="inlineStr"/>
+      <c r="CP21" t="inlineStr"/>
+      <c r="CQ21" t="inlineStr"/>
+      <c r="CR21" t="inlineStr"/>
+      <c r="CS21" t="inlineStr"/>
+      <c r="CT21" t="inlineStr"/>
+      <c r="CU21" t="inlineStr"/>
+      <c r="CV21" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW21" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX21" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY21" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ21" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA21" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB21" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC21" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD21" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE21" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF21" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG21" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH21" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI21" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ21" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK21" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL21" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM21" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN21" t="inlineStr"/>
+      <c r="DO21" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP21" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ21" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR21" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS21" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT21" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU21" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV21" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW21" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX21" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY21" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ21" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA21" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB21" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC21" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED21" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE21" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF21" t="inlineStr"/>
+      <c r="EG21" t="inlineStr"/>
+      <c r="EH21" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI21" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ21" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK21" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>08/06/2026, 12:17:55</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>84</v>
+      </c>
+      <c r="D22" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>408</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>408</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1780931370</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>08/06/2026 12:09</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE22" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
+      <c r="BO22" t="inlineStr"/>
+      <c r="BP22" t="inlineStr"/>
+      <c r="BQ22" t="inlineStr"/>
+      <c r="BR22" t="inlineStr"/>
+      <c r="BS22" t="inlineStr"/>
+      <c r="BT22" t="inlineStr"/>
+      <c r="BU22" t="inlineStr"/>
+      <c r="BV22" t="inlineStr"/>
+      <c r="BW22" t="inlineStr"/>
+      <c r="BX22" t="inlineStr"/>
+      <c r="BY22" t="inlineStr"/>
+      <c r="BZ22" t="inlineStr"/>
+      <c r="CA22" t="inlineStr"/>
+      <c r="CB22" t="inlineStr"/>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="inlineStr"/>
+      <c r="CM22" t="inlineStr"/>
+      <c r="CN22" t="inlineStr"/>
+      <c r="CO22" t="inlineStr"/>
+      <c r="CP22" t="inlineStr"/>
+      <c r="CQ22" t="inlineStr"/>
+      <c r="CR22" t="inlineStr"/>
+      <c r="CS22" t="inlineStr"/>
+      <c r="CT22" t="inlineStr"/>
+      <c r="CU22" t="inlineStr"/>
+      <c r="CV22" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW22" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX22" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY22" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ22" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA22" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB22" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC22" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD22" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE22" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF22" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG22" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH22" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI22" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ22" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK22" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL22" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM22" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN22" t="inlineStr"/>
+      <c r="DO22" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP22" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ22" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR22" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS22" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT22" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU22" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV22" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW22" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX22" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY22" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ22" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA22" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB22" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC22" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED22" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE22" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF22" t="inlineStr"/>
+      <c r="EG22" t="inlineStr"/>
+      <c r="EH22" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI22" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ22" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK22" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>08/06/2026, 12:22:00</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>84</v>
+      </c>
+      <c r="D23" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>408</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>408</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1780931615</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>08/06/2026 12:13</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z23" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE23" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
+      <c r="BO23" t="inlineStr"/>
+      <c r="BP23" t="inlineStr"/>
+      <c r="BQ23" t="inlineStr"/>
+      <c r="BR23" t="inlineStr"/>
+      <c r="BS23" t="inlineStr"/>
+      <c r="BT23" t="inlineStr"/>
+      <c r="BU23" t="inlineStr"/>
+      <c r="BV23" t="inlineStr"/>
+      <c r="BW23" t="inlineStr"/>
+      <c r="BX23" t="inlineStr"/>
+      <c r="BY23" t="inlineStr"/>
+      <c r="BZ23" t="inlineStr"/>
+      <c r="CA23" t="inlineStr"/>
+      <c r="CB23" t="inlineStr"/>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="inlineStr"/>
+      <c r="CM23" t="inlineStr"/>
+      <c r="CN23" t="inlineStr"/>
+      <c r="CO23" t="inlineStr"/>
+      <c r="CP23" t="inlineStr"/>
+      <c r="CQ23" t="inlineStr"/>
+      <c r="CR23" t="inlineStr"/>
+      <c r="CS23" t="inlineStr"/>
+      <c r="CT23" t="inlineStr"/>
+      <c r="CU23" t="inlineStr"/>
+      <c r="CV23" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW23" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX23" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY23" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ23" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA23" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB23" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC23" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD23" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE23" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF23" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG23" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH23" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI23" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ23" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK23" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL23" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM23" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN23" t="inlineStr"/>
+      <c r="DO23" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP23" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ23" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR23" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS23" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT23" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU23" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV23" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW23" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX23" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY23" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ23" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA23" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB23" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC23" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED23" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE23" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF23" t="inlineStr"/>
+      <c r="EG23" t="inlineStr"/>
+      <c r="EH23" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI23" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ23" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK23" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>08/06/2026, 14:30:41</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>84</v>
+      </c>
+      <c r="D24" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>408</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>408</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1780939335</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>08/06/2026 14:22</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z24" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE24" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr"/>
+      <c r="BJ24" t="inlineStr"/>
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="inlineStr"/>
+      <c r="BM24" t="inlineStr"/>
+      <c r="BN24" t="inlineStr"/>
+      <c r="BO24" t="inlineStr"/>
+      <c r="BP24" t="inlineStr"/>
+      <c r="BQ24" t="inlineStr"/>
+      <c r="BR24" t="inlineStr"/>
+      <c r="BS24" t="inlineStr"/>
+      <c r="BT24" t="inlineStr"/>
+      <c r="BU24" t="inlineStr"/>
+      <c r="BV24" t="inlineStr"/>
+      <c r="BW24" t="inlineStr"/>
+      <c r="BX24" t="inlineStr"/>
+      <c r="BY24" t="inlineStr"/>
+      <c r="BZ24" t="inlineStr"/>
+      <c r="CA24" t="inlineStr"/>
+      <c r="CB24" t="inlineStr"/>
+      <c r="CC24" t="inlineStr"/>
+      <c r="CD24" t="inlineStr"/>
+      <c r="CE24" t="inlineStr"/>
+      <c r="CF24" t="inlineStr"/>
+      <c r="CG24" t="inlineStr"/>
+      <c r="CH24" t="inlineStr"/>
+      <c r="CI24" t="inlineStr"/>
+      <c r="CJ24" t="inlineStr"/>
+      <c r="CK24" t="inlineStr"/>
+      <c r="CL24" t="inlineStr"/>
+      <c r="CM24" t="inlineStr"/>
+      <c r="CN24" t="inlineStr"/>
+      <c r="CO24" t="inlineStr"/>
+      <c r="CP24" t="inlineStr"/>
+      <c r="CQ24" t="inlineStr"/>
+      <c r="CR24" t="inlineStr"/>
+      <c r="CS24" t="inlineStr"/>
+      <c r="CT24" t="inlineStr"/>
+      <c r="CU24" t="inlineStr"/>
+      <c r="CV24" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW24" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX24" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY24" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ24" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA24" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB24" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC24" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD24" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE24" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF24" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG24" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH24" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI24" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ24" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK24" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL24" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM24" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN24" t="inlineStr"/>
+      <c r="DO24" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP24" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ24" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR24" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS24" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT24" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU24" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV24" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW24" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX24" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY24" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ24" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA24" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB24" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC24" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED24" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE24" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF24" t="inlineStr"/>
+      <c r="EG24" t="inlineStr"/>
+      <c r="EH24" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI24" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ24" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK24" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>08/06/2026, 14:38:09</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>84</v>
+      </c>
+      <c r="D25" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>408</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>408</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1780939784</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>08/06/2026 14:29</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE25" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr"/>
+      <c r="BJ25" t="inlineStr"/>
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="inlineStr"/>
+      <c r="BM25" t="inlineStr"/>
+      <c r="BN25" t="inlineStr"/>
+      <c r="BO25" t="inlineStr"/>
+      <c r="BP25" t="inlineStr"/>
+      <c r="BQ25" t="inlineStr"/>
+      <c r="BR25" t="inlineStr"/>
+      <c r="BS25" t="inlineStr"/>
+      <c r="BT25" t="inlineStr"/>
+      <c r="BU25" t="inlineStr"/>
+      <c r="BV25" t="inlineStr"/>
+      <c r="BW25" t="inlineStr"/>
+      <c r="BX25" t="inlineStr"/>
+      <c r="BY25" t="inlineStr"/>
+      <c r="BZ25" t="inlineStr"/>
+      <c r="CA25" t="inlineStr"/>
+      <c r="CB25" t="inlineStr"/>
+      <c r="CC25" t="inlineStr"/>
+      <c r="CD25" t="inlineStr"/>
+      <c r="CE25" t="inlineStr"/>
+      <c r="CF25" t="inlineStr"/>
+      <c r="CG25" t="inlineStr"/>
+      <c r="CH25" t="inlineStr"/>
+      <c r="CI25" t="inlineStr"/>
+      <c r="CJ25" t="inlineStr"/>
+      <c r="CK25" t="inlineStr"/>
+      <c r="CL25" t="inlineStr"/>
+      <c r="CM25" t="inlineStr"/>
+      <c r="CN25" t="inlineStr"/>
+      <c r="CO25" t="inlineStr"/>
+      <c r="CP25" t="inlineStr"/>
+      <c r="CQ25" t="inlineStr"/>
+      <c r="CR25" t="inlineStr"/>
+      <c r="CS25" t="inlineStr"/>
+      <c r="CT25" t="inlineStr"/>
+      <c r="CU25" t="inlineStr"/>
+      <c r="CV25" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW25" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX25" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY25" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ25" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA25" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB25" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC25" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD25" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE25" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF25" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG25" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH25" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI25" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ25" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK25" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL25" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM25" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN25" t="inlineStr"/>
+      <c r="DO25" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP25" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ25" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR25" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS25" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT25" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU25" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV25" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW25" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX25" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY25" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ25" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA25" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB25" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC25" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED25" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE25" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF25" t="inlineStr"/>
+      <c r="EG25" t="inlineStr"/>
+      <c r="EH25" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI25" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ25" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK25" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>08/06/2026, 14:45:04</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>0121000</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>01210000010</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1780887600</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1780940198</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>08/06/2026 14:36</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>3500.00</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr"/>
+      <c r="BJ26" t="inlineStr"/>
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="inlineStr"/>
+      <c r="BM26" t="inlineStr"/>
+      <c r="BN26" t="inlineStr"/>
+      <c r="BO26" t="inlineStr"/>
+      <c r="BP26" t="inlineStr"/>
+      <c r="BQ26" t="inlineStr"/>
+      <c r="BR26" t="inlineStr"/>
+      <c r="BS26" t="inlineStr"/>
+      <c r="BT26" t="inlineStr"/>
+      <c r="BU26" t="inlineStr"/>
+      <c r="BV26" t="inlineStr"/>
+      <c r="BW26" t="inlineStr"/>
+      <c r="BX26" t="inlineStr"/>
+      <c r="BY26" t="inlineStr"/>
+      <c r="BZ26" t="inlineStr"/>
+      <c r="CA26" t="inlineStr"/>
+      <c r="CB26" t="inlineStr"/>
+      <c r="CC26" t="inlineStr"/>
+      <c r="CD26" t="inlineStr"/>
+      <c r="CE26" t="inlineStr"/>
+      <c r="CF26" t="inlineStr"/>
+      <c r="CG26" t="inlineStr"/>
+      <c r="CH26" t="inlineStr"/>
+      <c r="CI26" t="inlineStr"/>
+      <c r="CJ26" t="inlineStr"/>
+      <c r="CK26" t="inlineStr"/>
+      <c r="CL26" t="inlineStr"/>
+      <c r="CM26" t="inlineStr"/>
+      <c r="CN26" t="inlineStr"/>
+      <c r="CO26" t="inlineStr"/>
+      <c r="CP26" t="inlineStr"/>
+      <c r="CQ26" t="inlineStr"/>
+      <c r="CR26" t="inlineStr"/>
+      <c r="CS26" t="inlineStr"/>
+      <c r="CT26" t="inlineStr"/>
+      <c r="CU26" t="inlineStr"/>
+      <c r="CV26" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW26" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX26" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY26" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ26" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA26" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB26" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC26" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD26" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE26" t="inlineStr">
+        <is>
+          <t>1121029128</t>
+        </is>
+      </c>
+      <c r="DF26" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG26" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH26" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI26" t="inlineStr">
+        <is>
+          <t>212122</t>
+        </is>
+      </c>
+      <c r="DJ26" t="inlineStr">
+        <is>
+          <t>12344</t>
+        </is>
+      </c>
+      <c r="DK26" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL26" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM26" t="inlineStr">
+        <is>
+          <t>121212212112</t>
+        </is>
+      </c>
+      <c r="DN26" t="inlineStr"/>
+      <c r="DO26" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP26" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ26" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR26" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+      <c r="DS26" t="inlineStr">
+        <is>
+          <t>3144</t>
+        </is>
+      </c>
+      <c r="DT26" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU26" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV26" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW26" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="DX26" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY26" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ26" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA26" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB26" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC26" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED26" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE26" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF26" t="inlineStr"/>
+      <c r="EG26" t="inlineStr"/>
+      <c r="EH26" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI26" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ26" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK26" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9005,13 +12493,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E5362F9-87DC-4D00-AC6A-0D4FA0E11BC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B6294CC-8429-4C63-A44E-44A628E2ACE5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60550303-CF0E-48C3-9117-6FA69E4BED68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{311BAE5D-3F8F-438D-BB80-DF8E8CD7C837}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F51F449-F139-4018-8D77-64162D58004A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A122744-7312-4534-8A32-66E24F2B507E}"/>
 </file>
--- a/dados_formularios.xlsx
+++ b/dados_formularios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL26"/>
+  <dimension ref="A1:EL37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11787,47 +11787,33 @@
           <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>0121000</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>01210000010</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C26" t="n">
+        <v>84</v>
+      </c>
+      <c r="D26" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>22133</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="L26" t="n">
+        <v>408</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -11839,25 +11825,19 @@
           <t>robo.relatorio@folhatech.com.br</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="O26" t="n">
+        <v>408</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Robo Cadastro Cliente</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>1780887600</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>1780940198</t>
-        </is>
+      <c r="Q26" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1780940198</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -11879,10 +11859,8 @@
           <t>03/06/2026 17:13</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="W26" t="n">
+        <v>22133</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -11894,35 +11872,27 @@
           <t>04/06/2026 17:25</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="Z26" t="n">
+        <v>127857</v>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>08 - Confecção e assinatura (Contrato)</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
+      <c r="AB26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>487</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
           <t>Pedro Santana</t>
         </is>
       </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>0121</t>
-        </is>
+      <c r="AE26" t="n">
+        <v>121</v>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
@@ -11939,10 +11909,8 @@
       <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr"/>
       <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>127857</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
@@ -11974,10 +11942,8 @@
           <t>Aumento de quadro</t>
         </is>
       </c>
-      <c r="AT26" t="inlineStr">
-        <is>
-          <t>3500.00</t>
-        </is>
+      <c r="AT26" t="n">
+        <v>3500</v>
       </c>
       <c r="AU26" t="inlineStr"/>
       <c r="AV26" t="inlineStr">
@@ -12105,10 +12071,8 @@
           <t>Pai</t>
         </is>
       </c>
-      <c r="DE26" t="inlineStr">
-        <is>
-          <t>1121029128</t>
-        </is>
+      <c r="DE26" t="n">
+        <v>1121029128</v>
       </c>
       <c r="DF26" t="inlineStr">
         <is>
@@ -12125,15 +12089,11 @@
           <t>Namorado(a)</t>
         </is>
       </c>
-      <c r="DI26" t="inlineStr">
-        <is>
-          <t>212122</t>
-        </is>
-      </c>
-      <c r="DJ26" t="inlineStr">
-        <is>
-          <t>12344</t>
-        </is>
+      <c r="DI26" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ26" t="n">
+        <v>12344</v>
       </c>
       <c r="DK26" t="inlineStr">
         <is>
@@ -12145,10 +12105,8 @@
           <t>pedro.santana@folhatech.com.br</t>
         </is>
       </c>
-      <c r="DM26" t="inlineStr">
-        <is>
-          <t>121212212112</t>
-        </is>
+      <c r="DM26" t="n">
+        <v>121212212112</v>
       </c>
       <c r="DN26" t="inlineStr"/>
       <c r="DO26" t="inlineStr">
@@ -12166,15 +12124,11 @@
           <t>Conta Corrente</t>
         </is>
       </c>
-      <c r="DR26" t="inlineStr">
-        <is>
-          <t>12121</t>
-        </is>
-      </c>
-      <c r="DS26" t="inlineStr">
-        <is>
-          <t>3144</t>
-        </is>
+      <c r="DR26" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS26" t="n">
+        <v>3144</v>
       </c>
       <c r="DT26" t="inlineStr">
         <is>
@@ -12191,10 +12145,8 @@
           <t>etetetet</t>
         </is>
       </c>
-      <c r="DW26" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="DW26" t="n">
+        <v>124</v>
       </c>
       <c r="DX26" t="inlineStr">
         <is>
@@ -12259,6 +12211,4850 @@
         </is>
       </c>
       <c r="EL26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>08/06/2026, 14:54:54</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>84</v>
+      </c>
+      <c r="D27" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>408</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>408</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1780940789</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>08/06/2026 14:46</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W27" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z27" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE27" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="inlineStr"/>
+      <c r="BM27" t="inlineStr"/>
+      <c r="BN27" t="inlineStr"/>
+      <c r="BO27" t="inlineStr"/>
+      <c r="BP27" t="inlineStr"/>
+      <c r="BQ27" t="inlineStr"/>
+      <c r="BR27" t="inlineStr"/>
+      <c r="BS27" t="inlineStr"/>
+      <c r="BT27" t="inlineStr"/>
+      <c r="BU27" t="inlineStr"/>
+      <c r="BV27" t="inlineStr"/>
+      <c r="BW27" t="inlineStr"/>
+      <c r="BX27" t="inlineStr"/>
+      <c r="BY27" t="inlineStr"/>
+      <c r="BZ27" t="inlineStr"/>
+      <c r="CA27" t="inlineStr"/>
+      <c r="CB27" t="inlineStr"/>
+      <c r="CC27" t="inlineStr"/>
+      <c r="CD27" t="inlineStr"/>
+      <c r="CE27" t="inlineStr"/>
+      <c r="CF27" t="inlineStr"/>
+      <c r="CG27" t="inlineStr"/>
+      <c r="CH27" t="inlineStr"/>
+      <c r="CI27" t="inlineStr"/>
+      <c r="CJ27" t="inlineStr"/>
+      <c r="CK27" t="inlineStr"/>
+      <c r="CL27" t="inlineStr"/>
+      <c r="CM27" t="inlineStr"/>
+      <c r="CN27" t="inlineStr"/>
+      <c r="CO27" t="inlineStr"/>
+      <c r="CP27" t="inlineStr"/>
+      <c r="CQ27" t="inlineStr"/>
+      <c r="CR27" t="inlineStr"/>
+      <c r="CS27" t="inlineStr"/>
+      <c r="CT27" t="inlineStr"/>
+      <c r="CU27" t="inlineStr"/>
+      <c r="CV27" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW27" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX27" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY27" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ27" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA27" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB27" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC27" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD27" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE27" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF27" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG27" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH27" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI27" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ27" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK27" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL27" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM27" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN27" t="inlineStr"/>
+      <c r="DO27" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP27" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ27" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR27" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS27" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT27" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU27" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV27" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW27" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX27" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY27" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ27" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA27" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB27" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC27" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED27" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE27" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF27" t="inlineStr"/>
+      <c r="EG27" t="inlineStr"/>
+      <c r="EH27" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI27" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ27" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK27" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>08/06/2026, 14:59:54</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>84</v>
+      </c>
+      <c r="D28" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>408</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>408</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1780941089</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>08/06/2026 14:51</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z28" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE28" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="inlineStr"/>
+      <c r="BM28" t="inlineStr"/>
+      <c r="BN28" t="inlineStr"/>
+      <c r="BO28" t="inlineStr"/>
+      <c r="BP28" t="inlineStr"/>
+      <c r="BQ28" t="inlineStr"/>
+      <c r="BR28" t="inlineStr"/>
+      <c r="BS28" t="inlineStr"/>
+      <c r="BT28" t="inlineStr"/>
+      <c r="BU28" t="inlineStr"/>
+      <c r="BV28" t="inlineStr"/>
+      <c r="BW28" t="inlineStr"/>
+      <c r="BX28" t="inlineStr"/>
+      <c r="BY28" t="inlineStr"/>
+      <c r="BZ28" t="inlineStr"/>
+      <c r="CA28" t="inlineStr"/>
+      <c r="CB28" t="inlineStr"/>
+      <c r="CC28" t="inlineStr"/>
+      <c r="CD28" t="inlineStr"/>
+      <c r="CE28" t="inlineStr"/>
+      <c r="CF28" t="inlineStr"/>
+      <c r="CG28" t="inlineStr"/>
+      <c r="CH28" t="inlineStr"/>
+      <c r="CI28" t="inlineStr"/>
+      <c r="CJ28" t="inlineStr"/>
+      <c r="CK28" t="inlineStr"/>
+      <c r="CL28" t="inlineStr"/>
+      <c r="CM28" t="inlineStr"/>
+      <c r="CN28" t="inlineStr"/>
+      <c r="CO28" t="inlineStr"/>
+      <c r="CP28" t="inlineStr"/>
+      <c r="CQ28" t="inlineStr"/>
+      <c r="CR28" t="inlineStr"/>
+      <c r="CS28" t="inlineStr"/>
+      <c r="CT28" t="inlineStr"/>
+      <c r="CU28" t="inlineStr"/>
+      <c r="CV28" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW28" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX28" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY28" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ28" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA28" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB28" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC28" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD28" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE28" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF28" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG28" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH28" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI28" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ28" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK28" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL28" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM28" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN28" t="inlineStr"/>
+      <c r="DO28" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP28" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ28" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR28" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS28" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT28" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU28" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV28" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW28" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX28" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY28" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ28" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA28" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB28" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC28" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED28" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE28" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF28" t="inlineStr"/>
+      <c r="EG28" t="inlineStr"/>
+      <c r="EH28" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI28" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ28" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK28" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>08/06/2026, 15:46:16</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>84</v>
+      </c>
+      <c r="D29" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>408</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>408</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1780943870</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>08/06/2026 15:37</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z29" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE29" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
+      <c r="BH29" t="inlineStr"/>
+      <c r="BI29" t="inlineStr"/>
+      <c r="BJ29" t="inlineStr"/>
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="inlineStr"/>
+      <c r="BM29" t="inlineStr"/>
+      <c r="BN29" t="inlineStr"/>
+      <c r="BO29" t="inlineStr"/>
+      <c r="BP29" t="inlineStr"/>
+      <c r="BQ29" t="inlineStr"/>
+      <c r="BR29" t="inlineStr"/>
+      <c r="BS29" t="inlineStr"/>
+      <c r="BT29" t="inlineStr"/>
+      <c r="BU29" t="inlineStr"/>
+      <c r="BV29" t="inlineStr"/>
+      <c r="BW29" t="inlineStr"/>
+      <c r="BX29" t="inlineStr"/>
+      <c r="BY29" t="inlineStr"/>
+      <c r="BZ29" t="inlineStr"/>
+      <c r="CA29" t="inlineStr"/>
+      <c r="CB29" t="inlineStr"/>
+      <c r="CC29" t="inlineStr"/>
+      <c r="CD29" t="inlineStr"/>
+      <c r="CE29" t="inlineStr"/>
+      <c r="CF29" t="inlineStr"/>
+      <c r="CG29" t="inlineStr"/>
+      <c r="CH29" t="inlineStr"/>
+      <c r="CI29" t="inlineStr"/>
+      <c r="CJ29" t="inlineStr"/>
+      <c r="CK29" t="inlineStr"/>
+      <c r="CL29" t="inlineStr"/>
+      <c r="CM29" t="inlineStr"/>
+      <c r="CN29" t="inlineStr"/>
+      <c r="CO29" t="inlineStr"/>
+      <c r="CP29" t="inlineStr"/>
+      <c r="CQ29" t="inlineStr"/>
+      <c r="CR29" t="inlineStr"/>
+      <c r="CS29" t="inlineStr"/>
+      <c r="CT29" t="inlineStr"/>
+      <c r="CU29" t="inlineStr"/>
+      <c r="CV29" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW29" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX29" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY29" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ29" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA29" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB29" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC29" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD29" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE29" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF29" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG29" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH29" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI29" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ29" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK29" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL29" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM29" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN29" t="inlineStr"/>
+      <c r="DO29" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP29" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ29" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR29" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS29" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT29" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU29" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV29" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW29" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX29" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY29" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ29" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA29" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB29" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC29" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED29" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE29" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF29" t="inlineStr"/>
+      <c r="EG29" t="inlineStr"/>
+      <c r="EH29" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI29" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ29" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK29" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>08/06/2026, 16:01:47</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>84</v>
+      </c>
+      <c r="D30" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>408</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>408</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1780944801</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>08/06/2026 15:53</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z30" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE30" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
+      <c r="BH30" t="inlineStr"/>
+      <c r="BI30" t="inlineStr"/>
+      <c r="BJ30" t="inlineStr"/>
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="inlineStr"/>
+      <c r="BM30" t="inlineStr"/>
+      <c r="BN30" t="inlineStr"/>
+      <c r="BO30" t="inlineStr"/>
+      <c r="BP30" t="inlineStr"/>
+      <c r="BQ30" t="inlineStr"/>
+      <c r="BR30" t="inlineStr"/>
+      <c r="BS30" t="inlineStr"/>
+      <c r="BT30" t="inlineStr"/>
+      <c r="BU30" t="inlineStr"/>
+      <c r="BV30" t="inlineStr"/>
+      <c r="BW30" t="inlineStr"/>
+      <c r="BX30" t="inlineStr"/>
+      <c r="BY30" t="inlineStr"/>
+      <c r="BZ30" t="inlineStr"/>
+      <c r="CA30" t="inlineStr"/>
+      <c r="CB30" t="inlineStr"/>
+      <c r="CC30" t="inlineStr"/>
+      <c r="CD30" t="inlineStr"/>
+      <c r="CE30" t="inlineStr"/>
+      <c r="CF30" t="inlineStr"/>
+      <c r="CG30" t="inlineStr"/>
+      <c r="CH30" t="inlineStr"/>
+      <c r="CI30" t="inlineStr"/>
+      <c r="CJ30" t="inlineStr"/>
+      <c r="CK30" t="inlineStr"/>
+      <c r="CL30" t="inlineStr"/>
+      <c r="CM30" t="inlineStr"/>
+      <c r="CN30" t="inlineStr"/>
+      <c r="CO30" t="inlineStr"/>
+      <c r="CP30" t="inlineStr"/>
+      <c r="CQ30" t="inlineStr"/>
+      <c r="CR30" t="inlineStr"/>
+      <c r="CS30" t="inlineStr"/>
+      <c r="CT30" t="inlineStr"/>
+      <c r="CU30" t="inlineStr"/>
+      <c r="CV30" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW30" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX30" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY30" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ30" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA30" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB30" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC30" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD30" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE30" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF30" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG30" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH30" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI30" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ30" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK30" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL30" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM30" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN30" t="inlineStr"/>
+      <c r="DO30" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP30" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ30" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR30" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS30" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT30" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU30" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV30" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW30" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX30" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY30" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ30" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA30" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB30" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC30" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED30" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE30" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF30" t="inlineStr"/>
+      <c r="EG30" t="inlineStr"/>
+      <c r="EH30" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI30" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ30" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK30" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>08/06/2026, 16:05:03</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>84</v>
+      </c>
+      <c r="D31" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>408</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>408</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1780944997</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>08/06/2026 15:56</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z31" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE31" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ31" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT31" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB31" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
+      <c r="BH31" t="inlineStr"/>
+      <c r="BI31" t="inlineStr"/>
+      <c r="BJ31" t="inlineStr"/>
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="inlineStr"/>
+      <c r="BM31" t="inlineStr"/>
+      <c r="BN31" t="inlineStr"/>
+      <c r="BO31" t="inlineStr"/>
+      <c r="BP31" t="inlineStr"/>
+      <c r="BQ31" t="inlineStr"/>
+      <c r="BR31" t="inlineStr"/>
+      <c r="BS31" t="inlineStr"/>
+      <c r="BT31" t="inlineStr"/>
+      <c r="BU31" t="inlineStr"/>
+      <c r="BV31" t="inlineStr"/>
+      <c r="BW31" t="inlineStr"/>
+      <c r="BX31" t="inlineStr"/>
+      <c r="BY31" t="inlineStr"/>
+      <c r="BZ31" t="inlineStr"/>
+      <c r="CA31" t="inlineStr"/>
+      <c r="CB31" t="inlineStr"/>
+      <c r="CC31" t="inlineStr"/>
+      <c r="CD31" t="inlineStr"/>
+      <c r="CE31" t="inlineStr"/>
+      <c r="CF31" t="inlineStr"/>
+      <c r="CG31" t="inlineStr"/>
+      <c r="CH31" t="inlineStr"/>
+      <c r="CI31" t="inlineStr"/>
+      <c r="CJ31" t="inlineStr"/>
+      <c r="CK31" t="inlineStr"/>
+      <c r="CL31" t="inlineStr"/>
+      <c r="CM31" t="inlineStr"/>
+      <c r="CN31" t="inlineStr"/>
+      <c r="CO31" t="inlineStr"/>
+      <c r="CP31" t="inlineStr"/>
+      <c r="CQ31" t="inlineStr"/>
+      <c r="CR31" t="inlineStr"/>
+      <c r="CS31" t="inlineStr"/>
+      <c r="CT31" t="inlineStr"/>
+      <c r="CU31" t="inlineStr"/>
+      <c r="CV31" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW31" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX31" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY31" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ31" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA31" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB31" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC31" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD31" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE31" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF31" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG31" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH31" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI31" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ31" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK31" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL31" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM31" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN31" t="inlineStr"/>
+      <c r="DO31" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP31" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ31" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR31" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS31" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT31" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU31" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV31" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW31" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX31" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY31" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ31" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA31" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB31" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC31" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED31" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE31" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF31" t="inlineStr"/>
+      <c r="EG31" t="inlineStr"/>
+      <c r="EH31" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI31" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ31" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK31" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>08/06/2026, 16:08:27</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>84</v>
+      </c>
+      <c r="D32" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>408</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>408</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1780945201</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>08/06/2026 16:00</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z32" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE32" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ32" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT32" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB32" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
+      <c r="BH32" t="inlineStr"/>
+      <c r="BI32" t="inlineStr"/>
+      <c r="BJ32" t="inlineStr"/>
+      <c r="BK32" t="inlineStr"/>
+      <c r="BL32" t="inlineStr"/>
+      <c r="BM32" t="inlineStr"/>
+      <c r="BN32" t="inlineStr"/>
+      <c r="BO32" t="inlineStr"/>
+      <c r="BP32" t="inlineStr"/>
+      <c r="BQ32" t="inlineStr"/>
+      <c r="BR32" t="inlineStr"/>
+      <c r="BS32" t="inlineStr"/>
+      <c r="BT32" t="inlineStr"/>
+      <c r="BU32" t="inlineStr"/>
+      <c r="BV32" t="inlineStr"/>
+      <c r="BW32" t="inlineStr"/>
+      <c r="BX32" t="inlineStr"/>
+      <c r="BY32" t="inlineStr"/>
+      <c r="BZ32" t="inlineStr"/>
+      <c r="CA32" t="inlineStr"/>
+      <c r="CB32" t="inlineStr"/>
+      <c r="CC32" t="inlineStr"/>
+      <c r="CD32" t="inlineStr"/>
+      <c r="CE32" t="inlineStr"/>
+      <c r="CF32" t="inlineStr"/>
+      <c r="CG32" t="inlineStr"/>
+      <c r="CH32" t="inlineStr"/>
+      <c r="CI32" t="inlineStr"/>
+      <c r="CJ32" t="inlineStr"/>
+      <c r="CK32" t="inlineStr"/>
+      <c r="CL32" t="inlineStr"/>
+      <c r="CM32" t="inlineStr"/>
+      <c r="CN32" t="inlineStr"/>
+      <c r="CO32" t="inlineStr"/>
+      <c r="CP32" t="inlineStr"/>
+      <c r="CQ32" t="inlineStr"/>
+      <c r="CR32" t="inlineStr"/>
+      <c r="CS32" t="inlineStr"/>
+      <c r="CT32" t="inlineStr"/>
+      <c r="CU32" t="inlineStr"/>
+      <c r="CV32" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW32" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX32" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY32" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ32" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA32" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB32" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC32" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD32" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE32" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF32" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG32" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH32" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI32" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ32" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK32" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL32" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM32" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN32" t="inlineStr"/>
+      <c r="DO32" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP32" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ32" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR32" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS32" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT32" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU32" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV32" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW32" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX32" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY32" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ32" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA32" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB32" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC32" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED32" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE32" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF32" t="inlineStr"/>
+      <c r="EG32" t="inlineStr"/>
+      <c r="EH32" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI32" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ32" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK32" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>08/06/2026, 16:09:45</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>84</v>
+      </c>
+      <c r="D33" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>408</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>408</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1780945279</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>08/06/2026 16:01</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z33" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE33" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="inlineStr"/>
+      <c r="AK33" t="inlineStr"/>
+      <c r="AL33" t="inlineStr"/>
+      <c r="AM33" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT33" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr"/>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
+      <c r="BI33" t="inlineStr"/>
+      <c r="BJ33" t="inlineStr"/>
+      <c r="BK33" t="inlineStr"/>
+      <c r="BL33" t="inlineStr"/>
+      <c r="BM33" t="inlineStr"/>
+      <c r="BN33" t="inlineStr"/>
+      <c r="BO33" t="inlineStr"/>
+      <c r="BP33" t="inlineStr"/>
+      <c r="BQ33" t="inlineStr"/>
+      <c r="BR33" t="inlineStr"/>
+      <c r="BS33" t="inlineStr"/>
+      <c r="BT33" t="inlineStr"/>
+      <c r="BU33" t="inlineStr"/>
+      <c r="BV33" t="inlineStr"/>
+      <c r="BW33" t="inlineStr"/>
+      <c r="BX33" t="inlineStr"/>
+      <c r="BY33" t="inlineStr"/>
+      <c r="BZ33" t="inlineStr"/>
+      <c r="CA33" t="inlineStr"/>
+      <c r="CB33" t="inlineStr"/>
+      <c r="CC33" t="inlineStr"/>
+      <c r="CD33" t="inlineStr"/>
+      <c r="CE33" t="inlineStr"/>
+      <c r="CF33" t="inlineStr"/>
+      <c r="CG33" t="inlineStr"/>
+      <c r="CH33" t="inlineStr"/>
+      <c r="CI33" t="inlineStr"/>
+      <c r="CJ33" t="inlineStr"/>
+      <c r="CK33" t="inlineStr"/>
+      <c r="CL33" t="inlineStr"/>
+      <c r="CM33" t="inlineStr"/>
+      <c r="CN33" t="inlineStr"/>
+      <c r="CO33" t="inlineStr"/>
+      <c r="CP33" t="inlineStr"/>
+      <c r="CQ33" t="inlineStr"/>
+      <c r="CR33" t="inlineStr"/>
+      <c r="CS33" t="inlineStr"/>
+      <c r="CT33" t="inlineStr"/>
+      <c r="CU33" t="inlineStr"/>
+      <c r="CV33" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW33" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX33" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY33" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ33" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA33" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB33" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC33" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD33" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE33" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF33" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG33" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH33" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI33" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ33" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK33" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL33" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM33" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN33" t="inlineStr"/>
+      <c r="DO33" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP33" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ33" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR33" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS33" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT33" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU33" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV33" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW33" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX33" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY33" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ33" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA33" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB33" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC33" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED33" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE33" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF33" t="inlineStr"/>
+      <c r="EG33" t="inlineStr"/>
+      <c r="EH33" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI33" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ33" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK33" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>08/06/2026, 16:10:54</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>84</v>
+      </c>
+      <c r="D34" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>408</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>408</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1780945349</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>08/06/2026 16:02</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W34" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z34" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE34" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
+      <c r="AL34" t="inlineStr"/>
+      <c r="AM34" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB34" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
+      <c r="BI34" t="inlineStr"/>
+      <c r="BJ34" t="inlineStr"/>
+      <c r="BK34" t="inlineStr"/>
+      <c r="BL34" t="inlineStr"/>
+      <c r="BM34" t="inlineStr"/>
+      <c r="BN34" t="inlineStr"/>
+      <c r="BO34" t="inlineStr"/>
+      <c r="BP34" t="inlineStr"/>
+      <c r="BQ34" t="inlineStr"/>
+      <c r="BR34" t="inlineStr"/>
+      <c r="BS34" t="inlineStr"/>
+      <c r="BT34" t="inlineStr"/>
+      <c r="BU34" t="inlineStr"/>
+      <c r="BV34" t="inlineStr"/>
+      <c r="BW34" t="inlineStr"/>
+      <c r="BX34" t="inlineStr"/>
+      <c r="BY34" t="inlineStr"/>
+      <c r="BZ34" t="inlineStr"/>
+      <c r="CA34" t="inlineStr"/>
+      <c r="CB34" t="inlineStr"/>
+      <c r="CC34" t="inlineStr"/>
+      <c r="CD34" t="inlineStr"/>
+      <c r="CE34" t="inlineStr"/>
+      <c r="CF34" t="inlineStr"/>
+      <c r="CG34" t="inlineStr"/>
+      <c r="CH34" t="inlineStr"/>
+      <c r="CI34" t="inlineStr"/>
+      <c r="CJ34" t="inlineStr"/>
+      <c r="CK34" t="inlineStr"/>
+      <c r="CL34" t="inlineStr"/>
+      <c r="CM34" t="inlineStr"/>
+      <c r="CN34" t="inlineStr"/>
+      <c r="CO34" t="inlineStr"/>
+      <c r="CP34" t="inlineStr"/>
+      <c r="CQ34" t="inlineStr"/>
+      <c r="CR34" t="inlineStr"/>
+      <c r="CS34" t="inlineStr"/>
+      <c r="CT34" t="inlineStr"/>
+      <c r="CU34" t="inlineStr"/>
+      <c r="CV34" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW34" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX34" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY34" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ34" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA34" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB34" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC34" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD34" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE34" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF34" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG34" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH34" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI34" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ34" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK34" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL34" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM34" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN34" t="inlineStr"/>
+      <c r="DO34" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP34" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ34" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR34" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS34" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT34" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU34" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV34" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW34" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX34" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY34" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ34" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA34" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB34" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC34" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED34" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE34" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF34" t="inlineStr"/>
+      <c r="EG34" t="inlineStr"/>
+      <c r="EH34" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI34" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ34" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK34" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>08/06/2026, 16:14:00</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>84</v>
+      </c>
+      <c r="D35" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>408</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>408</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1780945534</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>08/06/2026 16:05</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z35" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE35" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr"/>
+      <c r="AK35" t="inlineStr"/>
+      <c r="AL35" t="inlineStr"/>
+      <c r="AM35" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT35" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
+      <c r="BG35" t="inlineStr"/>
+      <c r="BH35" t="inlineStr"/>
+      <c r="BI35" t="inlineStr"/>
+      <c r="BJ35" t="inlineStr"/>
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="inlineStr"/>
+      <c r="BM35" t="inlineStr"/>
+      <c r="BN35" t="inlineStr"/>
+      <c r="BO35" t="inlineStr"/>
+      <c r="BP35" t="inlineStr"/>
+      <c r="BQ35" t="inlineStr"/>
+      <c r="BR35" t="inlineStr"/>
+      <c r="BS35" t="inlineStr"/>
+      <c r="BT35" t="inlineStr"/>
+      <c r="BU35" t="inlineStr"/>
+      <c r="BV35" t="inlineStr"/>
+      <c r="BW35" t="inlineStr"/>
+      <c r="BX35" t="inlineStr"/>
+      <c r="BY35" t="inlineStr"/>
+      <c r="BZ35" t="inlineStr"/>
+      <c r="CA35" t="inlineStr"/>
+      <c r="CB35" t="inlineStr"/>
+      <c r="CC35" t="inlineStr"/>
+      <c r="CD35" t="inlineStr"/>
+      <c r="CE35" t="inlineStr"/>
+      <c r="CF35" t="inlineStr"/>
+      <c r="CG35" t="inlineStr"/>
+      <c r="CH35" t="inlineStr"/>
+      <c r="CI35" t="inlineStr"/>
+      <c r="CJ35" t="inlineStr"/>
+      <c r="CK35" t="inlineStr"/>
+      <c r="CL35" t="inlineStr"/>
+      <c r="CM35" t="inlineStr"/>
+      <c r="CN35" t="inlineStr"/>
+      <c r="CO35" t="inlineStr"/>
+      <c r="CP35" t="inlineStr"/>
+      <c r="CQ35" t="inlineStr"/>
+      <c r="CR35" t="inlineStr"/>
+      <c r="CS35" t="inlineStr"/>
+      <c r="CT35" t="inlineStr"/>
+      <c r="CU35" t="inlineStr"/>
+      <c r="CV35" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW35" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX35" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY35" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ35" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA35" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB35" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC35" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD35" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE35" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF35" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG35" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH35" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI35" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ35" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK35" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL35" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM35" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN35" t="inlineStr"/>
+      <c r="DO35" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP35" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ35" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR35" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS35" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT35" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU35" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV35" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW35" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX35" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY35" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ35" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA35" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB35" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC35" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED35" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE35" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF35" t="inlineStr"/>
+      <c r="EG35" t="inlineStr"/>
+      <c r="EH35" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI35" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ35" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK35" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>08/06/2026, 16:15:04</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>84</v>
+      </c>
+      <c r="D36" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>408</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>408</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1780945598</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>08/06/2026 16:06</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z36" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE36" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="inlineStr"/>
+      <c r="AK36" t="inlineStr"/>
+      <c r="AL36" t="inlineStr"/>
+      <c r="AM36" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT36" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr"/>
+      <c r="BG36" t="inlineStr"/>
+      <c r="BH36" t="inlineStr"/>
+      <c r="BI36" t="inlineStr"/>
+      <c r="BJ36" t="inlineStr"/>
+      <c r="BK36" t="inlineStr"/>
+      <c r="BL36" t="inlineStr"/>
+      <c r="BM36" t="inlineStr"/>
+      <c r="BN36" t="inlineStr"/>
+      <c r="BO36" t="inlineStr"/>
+      <c r="BP36" t="inlineStr"/>
+      <c r="BQ36" t="inlineStr"/>
+      <c r="BR36" t="inlineStr"/>
+      <c r="BS36" t="inlineStr"/>
+      <c r="BT36" t="inlineStr"/>
+      <c r="BU36" t="inlineStr"/>
+      <c r="BV36" t="inlineStr"/>
+      <c r="BW36" t="inlineStr"/>
+      <c r="BX36" t="inlineStr"/>
+      <c r="BY36" t="inlineStr"/>
+      <c r="BZ36" t="inlineStr"/>
+      <c r="CA36" t="inlineStr"/>
+      <c r="CB36" t="inlineStr"/>
+      <c r="CC36" t="inlineStr"/>
+      <c r="CD36" t="inlineStr"/>
+      <c r="CE36" t="inlineStr"/>
+      <c r="CF36" t="inlineStr"/>
+      <c r="CG36" t="inlineStr"/>
+      <c r="CH36" t="inlineStr"/>
+      <c r="CI36" t="inlineStr"/>
+      <c r="CJ36" t="inlineStr"/>
+      <c r="CK36" t="inlineStr"/>
+      <c r="CL36" t="inlineStr"/>
+      <c r="CM36" t="inlineStr"/>
+      <c r="CN36" t="inlineStr"/>
+      <c r="CO36" t="inlineStr"/>
+      <c r="CP36" t="inlineStr"/>
+      <c r="CQ36" t="inlineStr"/>
+      <c r="CR36" t="inlineStr"/>
+      <c r="CS36" t="inlineStr"/>
+      <c r="CT36" t="inlineStr"/>
+      <c r="CU36" t="inlineStr"/>
+      <c r="CV36" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW36" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX36" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY36" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ36" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA36" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB36" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC36" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD36" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE36" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF36" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG36" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH36" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI36" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ36" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK36" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL36" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM36" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN36" t="inlineStr"/>
+      <c r="DO36" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP36" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ36" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR36" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS36" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT36" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU36" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV36" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW36" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX36" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY36" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ36" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA36" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB36" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC36" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED36" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE36" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF36" t="inlineStr"/>
+      <c r="EG36" t="inlineStr"/>
+      <c r="EH36" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI36" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ36" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK36" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>08/06/2026, 16:25:04</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0121000</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>01210000010</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1780887600</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1780946198</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>08/06/2026 16:16</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="inlineStr"/>
+      <c r="AK37" t="inlineStr"/>
+      <c r="AL37" t="inlineStr"/>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr">
+        <is>
+          <t>3500.00</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr"/>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr"/>
+      <c r="BG37" t="inlineStr"/>
+      <c r="BH37" t="inlineStr"/>
+      <c r="BI37" t="inlineStr"/>
+      <c r="BJ37" t="inlineStr"/>
+      <c r="BK37" t="inlineStr"/>
+      <c r="BL37" t="inlineStr"/>
+      <c r="BM37" t="inlineStr"/>
+      <c r="BN37" t="inlineStr"/>
+      <c r="BO37" t="inlineStr"/>
+      <c r="BP37" t="inlineStr"/>
+      <c r="BQ37" t="inlineStr"/>
+      <c r="BR37" t="inlineStr"/>
+      <c r="BS37" t="inlineStr"/>
+      <c r="BT37" t="inlineStr"/>
+      <c r="BU37" t="inlineStr"/>
+      <c r="BV37" t="inlineStr"/>
+      <c r="BW37" t="inlineStr"/>
+      <c r="BX37" t="inlineStr"/>
+      <c r="BY37" t="inlineStr"/>
+      <c r="BZ37" t="inlineStr"/>
+      <c r="CA37" t="inlineStr"/>
+      <c r="CB37" t="inlineStr"/>
+      <c r="CC37" t="inlineStr"/>
+      <c r="CD37" t="inlineStr"/>
+      <c r="CE37" t="inlineStr"/>
+      <c r="CF37" t="inlineStr"/>
+      <c r="CG37" t="inlineStr"/>
+      <c r="CH37" t="inlineStr"/>
+      <c r="CI37" t="inlineStr"/>
+      <c r="CJ37" t="inlineStr"/>
+      <c r="CK37" t="inlineStr"/>
+      <c r="CL37" t="inlineStr"/>
+      <c r="CM37" t="inlineStr"/>
+      <c r="CN37" t="inlineStr"/>
+      <c r="CO37" t="inlineStr"/>
+      <c r="CP37" t="inlineStr"/>
+      <c r="CQ37" t="inlineStr"/>
+      <c r="CR37" t="inlineStr"/>
+      <c r="CS37" t="inlineStr"/>
+      <c r="CT37" t="inlineStr"/>
+      <c r="CU37" t="inlineStr"/>
+      <c r="CV37" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW37" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX37" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY37" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ37" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA37" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB37" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC37" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD37" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE37" t="inlineStr">
+        <is>
+          <t>1121029128</t>
+        </is>
+      </c>
+      <c r="DF37" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG37" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH37" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI37" t="inlineStr">
+        <is>
+          <t>212122</t>
+        </is>
+      </c>
+      <c r="DJ37" t="inlineStr">
+        <is>
+          <t>12344</t>
+        </is>
+      </c>
+      <c r="DK37" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL37" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM37" t="inlineStr">
+        <is>
+          <t>121212212112</t>
+        </is>
+      </c>
+      <c r="DN37" t="inlineStr"/>
+      <c r="DO37" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP37" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ37" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR37" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+      <c r="DS37" t="inlineStr">
+        <is>
+          <t>3144</t>
+        </is>
+      </c>
+      <c r="DT37" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU37" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV37" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW37" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="DX37" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY37" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ37" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA37" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB37" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC37" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED37" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE37" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF37" t="inlineStr"/>
+      <c r="EG37" t="inlineStr"/>
+      <c r="EH37" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI37" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ37" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK37" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12493,13 +17289,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B6294CC-8429-4C63-A44E-44A628E2ACE5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE751E45-8382-40E1-801A-0A2FC209627A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{311BAE5D-3F8F-438D-BB80-DF8E8CD7C837}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55EDDF23-E659-4E27-95CB-CE6FF0CB7BA8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A122744-7312-4534-8A32-66E24F2B507E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{470B21B9-7EA8-4B86-B102-AA8A96485515}"/>
 </file>
--- a/dados_formularios.xlsx
+++ b/dados_formularios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL37"/>
+  <dimension ref="A1:EL38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16583,47 +16583,33 @@
           <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>0121000</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>01210000010</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C37" t="n">
+        <v>84</v>
+      </c>
+      <c r="D37" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>22133</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="L37" t="n">
+        <v>408</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -16635,25 +16621,19 @@
           <t>robo.relatorio@folhatech.com.br</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="O37" t="n">
+        <v>408</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Robo Cadastro Cliente</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>1780887600</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>1780946198</t>
-        </is>
+      <c r="Q37" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1780946198</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -16675,10 +16655,8 @@
           <t>03/06/2026 17:13</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="W37" t="n">
+        <v>22133</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -16690,35 +16668,27 @@
           <t>04/06/2026 17:25</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="Z37" t="n">
+        <v>127857</v>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>08 - Confecção e assinatura (Contrato)</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
+      <c r="AB37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>487</v>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
           <t>Pedro Santana</t>
         </is>
       </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>0121</t>
-        </is>
+      <c r="AE37" t="n">
+        <v>121</v>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
@@ -16735,10 +16705,8 @@
       <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr"/>
       <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>127857</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
@@ -16770,10 +16738,8 @@
           <t>Aumento de quadro</t>
         </is>
       </c>
-      <c r="AT37" t="inlineStr">
-        <is>
-          <t>3500.00</t>
-        </is>
+      <c r="AT37" t="n">
+        <v>3500</v>
       </c>
       <c r="AU37" t="inlineStr"/>
       <c r="AV37" t="inlineStr">
@@ -16901,10 +16867,8 @@
           <t>Pai</t>
         </is>
       </c>
-      <c r="DE37" t="inlineStr">
-        <is>
-          <t>1121029128</t>
-        </is>
+      <c r="DE37" t="n">
+        <v>1121029128</v>
       </c>
       <c r="DF37" t="inlineStr">
         <is>
@@ -16921,15 +16885,11 @@
           <t>Namorado(a)</t>
         </is>
       </c>
-      <c r="DI37" t="inlineStr">
-        <is>
-          <t>212122</t>
-        </is>
-      </c>
-      <c r="DJ37" t="inlineStr">
-        <is>
-          <t>12344</t>
-        </is>
+      <c r="DI37" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ37" t="n">
+        <v>12344</v>
       </c>
       <c r="DK37" t="inlineStr">
         <is>
@@ -16941,10 +16901,8 @@
           <t>pedro.santana@folhatech.com.br</t>
         </is>
       </c>
-      <c r="DM37" t="inlineStr">
-        <is>
-          <t>121212212112</t>
-        </is>
+      <c r="DM37" t="n">
+        <v>121212212112</v>
       </c>
       <c r="DN37" t="inlineStr"/>
       <c r="DO37" t="inlineStr">
@@ -16962,15 +16920,11 @@
           <t>Conta Corrente</t>
         </is>
       </c>
-      <c r="DR37" t="inlineStr">
-        <is>
-          <t>12121</t>
-        </is>
-      </c>
-      <c r="DS37" t="inlineStr">
-        <is>
-          <t>3144</t>
-        </is>
+      <c r="DR37" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS37" t="n">
+        <v>3144</v>
       </c>
       <c r="DT37" t="inlineStr">
         <is>
@@ -16987,10 +16941,8 @@
           <t>etetetet</t>
         </is>
       </c>
-      <c r="DW37" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="DW37" t="n">
+        <v>124</v>
       </c>
       <c r="DX37" t="inlineStr">
         <is>
@@ -17055,6 +17007,490 @@
         </is>
       </c>
       <c r="EL37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>08/06/2026, 16:41:31</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0121000</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>01210000010</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1780887600</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1780947185</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>08/06/2026 16:33</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="inlineStr"/>
+      <c r="AK38" t="inlineStr"/>
+      <c r="AL38" t="inlineStr"/>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr">
+        <is>
+          <t>3500.00</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr"/>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr"/>
+      <c r="BG38" t="inlineStr"/>
+      <c r="BH38" t="inlineStr"/>
+      <c r="BI38" t="inlineStr"/>
+      <c r="BJ38" t="inlineStr"/>
+      <c r="BK38" t="inlineStr"/>
+      <c r="BL38" t="inlineStr"/>
+      <c r="BM38" t="inlineStr"/>
+      <c r="BN38" t="inlineStr"/>
+      <c r="BO38" t="inlineStr"/>
+      <c r="BP38" t="inlineStr"/>
+      <c r="BQ38" t="inlineStr"/>
+      <c r="BR38" t="inlineStr"/>
+      <c r="BS38" t="inlineStr"/>
+      <c r="BT38" t="inlineStr"/>
+      <c r="BU38" t="inlineStr"/>
+      <c r="BV38" t="inlineStr"/>
+      <c r="BW38" t="inlineStr"/>
+      <c r="BX38" t="inlineStr"/>
+      <c r="BY38" t="inlineStr"/>
+      <c r="BZ38" t="inlineStr"/>
+      <c r="CA38" t="inlineStr"/>
+      <c r="CB38" t="inlineStr"/>
+      <c r="CC38" t="inlineStr"/>
+      <c r="CD38" t="inlineStr"/>
+      <c r="CE38" t="inlineStr"/>
+      <c r="CF38" t="inlineStr"/>
+      <c r="CG38" t="inlineStr"/>
+      <c r="CH38" t="inlineStr"/>
+      <c r="CI38" t="inlineStr"/>
+      <c r="CJ38" t="inlineStr"/>
+      <c r="CK38" t="inlineStr"/>
+      <c r="CL38" t="inlineStr"/>
+      <c r="CM38" t="inlineStr"/>
+      <c r="CN38" t="inlineStr"/>
+      <c r="CO38" t="inlineStr"/>
+      <c r="CP38" t="inlineStr"/>
+      <c r="CQ38" t="inlineStr"/>
+      <c r="CR38" t="inlineStr"/>
+      <c r="CS38" t="inlineStr"/>
+      <c r="CT38" t="inlineStr"/>
+      <c r="CU38" t="inlineStr"/>
+      <c r="CV38" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW38" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX38" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY38" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ38" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA38" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB38" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC38" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD38" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE38" t="inlineStr">
+        <is>
+          <t>1121029128</t>
+        </is>
+      </c>
+      <c r="DF38" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG38" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH38" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI38" t="inlineStr">
+        <is>
+          <t>212122</t>
+        </is>
+      </c>
+      <c r="DJ38" t="inlineStr">
+        <is>
+          <t>12344</t>
+        </is>
+      </c>
+      <c r="DK38" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL38" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM38" t="inlineStr">
+        <is>
+          <t>121212212112</t>
+        </is>
+      </c>
+      <c r="DN38" t="inlineStr"/>
+      <c r="DO38" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP38" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ38" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR38" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+      <c r="DS38" t="inlineStr">
+        <is>
+          <t>3144</t>
+        </is>
+      </c>
+      <c r="DT38" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU38" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV38" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW38" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="DX38" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY38" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ38" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA38" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB38" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC38" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED38" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE38" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF38" t="inlineStr"/>
+      <c r="EG38" t="inlineStr"/>
+      <c r="EH38" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI38" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ38" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK38" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17289,13 +17725,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EE751E45-8382-40E1-801A-0A2FC209627A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9162617-93AF-40BB-9DCB-EBC8E391BA75}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55EDDF23-E659-4E27-95CB-CE6FF0CB7BA8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78CF7E72-26DD-410D-9C19-B1F12050467C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{470B21B9-7EA8-4B86-B102-AA8A96485515}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BED12907-72DE-4F09-AD72-39393081ED76}"/>
 </file>
--- a/dados_formularios.xlsx
+++ b/dados_formularios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL38"/>
+  <dimension ref="A1:EL51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17019,47 +17019,33 @@
           <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>0121000</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>01210000010</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C38" t="n">
+        <v>84</v>
+      </c>
+      <c r="D38" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>22133</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="L38" t="n">
+        <v>408</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -17071,25 +17057,19 @@
           <t>robo.relatorio@folhatech.com.br</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="O38" t="n">
+        <v>408</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Robo Cadastro Cliente</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>1780887600</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>1780947185</t>
-        </is>
+      <c r="Q38" t="n">
+        <v>1780887600</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1780947185</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -17111,10 +17091,8 @@
           <t>03/06/2026 17:13</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="W38" t="n">
+        <v>22133</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -17126,35 +17104,27 @@
           <t>04/06/2026 17:25</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="Z38" t="n">
+        <v>127857</v>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>08 - Confecção e assinatura (Contrato)</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
+      <c r="AB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>487</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
           <t>Pedro Santana</t>
         </is>
       </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>0121</t>
-        </is>
+      <c r="AE38" t="n">
+        <v>121</v>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
@@ -17171,10 +17141,8 @@
       <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr"/>
       <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>127857</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
@@ -17206,10 +17174,8 @@
           <t>Aumento de quadro</t>
         </is>
       </c>
-      <c r="AT38" t="inlineStr">
-        <is>
-          <t>3500.00</t>
-        </is>
+      <c r="AT38" t="n">
+        <v>3500</v>
       </c>
       <c r="AU38" t="inlineStr"/>
       <c r="AV38" t="inlineStr">
@@ -17337,10 +17303,8 @@
           <t>Pai</t>
         </is>
       </c>
-      <c r="DE38" t="inlineStr">
-        <is>
-          <t>1121029128</t>
-        </is>
+      <c r="DE38" t="n">
+        <v>1121029128</v>
       </c>
       <c r="DF38" t="inlineStr">
         <is>
@@ -17357,15 +17321,11 @@
           <t>Namorado(a)</t>
         </is>
       </c>
-      <c r="DI38" t="inlineStr">
-        <is>
-          <t>212122</t>
-        </is>
-      </c>
-      <c r="DJ38" t="inlineStr">
-        <is>
-          <t>12344</t>
-        </is>
+      <c r="DI38" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ38" t="n">
+        <v>12344</v>
       </c>
       <c r="DK38" t="inlineStr">
         <is>
@@ -17377,10 +17337,8 @@
           <t>pedro.santana@folhatech.com.br</t>
         </is>
       </c>
-      <c r="DM38" t="inlineStr">
-        <is>
-          <t>121212212112</t>
-        </is>
+      <c r="DM38" t="n">
+        <v>121212212112</v>
       </c>
       <c r="DN38" t="inlineStr"/>
       <c r="DO38" t="inlineStr">
@@ -17398,15 +17356,11 @@
           <t>Conta Corrente</t>
         </is>
       </c>
-      <c r="DR38" t="inlineStr">
-        <is>
-          <t>12121</t>
-        </is>
-      </c>
-      <c r="DS38" t="inlineStr">
-        <is>
-          <t>3144</t>
-        </is>
+      <c r="DR38" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS38" t="n">
+        <v>3144</v>
       </c>
       <c r="DT38" t="inlineStr">
         <is>
@@ -17423,10 +17377,8 @@
           <t>etetetet</t>
         </is>
       </c>
-      <c r="DW38" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="DW38" t="n">
+        <v>124</v>
       </c>
       <c r="DX38" t="inlineStr">
         <is>
@@ -17491,6 +17443,5722 @@
         </is>
       </c>
       <c r="EL38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>09/06/2026, 19:21:36</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>84</v>
+      </c>
+      <c r="D39" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>408</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>408</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>1780974000</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1781043181</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>09/06/2026 19:13</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W39" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z39" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE39" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr"/>
+      <c r="AK39" t="inlineStr"/>
+      <c r="AL39" t="inlineStr"/>
+      <c r="AM39" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT39" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU39" t="inlineStr"/>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
+      <c r="BG39" t="inlineStr"/>
+      <c r="BH39" t="inlineStr"/>
+      <c r="BI39" t="inlineStr"/>
+      <c r="BJ39" t="inlineStr"/>
+      <c r="BK39" t="inlineStr"/>
+      <c r="BL39" t="inlineStr"/>
+      <c r="BM39" t="inlineStr"/>
+      <c r="BN39" t="inlineStr"/>
+      <c r="BO39" t="inlineStr"/>
+      <c r="BP39" t="inlineStr"/>
+      <c r="BQ39" t="inlineStr"/>
+      <c r="BR39" t="inlineStr"/>
+      <c r="BS39" t="inlineStr"/>
+      <c r="BT39" t="inlineStr"/>
+      <c r="BU39" t="inlineStr"/>
+      <c r="BV39" t="inlineStr"/>
+      <c r="BW39" t="inlineStr"/>
+      <c r="BX39" t="inlineStr"/>
+      <c r="BY39" t="inlineStr"/>
+      <c r="BZ39" t="inlineStr"/>
+      <c r="CA39" t="inlineStr"/>
+      <c r="CB39" t="inlineStr"/>
+      <c r="CC39" t="inlineStr"/>
+      <c r="CD39" t="inlineStr"/>
+      <c r="CE39" t="inlineStr"/>
+      <c r="CF39" t="inlineStr"/>
+      <c r="CG39" t="inlineStr"/>
+      <c r="CH39" t="inlineStr"/>
+      <c r="CI39" t="inlineStr"/>
+      <c r="CJ39" t="inlineStr"/>
+      <c r="CK39" t="inlineStr"/>
+      <c r="CL39" t="inlineStr"/>
+      <c r="CM39" t="inlineStr"/>
+      <c r="CN39" t="inlineStr"/>
+      <c r="CO39" t="inlineStr"/>
+      <c r="CP39" t="inlineStr"/>
+      <c r="CQ39" t="inlineStr"/>
+      <c r="CR39" t="inlineStr"/>
+      <c r="CS39" t="inlineStr"/>
+      <c r="CT39" t="inlineStr"/>
+      <c r="CU39" t="inlineStr"/>
+      <c r="CV39" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW39" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX39" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY39" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ39" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA39" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB39" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC39" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD39" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE39" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF39" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG39" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH39" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI39" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ39" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK39" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL39" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM39" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN39" t="inlineStr"/>
+      <c r="DO39" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP39" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ39" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR39" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS39" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT39" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU39" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV39" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW39" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX39" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY39" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ39" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA39" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB39" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC39" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED39" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE39" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF39" t="inlineStr"/>
+      <c r="EG39" t="inlineStr"/>
+      <c r="EH39" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI39" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ39" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK39" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>09/06/2026, 19:28:20</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>84</v>
+      </c>
+      <c r="D40" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>408</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>408</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>1780974000</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1781043585</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>09/06/2026 19:19</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W40" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z40" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE40" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="inlineStr"/>
+      <c r="AK40" t="inlineStr"/>
+      <c r="AL40" t="inlineStr"/>
+      <c r="AM40" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT40" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU40" t="inlineStr"/>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr"/>
+      <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr"/>
+      <c r="BF40" t="inlineStr"/>
+      <c r="BG40" t="inlineStr"/>
+      <c r="BH40" t="inlineStr"/>
+      <c r="BI40" t="inlineStr"/>
+      <c r="BJ40" t="inlineStr"/>
+      <c r="BK40" t="inlineStr"/>
+      <c r="BL40" t="inlineStr"/>
+      <c r="BM40" t="inlineStr"/>
+      <c r="BN40" t="inlineStr"/>
+      <c r="BO40" t="inlineStr"/>
+      <c r="BP40" t="inlineStr"/>
+      <c r="BQ40" t="inlineStr"/>
+      <c r="BR40" t="inlineStr"/>
+      <c r="BS40" t="inlineStr"/>
+      <c r="BT40" t="inlineStr"/>
+      <c r="BU40" t="inlineStr"/>
+      <c r="BV40" t="inlineStr"/>
+      <c r="BW40" t="inlineStr"/>
+      <c r="BX40" t="inlineStr"/>
+      <c r="BY40" t="inlineStr"/>
+      <c r="BZ40" t="inlineStr"/>
+      <c r="CA40" t="inlineStr"/>
+      <c r="CB40" t="inlineStr"/>
+      <c r="CC40" t="inlineStr"/>
+      <c r="CD40" t="inlineStr"/>
+      <c r="CE40" t="inlineStr"/>
+      <c r="CF40" t="inlineStr"/>
+      <c r="CG40" t="inlineStr"/>
+      <c r="CH40" t="inlineStr"/>
+      <c r="CI40" t="inlineStr"/>
+      <c r="CJ40" t="inlineStr"/>
+      <c r="CK40" t="inlineStr"/>
+      <c r="CL40" t="inlineStr"/>
+      <c r="CM40" t="inlineStr"/>
+      <c r="CN40" t="inlineStr"/>
+      <c r="CO40" t="inlineStr"/>
+      <c r="CP40" t="inlineStr"/>
+      <c r="CQ40" t="inlineStr"/>
+      <c r="CR40" t="inlineStr"/>
+      <c r="CS40" t="inlineStr"/>
+      <c r="CT40" t="inlineStr"/>
+      <c r="CU40" t="inlineStr"/>
+      <c r="CV40" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW40" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX40" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY40" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ40" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA40" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB40" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC40" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD40" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE40" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF40" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG40" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH40" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI40" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ40" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK40" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL40" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM40" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN40" t="inlineStr"/>
+      <c r="DO40" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP40" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ40" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR40" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS40" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT40" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU40" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV40" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW40" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX40" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY40" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ40" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA40" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB40" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC40" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED40" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE40" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF40" t="inlineStr"/>
+      <c r="EG40" t="inlineStr"/>
+      <c r="EH40" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI40" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ40" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK40" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>09/06/2026, 19:30:38</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>84</v>
+      </c>
+      <c r="D41" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>408</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>408</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>1780974000</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1781043723</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>09/06/2026 19:22</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W41" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z41" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE41" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="inlineStr"/>
+      <c r="AK41" t="inlineStr"/>
+      <c r="AL41" t="inlineStr"/>
+      <c r="AM41" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ41" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT41" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU41" t="inlineStr"/>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr"/>
+      <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="inlineStr"/>
+      <c r="BG41" t="inlineStr"/>
+      <c r="BH41" t="inlineStr"/>
+      <c r="BI41" t="inlineStr"/>
+      <c r="BJ41" t="inlineStr"/>
+      <c r="BK41" t="inlineStr"/>
+      <c r="BL41" t="inlineStr"/>
+      <c r="BM41" t="inlineStr"/>
+      <c r="BN41" t="inlineStr"/>
+      <c r="BO41" t="inlineStr"/>
+      <c r="BP41" t="inlineStr"/>
+      <c r="BQ41" t="inlineStr"/>
+      <c r="BR41" t="inlineStr"/>
+      <c r="BS41" t="inlineStr"/>
+      <c r="BT41" t="inlineStr"/>
+      <c r="BU41" t="inlineStr"/>
+      <c r="BV41" t="inlineStr"/>
+      <c r="BW41" t="inlineStr"/>
+      <c r="BX41" t="inlineStr"/>
+      <c r="BY41" t="inlineStr"/>
+      <c r="BZ41" t="inlineStr"/>
+      <c r="CA41" t="inlineStr"/>
+      <c r="CB41" t="inlineStr"/>
+      <c r="CC41" t="inlineStr"/>
+      <c r="CD41" t="inlineStr"/>
+      <c r="CE41" t="inlineStr"/>
+      <c r="CF41" t="inlineStr"/>
+      <c r="CG41" t="inlineStr"/>
+      <c r="CH41" t="inlineStr"/>
+      <c r="CI41" t="inlineStr"/>
+      <c r="CJ41" t="inlineStr"/>
+      <c r="CK41" t="inlineStr"/>
+      <c r="CL41" t="inlineStr"/>
+      <c r="CM41" t="inlineStr"/>
+      <c r="CN41" t="inlineStr"/>
+      <c r="CO41" t="inlineStr"/>
+      <c r="CP41" t="inlineStr"/>
+      <c r="CQ41" t="inlineStr"/>
+      <c r="CR41" t="inlineStr"/>
+      <c r="CS41" t="inlineStr"/>
+      <c r="CT41" t="inlineStr"/>
+      <c r="CU41" t="inlineStr"/>
+      <c r="CV41" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW41" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX41" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY41" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ41" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA41" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB41" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC41" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD41" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE41" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF41" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG41" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH41" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI41" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ41" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK41" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL41" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM41" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN41" t="inlineStr"/>
+      <c r="DO41" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP41" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ41" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR41" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS41" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT41" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU41" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV41" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW41" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX41" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY41" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ41" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA41" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB41" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC41" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED41" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE41" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF41" t="inlineStr"/>
+      <c r="EG41" t="inlineStr"/>
+      <c r="EH41" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI41" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ41" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK41" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>09/06/2026, 19:34:31</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>84</v>
+      </c>
+      <c r="D42" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>408</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>408</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>1780974000</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1781043957</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>09/06/2026 19:25</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W42" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z42" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE42" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="inlineStr"/>
+      <c r="AK42" t="inlineStr"/>
+      <c r="AL42" t="inlineStr"/>
+      <c r="AM42" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ42" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT42" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU42" t="inlineStr"/>
+      <c r="AV42" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB42" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC42" t="inlineStr"/>
+      <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr"/>
+      <c r="BG42" t="inlineStr"/>
+      <c r="BH42" t="inlineStr"/>
+      <c r="BI42" t="inlineStr"/>
+      <c r="BJ42" t="inlineStr"/>
+      <c r="BK42" t="inlineStr"/>
+      <c r="BL42" t="inlineStr"/>
+      <c r="BM42" t="inlineStr"/>
+      <c r="BN42" t="inlineStr"/>
+      <c r="BO42" t="inlineStr"/>
+      <c r="BP42" t="inlineStr"/>
+      <c r="BQ42" t="inlineStr"/>
+      <c r="BR42" t="inlineStr"/>
+      <c r="BS42" t="inlineStr"/>
+      <c r="BT42" t="inlineStr"/>
+      <c r="BU42" t="inlineStr"/>
+      <c r="BV42" t="inlineStr"/>
+      <c r="BW42" t="inlineStr"/>
+      <c r="BX42" t="inlineStr"/>
+      <c r="BY42" t="inlineStr"/>
+      <c r="BZ42" t="inlineStr"/>
+      <c r="CA42" t="inlineStr"/>
+      <c r="CB42" t="inlineStr"/>
+      <c r="CC42" t="inlineStr"/>
+      <c r="CD42" t="inlineStr"/>
+      <c r="CE42" t="inlineStr"/>
+      <c r="CF42" t="inlineStr"/>
+      <c r="CG42" t="inlineStr"/>
+      <c r="CH42" t="inlineStr"/>
+      <c r="CI42" t="inlineStr"/>
+      <c r="CJ42" t="inlineStr"/>
+      <c r="CK42" t="inlineStr"/>
+      <c r="CL42" t="inlineStr"/>
+      <c r="CM42" t="inlineStr"/>
+      <c r="CN42" t="inlineStr"/>
+      <c r="CO42" t="inlineStr"/>
+      <c r="CP42" t="inlineStr"/>
+      <c r="CQ42" t="inlineStr"/>
+      <c r="CR42" t="inlineStr"/>
+      <c r="CS42" t="inlineStr"/>
+      <c r="CT42" t="inlineStr"/>
+      <c r="CU42" t="inlineStr"/>
+      <c r="CV42" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW42" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX42" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY42" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ42" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA42" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB42" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC42" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD42" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE42" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF42" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG42" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH42" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI42" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ42" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK42" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL42" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM42" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN42" t="inlineStr"/>
+      <c r="DO42" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP42" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ42" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR42" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS42" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT42" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU42" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV42" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW42" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX42" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY42" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ42" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA42" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB42" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC42" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED42" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE42" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF42" t="inlineStr"/>
+      <c r="EG42" t="inlineStr"/>
+      <c r="EH42" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI42" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ42" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK42" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>09/06/2026, 19:57:34</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>84</v>
+      </c>
+      <c r="D43" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>408</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>408</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>1780974000</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1781045339</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>19:48</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>09/06/2026 19:48</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W43" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z43" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE43" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="inlineStr"/>
+      <c r="AK43" t="inlineStr"/>
+      <c r="AL43" t="inlineStr"/>
+      <c r="AM43" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP43" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ43" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT43" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU43" t="inlineStr"/>
+      <c r="AV43" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr"/>
+      <c r="BD43" t="inlineStr"/>
+      <c r="BE43" t="inlineStr"/>
+      <c r="BF43" t="inlineStr"/>
+      <c r="BG43" t="inlineStr"/>
+      <c r="BH43" t="inlineStr"/>
+      <c r="BI43" t="inlineStr"/>
+      <c r="BJ43" t="inlineStr"/>
+      <c r="BK43" t="inlineStr"/>
+      <c r="BL43" t="inlineStr"/>
+      <c r="BM43" t="inlineStr"/>
+      <c r="BN43" t="inlineStr"/>
+      <c r="BO43" t="inlineStr"/>
+      <c r="BP43" t="inlineStr"/>
+      <c r="BQ43" t="inlineStr"/>
+      <c r="BR43" t="inlineStr"/>
+      <c r="BS43" t="inlineStr"/>
+      <c r="BT43" t="inlineStr"/>
+      <c r="BU43" t="inlineStr"/>
+      <c r="BV43" t="inlineStr"/>
+      <c r="BW43" t="inlineStr"/>
+      <c r="BX43" t="inlineStr"/>
+      <c r="BY43" t="inlineStr"/>
+      <c r="BZ43" t="inlineStr"/>
+      <c r="CA43" t="inlineStr"/>
+      <c r="CB43" t="inlineStr"/>
+      <c r="CC43" t="inlineStr"/>
+      <c r="CD43" t="inlineStr"/>
+      <c r="CE43" t="inlineStr"/>
+      <c r="CF43" t="inlineStr"/>
+      <c r="CG43" t="inlineStr"/>
+      <c r="CH43" t="inlineStr"/>
+      <c r="CI43" t="inlineStr"/>
+      <c r="CJ43" t="inlineStr"/>
+      <c r="CK43" t="inlineStr"/>
+      <c r="CL43" t="inlineStr"/>
+      <c r="CM43" t="inlineStr"/>
+      <c r="CN43" t="inlineStr"/>
+      <c r="CO43" t="inlineStr"/>
+      <c r="CP43" t="inlineStr"/>
+      <c r="CQ43" t="inlineStr"/>
+      <c r="CR43" t="inlineStr"/>
+      <c r="CS43" t="inlineStr"/>
+      <c r="CT43" t="inlineStr"/>
+      <c r="CU43" t="inlineStr"/>
+      <c r="CV43" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW43" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX43" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY43" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ43" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA43" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB43" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC43" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD43" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE43" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF43" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG43" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH43" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI43" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ43" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK43" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL43" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM43" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN43" t="inlineStr"/>
+      <c r="DO43" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP43" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ43" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR43" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS43" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT43" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU43" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV43" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW43" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX43" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY43" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ43" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA43" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB43" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC43" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED43" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE43" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF43" t="inlineStr"/>
+      <c r="EG43" t="inlineStr"/>
+      <c r="EH43" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI43" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ43" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK43" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>09/06/2026, 20:00:45</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>84</v>
+      </c>
+      <c r="D44" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>408</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>408</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>1780974000</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1781045530</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>09/06/2026 19:52</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W44" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z44" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE44" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="inlineStr"/>
+      <c r="AK44" t="inlineStr"/>
+      <c r="AL44" t="inlineStr"/>
+      <c r="AM44" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP44" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ44" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT44" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU44" t="inlineStr"/>
+      <c r="AV44" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB44" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC44" t="inlineStr"/>
+      <c r="BD44" t="inlineStr"/>
+      <c r="BE44" t="inlineStr"/>
+      <c r="BF44" t="inlineStr"/>
+      <c r="BG44" t="inlineStr"/>
+      <c r="BH44" t="inlineStr"/>
+      <c r="BI44" t="inlineStr"/>
+      <c r="BJ44" t="inlineStr"/>
+      <c r="BK44" t="inlineStr"/>
+      <c r="BL44" t="inlineStr"/>
+      <c r="BM44" t="inlineStr"/>
+      <c r="BN44" t="inlineStr"/>
+      <c r="BO44" t="inlineStr"/>
+      <c r="BP44" t="inlineStr"/>
+      <c r="BQ44" t="inlineStr"/>
+      <c r="BR44" t="inlineStr"/>
+      <c r="BS44" t="inlineStr"/>
+      <c r="BT44" t="inlineStr"/>
+      <c r="BU44" t="inlineStr"/>
+      <c r="BV44" t="inlineStr"/>
+      <c r="BW44" t="inlineStr"/>
+      <c r="BX44" t="inlineStr"/>
+      <c r="BY44" t="inlineStr"/>
+      <c r="BZ44" t="inlineStr"/>
+      <c r="CA44" t="inlineStr"/>
+      <c r="CB44" t="inlineStr"/>
+      <c r="CC44" t="inlineStr"/>
+      <c r="CD44" t="inlineStr"/>
+      <c r="CE44" t="inlineStr"/>
+      <c r="CF44" t="inlineStr"/>
+      <c r="CG44" t="inlineStr"/>
+      <c r="CH44" t="inlineStr"/>
+      <c r="CI44" t="inlineStr"/>
+      <c r="CJ44" t="inlineStr"/>
+      <c r="CK44" t="inlineStr"/>
+      <c r="CL44" t="inlineStr"/>
+      <c r="CM44" t="inlineStr"/>
+      <c r="CN44" t="inlineStr"/>
+      <c r="CO44" t="inlineStr"/>
+      <c r="CP44" t="inlineStr"/>
+      <c r="CQ44" t="inlineStr"/>
+      <c r="CR44" t="inlineStr"/>
+      <c r="CS44" t="inlineStr"/>
+      <c r="CT44" t="inlineStr"/>
+      <c r="CU44" t="inlineStr"/>
+      <c r="CV44" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW44" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX44" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY44" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ44" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA44" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB44" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC44" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD44" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE44" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF44" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG44" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH44" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI44" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ44" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK44" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL44" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM44" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN44" t="inlineStr"/>
+      <c r="DO44" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP44" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ44" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR44" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS44" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT44" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU44" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV44" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW44" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX44" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY44" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ44" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA44" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB44" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC44" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED44" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE44" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF44" t="inlineStr"/>
+      <c r="EG44" t="inlineStr"/>
+      <c r="EH44" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI44" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ44" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK44" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>09/06/2026, 20:07:27</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>84</v>
+      </c>
+      <c r="D45" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>408</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>408</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>1780974000</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1781045932</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>09/06/2026 19:58</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W45" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z45" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE45" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="inlineStr"/>
+      <c r="AK45" t="inlineStr"/>
+      <c r="AL45" t="inlineStr"/>
+      <c r="AM45" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP45" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ45" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT45" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU45" t="inlineStr"/>
+      <c r="AV45" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr"/>
+      <c r="BD45" t="inlineStr"/>
+      <c r="BE45" t="inlineStr"/>
+      <c r="BF45" t="inlineStr"/>
+      <c r="BG45" t="inlineStr"/>
+      <c r="BH45" t="inlineStr"/>
+      <c r="BI45" t="inlineStr"/>
+      <c r="BJ45" t="inlineStr"/>
+      <c r="BK45" t="inlineStr"/>
+      <c r="BL45" t="inlineStr"/>
+      <c r="BM45" t="inlineStr"/>
+      <c r="BN45" t="inlineStr"/>
+      <c r="BO45" t="inlineStr"/>
+      <c r="BP45" t="inlineStr"/>
+      <c r="BQ45" t="inlineStr"/>
+      <c r="BR45" t="inlineStr"/>
+      <c r="BS45" t="inlineStr"/>
+      <c r="BT45" t="inlineStr"/>
+      <c r="BU45" t="inlineStr"/>
+      <c r="BV45" t="inlineStr"/>
+      <c r="BW45" t="inlineStr"/>
+      <c r="BX45" t="inlineStr"/>
+      <c r="BY45" t="inlineStr"/>
+      <c r="BZ45" t="inlineStr"/>
+      <c r="CA45" t="inlineStr"/>
+      <c r="CB45" t="inlineStr"/>
+      <c r="CC45" t="inlineStr"/>
+      <c r="CD45" t="inlineStr"/>
+      <c r="CE45" t="inlineStr"/>
+      <c r="CF45" t="inlineStr"/>
+      <c r="CG45" t="inlineStr"/>
+      <c r="CH45" t="inlineStr"/>
+      <c r="CI45" t="inlineStr"/>
+      <c r="CJ45" t="inlineStr"/>
+      <c r="CK45" t="inlineStr"/>
+      <c r="CL45" t="inlineStr"/>
+      <c r="CM45" t="inlineStr"/>
+      <c r="CN45" t="inlineStr"/>
+      <c r="CO45" t="inlineStr"/>
+      <c r="CP45" t="inlineStr"/>
+      <c r="CQ45" t="inlineStr"/>
+      <c r="CR45" t="inlineStr"/>
+      <c r="CS45" t="inlineStr"/>
+      <c r="CT45" t="inlineStr"/>
+      <c r="CU45" t="inlineStr"/>
+      <c r="CV45" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW45" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX45" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY45" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ45" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA45" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB45" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC45" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD45" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE45" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF45" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG45" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH45" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI45" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ45" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK45" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL45" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM45" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN45" t="inlineStr"/>
+      <c r="DO45" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP45" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ45" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR45" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS45" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT45" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU45" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV45" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW45" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX45" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY45" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ45" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA45" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB45" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC45" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED45" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE45" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF45" t="inlineStr"/>
+      <c r="EG45" t="inlineStr"/>
+      <c r="EH45" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI45" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ45" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK45" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>09/06/2026, 21:54:10</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>84</v>
+      </c>
+      <c r="D46" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>408</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>408</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>1780974000</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1781052335</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>09/06/2026 21:45</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W46" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z46" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE46" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="inlineStr"/>
+      <c r="AK46" t="inlineStr"/>
+      <c r="AL46" t="inlineStr"/>
+      <c r="AM46" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ46" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS46" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT46" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU46" t="inlineStr"/>
+      <c r="AV46" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB46" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC46" t="inlineStr"/>
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="inlineStr"/>
+      <c r="BG46" t="inlineStr"/>
+      <c r="BH46" t="inlineStr"/>
+      <c r="BI46" t="inlineStr"/>
+      <c r="BJ46" t="inlineStr"/>
+      <c r="BK46" t="inlineStr"/>
+      <c r="BL46" t="inlineStr"/>
+      <c r="BM46" t="inlineStr"/>
+      <c r="BN46" t="inlineStr"/>
+      <c r="BO46" t="inlineStr"/>
+      <c r="BP46" t="inlineStr"/>
+      <c r="BQ46" t="inlineStr"/>
+      <c r="BR46" t="inlineStr"/>
+      <c r="BS46" t="inlineStr"/>
+      <c r="BT46" t="inlineStr"/>
+      <c r="BU46" t="inlineStr"/>
+      <c r="BV46" t="inlineStr"/>
+      <c r="BW46" t="inlineStr"/>
+      <c r="BX46" t="inlineStr"/>
+      <c r="BY46" t="inlineStr"/>
+      <c r="BZ46" t="inlineStr"/>
+      <c r="CA46" t="inlineStr"/>
+      <c r="CB46" t="inlineStr"/>
+      <c r="CC46" t="inlineStr"/>
+      <c r="CD46" t="inlineStr"/>
+      <c r="CE46" t="inlineStr"/>
+      <c r="CF46" t="inlineStr"/>
+      <c r="CG46" t="inlineStr"/>
+      <c r="CH46" t="inlineStr"/>
+      <c r="CI46" t="inlineStr"/>
+      <c r="CJ46" t="inlineStr"/>
+      <c r="CK46" t="inlineStr"/>
+      <c r="CL46" t="inlineStr"/>
+      <c r="CM46" t="inlineStr"/>
+      <c r="CN46" t="inlineStr"/>
+      <c r="CO46" t="inlineStr"/>
+      <c r="CP46" t="inlineStr"/>
+      <c r="CQ46" t="inlineStr"/>
+      <c r="CR46" t="inlineStr"/>
+      <c r="CS46" t="inlineStr"/>
+      <c r="CT46" t="inlineStr"/>
+      <c r="CU46" t="inlineStr"/>
+      <c r="CV46" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW46" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX46" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY46" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ46" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA46" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB46" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC46" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD46" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE46" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF46" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG46" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH46" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI46" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ46" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK46" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL46" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM46" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN46" t="inlineStr"/>
+      <c r="DO46" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP46" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ46" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR46" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS46" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT46" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU46" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV46" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW46" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX46" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY46" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ46" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA46" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB46" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC46" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED46" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE46" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF46" t="inlineStr"/>
+      <c r="EG46" t="inlineStr"/>
+      <c r="EH46" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI46" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ46" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK46" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>09/06/2026, 21:59:42</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>84</v>
+      </c>
+      <c r="D47" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>408</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>408</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>1780974000</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1781052667</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>21:51</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>09/06/2026 21:51</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W47" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z47" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE47" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="inlineStr"/>
+      <c r="AK47" t="inlineStr"/>
+      <c r="AL47" t="inlineStr"/>
+      <c r="AM47" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN47" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP47" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ47" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT47" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU47" t="inlineStr"/>
+      <c r="AV47" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB47" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC47" t="inlineStr"/>
+      <c r="BD47" t="inlineStr"/>
+      <c r="BE47" t="inlineStr"/>
+      <c r="BF47" t="inlineStr"/>
+      <c r="BG47" t="inlineStr"/>
+      <c r="BH47" t="inlineStr"/>
+      <c r="BI47" t="inlineStr"/>
+      <c r="BJ47" t="inlineStr"/>
+      <c r="BK47" t="inlineStr"/>
+      <c r="BL47" t="inlineStr"/>
+      <c r="BM47" t="inlineStr"/>
+      <c r="BN47" t="inlineStr"/>
+      <c r="BO47" t="inlineStr"/>
+      <c r="BP47" t="inlineStr"/>
+      <c r="BQ47" t="inlineStr"/>
+      <c r="BR47" t="inlineStr"/>
+      <c r="BS47" t="inlineStr"/>
+      <c r="BT47" t="inlineStr"/>
+      <c r="BU47" t="inlineStr"/>
+      <c r="BV47" t="inlineStr"/>
+      <c r="BW47" t="inlineStr"/>
+      <c r="BX47" t="inlineStr"/>
+      <c r="BY47" t="inlineStr"/>
+      <c r="BZ47" t="inlineStr"/>
+      <c r="CA47" t="inlineStr"/>
+      <c r="CB47" t="inlineStr"/>
+      <c r="CC47" t="inlineStr"/>
+      <c r="CD47" t="inlineStr"/>
+      <c r="CE47" t="inlineStr"/>
+      <c r="CF47" t="inlineStr"/>
+      <c r="CG47" t="inlineStr"/>
+      <c r="CH47" t="inlineStr"/>
+      <c r="CI47" t="inlineStr"/>
+      <c r="CJ47" t="inlineStr"/>
+      <c r="CK47" t="inlineStr"/>
+      <c r="CL47" t="inlineStr"/>
+      <c r="CM47" t="inlineStr"/>
+      <c r="CN47" t="inlineStr"/>
+      <c r="CO47" t="inlineStr"/>
+      <c r="CP47" t="inlineStr"/>
+      <c r="CQ47" t="inlineStr"/>
+      <c r="CR47" t="inlineStr"/>
+      <c r="CS47" t="inlineStr"/>
+      <c r="CT47" t="inlineStr"/>
+      <c r="CU47" t="inlineStr"/>
+      <c r="CV47" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW47" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX47" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY47" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ47" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA47" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB47" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC47" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD47" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE47" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF47" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG47" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH47" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI47" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ47" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK47" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL47" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM47" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN47" t="inlineStr"/>
+      <c r="DO47" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP47" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ47" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR47" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS47" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT47" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU47" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV47" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW47" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX47" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY47" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ47" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA47" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB47" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC47" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED47" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE47" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF47" t="inlineStr"/>
+      <c r="EG47" t="inlineStr"/>
+      <c r="EH47" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI47" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ47" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK47" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>09/06/2026, 22:01:32</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>84</v>
+      </c>
+      <c r="D48" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>408</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>408</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>1780974000</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1781052776</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>21:52</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>09/06/2026 21:52</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W48" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z48" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE48" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
+      <c r="AL48" t="inlineStr"/>
+      <c r="AM48" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP48" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ48" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT48" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU48" t="inlineStr"/>
+      <c r="AV48" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB48" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC48" t="inlineStr"/>
+      <c r="BD48" t="inlineStr"/>
+      <c r="BE48" t="inlineStr"/>
+      <c r="BF48" t="inlineStr"/>
+      <c r="BG48" t="inlineStr"/>
+      <c r="BH48" t="inlineStr"/>
+      <c r="BI48" t="inlineStr"/>
+      <c r="BJ48" t="inlineStr"/>
+      <c r="BK48" t="inlineStr"/>
+      <c r="BL48" t="inlineStr"/>
+      <c r="BM48" t="inlineStr"/>
+      <c r="BN48" t="inlineStr"/>
+      <c r="BO48" t="inlineStr"/>
+      <c r="BP48" t="inlineStr"/>
+      <c r="BQ48" t="inlineStr"/>
+      <c r="BR48" t="inlineStr"/>
+      <c r="BS48" t="inlineStr"/>
+      <c r="BT48" t="inlineStr"/>
+      <c r="BU48" t="inlineStr"/>
+      <c r="BV48" t="inlineStr"/>
+      <c r="BW48" t="inlineStr"/>
+      <c r="BX48" t="inlineStr"/>
+      <c r="BY48" t="inlineStr"/>
+      <c r="BZ48" t="inlineStr"/>
+      <c r="CA48" t="inlineStr"/>
+      <c r="CB48" t="inlineStr"/>
+      <c r="CC48" t="inlineStr"/>
+      <c r="CD48" t="inlineStr"/>
+      <c r="CE48" t="inlineStr"/>
+      <c r="CF48" t="inlineStr"/>
+      <c r="CG48" t="inlineStr"/>
+      <c r="CH48" t="inlineStr"/>
+      <c r="CI48" t="inlineStr"/>
+      <c r="CJ48" t="inlineStr"/>
+      <c r="CK48" t="inlineStr"/>
+      <c r="CL48" t="inlineStr"/>
+      <c r="CM48" t="inlineStr"/>
+      <c r="CN48" t="inlineStr"/>
+      <c r="CO48" t="inlineStr"/>
+      <c r="CP48" t="inlineStr"/>
+      <c r="CQ48" t="inlineStr"/>
+      <c r="CR48" t="inlineStr"/>
+      <c r="CS48" t="inlineStr"/>
+      <c r="CT48" t="inlineStr"/>
+      <c r="CU48" t="inlineStr"/>
+      <c r="CV48" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW48" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX48" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY48" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ48" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA48" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB48" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC48" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD48" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE48" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF48" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG48" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH48" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI48" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ48" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK48" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL48" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM48" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN48" t="inlineStr"/>
+      <c r="DO48" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP48" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ48" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR48" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS48" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT48" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU48" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV48" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW48" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX48" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY48" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ48" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA48" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB48" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC48" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED48" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE48" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF48" t="inlineStr"/>
+      <c r="EG48" t="inlineStr"/>
+      <c r="EH48" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI48" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ48" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK48" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>09/06/2026, 22:08:56</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>84</v>
+      </c>
+      <c r="D49" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>408</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>408</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>1780974000</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1781053221</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>09/06/2026 22:00</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W49" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z49" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE49" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="inlineStr"/>
+      <c r="AK49" t="inlineStr"/>
+      <c r="AL49" t="inlineStr"/>
+      <c r="AM49" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN49" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP49" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS49" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT49" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU49" t="inlineStr"/>
+      <c r="AV49" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB49" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC49" t="inlineStr"/>
+      <c r="BD49" t="inlineStr"/>
+      <c r="BE49" t="inlineStr"/>
+      <c r="BF49" t="inlineStr"/>
+      <c r="BG49" t="inlineStr"/>
+      <c r="BH49" t="inlineStr"/>
+      <c r="BI49" t="inlineStr"/>
+      <c r="BJ49" t="inlineStr"/>
+      <c r="BK49" t="inlineStr"/>
+      <c r="BL49" t="inlineStr"/>
+      <c r="BM49" t="inlineStr"/>
+      <c r="BN49" t="inlineStr"/>
+      <c r="BO49" t="inlineStr"/>
+      <c r="BP49" t="inlineStr"/>
+      <c r="BQ49" t="inlineStr"/>
+      <c r="BR49" t="inlineStr"/>
+      <c r="BS49" t="inlineStr"/>
+      <c r="BT49" t="inlineStr"/>
+      <c r="BU49" t="inlineStr"/>
+      <c r="BV49" t="inlineStr"/>
+      <c r="BW49" t="inlineStr"/>
+      <c r="BX49" t="inlineStr"/>
+      <c r="BY49" t="inlineStr"/>
+      <c r="BZ49" t="inlineStr"/>
+      <c r="CA49" t="inlineStr"/>
+      <c r="CB49" t="inlineStr"/>
+      <c r="CC49" t="inlineStr"/>
+      <c r="CD49" t="inlineStr"/>
+      <c r="CE49" t="inlineStr"/>
+      <c r="CF49" t="inlineStr"/>
+      <c r="CG49" t="inlineStr"/>
+      <c r="CH49" t="inlineStr"/>
+      <c r="CI49" t="inlineStr"/>
+      <c r="CJ49" t="inlineStr"/>
+      <c r="CK49" t="inlineStr"/>
+      <c r="CL49" t="inlineStr"/>
+      <c r="CM49" t="inlineStr"/>
+      <c r="CN49" t="inlineStr"/>
+      <c r="CO49" t="inlineStr"/>
+      <c r="CP49" t="inlineStr"/>
+      <c r="CQ49" t="inlineStr"/>
+      <c r="CR49" t="inlineStr"/>
+      <c r="CS49" t="inlineStr"/>
+      <c r="CT49" t="inlineStr"/>
+      <c r="CU49" t="inlineStr"/>
+      <c r="CV49" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW49" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX49" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY49" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ49" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA49" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB49" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC49" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD49" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE49" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF49" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG49" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH49" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI49" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ49" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK49" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL49" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM49" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN49" t="inlineStr"/>
+      <c r="DO49" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP49" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ49" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR49" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS49" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT49" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU49" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV49" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW49" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX49" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY49" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ49" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA49" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB49" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC49" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED49" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE49" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF49" t="inlineStr"/>
+      <c r="EG49" t="inlineStr"/>
+      <c r="EH49" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI49" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ49" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK49" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>09/06/2026, 22:09:41</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>84</v>
+      </c>
+      <c r="D50" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>408</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>408</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>1780974000</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1781053266</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>09/06/2026 22:01</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W50" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z50" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE50" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
+      <c r="AL50" t="inlineStr"/>
+      <c r="AM50" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ50" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT50" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU50" t="inlineStr"/>
+      <c r="AV50" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB50" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC50" t="inlineStr"/>
+      <c r="BD50" t="inlineStr"/>
+      <c r="BE50" t="inlineStr"/>
+      <c r="BF50" t="inlineStr"/>
+      <c r="BG50" t="inlineStr"/>
+      <c r="BH50" t="inlineStr"/>
+      <c r="BI50" t="inlineStr"/>
+      <c r="BJ50" t="inlineStr"/>
+      <c r="BK50" t="inlineStr"/>
+      <c r="BL50" t="inlineStr"/>
+      <c r="BM50" t="inlineStr"/>
+      <c r="BN50" t="inlineStr"/>
+      <c r="BO50" t="inlineStr"/>
+      <c r="BP50" t="inlineStr"/>
+      <c r="BQ50" t="inlineStr"/>
+      <c r="BR50" t="inlineStr"/>
+      <c r="BS50" t="inlineStr"/>
+      <c r="BT50" t="inlineStr"/>
+      <c r="BU50" t="inlineStr"/>
+      <c r="BV50" t="inlineStr"/>
+      <c r="BW50" t="inlineStr"/>
+      <c r="BX50" t="inlineStr"/>
+      <c r="BY50" t="inlineStr"/>
+      <c r="BZ50" t="inlineStr"/>
+      <c r="CA50" t="inlineStr"/>
+      <c r="CB50" t="inlineStr"/>
+      <c r="CC50" t="inlineStr"/>
+      <c r="CD50" t="inlineStr"/>
+      <c r="CE50" t="inlineStr"/>
+      <c r="CF50" t="inlineStr"/>
+      <c r="CG50" t="inlineStr"/>
+      <c r="CH50" t="inlineStr"/>
+      <c r="CI50" t="inlineStr"/>
+      <c r="CJ50" t="inlineStr"/>
+      <c r="CK50" t="inlineStr"/>
+      <c r="CL50" t="inlineStr"/>
+      <c r="CM50" t="inlineStr"/>
+      <c r="CN50" t="inlineStr"/>
+      <c r="CO50" t="inlineStr"/>
+      <c r="CP50" t="inlineStr"/>
+      <c r="CQ50" t="inlineStr"/>
+      <c r="CR50" t="inlineStr"/>
+      <c r="CS50" t="inlineStr"/>
+      <c r="CT50" t="inlineStr"/>
+      <c r="CU50" t="inlineStr"/>
+      <c r="CV50" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW50" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX50" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY50" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ50" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA50" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB50" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC50" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD50" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE50" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF50" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG50" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH50" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI50" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ50" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK50" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL50" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM50" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN50" t="inlineStr"/>
+      <c r="DO50" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP50" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ50" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR50" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS50" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT50" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU50" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV50" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW50" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX50" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY50" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ50" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA50" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB50" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC50" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED50" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE50" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF50" t="inlineStr"/>
+      <c r="EG50" t="inlineStr"/>
+      <c r="EH50" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI50" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ50" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK50" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>09/06/2026, 22:16:42</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0121000</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>01210000010</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1780974000</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1781053687</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>09/06/2026 22:08</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="inlineStr"/>
+      <c r="AK51" t="inlineStr"/>
+      <c r="AL51" t="inlineStr"/>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr">
+        <is>
+          <t>3500.00</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr"/>
+      <c r="AV51" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr"/>
+      <c r="BD51" t="inlineStr"/>
+      <c r="BE51" t="inlineStr"/>
+      <c r="BF51" t="inlineStr"/>
+      <c r="BG51" t="inlineStr"/>
+      <c r="BH51" t="inlineStr"/>
+      <c r="BI51" t="inlineStr"/>
+      <c r="BJ51" t="inlineStr"/>
+      <c r="BK51" t="inlineStr"/>
+      <c r="BL51" t="inlineStr"/>
+      <c r="BM51" t="inlineStr"/>
+      <c r="BN51" t="inlineStr"/>
+      <c r="BO51" t="inlineStr"/>
+      <c r="BP51" t="inlineStr"/>
+      <c r="BQ51" t="inlineStr"/>
+      <c r="BR51" t="inlineStr"/>
+      <c r="BS51" t="inlineStr"/>
+      <c r="BT51" t="inlineStr"/>
+      <c r="BU51" t="inlineStr"/>
+      <c r="BV51" t="inlineStr"/>
+      <c r="BW51" t="inlineStr"/>
+      <c r="BX51" t="inlineStr"/>
+      <c r="BY51" t="inlineStr"/>
+      <c r="BZ51" t="inlineStr"/>
+      <c r="CA51" t="inlineStr"/>
+      <c r="CB51" t="inlineStr"/>
+      <c r="CC51" t="inlineStr"/>
+      <c r="CD51" t="inlineStr"/>
+      <c r="CE51" t="inlineStr"/>
+      <c r="CF51" t="inlineStr"/>
+      <c r="CG51" t="inlineStr"/>
+      <c r="CH51" t="inlineStr"/>
+      <c r="CI51" t="inlineStr"/>
+      <c r="CJ51" t="inlineStr"/>
+      <c r="CK51" t="inlineStr"/>
+      <c r="CL51" t="inlineStr"/>
+      <c r="CM51" t="inlineStr"/>
+      <c r="CN51" t="inlineStr"/>
+      <c r="CO51" t="inlineStr"/>
+      <c r="CP51" t="inlineStr"/>
+      <c r="CQ51" t="inlineStr"/>
+      <c r="CR51" t="inlineStr"/>
+      <c r="CS51" t="inlineStr"/>
+      <c r="CT51" t="inlineStr"/>
+      <c r="CU51" t="inlineStr"/>
+      <c r="CV51" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW51" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX51" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY51" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ51" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA51" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB51" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC51" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD51" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE51" t="inlineStr">
+        <is>
+          <t>1121029128</t>
+        </is>
+      </c>
+      <c r="DF51" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG51" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH51" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI51" t="inlineStr">
+        <is>
+          <t>212122</t>
+        </is>
+      </c>
+      <c r="DJ51" t="inlineStr">
+        <is>
+          <t>12344</t>
+        </is>
+      </c>
+      <c r="DK51" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL51" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM51" t="inlineStr">
+        <is>
+          <t>121212212112</t>
+        </is>
+      </c>
+      <c r="DN51" t="inlineStr"/>
+      <c r="DO51" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP51" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ51" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR51" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+      <c r="DS51" t="inlineStr">
+        <is>
+          <t>3144</t>
+        </is>
+      </c>
+      <c r="DT51" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU51" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV51" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW51" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="DX51" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY51" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ51" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA51" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB51" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC51" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED51" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE51" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF51" t="inlineStr"/>
+      <c r="EG51" t="inlineStr"/>
+      <c r="EH51" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI51" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ51" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK51" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17725,13 +23393,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9162617-93AF-40BB-9DCB-EBC8E391BA75}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0AD173E-02E4-44B4-B9A9-35A413A9532A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78CF7E72-26DD-410D-9C19-B1F12050467C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09A9F1D5-FB0F-446E-A87A-7CDF91E228EB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BED12907-72DE-4F09-AD72-39393081ED76}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0336733E-B746-4DDA-B755-3AF2BC5749A3}"/>
 </file>
--- a/dados_formularios.xlsx
+++ b/dados_formularios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL51"/>
+  <dimension ref="A1:EL59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22687,47 +22687,33 @@
           <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>0121000</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>01210000010</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C51" t="n">
+        <v>84</v>
+      </c>
+      <c r="D51" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>22133</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="L51" t="n">
+        <v>408</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -22739,25 +22725,19 @@
           <t>robo.relatorio@folhatech.com.br</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="O51" t="n">
+        <v>408</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Robo Cadastro Cliente</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>1780974000</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>1781053687</t>
-        </is>
+      <c r="Q51" t="n">
+        <v>1780974000</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1781053687</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -22779,10 +22759,8 @@
           <t>03/06/2026 17:13</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="W51" t="n">
+        <v>22133</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -22794,35 +22772,27 @@
           <t>04/06/2026 17:25</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="Z51" t="n">
+        <v>127857</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>08 - Confecção e assinatura (Contrato)</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
+      <c r="AB51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>487</v>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
           <t>Pedro Santana</t>
         </is>
       </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>0121</t>
-        </is>
+      <c r="AE51" t="n">
+        <v>121</v>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
@@ -22839,10 +22809,8 @@
       <c r="AJ51" t="inlineStr"/>
       <c r="AK51" t="inlineStr"/>
       <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>127857</v>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
@@ -22874,10 +22842,8 @@
           <t>Aumento de quadro</t>
         </is>
       </c>
-      <c r="AT51" t="inlineStr">
-        <is>
-          <t>3500.00</t>
-        </is>
+      <c r="AT51" t="n">
+        <v>3500</v>
       </c>
       <c r="AU51" t="inlineStr"/>
       <c r="AV51" t="inlineStr">
@@ -23005,10 +22971,8 @@
           <t>Pai</t>
         </is>
       </c>
-      <c r="DE51" t="inlineStr">
-        <is>
-          <t>1121029128</t>
-        </is>
+      <c r="DE51" t="n">
+        <v>1121029128</v>
       </c>
       <c r="DF51" t="inlineStr">
         <is>
@@ -23025,15 +22989,11 @@
           <t>Namorado(a)</t>
         </is>
       </c>
-      <c r="DI51" t="inlineStr">
-        <is>
-          <t>212122</t>
-        </is>
-      </c>
-      <c r="DJ51" t="inlineStr">
-        <is>
-          <t>12344</t>
-        </is>
+      <c r="DI51" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ51" t="n">
+        <v>12344</v>
       </c>
       <c r="DK51" t="inlineStr">
         <is>
@@ -23045,10 +23005,8 @@
           <t>pedro.santana@folhatech.com.br</t>
         </is>
       </c>
-      <c r="DM51" t="inlineStr">
-        <is>
-          <t>121212212112</t>
-        </is>
+      <c r="DM51" t="n">
+        <v>121212212112</v>
       </c>
       <c r="DN51" t="inlineStr"/>
       <c r="DO51" t="inlineStr">
@@ -23066,15 +23024,11 @@
           <t>Conta Corrente</t>
         </is>
       </c>
-      <c r="DR51" t="inlineStr">
-        <is>
-          <t>12121</t>
-        </is>
-      </c>
-      <c r="DS51" t="inlineStr">
-        <is>
-          <t>3144</t>
-        </is>
+      <c r="DR51" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS51" t="n">
+        <v>3144</v>
       </c>
       <c r="DT51" t="inlineStr">
         <is>
@@ -23091,10 +23045,8 @@
           <t>etetetet</t>
         </is>
       </c>
-      <c r="DW51" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="DW51" t="n">
+        <v>124</v>
       </c>
       <c r="DX51" t="inlineStr">
         <is>
@@ -23159,6 +23111,3542 @@
         </is>
       </c>
       <c r="EL51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>10/06/2026, 08:48:09</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>84</v>
+      </c>
+      <c r="D52" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>408</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>408</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>1781060400</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1781091571</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>10/06/2026 08:39</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W52" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z52" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE52" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN52" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT52" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU52" t="inlineStr"/>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr"/>
+      <c r="BD52" t="inlineStr"/>
+      <c r="BE52" t="inlineStr"/>
+      <c r="BF52" t="inlineStr"/>
+      <c r="BG52" t="inlineStr"/>
+      <c r="BH52" t="inlineStr"/>
+      <c r="BI52" t="inlineStr"/>
+      <c r="BJ52" t="inlineStr"/>
+      <c r="BK52" t="inlineStr"/>
+      <c r="BL52" t="inlineStr"/>
+      <c r="BM52" t="inlineStr"/>
+      <c r="BN52" t="inlineStr"/>
+      <c r="BO52" t="inlineStr"/>
+      <c r="BP52" t="inlineStr"/>
+      <c r="BQ52" t="inlineStr"/>
+      <c r="BR52" t="inlineStr"/>
+      <c r="BS52" t="inlineStr"/>
+      <c r="BT52" t="inlineStr"/>
+      <c r="BU52" t="inlineStr"/>
+      <c r="BV52" t="inlineStr"/>
+      <c r="BW52" t="inlineStr"/>
+      <c r="BX52" t="inlineStr"/>
+      <c r="BY52" t="inlineStr"/>
+      <c r="BZ52" t="inlineStr"/>
+      <c r="CA52" t="inlineStr"/>
+      <c r="CB52" t="inlineStr"/>
+      <c r="CC52" t="inlineStr"/>
+      <c r="CD52" t="inlineStr"/>
+      <c r="CE52" t="inlineStr"/>
+      <c r="CF52" t="inlineStr"/>
+      <c r="CG52" t="inlineStr"/>
+      <c r="CH52" t="inlineStr"/>
+      <c r="CI52" t="inlineStr"/>
+      <c r="CJ52" t="inlineStr"/>
+      <c r="CK52" t="inlineStr"/>
+      <c r="CL52" t="inlineStr"/>
+      <c r="CM52" t="inlineStr"/>
+      <c r="CN52" t="inlineStr"/>
+      <c r="CO52" t="inlineStr"/>
+      <c r="CP52" t="inlineStr"/>
+      <c r="CQ52" t="inlineStr"/>
+      <c r="CR52" t="inlineStr"/>
+      <c r="CS52" t="inlineStr"/>
+      <c r="CT52" t="inlineStr"/>
+      <c r="CU52" t="inlineStr"/>
+      <c r="CV52" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW52" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX52" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY52" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ52" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA52" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB52" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC52" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD52" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE52" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF52" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG52" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH52" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI52" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ52" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK52" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL52" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM52" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN52" t="inlineStr"/>
+      <c r="DO52" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP52" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ52" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR52" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS52" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT52" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU52" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV52" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW52" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX52" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY52" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ52" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA52" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB52" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC52" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED52" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE52" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF52" t="inlineStr"/>
+      <c r="EG52" t="inlineStr"/>
+      <c r="EH52" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI52" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ52" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK52" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>10/06/2026, 08:52:40</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>84</v>
+      </c>
+      <c r="D53" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>408</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>408</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>1781060400</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1781091842</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>10/06/2026 08:44</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W53" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z53" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE53" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="inlineStr"/>
+      <c r="AK53" t="inlineStr"/>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN53" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT53" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU53" t="inlineStr"/>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB53" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC53" t="inlineStr"/>
+      <c r="BD53" t="inlineStr"/>
+      <c r="BE53" t="inlineStr"/>
+      <c r="BF53" t="inlineStr"/>
+      <c r="BG53" t="inlineStr"/>
+      <c r="BH53" t="inlineStr"/>
+      <c r="BI53" t="inlineStr"/>
+      <c r="BJ53" t="inlineStr"/>
+      <c r="BK53" t="inlineStr"/>
+      <c r="BL53" t="inlineStr"/>
+      <c r="BM53" t="inlineStr"/>
+      <c r="BN53" t="inlineStr"/>
+      <c r="BO53" t="inlineStr"/>
+      <c r="BP53" t="inlineStr"/>
+      <c r="BQ53" t="inlineStr"/>
+      <c r="BR53" t="inlineStr"/>
+      <c r="BS53" t="inlineStr"/>
+      <c r="BT53" t="inlineStr"/>
+      <c r="BU53" t="inlineStr"/>
+      <c r="BV53" t="inlineStr"/>
+      <c r="BW53" t="inlineStr"/>
+      <c r="BX53" t="inlineStr"/>
+      <c r="BY53" t="inlineStr"/>
+      <c r="BZ53" t="inlineStr"/>
+      <c r="CA53" t="inlineStr"/>
+      <c r="CB53" t="inlineStr"/>
+      <c r="CC53" t="inlineStr"/>
+      <c r="CD53" t="inlineStr"/>
+      <c r="CE53" t="inlineStr"/>
+      <c r="CF53" t="inlineStr"/>
+      <c r="CG53" t="inlineStr"/>
+      <c r="CH53" t="inlineStr"/>
+      <c r="CI53" t="inlineStr"/>
+      <c r="CJ53" t="inlineStr"/>
+      <c r="CK53" t="inlineStr"/>
+      <c r="CL53" t="inlineStr"/>
+      <c r="CM53" t="inlineStr"/>
+      <c r="CN53" t="inlineStr"/>
+      <c r="CO53" t="inlineStr"/>
+      <c r="CP53" t="inlineStr"/>
+      <c r="CQ53" t="inlineStr"/>
+      <c r="CR53" t="inlineStr"/>
+      <c r="CS53" t="inlineStr"/>
+      <c r="CT53" t="inlineStr"/>
+      <c r="CU53" t="inlineStr"/>
+      <c r="CV53" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW53" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX53" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY53" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ53" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA53" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB53" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC53" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD53" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE53" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF53" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG53" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH53" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI53" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ53" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK53" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL53" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM53" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN53" t="inlineStr"/>
+      <c r="DO53" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP53" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ53" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR53" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS53" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT53" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU53" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV53" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW53" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX53" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY53" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ53" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA53" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB53" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC53" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED53" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE53" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF53" t="inlineStr"/>
+      <c r="EG53" t="inlineStr"/>
+      <c r="EH53" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI53" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ53" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK53" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>10/06/2026, 09:08:41</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>84</v>
+      </c>
+      <c r="D54" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>408</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>408</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>1781060400</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1781092803</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>10/06/2026 09:00</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W54" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z54" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE54" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="inlineStr"/>
+      <c r="AK54" t="inlineStr"/>
+      <c r="AL54" t="inlineStr"/>
+      <c r="AM54" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN54" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT54" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU54" t="inlineStr"/>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr"/>
+      <c r="BD54" t="inlineStr"/>
+      <c r="BE54" t="inlineStr"/>
+      <c r="BF54" t="inlineStr"/>
+      <c r="BG54" t="inlineStr"/>
+      <c r="BH54" t="inlineStr"/>
+      <c r="BI54" t="inlineStr"/>
+      <c r="BJ54" t="inlineStr"/>
+      <c r="BK54" t="inlineStr"/>
+      <c r="BL54" t="inlineStr"/>
+      <c r="BM54" t="inlineStr"/>
+      <c r="BN54" t="inlineStr"/>
+      <c r="BO54" t="inlineStr"/>
+      <c r="BP54" t="inlineStr"/>
+      <c r="BQ54" t="inlineStr"/>
+      <c r="BR54" t="inlineStr"/>
+      <c r="BS54" t="inlineStr"/>
+      <c r="BT54" t="inlineStr"/>
+      <c r="BU54" t="inlineStr"/>
+      <c r="BV54" t="inlineStr"/>
+      <c r="BW54" t="inlineStr"/>
+      <c r="BX54" t="inlineStr"/>
+      <c r="BY54" t="inlineStr"/>
+      <c r="BZ54" t="inlineStr"/>
+      <c r="CA54" t="inlineStr"/>
+      <c r="CB54" t="inlineStr"/>
+      <c r="CC54" t="inlineStr"/>
+      <c r="CD54" t="inlineStr"/>
+      <c r="CE54" t="inlineStr"/>
+      <c r="CF54" t="inlineStr"/>
+      <c r="CG54" t="inlineStr"/>
+      <c r="CH54" t="inlineStr"/>
+      <c r="CI54" t="inlineStr"/>
+      <c r="CJ54" t="inlineStr"/>
+      <c r="CK54" t="inlineStr"/>
+      <c r="CL54" t="inlineStr"/>
+      <c r="CM54" t="inlineStr"/>
+      <c r="CN54" t="inlineStr"/>
+      <c r="CO54" t="inlineStr"/>
+      <c r="CP54" t="inlineStr"/>
+      <c r="CQ54" t="inlineStr"/>
+      <c r="CR54" t="inlineStr"/>
+      <c r="CS54" t="inlineStr"/>
+      <c r="CT54" t="inlineStr"/>
+      <c r="CU54" t="inlineStr"/>
+      <c r="CV54" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW54" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX54" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY54" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ54" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA54" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB54" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC54" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD54" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE54" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF54" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG54" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH54" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI54" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ54" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK54" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL54" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM54" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN54" t="inlineStr"/>
+      <c r="DO54" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP54" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ54" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR54" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS54" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT54" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU54" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV54" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW54" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX54" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY54" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ54" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA54" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB54" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC54" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED54" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE54" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF54" t="inlineStr"/>
+      <c r="EG54" t="inlineStr"/>
+      <c r="EH54" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI54" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ54" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK54" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>10/06/2026, 09:10:49</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>84</v>
+      </c>
+      <c r="D55" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>408</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>408</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>1781060400</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1781092931</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>10/06/2026 09:02</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W55" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z55" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE55" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="inlineStr"/>
+      <c r="AK55" t="inlineStr"/>
+      <c r="AL55" t="inlineStr"/>
+      <c r="AM55" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN55" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT55" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU55" t="inlineStr"/>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr"/>
+      <c r="BD55" t="inlineStr"/>
+      <c r="BE55" t="inlineStr"/>
+      <c r="BF55" t="inlineStr"/>
+      <c r="BG55" t="inlineStr"/>
+      <c r="BH55" t="inlineStr"/>
+      <c r="BI55" t="inlineStr"/>
+      <c r="BJ55" t="inlineStr"/>
+      <c r="BK55" t="inlineStr"/>
+      <c r="BL55" t="inlineStr"/>
+      <c r="BM55" t="inlineStr"/>
+      <c r="BN55" t="inlineStr"/>
+      <c r="BO55" t="inlineStr"/>
+      <c r="BP55" t="inlineStr"/>
+      <c r="BQ55" t="inlineStr"/>
+      <c r="BR55" t="inlineStr"/>
+      <c r="BS55" t="inlineStr"/>
+      <c r="BT55" t="inlineStr"/>
+      <c r="BU55" t="inlineStr"/>
+      <c r="BV55" t="inlineStr"/>
+      <c r="BW55" t="inlineStr"/>
+      <c r="BX55" t="inlineStr"/>
+      <c r="BY55" t="inlineStr"/>
+      <c r="BZ55" t="inlineStr"/>
+      <c r="CA55" t="inlineStr"/>
+      <c r="CB55" t="inlineStr"/>
+      <c r="CC55" t="inlineStr"/>
+      <c r="CD55" t="inlineStr"/>
+      <c r="CE55" t="inlineStr"/>
+      <c r="CF55" t="inlineStr"/>
+      <c r="CG55" t="inlineStr"/>
+      <c r="CH55" t="inlineStr"/>
+      <c r="CI55" t="inlineStr"/>
+      <c r="CJ55" t="inlineStr"/>
+      <c r="CK55" t="inlineStr"/>
+      <c r="CL55" t="inlineStr"/>
+      <c r="CM55" t="inlineStr"/>
+      <c r="CN55" t="inlineStr"/>
+      <c r="CO55" t="inlineStr"/>
+      <c r="CP55" t="inlineStr"/>
+      <c r="CQ55" t="inlineStr"/>
+      <c r="CR55" t="inlineStr"/>
+      <c r="CS55" t="inlineStr"/>
+      <c r="CT55" t="inlineStr"/>
+      <c r="CU55" t="inlineStr"/>
+      <c r="CV55" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW55" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX55" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY55" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ55" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA55" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB55" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC55" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD55" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE55" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF55" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG55" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH55" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI55" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ55" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK55" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL55" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM55" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN55" t="inlineStr"/>
+      <c r="DO55" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP55" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ55" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR55" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS55" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT55" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU55" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV55" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW55" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX55" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY55" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ55" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA55" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB55" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC55" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED55" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE55" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF55" t="inlineStr"/>
+      <c r="EG55" t="inlineStr"/>
+      <c r="EH55" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI55" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ55" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK55" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>10/06/2026, 09:19:19</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>84</v>
+      </c>
+      <c r="D56" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>408</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>408</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>1781060400</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1781093441</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>10/06/2026 09:10</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W56" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z56" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE56" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="inlineStr"/>
+      <c r="AK56" t="inlineStr"/>
+      <c r="AL56" t="inlineStr"/>
+      <c r="AM56" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN56" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT56" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU56" t="inlineStr"/>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr"/>
+      <c r="BD56" t="inlineStr"/>
+      <c r="BE56" t="inlineStr"/>
+      <c r="BF56" t="inlineStr"/>
+      <c r="BG56" t="inlineStr"/>
+      <c r="BH56" t="inlineStr"/>
+      <c r="BI56" t="inlineStr"/>
+      <c r="BJ56" t="inlineStr"/>
+      <c r="BK56" t="inlineStr"/>
+      <c r="BL56" t="inlineStr"/>
+      <c r="BM56" t="inlineStr"/>
+      <c r="BN56" t="inlineStr"/>
+      <c r="BO56" t="inlineStr"/>
+      <c r="BP56" t="inlineStr"/>
+      <c r="BQ56" t="inlineStr"/>
+      <c r="BR56" t="inlineStr"/>
+      <c r="BS56" t="inlineStr"/>
+      <c r="BT56" t="inlineStr"/>
+      <c r="BU56" t="inlineStr"/>
+      <c r="BV56" t="inlineStr"/>
+      <c r="BW56" t="inlineStr"/>
+      <c r="BX56" t="inlineStr"/>
+      <c r="BY56" t="inlineStr"/>
+      <c r="BZ56" t="inlineStr"/>
+      <c r="CA56" t="inlineStr"/>
+      <c r="CB56" t="inlineStr"/>
+      <c r="CC56" t="inlineStr"/>
+      <c r="CD56" t="inlineStr"/>
+      <c r="CE56" t="inlineStr"/>
+      <c r="CF56" t="inlineStr"/>
+      <c r="CG56" t="inlineStr"/>
+      <c r="CH56" t="inlineStr"/>
+      <c r="CI56" t="inlineStr"/>
+      <c r="CJ56" t="inlineStr"/>
+      <c r="CK56" t="inlineStr"/>
+      <c r="CL56" t="inlineStr"/>
+      <c r="CM56" t="inlineStr"/>
+      <c r="CN56" t="inlineStr"/>
+      <c r="CO56" t="inlineStr"/>
+      <c r="CP56" t="inlineStr"/>
+      <c r="CQ56" t="inlineStr"/>
+      <c r="CR56" t="inlineStr"/>
+      <c r="CS56" t="inlineStr"/>
+      <c r="CT56" t="inlineStr"/>
+      <c r="CU56" t="inlineStr"/>
+      <c r="CV56" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW56" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX56" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY56" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ56" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA56" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB56" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC56" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD56" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE56" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF56" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG56" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH56" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI56" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ56" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK56" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL56" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM56" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN56" t="inlineStr"/>
+      <c r="DO56" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP56" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ56" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR56" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS56" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT56" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU56" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV56" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW56" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX56" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY56" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ56" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA56" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB56" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC56" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED56" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE56" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF56" t="inlineStr"/>
+      <c r="EG56" t="inlineStr"/>
+      <c r="EH56" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI56" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ56" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK56" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>10/06/2026, 09:22:37</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>84</v>
+      </c>
+      <c r="D57" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>408</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>408</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>1781060400</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1781093639</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>10/06/2026 09:13</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W57" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z57" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE57" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
+      <c r="AL57" t="inlineStr"/>
+      <c r="AM57" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN57" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT57" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU57" t="inlineStr"/>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr"/>
+      <c r="BD57" t="inlineStr"/>
+      <c r="BE57" t="inlineStr"/>
+      <c r="BF57" t="inlineStr"/>
+      <c r="BG57" t="inlineStr"/>
+      <c r="BH57" t="inlineStr"/>
+      <c r="BI57" t="inlineStr"/>
+      <c r="BJ57" t="inlineStr"/>
+      <c r="BK57" t="inlineStr"/>
+      <c r="BL57" t="inlineStr"/>
+      <c r="BM57" t="inlineStr"/>
+      <c r="BN57" t="inlineStr"/>
+      <c r="BO57" t="inlineStr"/>
+      <c r="BP57" t="inlineStr"/>
+      <c r="BQ57" t="inlineStr"/>
+      <c r="BR57" t="inlineStr"/>
+      <c r="BS57" t="inlineStr"/>
+      <c r="BT57" t="inlineStr"/>
+      <c r="BU57" t="inlineStr"/>
+      <c r="BV57" t="inlineStr"/>
+      <c r="BW57" t="inlineStr"/>
+      <c r="BX57" t="inlineStr"/>
+      <c r="BY57" t="inlineStr"/>
+      <c r="BZ57" t="inlineStr"/>
+      <c r="CA57" t="inlineStr"/>
+      <c r="CB57" t="inlineStr"/>
+      <c r="CC57" t="inlineStr"/>
+      <c r="CD57" t="inlineStr"/>
+      <c r="CE57" t="inlineStr"/>
+      <c r="CF57" t="inlineStr"/>
+      <c r="CG57" t="inlineStr"/>
+      <c r="CH57" t="inlineStr"/>
+      <c r="CI57" t="inlineStr"/>
+      <c r="CJ57" t="inlineStr"/>
+      <c r="CK57" t="inlineStr"/>
+      <c r="CL57" t="inlineStr"/>
+      <c r="CM57" t="inlineStr"/>
+      <c r="CN57" t="inlineStr"/>
+      <c r="CO57" t="inlineStr"/>
+      <c r="CP57" t="inlineStr"/>
+      <c r="CQ57" t="inlineStr"/>
+      <c r="CR57" t="inlineStr"/>
+      <c r="CS57" t="inlineStr"/>
+      <c r="CT57" t="inlineStr"/>
+      <c r="CU57" t="inlineStr"/>
+      <c r="CV57" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW57" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX57" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY57" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ57" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA57" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB57" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC57" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD57" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE57" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF57" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG57" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH57" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI57" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ57" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK57" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL57" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM57" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN57" t="inlineStr"/>
+      <c r="DO57" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP57" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ57" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR57" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS57" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT57" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU57" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV57" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW57" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX57" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY57" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ57" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA57" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB57" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC57" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED57" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE57" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF57" t="inlineStr"/>
+      <c r="EG57" t="inlineStr"/>
+      <c r="EH57" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI57" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ57" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK57" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>10/06/2026, 09:24:19</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>84</v>
+      </c>
+      <c r="D58" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>22133</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>408</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>408</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>1781060400</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1781093741</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>10/06/2026 09:15</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W58" t="n">
+        <v>22133</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z58" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>487</v>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE58" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="inlineStr"/>
+      <c r="AK58" t="inlineStr"/>
+      <c r="AL58" t="inlineStr"/>
+      <c r="AM58" t="n">
+        <v>127857</v>
+      </c>
+      <c r="AN58" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT58" t="n">
+        <v>3500</v>
+      </c>
+      <c r="AU58" t="inlineStr"/>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB58" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC58" t="inlineStr"/>
+      <c r="BD58" t="inlineStr"/>
+      <c r="BE58" t="inlineStr"/>
+      <c r="BF58" t="inlineStr"/>
+      <c r="BG58" t="inlineStr"/>
+      <c r="BH58" t="inlineStr"/>
+      <c r="BI58" t="inlineStr"/>
+      <c r="BJ58" t="inlineStr"/>
+      <c r="BK58" t="inlineStr"/>
+      <c r="BL58" t="inlineStr"/>
+      <c r="BM58" t="inlineStr"/>
+      <c r="BN58" t="inlineStr"/>
+      <c r="BO58" t="inlineStr"/>
+      <c r="BP58" t="inlineStr"/>
+      <c r="BQ58" t="inlineStr"/>
+      <c r="BR58" t="inlineStr"/>
+      <c r="BS58" t="inlineStr"/>
+      <c r="BT58" t="inlineStr"/>
+      <c r="BU58" t="inlineStr"/>
+      <c r="BV58" t="inlineStr"/>
+      <c r="BW58" t="inlineStr"/>
+      <c r="BX58" t="inlineStr"/>
+      <c r="BY58" t="inlineStr"/>
+      <c r="BZ58" t="inlineStr"/>
+      <c r="CA58" t="inlineStr"/>
+      <c r="CB58" t="inlineStr"/>
+      <c r="CC58" t="inlineStr"/>
+      <c r="CD58" t="inlineStr"/>
+      <c r="CE58" t="inlineStr"/>
+      <c r="CF58" t="inlineStr"/>
+      <c r="CG58" t="inlineStr"/>
+      <c r="CH58" t="inlineStr"/>
+      <c r="CI58" t="inlineStr"/>
+      <c r="CJ58" t="inlineStr"/>
+      <c r="CK58" t="inlineStr"/>
+      <c r="CL58" t="inlineStr"/>
+      <c r="CM58" t="inlineStr"/>
+      <c r="CN58" t="inlineStr"/>
+      <c r="CO58" t="inlineStr"/>
+      <c r="CP58" t="inlineStr"/>
+      <c r="CQ58" t="inlineStr"/>
+      <c r="CR58" t="inlineStr"/>
+      <c r="CS58" t="inlineStr"/>
+      <c r="CT58" t="inlineStr"/>
+      <c r="CU58" t="inlineStr"/>
+      <c r="CV58" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW58" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX58" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY58" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ58" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA58" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB58" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC58" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD58" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE58" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF58" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG58" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH58" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI58" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ58" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK58" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL58" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM58" t="n">
+        <v>121212212112</v>
+      </c>
+      <c r="DN58" t="inlineStr"/>
+      <c r="DO58" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP58" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ58" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR58" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS58" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT58" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU58" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV58" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW58" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX58" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY58" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ58" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA58" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB58" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC58" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED58" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE58" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF58" t="inlineStr"/>
+      <c r="EG58" t="inlineStr"/>
+      <c r="EH58" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI58" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ58" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK58" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>10/06/2026, 09:25:20</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>0121000</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>01210000010</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1781060400</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1781093802</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>10/06/2026 09:16</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
+      <c r="AL59" t="inlineStr"/>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AN59" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ59" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr">
+        <is>
+          <t>3500.00</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr"/>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr"/>
+      <c r="BD59" t="inlineStr"/>
+      <c r="BE59" t="inlineStr"/>
+      <c r="BF59" t="inlineStr"/>
+      <c r="BG59" t="inlineStr"/>
+      <c r="BH59" t="inlineStr"/>
+      <c r="BI59" t="inlineStr"/>
+      <c r="BJ59" t="inlineStr"/>
+      <c r="BK59" t="inlineStr"/>
+      <c r="BL59" t="inlineStr"/>
+      <c r="BM59" t="inlineStr"/>
+      <c r="BN59" t="inlineStr"/>
+      <c r="BO59" t="inlineStr"/>
+      <c r="BP59" t="inlineStr"/>
+      <c r="BQ59" t="inlineStr"/>
+      <c r="BR59" t="inlineStr"/>
+      <c r="BS59" t="inlineStr"/>
+      <c r="BT59" t="inlineStr"/>
+      <c r="BU59" t="inlineStr"/>
+      <c r="BV59" t="inlineStr"/>
+      <c r="BW59" t="inlineStr"/>
+      <c r="BX59" t="inlineStr"/>
+      <c r="BY59" t="inlineStr"/>
+      <c r="BZ59" t="inlineStr"/>
+      <c r="CA59" t="inlineStr"/>
+      <c r="CB59" t="inlineStr"/>
+      <c r="CC59" t="inlineStr"/>
+      <c r="CD59" t="inlineStr"/>
+      <c r="CE59" t="inlineStr"/>
+      <c r="CF59" t="inlineStr"/>
+      <c r="CG59" t="inlineStr"/>
+      <c r="CH59" t="inlineStr"/>
+      <c r="CI59" t="inlineStr"/>
+      <c r="CJ59" t="inlineStr"/>
+      <c r="CK59" t="inlineStr"/>
+      <c r="CL59" t="inlineStr"/>
+      <c r="CM59" t="inlineStr"/>
+      <c r="CN59" t="inlineStr"/>
+      <c r="CO59" t="inlineStr"/>
+      <c r="CP59" t="inlineStr"/>
+      <c r="CQ59" t="inlineStr"/>
+      <c r="CR59" t="inlineStr"/>
+      <c r="CS59" t="inlineStr"/>
+      <c r="CT59" t="inlineStr"/>
+      <c r="CU59" t="inlineStr"/>
+      <c r="CV59" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW59" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX59" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY59" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ59" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA59" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB59" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC59" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD59" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE59" t="inlineStr">
+        <is>
+          <t>1121029128</t>
+        </is>
+      </c>
+      <c r="DF59" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG59" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH59" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI59" t="inlineStr">
+        <is>
+          <t>212122</t>
+        </is>
+      </c>
+      <c r="DJ59" t="inlineStr">
+        <is>
+          <t>12344</t>
+        </is>
+      </c>
+      <c r="DK59" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL59" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM59" t="inlineStr">
+        <is>
+          <t>121212212112</t>
+        </is>
+      </c>
+      <c r="DN59" t="inlineStr"/>
+      <c r="DO59" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP59" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ59" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR59" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+      <c r="DS59" t="inlineStr">
+        <is>
+          <t>3144</t>
+        </is>
+      </c>
+      <c r="DT59" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU59" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV59" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW59" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="DX59" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY59" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ59" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA59" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB59" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC59" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED59" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE59" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF59" t="inlineStr"/>
+      <c r="EG59" t="inlineStr"/>
+      <c r="EH59" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI59" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ59" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK59" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23393,13 +26881,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0AD173E-02E4-44B4-B9A9-35A413A9532A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C2A788E-BB37-4653-AD65-3C999FF24002}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09A9F1D5-FB0F-446E-A87A-7CDF91E228EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AA4E6DB-2AC6-4FB4-A24F-B38DFC99D9AB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0336733E-B746-4DDA-B755-3AF2BC5749A3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADDB313E-B6AC-45C9-A851-3A4EE982B7B3}"/>
 </file>
--- a/dados_formularios.xlsx
+++ b/dados_formularios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL59"/>
+  <dimension ref="A1:EL60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26175,47 +26175,33 @@
           <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>0121000</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>01210000010</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C59" t="n">
+        <v>84</v>
+      </c>
+      <c r="D59" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>22133</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="L59" t="n">
+        <v>408</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -26227,25 +26213,19 @@
           <t>robo.relatorio@folhatech.com.br</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="O59" t="n">
+        <v>408</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Robo Cadastro Cliente</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>1781060400</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>1781093802</t>
-        </is>
+      <c r="Q59" t="n">
+        <v>1781060400</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1781093802</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -26267,10 +26247,8 @@
           <t>03/06/2026 17:13</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="W59" t="n">
+        <v>22133</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -26282,35 +26260,27 @@
           <t>04/06/2026 17:25</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="Z59" t="n">
+        <v>127857</v>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>08 - Confecção e assinatura (Contrato)</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
+      <c r="AB59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>487</v>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
           <t>Pedro Santana</t>
         </is>
       </c>
-      <c r="AE59" t="inlineStr">
-        <is>
-          <t>0121</t>
-        </is>
+      <c r="AE59" t="n">
+        <v>121</v>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
@@ -26327,10 +26297,8 @@
       <c r="AJ59" t="inlineStr"/>
       <c r="AK59" t="inlineStr"/>
       <c r="AL59" t="inlineStr"/>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>127857</v>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
@@ -26362,10 +26330,8 @@
           <t>Aumento de quadro</t>
         </is>
       </c>
-      <c r="AT59" t="inlineStr">
-        <is>
-          <t>3500.00</t>
-        </is>
+      <c r="AT59" t="n">
+        <v>3500</v>
       </c>
       <c r="AU59" t="inlineStr"/>
       <c r="AV59" t="inlineStr">
@@ -26493,10 +26459,8 @@
           <t>Pai</t>
         </is>
       </c>
-      <c r="DE59" t="inlineStr">
-        <is>
-          <t>1121029128</t>
-        </is>
+      <c r="DE59" t="n">
+        <v>1121029128</v>
       </c>
       <c r="DF59" t="inlineStr">
         <is>
@@ -26513,15 +26477,11 @@
           <t>Namorado(a)</t>
         </is>
       </c>
-      <c r="DI59" t="inlineStr">
-        <is>
-          <t>212122</t>
-        </is>
-      </c>
-      <c r="DJ59" t="inlineStr">
-        <is>
-          <t>12344</t>
-        </is>
+      <c r="DI59" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ59" t="n">
+        <v>12344</v>
       </c>
       <c r="DK59" t="inlineStr">
         <is>
@@ -26533,10 +26493,8 @@
           <t>pedro.santana@folhatech.com.br</t>
         </is>
       </c>
-      <c r="DM59" t="inlineStr">
-        <is>
-          <t>121212212112</t>
-        </is>
+      <c r="DM59" t="n">
+        <v>121212212112</v>
       </c>
       <c r="DN59" t="inlineStr"/>
       <c r="DO59" t="inlineStr">
@@ -26554,15 +26512,11 @@
           <t>Conta Corrente</t>
         </is>
       </c>
-      <c r="DR59" t="inlineStr">
-        <is>
-          <t>12121</t>
-        </is>
-      </c>
-      <c r="DS59" t="inlineStr">
-        <is>
-          <t>3144</t>
-        </is>
+      <c r="DR59" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS59" t="n">
+        <v>3144</v>
       </c>
       <c r="DT59" t="inlineStr">
         <is>
@@ -26579,10 +26533,8 @@
           <t>etetetet</t>
         </is>
       </c>
-      <c r="DW59" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="DW59" t="n">
+        <v>124</v>
       </c>
       <c r="DX59" t="inlineStr">
         <is>
@@ -26647,6 +26599,490 @@
         </is>
       </c>
       <c r="EL59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>10/06/2026, 10:05:10</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>0121000</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>01210000010</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1781060400</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1781096192</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>10/06/2026 09:56</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:13</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>03/06/2026 17:24</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>04/06/2026 17:25</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="inlineStr"/>
+      <c r="AK60" t="inlineStr"/>
+      <c r="AL60" t="inlineStr"/>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>127857</t>
+        </is>
+      </c>
+      <c r="AN60" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr">
+        <is>
+          <t>3500.00</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr"/>
+      <c r="AV60" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA60" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB60" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC60" t="inlineStr"/>
+      <c r="BD60" t="inlineStr"/>
+      <c r="BE60" t="inlineStr"/>
+      <c r="BF60" t="inlineStr"/>
+      <c r="BG60" t="inlineStr"/>
+      <c r="BH60" t="inlineStr"/>
+      <c r="BI60" t="inlineStr"/>
+      <c r="BJ60" t="inlineStr"/>
+      <c r="BK60" t="inlineStr"/>
+      <c r="BL60" t="inlineStr"/>
+      <c r="BM60" t="inlineStr"/>
+      <c r="BN60" t="inlineStr"/>
+      <c r="BO60" t="inlineStr"/>
+      <c r="BP60" t="inlineStr"/>
+      <c r="BQ60" t="inlineStr"/>
+      <c r="BR60" t="inlineStr"/>
+      <c r="BS60" t="inlineStr"/>
+      <c r="BT60" t="inlineStr"/>
+      <c r="BU60" t="inlineStr"/>
+      <c r="BV60" t="inlineStr"/>
+      <c r="BW60" t="inlineStr"/>
+      <c r="BX60" t="inlineStr"/>
+      <c r="BY60" t="inlineStr"/>
+      <c r="BZ60" t="inlineStr"/>
+      <c r="CA60" t="inlineStr"/>
+      <c r="CB60" t="inlineStr"/>
+      <c r="CC60" t="inlineStr"/>
+      <c r="CD60" t="inlineStr"/>
+      <c r="CE60" t="inlineStr"/>
+      <c r="CF60" t="inlineStr"/>
+      <c r="CG60" t="inlineStr"/>
+      <c r="CH60" t="inlineStr"/>
+      <c r="CI60" t="inlineStr"/>
+      <c r="CJ60" t="inlineStr"/>
+      <c r="CK60" t="inlineStr"/>
+      <c r="CL60" t="inlineStr"/>
+      <c r="CM60" t="inlineStr"/>
+      <c r="CN60" t="inlineStr"/>
+      <c r="CO60" t="inlineStr"/>
+      <c r="CP60" t="inlineStr"/>
+      <c r="CQ60" t="inlineStr"/>
+      <c r="CR60" t="inlineStr"/>
+      <c r="CS60" t="inlineStr"/>
+      <c r="CT60" t="inlineStr"/>
+      <c r="CU60" t="inlineStr"/>
+      <c r="CV60" t="inlineStr">
+        <is>
+          <t>alex de Niterói</t>
+        </is>
+      </c>
+      <c r="CW60" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX60" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY60" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ60" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="DA60" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="DB60" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="DC60" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD60" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE60" t="inlineStr">
+        <is>
+          <t>1121029128</t>
+        </is>
+      </c>
+      <c r="DF60" t="inlineStr">
+        <is>
+          <t>maria</t>
+        </is>
+      </c>
+      <c r="DG60" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DH60" t="inlineStr">
+        <is>
+          <t>Namorado(a)</t>
+        </is>
+      </c>
+      <c r="DI60" t="inlineStr">
+        <is>
+          <t>212122</t>
+        </is>
+      </c>
+      <c r="DJ60" t="inlineStr">
+        <is>
+          <t>12344</t>
+        </is>
+      </c>
+      <c r="DK60" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL60" t="inlineStr">
+        <is>
+          <t>pedro.santana@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="DM60" t="inlineStr">
+        <is>
+          <t>121212212112</t>
+        </is>
+      </c>
+      <c r="DN60" t="inlineStr"/>
+      <c r="DO60" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP60" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ60" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR60" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+      <c r="DS60" t="inlineStr">
+        <is>
+          <t>3144</t>
+        </is>
+      </c>
+      <c r="DT60" t="inlineStr">
+        <is>
+          <t>dadadqr</t>
+        </is>
+      </c>
+      <c r="DU60" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV60" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW60" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="DX60" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY60" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ60" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA60" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB60" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC60" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED60" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE60" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF60" t="inlineStr"/>
+      <c r="EG60" t="inlineStr"/>
+      <c r="EH60" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Eduardo Rocha - {{2026-06-03 17:24:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-03 17:23:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Proposta&lt;br&gt;Adrielly Santana - {{2026-06-03 17:23:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;avançar &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-06-03 17:21:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;teste &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Pedro Santana - {{2026-06-03 17:20:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aprovado &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-03 17:20:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Fernando Andrade - {{2026-06-03 17:17:36}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-03 17:15:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;prosseguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Pedro Santana - {{2026-06-03 17:14:43}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;prosseguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI60" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção e assinatura (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ60" t="inlineStr">
+        <is>
+          <t>08 - Confecção e assinatura (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK60" t="inlineStr">
+        <is>
+          <t>Alexzinho de Niterói</t>
+        </is>
+      </c>
+      <c r="EL60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26881,13 +27317,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C2A788E-BB37-4653-AD65-3C999FF24002}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B6DED49-4544-4F67-92B4-9E092453F3D4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AA4E6DB-2AC6-4FB4-A24F-B38DFC99D9AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8FE719D-3A16-4E9D-A781-50F7FAA18732}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADDB313E-B6AC-45C9-A851-3A4EE982B7B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD1F9D2B-42E5-4F25-BC17-AB66A6B1A310}"/>
 </file>
--- a/dados_formularios.xlsx
+++ b/dados_formularios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL60"/>
+  <dimension ref="A1:EL62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26611,47 +26611,33 @@
           <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>0121000</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>01210000010</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C60" t="n">
+        <v>84</v>
+      </c>
+      <c r="D60" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1210000010</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>22133</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="L60" t="n">
+        <v>408</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -26663,25 +26649,19 @@
           <t>robo.relatorio@folhatech.com.br</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="O60" t="n">
+        <v>408</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Robo Cadastro Cliente</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>1781060400</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>1781096192</t>
-        </is>
+      <c r="Q60" t="n">
+        <v>1781060400</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1781096192</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -26703,10 +26683,8 @@
           <t>03/06/2026 17:13</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>22133</t>
-        </is>
+      <c r="W60" t="n">
+        <v>22133</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -26718,35 +26696,27 @@
           <t>04/06/2026 17:25</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="Z60" t="n">
+        <v>127857</v>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>08 - Confecção e assinatura (Contrato)</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
+      <c r="AB60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>487</v>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
           <t>Pedro Santana</t>
         </is>
       </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>0121</t>
-        </is>
+      <c r="AE60" t="n">
+        <v>121</v>
       </c>
       <c r="AF60" t="inlineStr">
         <is>
@@ -26763,10 +26733,8 @@
       <c r="AJ60" t="inlineStr"/>
       <c r="AK60" t="inlineStr"/>
       <c r="AL60" t="inlineStr"/>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>127857</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>127857</v>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
@@ -26798,10 +26766,8 @@
           <t>Aumento de quadro</t>
         </is>
       </c>
-      <c r="AT60" t="inlineStr">
-        <is>
-          <t>3500.00</t>
-        </is>
+      <c r="AT60" t="n">
+        <v>3500</v>
       </c>
       <c r="AU60" t="inlineStr"/>
       <c r="AV60" t="inlineStr">
@@ -26929,10 +26895,8 @@
           <t>Pai</t>
         </is>
       </c>
-      <c r="DE60" t="inlineStr">
-        <is>
-          <t>1121029128</t>
-        </is>
+      <c r="DE60" t="n">
+        <v>1121029128</v>
       </c>
       <c r="DF60" t="inlineStr">
         <is>
@@ -26949,15 +26913,11 @@
           <t>Namorado(a)</t>
         </is>
       </c>
-      <c r="DI60" t="inlineStr">
-        <is>
-          <t>212122</t>
-        </is>
-      </c>
-      <c r="DJ60" t="inlineStr">
-        <is>
-          <t>12344</t>
-        </is>
+      <c r="DI60" t="n">
+        <v>212122</v>
+      </c>
+      <c r="DJ60" t="n">
+        <v>12344</v>
       </c>
       <c r="DK60" t="inlineStr">
         <is>
@@ -26969,10 +26929,8 @@
           <t>pedro.santana@folhatech.com.br</t>
         </is>
       </c>
-      <c r="DM60" t="inlineStr">
-        <is>
-          <t>121212212112</t>
-        </is>
+      <c r="DM60" t="n">
+        <v>121212212112</v>
       </c>
       <c r="DN60" t="inlineStr"/>
       <c r="DO60" t="inlineStr">
@@ -26990,15 +26948,11 @@
           <t>Conta Corrente</t>
         </is>
       </c>
-      <c r="DR60" t="inlineStr">
-        <is>
-          <t>12121</t>
-        </is>
-      </c>
-      <c r="DS60" t="inlineStr">
-        <is>
-          <t>3144</t>
-        </is>
+      <c r="DR60" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS60" t="n">
+        <v>3144</v>
       </c>
       <c r="DT60" t="inlineStr">
         <is>
@@ -27015,10 +26969,8 @@
           <t>etetetet</t>
         </is>
       </c>
-      <c r="DW60" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="DW60" t="n">
+        <v>124</v>
       </c>
       <c r="DX60" t="inlineStr">
         <is>
@@ -27083,6 +27035,1110 @@
         </is>
       </c>
       <c r="EL60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>15/06/2026, 10:21:54</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>102</v>
+      </c>
+      <c r="D61" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>22250</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>408</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>408</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>1781492400</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1781529158</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>15/06/2026 10:12</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>10/06/2026 11:40</t>
+        </is>
+      </c>
+      <c r="W61" t="n">
+        <v>22250</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>10/06/2026 11:45</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>11/06/2026 11:46</t>
+        </is>
+      </c>
+      <c r="Z61" t="n">
+        <v>128496</v>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>363</v>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>Karolina Navarro</t>
+        </is>
+      </c>
+      <c r="AE61" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="inlineStr"/>
+      <c r="AK61" t="inlineStr"/>
+      <c r="AL61" t="inlineStr"/>
+      <c r="AM61" t="n">
+        <v>128496</v>
+      </c>
+      <c r="AN61" t="inlineStr">
+        <is>
+          <t>Karolina Navarro</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>karolina.navarro@arantesarimura.adv.br</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>Arantes Arimura Advocacia</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>Arantes Arimura Advocacia</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT61" t="n">
+        <v>20000</v>
+      </c>
+      <c r="AU61" t="inlineStr"/>
+      <c r="AV61" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Arantes Arimura Advocacia</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Arantes Arimura Advocacia</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Raphaella Arantes (Arantes)</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>Raphaella Arantes  (Arantes)</t>
+        </is>
+      </c>
+      <c r="BA61" t="inlineStr">
+        <is>
+          <t>raphaella@arantesarimura.adv.br</t>
+        </is>
+      </c>
+      <c r="BB61" t="inlineStr">
+        <is>
+          <t>raphaella@arantesarimura.adv.br</t>
+        </is>
+      </c>
+      <c r="BC61" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE61" t="inlineStr"/>
+      <c r="BF61" t="inlineStr">
+        <is>
+          <t>[ ] Celular</t>
+        </is>
+      </c>
+      <c r="BG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH61" t="inlineStr"/>
+      <c r="BI61" t="inlineStr">
+        <is>
+          <t>[x] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ61" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BK61" t="inlineStr"/>
+      <c r="BL61" t="inlineStr">
+        <is>
+          <t>[x] Mouse</t>
+        </is>
+      </c>
+      <c r="BM61" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN61" t="inlineStr"/>
+      <c r="BO61" t="inlineStr">
+        <is>
+          <t>[x] Fone</t>
+        </is>
+      </c>
+      <c r="BP61" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BQ61" t="inlineStr"/>
+      <c r="BR61" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT61" t="inlineStr"/>
+      <c r="BU61" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV61" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW61" t="inlineStr"/>
+      <c r="BX61" t="inlineStr">
+        <is>
+          <t>[x] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY61" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BZ61" t="inlineStr"/>
+      <c r="CA61" t="inlineStr">
+        <is>
+          <t>[x] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB61" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="CC61" t="inlineStr"/>
+      <c r="CD61" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF61" t="inlineStr"/>
+      <c r="CG61" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI61" t="inlineStr"/>
+      <c r="CJ61" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL61" t="inlineStr"/>
+      <c r="CM61" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO61" t="inlineStr"/>
+      <c r="CP61" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR61" t="inlineStr"/>
+      <c r="CS61" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT61" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU61" t="inlineStr"/>
+      <c r="CV61" t="inlineStr">
+        <is>
+          <t>Alessandra Maitê Rocha</t>
+        </is>
+      </c>
+      <c r="CW61" t="inlineStr">
+        <is>
+          <t>09/01/2000</t>
+        </is>
+      </c>
+      <c r="CX61" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY61" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ61" t="inlineStr">
+        <is>
+          <t>Fernando Sérgio Pedro Henrique Rocha</t>
+        </is>
+      </c>
+      <c r="DA61" t="inlineStr">
+        <is>
+          <t>Laís Giovanna</t>
+        </is>
+      </c>
+      <c r="DB61" t="inlineStr">
+        <is>
+          <t>Fernando Sérgio Pedro Henrique Rocha</t>
+        </is>
+      </c>
+      <c r="DC61" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD61" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE61" t="n">
+        <v>1121029128</v>
+      </c>
+      <c r="DF61" t="inlineStr"/>
+      <c r="DG61" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH61" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI61" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ61" t="n">
+        <v>392003077</v>
+      </c>
+      <c r="DK61" t="inlineStr">
+        <is>
+          <t>620.969.828-04</t>
+        </is>
+      </c>
+      <c r="DL61" t="inlineStr">
+        <is>
+          <t>alessandra.maite.rocha@hardquality.com.br</t>
+        </is>
+      </c>
+      <c r="DM61" t="n">
+        <v>27999923013</v>
+      </c>
+      <c r="DN61" t="inlineStr"/>
+      <c r="DO61" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP61" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ61" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR61" t="n">
+        <v>302</v>
+      </c>
+      <c r="DS61" t="n">
+        <v>10517413</v>
+      </c>
+      <c r="DT61" t="inlineStr">
+        <is>
+          <t>alessandra.maite.rocha@hardquality.com.b</t>
+        </is>
+      </c>
+      <c r="DU61" t="inlineStr">
+        <is>
+          <t>Alessandra Maitê Rocha</t>
+        </is>
+      </c>
+      <c r="DV61" t="inlineStr">
+        <is>
+          <t>Rua Seis</t>
+        </is>
+      </c>
+      <c r="DW61" t="n">
+        <v>808</v>
+      </c>
+      <c r="DX61" t="inlineStr"/>
+      <c r="DY61" t="inlineStr">
+        <is>
+          <t>29141-102</t>
+        </is>
+      </c>
+      <c r="DZ61" t="inlineStr">
+        <is>
+          <t>Alzira Ramos</t>
+        </is>
+      </c>
+      <c r="EA61" t="inlineStr">
+        <is>
+          <t>Cariacica</t>
+        </is>
+      </c>
+      <c r="EB61" t="inlineStr">
+        <is>
+          <t>Ensino superior incompleto</t>
+        </is>
+      </c>
+      <c r="EC61" t="inlineStr">
+        <is>
+          <t>Ensino superior incompleto</t>
+        </is>
+      </c>
+      <c r="ED61" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="EE61" t="inlineStr">
+        <is>
+          <t>12/09/2027</t>
+        </is>
+      </c>
+      <c r="EF61" t="inlineStr"/>
+      <c r="EG61" t="inlineStr"/>
+      <c r="EH61" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Karolina Navarro - {{2026-06-10 11:45:53}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;Segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-10 11:45:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;Segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Raphaella Arimura - {{2026-06-10 11:42:05}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;Segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-10 11:41:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;Segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Karolina Navarro - {{2026-06-10 11:41:09}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;3 &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI61" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ61" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK61" t="inlineStr"/>
+      <c r="EL61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>15/06/2026, 10:27:11</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>0121000</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>01210000013</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>22250</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1781492400</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1781529474</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>15/06/2026 10:17</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>10/06/2026 11:40</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>22250</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>10/06/2026 11:45</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>11/06/2026 11:46</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>128496</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>Karolina Navarro</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="inlineStr"/>
+      <c r="AK62" t="inlineStr"/>
+      <c r="AL62" t="inlineStr"/>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>128496</t>
+        </is>
+      </c>
+      <c r="AN62" t="inlineStr">
+        <is>
+          <t>Karolina Navarro</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>karolina.navarro@arantesarimura.adv.br</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>Arantes Arimura Advocacia</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr">
+        <is>
+          <t>Arantes Arimura Advocacia</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr">
+        <is>
+          <t>20000.00</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr"/>
+      <c r="AV62" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Arantes Arimura Advocacia</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Arantes Arimura Advocacia</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Raphaella Arantes (Arantes)</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>Raphaella Arantes  (Arantes)</t>
+        </is>
+      </c>
+      <c r="BA62" t="inlineStr">
+        <is>
+          <t>raphaella@arantesarimura.adv.br</t>
+        </is>
+      </c>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>raphaella@arantesarimura.adv.br</t>
+        </is>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE62" t="inlineStr"/>
+      <c r="BF62" t="inlineStr">
+        <is>
+          <t>[ ] Celular</t>
+        </is>
+      </c>
+      <c r="BG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH62" t="inlineStr"/>
+      <c r="BI62" t="inlineStr">
+        <is>
+          <t>[x] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ62" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BK62" t="inlineStr"/>
+      <c r="BL62" t="inlineStr">
+        <is>
+          <t>[x] Mouse</t>
+        </is>
+      </c>
+      <c r="BM62" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN62" t="inlineStr"/>
+      <c r="BO62" t="inlineStr">
+        <is>
+          <t>[x] Fone</t>
+        </is>
+      </c>
+      <c r="BP62" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BQ62" t="inlineStr"/>
+      <c r="BR62" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS62" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT62" t="inlineStr"/>
+      <c r="BU62" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV62" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW62" t="inlineStr"/>
+      <c r="BX62" t="inlineStr">
+        <is>
+          <t>[x] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY62" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BZ62" t="inlineStr"/>
+      <c r="CA62" t="inlineStr">
+        <is>
+          <t>[x] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB62" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="CC62" t="inlineStr"/>
+      <c r="CD62" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF62" t="inlineStr"/>
+      <c r="CG62" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI62" t="inlineStr"/>
+      <c r="CJ62" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL62" t="inlineStr"/>
+      <c r="CM62" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO62" t="inlineStr"/>
+      <c r="CP62" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR62" t="inlineStr"/>
+      <c r="CS62" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT62" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU62" t="inlineStr"/>
+      <c r="CV62" t="inlineStr">
+        <is>
+          <t>Alessandra Maitê Rocha</t>
+        </is>
+      </c>
+      <c r="CW62" t="inlineStr">
+        <is>
+          <t>09/01/2000</t>
+        </is>
+      </c>
+      <c r="CX62" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY62" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ62" t="inlineStr">
+        <is>
+          <t>Fernando Sérgio Pedro Henrique Rocha</t>
+        </is>
+      </c>
+      <c r="DA62" t="inlineStr">
+        <is>
+          <t>Laís Giovanna</t>
+        </is>
+      </c>
+      <c r="DB62" t="inlineStr">
+        <is>
+          <t>Fernando Sérgio Pedro Henrique Rocha</t>
+        </is>
+      </c>
+      <c r="DC62" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD62" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE62" t="inlineStr">
+        <is>
+          <t>1121029128</t>
+        </is>
+      </c>
+      <c r="DF62" t="inlineStr"/>
+      <c r="DG62" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH62" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DJ62" t="inlineStr">
+        <is>
+          <t>392003077</t>
+        </is>
+      </c>
+      <c r="DK62" t="inlineStr">
+        <is>
+          <t>620.969.828-04</t>
+        </is>
+      </c>
+      <c r="DL62" t="inlineStr">
+        <is>
+          <t>alessandra.maite.rocha@hardquality.com.br</t>
+        </is>
+      </c>
+      <c r="DM62" t="inlineStr">
+        <is>
+          <t>27999923013</t>
+        </is>
+      </c>
+      <c r="DN62" t="inlineStr"/>
+      <c r="DO62" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP62" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ62" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR62" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="DS62" t="inlineStr">
+        <is>
+          <t>10517413</t>
+        </is>
+      </c>
+      <c r="DT62" t="inlineStr">
+        <is>
+          <t>alessandra.maite.rocha@hardquality.com.b</t>
+        </is>
+      </c>
+      <c r="DU62" t="inlineStr">
+        <is>
+          <t>Alessandra Maitê Rocha</t>
+        </is>
+      </c>
+      <c r="DV62" t="inlineStr">
+        <is>
+          <t>Rua Seis</t>
+        </is>
+      </c>
+      <c r="DW62" t="inlineStr">
+        <is>
+          <t>808</t>
+        </is>
+      </c>
+      <c r="DX62" t="inlineStr"/>
+      <c r="DY62" t="inlineStr">
+        <is>
+          <t>29141-102</t>
+        </is>
+      </c>
+      <c r="DZ62" t="inlineStr">
+        <is>
+          <t>Alzira Ramos</t>
+        </is>
+      </c>
+      <c r="EA62" t="inlineStr">
+        <is>
+          <t>Cariacica</t>
+        </is>
+      </c>
+      <c r="EB62" t="inlineStr">
+        <is>
+          <t>Ensino superior incompleto</t>
+        </is>
+      </c>
+      <c r="EC62" t="inlineStr">
+        <is>
+          <t>Ensino superior incompleto</t>
+        </is>
+      </c>
+      <c r="ED62" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="EE62" t="inlineStr">
+        <is>
+          <t>12/09/2027</t>
+        </is>
+      </c>
+      <c r="EF62" t="inlineStr"/>
+      <c r="EG62" t="inlineStr"/>
+      <c r="EH62" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Karolina Navarro - {{2026-06-10 11:45:53}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;Segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-10 11:45:35}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;Segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02.5 - Aprovação Recrutamento&lt;br&gt;Raphaella Arimura - {{2026-06-10 11:42:05}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;Segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-10 11:41:42}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;Segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Karolina Navarro - {{2026-06-10 11:41:09}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;3 &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI62" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ62" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK62" t="inlineStr"/>
+      <c r="EL62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -27317,13 +28373,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B6DED49-4544-4F67-92B4-9E092453F3D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B807571-995F-4DD0-8353-F6F31947D694}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8FE719D-3A16-4E9D-A781-50F7FAA18732}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAEBDD51-810A-46D5-A7EB-DE0197B4B33A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD1F9D2B-42E5-4F25-BC17-AB66A6B1A310}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A965ED70-0358-4620-ACC7-2A7AECBE31FE}"/>
 </file>
--- a/dados_formularios.xlsx
+++ b/dados_formularios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL62"/>
+  <dimension ref="A1:EL63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27575,47 +27575,33 @@
           <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>0121000</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>01210000013</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C62" t="n">
+        <v>102</v>
+      </c>
+      <c r="D62" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>22250</t>
-        </is>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>22250</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="L62" t="n">
+        <v>408</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -27627,25 +27613,19 @@
           <t>robo.relatorio@folhatech.com.br</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="O62" t="n">
+        <v>408</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Robo Cadastro Cliente</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>1781492400</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>1781529474</t>
-        </is>
+      <c r="Q62" t="n">
+        <v>1781492400</v>
+      </c>
+      <c r="R62" t="n">
+        <v>1781529474</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -27667,10 +27647,8 @@
           <t>10/06/2026 11:40</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>22250</t>
-        </is>
+      <c r="W62" t="n">
+        <v>22250</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -27682,35 +27660,27 @@
           <t>11/06/2026 11:46</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>128496</t>
-        </is>
+      <c r="Z62" t="n">
+        <v>128496</v>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>05.1 - Confecção Proposta</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
+      <c r="AB62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>363</v>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
           <t>Karolina Navarro</t>
         </is>
       </c>
-      <c r="AE62" t="inlineStr">
-        <is>
-          <t>0121</t>
-        </is>
+      <c r="AE62" t="n">
+        <v>121</v>
       </c>
       <c r="AF62" t="inlineStr">
         <is>
@@ -27727,10 +27697,8 @@
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="inlineStr"/>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>128496</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>128496</v>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
@@ -27762,10 +27730,8 @@
           <t>Aumento de quadro</t>
         </is>
       </c>
-      <c r="AT62" t="inlineStr">
-        <is>
-          <t>20000.00</t>
-        </is>
+      <c r="AT62" t="n">
+        <v>20000</v>
       </c>
       <c r="AU62" t="inlineStr"/>
       <c r="AV62" t="inlineStr">
@@ -27997,10 +27963,8 @@
           <t>Pai</t>
         </is>
       </c>
-      <c r="DE62" t="inlineStr">
-        <is>
-          <t>1121029128</t>
-        </is>
+      <c r="DE62" t="n">
+        <v>1121029128</v>
       </c>
       <c r="DF62" t="inlineStr"/>
       <c r="DG62" t="inlineStr">
@@ -28013,15 +27977,11 @@
           <t>- Selecione algo -</t>
         </is>
       </c>
-      <c r="DI62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DJ62" t="inlineStr">
-        <is>
-          <t>392003077</t>
-        </is>
+      <c r="DI62" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ62" t="n">
+        <v>392003077</v>
       </c>
       <c r="DK62" t="inlineStr">
         <is>
@@ -28033,10 +27993,8 @@
           <t>alessandra.maite.rocha@hardquality.com.br</t>
         </is>
       </c>
-      <c r="DM62" t="inlineStr">
-        <is>
-          <t>27999923013</t>
-        </is>
+      <c r="DM62" t="n">
+        <v>27999923013</v>
       </c>
       <c r="DN62" t="inlineStr"/>
       <c r="DO62" t="inlineStr">
@@ -28054,15 +28012,11 @@
           <t>Conta Corrente</t>
         </is>
       </c>
-      <c r="DR62" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="DS62" t="inlineStr">
-        <is>
-          <t>10517413</t>
-        </is>
+      <c r="DR62" t="n">
+        <v>302</v>
+      </c>
+      <c r="DS62" t="n">
+        <v>10517413</v>
       </c>
       <c r="DT62" t="inlineStr">
         <is>
@@ -28079,10 +28033,8 @@
           <t>Rua Seis</t>
         </is>
       </c>
-      <c r="DW62" t="inlineStr">
-        <is>
-          <t>808</t>
-        </is>
+      <c r="DW62" t="n">
+        <v>808</v>
       </c>
       <c r="DX62" t="inlineStr"/>
       <c r="DY62" t="inlineStr">
@@ -28139,247 +28091,586 @@
       </c>
       <c r="EK62" t="inlineStr"/>
       <c r="EL62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>24/06/2026, 09:52:42</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0121000</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>01210000013</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>22612</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1782270000</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1782304941</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>24/06/2026 09:42</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>24/06/2026 09:10</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>22612</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>24/06/2026 09:20</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>25/06/2026 09:21</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>130404</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="inlineStr"/>
+      <c r="AK63" t="inlineStr"/>
+      <c r="AL63" t="inlineStr"/>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>130404</t>
+        </is>
+      </c>
+      <c r="AN63" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr">
+        <is>
+          <t>50000.00</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr"/>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE63" t="inlineStr"/>
+      <c r="BF63" t="inlineStr">
+        <is>
+          <t>[x] Celular</t>
+        </is>
+      </c>
+      <c r="BG63" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BH63" t="inlineStr"/>
+      <c r="BI63" t="inlineStr">
+        <is>
+          <t>[ ] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ63" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK63" t="inlineStr"/>
+      <c r="BL63" t="inlineStr">
+        <is>
+          <t>[ ] Mouse</t>
+        </is>
+      </c>
+      <c r="BM63" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN63" t="inlineStr"/>
+      <c r="BO63" t="inlineStr">
+        <is>
+          <t>[ ] Fone</t>
+        </is>
+      </c>
+      <c r="BP63" t="b">
+        <v>0</v>
+      </c>
+      <c r="BQ63" t="inlineStr"/>
+      <c r="BR63" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS63" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT63" t="inlineStr"/>
+      <c r="BU63" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV63" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW63" t="inlineStr"/>
+      <c r="BX63" t="inlineStr">
+        <is>
+          <t>[x] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY63" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BZ63" t="inlineStr"/>
+      <c r="CA63" t="inlineStr">
+        <is>
+          <t>[ ] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB63" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC63" t="inlineStr"/>
+      <c r="CD63" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF63" t="inlineStr"/>
+      <c r="CG63" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI63" t="inlineStr"/>
+      <c r="CJ63" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL63" t="inlineStr"/>
+      <c r="CM63" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO63" t="inlineStr"/>
+      <c r="CP63" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR63" t="inlineStr"/>
+      <c r="CS63" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU63" t="inlineStr"/>
+      <c r="CV63" t="inlineStr">
+        <is>
+          <t>Sérgio Nicolas Vieira</t>
+        </is>
+      </c>
+      <c r="CW63" t="inlineStr">
+        <is>
+          <t>14/05/1998</t>
+        </is>
+      </c>
+      <c r="CX63" t="inlineStr">
+        <is>
+          <t>Casado</t>
+        </is>
+      </c>
+      <c r="CY63" t="inlineStr">
+        <is>
+          <t>Casado</t>
+        </is>
+      </c>
+      <c r="CZ63" t="inlineStr">
+        <is>
+          <t>Pedro Henrique Anthony Roberto Vieira</t>
+        </is>
+      </c>
+      <c r="DA63" t="inlineStr">
+        <is>
+          <t>Adriana Isabelle</t>
+        </is>
+      </c>
+      <c r="DB63" t="inlineStr">
+        <is>
+          <t>Adriana Isabelle</t>
+        </is>
+      </c>
+      <c r="DC63" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="DD63" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="DE63" t="inlineStr">
+        <is>
+          <t>79999552575</t>
+        </is>
+      </c>
+      <c r="DF63" t="inlineStr"/>
+      <c r="DG63" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH63" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DJ63" t="inlineStr">
+        <is>
+          <t>339799149</t>
+        </is>
+      </c>
+      <c r="DK63" t="inlineStr">
+        <is>
+          <t>009.510.135-72</t>
+        </is>
+      </c>
+      <c r="DL63" t="inlineStr">
+        <is>
+          <t>sergionicolasvieira@tursi.com.br</t>
+        </is>
+      </c>
+      <c r="DM63" t="inlineStr">
+        <is>
+          <t>69994528502</t>
+        </is>
+      </c>
+      <c r="DN63" t="inlineStr">
+        <is>
+          <t>43.169.616/0001-01</t>
+        </is>
+      </c>
+      <c r="DO63" t="inlineStr">
+        <is>
+          <t>Itau</t>
+        </is>
+      </c>
+      <c r="DP63" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ63" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR63" t="inlineStr">
+        <is>
+          <t>1650</t>
+        </is>
+      </c>
+      <c r="DS63" t="inlineStr">
+        <is>
+          <t>324401</t>
+        </is>
+      </c>
+      <c r="DT63" t="inlineStr">
+        <is>
+          <t>sergionicolasvieira@tursi.com.br</t>
+        </is>
+      </c>
+      <c r="DU63" t="inlineStr">
+        <is>
+          <t>Sérgio Nicolas Vieira</t>
+        </is>
+      </c>
+      <c r="DV63" t="inlineStr">
+        <is>
+          <t>Rua A</t>
+        </is>
+      </c>
+      <c r="DW63" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="DX63" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY63" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ63" t="inlineStr">
+        <is>
+          <t>Jabotiana</t>
+        </is>
+      </c>
+      <c r="EA63" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB63" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC63" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED63" t="inlineStr">
+        <is>
+          <t>Mecanica</t>
+        </is>
+      </c>
+      <c r="EE63" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF63" t="inlineStr"/>
+      <c r="EG63" t="inlineStr"/>
+      <c r="EH63" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-24 09:20:15}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;seguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-06-24 09:19:59}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;Seguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-24 09:19:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;Seguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-24 09:11:53}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;Seguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-06-24 09:11:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;Seguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI63" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ63" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK63" t="inlineStr"/>
+      <c r="EL63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B5FCC50092DEF84396333E47DAEFEB5E" ma:contentTypeVersion="13" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="3f5dff31fa7a2b799118bc7c00128ae3">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5df11fd7-6aff-4cc6-9d69-481ebafd3f51" xmlns:ns3="ba98ff8d-cf9c-4574-b9ff-8782fca0b7db" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5a22452f93ee1f3c8f432c572ea5d732" ns2:_="" ns3:_="">
-    <xsd:import namespace="5df11fd7-6aff-4cc6-9d69-481ebafd3f51"/>
-    <xsd:import namespace="ba98ff8d-cf9c-4574-b9ff-8782fca0b7db"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="5df11fd7-6aff-4cc6-9d69-481ebafd3f51" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4410abd1-e841-4d52-8c09-cc5936d54c0f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ba98ff8d-cf9c-4574-b9ff-8782fca0b7db" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{78d918e0-dd2a-4d55-9cd7-b9c5d47e1b97}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="ba98ff8d-cf9c-4574-b9ff-8782fca0b7db">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ba98ff8d-cf9c-4574-b9ff-8782fca0b7db" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5df11fd7-6aff-4cc6-9d69-481ebafd3f51">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B807571-995F-4DD0-8353-F6F31947D694}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAEBDD51-810A-46D5-A7EB-DE0197B4B33A}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A965ED70-0358-4620-ACC7-2A7AECBE31FE}"/>
 </file>
--- a/dados_formularios.xlsx
+++ b/dados_formularios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL63"/>
+  <dimension ref="A1:EL65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28103,47 +28103,33 @@
           <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>0121000</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>01210000013</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C63" t="n">
+        <v>108</v>
+      </c>
+      <c r="D63" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>22612</t>
-        </is>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>22612</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="L63" t="n">
+        <v>408</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -28155,25 +28141,19 @@
           <t>robo.relatorio@folhatech.com.br</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="O63" t="n">
+        <v>408</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Robo Cadastro Cliente</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>1782270000</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>1782304941</t>
-        </is>
+      <c r="Q63" t="n">
+        <v>1782270000</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1782304941</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -28195,10 +28175,8 @@
           <t>24/06/2026 09:10</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>22612</t>
-        </is>
+      <c r="W63" t="n">
+        <v>22612</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -28210,35 +28188,27 @@
           <t>25/06/2026 09:21</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>130404</t>
-        </is>
+      <c r="Z63" t="n">
+        <v>130404</v>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>05.1 - Confecção Proposta</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
+      <c r="AB63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>427</v>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
           <t>tiago izaias</t>
         </is>
       </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>0121</t>
-        </is>
+      <c r="AE63" t="n">
+        <v>121</v>
       </c>
       <c r="AF63" t="inlineStr">
         <is>
@@ -28255,10 +28225,8 @@
       <c r="AJ63" t="inlineStr"/>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="inlineStr"/>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>130404</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>130404</v>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
@@ -28290,10 +28258,8 @@
           <t>Aumento de quadro</t>
         </is>
       </c>
-      <c r="AT63" t="inlineStr">
-        <is>
-          <t>50000.00</t>
-        </is>
+      <c r="AT63" t="n">
+        <v>50000</v>
       </c>
       <c r="AU63" t="inlineStr"/>
       <c r="AV63" t="inlineStr">
@@ -28367,7 +28333,7 @@
           <t>[ ] Mouse</t>
         </is>
       </c>
-      <c r="BM63" t="b">
+      <c r="BM63" t="n">
         <v>0</v>
       </c>
       <c r="BN63" t="inlineStr"/>
@@ -28376,7 +28342,7 @@
           <t>[ ] Fone</t>
         </is>
       </c>
-      <c r="BP63" t="b">
+      <c r="BP63" t="n">
         <v>0</v>
       </c>
       <c r="BQ63" t="inlineStr"/>
@@ -28519,10 +28485,8 @@
           <t>Mãe</t>
         </is>
       </c>
-      <c r="DE63" t="inlineStr">
-        <is>
-          <t>79999552575</t>
-        </is>
+      <c r="DE63" t="n">
+        <v>79999552575</v>
       </c>
       <c r="DF63" t="inlineStr"/>
       <c r="DG63" t="inlineStr">
@@ -28535,15 +28499,11 @@
           <t>- Selecione algo -</t>
         </is>
       </c>
-      <c r="DI63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DJ63" t="inlineStr">
-        <is>
-          <t>339799149</t>
-        </is>
+      <c r="DI63" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ63" t="n">
+        <v>339799149</v>
       </c>
       <c r="DK63" t="inlineStr">
         <is>
@@ -28555,10 +28515,8 @@
           <t>sergionicolasvieira@tursi.com.br</t>
         </is>
       </c>
-      <c r="DM63" t="inlineStr">
-        <is>
-          <t>69994528502</t>
-        </is>
+      <c r="DM63" t="n">
+        <v>69994528502</v>
       </c>
       <c r="DN63" t="inlineStr">
         <is>
@@ -28580,15 +28538,11 @@
           <t>Conta Corrente</t>
         </is>
       </c>
-      <c r="DR63" t="inlineStr">
-        <is>
-          <t>1650</t>
-        </is>
-      </c>
-      <c r="DS63" t="inlineStr">
-        <is>
-          <t>324401</t>
-        </is>
+      <c r="DR63" t="n">
+        <v>1650</v>
+      </c>
+      <c r="DS63" t="n">
+        <v>324401</v>
       </c>
       <c r="DT63" t="inlineStr">
         <is>
@@ -28605,10 +28559,8 @@
           <t>Rua A</t>
         </is>
       </c>
-      <c r="DW63" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="DW63" t="n">
+        <v>124</v>
       </c>
       <c r="DX63" t="inlineStr">
         <is>
@@ -28669,6 +28621,1114 @@
       </c>
       <c r="EK63" t="inlineStr"/>
       <c r="EL63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>29/06/2026, 13:04:54</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>108</v>
+      </c>
+      <c r="D64" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>22612</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>408</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>408</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>1782702000</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1782748434</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>29/06/2026 12:53</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>24/06/2026 09:10</t>
+        </is>
+      </c>
+      <c r="W64" t="n">
+        <v>22612</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>24/06/2026 09:20</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>25/06/2026 09:21</t>
+        </is>
+      </c>
+      <c r="Z64" t="n">
+        <v>130404</v>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE64" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
+      <c r="AL64" t="inlineStr"/>
+      <c r="AM64" t="n">
+        <v>130404</v>
+      </c>
+      <c r="AN64" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT64" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AU64" t="inlineStr"/>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE64" t="inlineStr"/>
+      <c r="BF64" t="inlineStr">
+        <is>
+          <t>[x] Celular</t>
+        </is>
+      </c>
+      <c r="BG64" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BH64" t="inlineStr"/>
+      <c r="BI64" t="inlineStr">
+        <is>
+          <t>[ ] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ64" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK64" t="inlineStr"/>
+      <c r="BL64" t="inlineStr">
+        <is>
+          <t>[ ] Mouse</t>
+        </is>
+      </c>
+      <c r="BM64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN64" t="inlineStr"/>
+      <c r="BO64" t="inlineStr">
+        <is>
+          <t>[ ] Fone</t>
+        </is>
+      </c>
+      <c r="BP64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ64" t="inlineStr"/>
+      <c r="BR64" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT64" t="inlineStr"/>
+      <c r="BU64" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV64" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW64" t="inlineStr"/>
+      <c r="BX64" t="inlineStr">
+        <is>
+          <t>[x] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY64" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BZ64" t="inlineStr"/>
+      <c r="CA64" t="inlineStr">
+        <is>
+          <t>[ ] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB64" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC64" t="inlineStr"/>
+      <c r="CD64" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF64" t="inlineStr"/>
+      <c r="CG64" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI64" t="inlineStr"/>
+      <c r="CJ64" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL64" t="inlineStr"/>
+      <c r="CM64" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO64" t="inlineStr"/>
+      <c r="CP64" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR64" t="inlineStr"/>
+      <c r="CS64" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU64" t="inlineStr"/>
+      <c r="CV64" t="inlineStr">
+        <is>
+          <t>Sérgio Nicolas Vieira</t>
+        </is>
+      </c>
+      <c r="CW64" t="inlineStr">
+        <is>
+          <t>14/05/1998</t>
+        </is>
+      </c>
+      <c r="CX64" t="inlineStr">
+        <is>
+          <t>Casado</t>
+        </is>
+      </c>
+      <c r="CY64" t="inlineStr">
+        <is>
+          <t>Casado</t>
+        </is>
+      </c>
+      <c r="CZ64" t="inlineStr">
+        <is>
+          <t>Pedro Henrique Anthony Roberto Vieira</t>
+        </is>
+      </c>
+      <c r="DA64" t="inlineStr">
+        <is>
+          <t>Adriana Isabelle</t>
+        </is>
+      </c>
+      <c r="DB64" t="inlineStr">
+        <is>
+          <t>Adriana Isabelle</t>
+        </is>
+      </c>
+      <c r="DC64" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="DD64" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="DE64" t="n">
+        <v>79999552575</v>
+      </c>
+      <c r="DF64" t="inlineStr"/>
+      <c r="DG64" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH64" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ64" t="n">
+        <v>339799149</v>
+      </c>
+      <c r="DK64" t="inlineStr">
+        <is>
+          <t>009.510.135-72</t>
+        </is>
+      </c>
+      <c r="DL64" t="inlineStr">
+        <is>
+          <t>sergionicolasvieira@tursi.com.br</t>
+        </is>
+      </c>
+      <c r="DM64" t="n">
+        <v>69994528502</v>
+      </c>
+      <c r="DN64" t="inlineStr">
+        <is>
+          <t>43.169.616/0001-01</t>
+        </is>
+      </c>
+      <c r="DO64" t="inlineStr">
+        <is>
+          <t>Itau</t>
+        </is>
+      </c>
+      <c r="DP64" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ64" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR64" t="n">
+        <v>1650</v>
+      </c>
+      <c r="DS64" t="n">
+        <v>324401</v>
+      </c>
+      <c r="DT64" t="inlineStr">
+        <is>
+          <t>sergionicolasvieira@tursi.com.br</t>
+        </is>
+      </c>
+      <c r="DU64" t="inlineStr">
+        <is>
+          <t>Sérgio Nicolas Vieira</t>
+        </is>
+      </c>
+      <c r="DV64" t="inlineStr">
+        <is>
+          <t>Rua A</t>
+        </is>
+      </c>
+      <c r="DW64" t="n">
+        <v>124</v>
+      </c>
+      <c r="DX64" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY64" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ64" t="inlineStr">
+        <is>
+          <t>Jabotiana</t>
+        </is>
+      </c>
+      <c r="EA64" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB64" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC64" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED64" t="inlineStr">
+        <is>
+          <t>Mecanica</t>
+        </is>
+      </c>
+      <c r="EE64" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF64" t="inlineStr"/>
+      <c r="EG64" t="inlineStr"/>
+      <c r="EH64" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-24 09:20:15}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;seguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-06-24 09:19:59}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;Seguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-24 09:19:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;Seguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-24 09:11:53}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;Seguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-06-24 09:11:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;Seguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI64" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ64" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK64" t="inlineStr"/>
+      <c r="EL64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>29/06/2026, 13:07:51</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>0121000</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>01210000013</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>22612</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1782702000</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1782748611</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>29/06/2026</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>29/06/2026 12:56</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>24/06/2026 09:10</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>22612</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>24/06/2026 09:20</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>25/06/2026 09:21</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>130404</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="inlineStr"/>
+      <c r="AK65" t="inlineStr"/>
+      <c r="AL65" t="inlineStr"/>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>130404</t>
+        </is>
+      </c>
+      <c r="AN65" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr">
+        <is>
+          <t>50000.00</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr"/>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE65" t="inlineStr"/>
+      <c r="BF65" t="inlineStr">
+        <is>
+          <t>[x] Celular</t>
+        </is>
+      </c>
+      <c r="BG65" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BH65" t="inlineStr"/>
+      <c r="BI65" t="inlineStr">
+        <is>
+          <t>[ ] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ65" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK65" t="inlineStr"/>
+      <c r="BL65" t="inlineStr">
+        <is>
+          <t>[ ] Mouse</t>
+        </is>
+      </c>
+      <c r="BM65" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN65" t="inlineStr"/>
+      <c r="BO65" t="inlineStr">
+        <is>
+          <t>[ ] Fone</t>
+        </is>
+      </c>
+      <c r="BP65" t="b">
+        <v>0</v>
+      </c>
+      <c r="BQ65" t="inlineStr"/>
+      <c r="BR65" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT65" t="inlineStr"/>
+      <c r="BU65" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV65" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW65" t="inlineStr"/>
+      <c r="BX65" t="inlineStr">
+        <is>
+          <t>[x] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY65" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BZ65" t="inlineStr"/>
+      <c r="CA65" t="inlineStr">
+        <is>
+          <t>[ ] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB65" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC65" t="inlineStr"/>
+      <c r="CD65" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF65" t="inlineStr"/>
+      <c r="CG65" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI65" t="inlineStr"/>
+      <c r="CJ65" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL65" t="inlineStr"/>
+      <c r="CM65" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO65" t="inlineStr"/>
+      <c r="CP65" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR65" t="inlineStr"/>
+      <c r="CS65" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU65" t="inlineStr"/>
+      <c r="CV65" t="inlineStr">
+        <is>
+          <t>Sérgio Nicolas Vieira</t>
+        </is>
+      </c>
+      <c r="CW65" t="inlineStr">
+        <is>
+          <t>14/05/1998</t>
+        </is>
+      </c>
+      <c r="CX65" t="inlineStr">
+        <is>
+          <t>Casado</t>
+        </is>
+      </c>
+      <c r="CY65" t="inlineStr">
+        <is>
+          <t>Casado</t>
+        </is>
+      </c>
+      <c r="CZ65" t="inlineStr">
+        <is>
+          <t>Pedro Henrique Anthony Roberto Vieira</t>
+        </is>
+      </c>
+      <c r="DA65" t="inlineStr">
+        <is>
+          <t>Adriana Isabelle</t>
+        </is>
+      </c>
+      <c r="DB65" t="inlineStr">
+        <is>
+          <t>Adriana Isabelle</t>
+        </is>
+      </c>
+      <c r="DC65" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="DD65" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="DE65" t="inlineStr">
+        <is>
+          <t>79999552575</t>
+        </is>
+      </c>
+      <c r="DF65" t="inlineStr"/>
+      <c r="DG65" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH65" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DJ65" t="inlineStr">
+        <is>
+          <t>339799149</t>
+        </is>
+      </c>
+      <c r="DK65" t="inlineStr">
+        <is>
+          <t>009.510.135-72</t>
+        </is>
+      </c>
+      <c r="DL65" t="inlineStr">
+        <is>
+          <t>sergionicolasvieira@tursi.com.br</t>
+        </is>
+      </c>
+      <c r="DM65" t="inlineStr">
+        <is>
+          <t>69994528502</t>
+        </is>
+      </c>
+      <c r="DN65" t="inlineStr">
+        <is>
+          <t>43.169.616/0001-01</t>
+        </is>
+      </c>
+      <c r="DO65" t="inlineStr">
+        <is>
+          <t>Itau</t>
+        </is>
+      </c>
+      <c r="DP65" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ65" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR65" t="inlineStr">
+        <is>
+          <t>1650</t>
+        </is>
+      </c>
+      <c r="DS65" t="inlineStr">
+        <is>
+          <t>324401</t>
+        </is>
+      </c>
+      <c r="DT65" t="inlineStr">
+        <is>
+          <t>sergionicolasvieira@tursi.com.br</t>
+        </is>
+      </c>
+      <c r="DU65" t="inlineStr">
+        <is>
+          <t>Sérgio Nicolas Vieira</t>
+        </is>
+      </c>
+      <c r="DV65" t="inlineStr">
+        <is>
+          <t>Rua A</t>
+        </is>
+      </c>
+      <c r="DW65" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="DX65" t="inlineStr">
+        <is>
+          <t>fwfwee</t>
+        </is>
+      </c>
+      <c r="DY65" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ65" t="inlineStr">
+        <is>
+          <t>Jabotiana</t>
+        </is>
+      </c>
+      <c r="EA65" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB65" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC65" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED65" t="inlineStr">
+        <is>
+          <t>Mecanica</t>
+        </is>
+      </c>
+      <c r="EE65" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF65" t="inlineStr"/>
+      <c r="EG65" t="inlineStr"/>
+      <c r="EH65" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-06-24 09:20:15}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;seguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-06-24 09:19:59}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;Seguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-06-24 09:19:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;Seguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-06-24 09:11:53}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;Seguir &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-06-24 09:11:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;Seguir &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI65" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ65" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK65" t="inlineStr"/>
+      <c r="EL65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados_formularios.xlsx
+++ b/dados_formularios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL65"/>
+  <dimension ref="A1:EL80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29163,47 +29163,33 @@
           <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>0121000</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>01210000013</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C65" t="n">
+        <v>108</v>
+      </c>
+      <c r="D65" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>22612</t>
-        </is>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>22612</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="L65" t="n">
+        <v>408</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -29215,25 +29201,19 @@
           <t>robo.relatorio@folhatech.com.br</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="O65" t="n">
+        <v>408</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Robo Cadastro Cliente</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>1782702000</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>1782748611</t>
-        </is>
+      <c r="Q65" t="n">
+        <v>1782702000</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1782748611</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -29255,10 +29235,8 @@
           <t>24/06/2026 09:10</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>22612</t>
-        </is>
+      <c r="W65" t="n">
+        <v>22612</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -29270,35 +29248,27 @@
           <t>25/06/2026 09:21</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>130404</t>
-        </is>
+      <c r="Z65" t="n">
+        <v>130404</v>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>05.1 - Confecção Proposta</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
+      <c r="AB65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>427</v>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
           <t>tiago izaias</t>
         </is>
       </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>0121</t>
-        </is>
+      <c r="AE65" t="n">
+        <v>121</v>
       </c>
       <c r="AF65" t="inlineStr">
         <is>
@@ -29315,10 +29285,8 @@
       <c r="AJ65" t="inlineStr"/>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="inlineStr"/>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>130404</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>130404</v>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
@@ -29350,10 +29318,8 @@
           <t>Aumento de quadro</t>
         </is>
       </c>
-      <c r="AT65" t="inlineStr">
-        <is>
-          <t>50000.00</t>
-        </is>
+      <c r="AT65" t="n">
+        <v>50000</v>
       </c>
       <c r="AU65" t="inlineStr"/>
       <c r="AV65" t="inlineStr">
@@ -29427,7 +29393,7 @@
           <t>[ ] Mouse</t>
         </is>
       </c>
-      <c r="BM65" t="b">
+      <c r="BM65" t="n">
         <v>0</v>
       </c>
       <c r="BN65" t="inlineStr"/>
@@ -29436,7 +29402,7 @@
           <t>[ ] Fone</t>
         </is>
       </c>
-      <c r="BP65" t="b">
+      <c r="BP65" t="n">
         <v>0</v>
       </c>
       <c r="BQ65" t="inlineStr"/>
@@ -29579,10 +29545,8 @@
           <t>Mãe</t>
         </is>
       </c>
-      <c r="DE65" t="inlineStr">
-        <is>
-          <t>79999552575</t>
-        </is>
+      <c r="DE65" t="n">
+        <v>79999552575</v>
       </c>
       <c r="DF65" t="inlineStr"/>
       <c r="DG65" t="inlineStr">
@@ -29595,15 +29559,11 @@
           <t>- Selecione algo -</t>
         </is>
       </c>
-      <c r="DI65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DJ65" t="inlineStr">
-        <is>
-          <t>339799149</t>
-        </is>
+      <c r="DI65" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ65" t="n">
+        <v>339799149</v>
       </c>
       <c r="DK65" t="inlineStr">
         <is>
@@ -29615,10 +29575,8 @@
           <t>sergionicolasvieira@tursi.com.br</t>
         </is>
       </c>
-      <c r="DM65" t="inlineStr">
-        <is>
-          <t>69994528502</t>
-        </is>
+      <c r="DM65" t="n">
+        <v>69994528502</v>
       </c>
       <c r="DN65" t="inlineStr">
         <is>
@@ -29640,15 +29598,11 @@
           <t>Conta Corrente</t>
         </is>
       </c>
-      <c r="DR65" t="inlineStr">
-        <is>
-          <t>1650</t>
-        </is>
-      </c>
-      <c r="DS65" t="inlineStr">
-        <is>
-          <t>324401</t>
-        </is>
+      <c r="DR65" t="n">
+        <v>1650</v>
+      </c>
+      <c r="DS65" t="n">
+        <v>324401</v>
       </c>
       <c r="DT65" t="inlineStr">
         <is>
@@ -29665,10 +29619,8 @@
           <t>Rua A</t>
         </is>
       </c>
-      <c r="DW65" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="DW65" t="n">
+        <v>124</v>
       </c>
       <c r="DX65" t="inlineStr">
         <is>
@@ -29729,6 +29681,7942 @@
       </c>
       <c r="EK65" t="inlineStr"/>
       <c r="EL65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>01/07/2026, 10:14:40</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>137</v>
+      </c>
+      <c r="D66" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>22823</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>408</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>408</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>1782874800</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1782911565</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>01/07/2026 10:12</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:42</t>
+        </is>
+      </c>
+      <c r="W66" t="n">
+        <v>22823</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:46</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>02/07/2026 09:47</t>
+        </is>
+      </c>
+      <c r="Z66" t="n">
+        <v>131450</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>363</v>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>Karolina Navarro</t>
+        </is>
+      </c>
+      <c r="AE66" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="inlineStr"/>
+      <c r="AK66" t="inlineStr"/>
+      <c r="AL66" t="inlineStr"/>
+      <c r="AM66" t="n">
+        <v>131450</v>
+      </c>
+      <c r="AN66" t="inlineStr">
+        <is>
+          <t>Karolina Navarro</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>karolina.navarro@arantesarimura.adv.br</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>Arantes Arimura Advocacia</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr">
+        <is>
+          <t>Arantes Arimura Advocacia</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT66" t="n">
+        <v>5600</v>
+      </c>
+      <c r="AU66" t="inlineStr"/>
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Arantes Arimura Advocacia</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Arantes Arimura Advocacia</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Raphaella Arantes (Arantes)</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>Raphaella Arantes  (Arantes)</t>
+        </is>
+      </c>
+      <c r="BA66" t="inlineStr">
+        <is>
+          <t>raphaella@arantesarimura.adv.br</t>
+        </is>
+      </c>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>raphaella@arantesarimura.adv.br</t>
+        </is>
+      </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE66" t="inlineStr"/>
+      <c r="BF66" t="inlineStr">
+        <is>
+          <t>[x] Celular</t>
+        </is>
+      </c>
+      <c r="BG66" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BH66" t="inlineStr"/>
+      <c r="BI66" t="inlineStr">
+        <is>
+          <t>[x] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ66" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BK66" t="inlineStr"/>
+      <c r="BL66" t="inlineStr">
+        <is>
+          <t>[x] Mouse</t>
+        </is>
+      </c>
+      <c r="BM66" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN66" t="inlineStr"/>
+      <c r="BO66" t="inlineStr">
+        <is>
+          <t>[ ] Fone</t>
+        </is>
+      </c>
+      <c r="BP66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ66" t="inlineStr"/>
+      <c r="BR66" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT66" t="inlineStr"/>
+      <c r="BU66" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV66" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW66" t="inlineStr"/>
+      <c r="BX66" t="inlineStr">
+        <is>
+          <t>[x] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY66" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BZ66" t="inlineStr"/>
+      <c r="CA66" t="inlineStr">
+        <is>
+          <t>[x] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB66" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="CC66" t="inlineStr"/>
+      <c r="CD66" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF66" t="inlineStr"/>
+      <c r="CG66" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI66" t="inlineStr"/>
+      <c r="CJ66" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL66" t="inlineStr"/>
+      <c r="CM66" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO66" t="inlineStr"/>
+      <c r="CP66" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR66" t="inlineStr"/>
+      <c r="CS66" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT66" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU66" t="inlineStr"/>
+      <c r="CV66" t="inlineStr">
+        <is>
+          <t>Raul Augusto de Paula</t>
+        </is>
+      </c>
+      <c r="CW66" t="inlineStr">
+        <is>
+          <t>21/06/1984</t>
+        </is>
+      </c>
+      <c r="CX66" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY66" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ66" t="inlineStr">
+        <is>
+          <t>Diego Ian Sérgio de Paula</t>
+        </is>
+      </c>
+      <c r="DA66" t="inlineStr">
+        <is>
+          <t>Giovana Isabel Rosângela</t>
+        </is>
+      </c>
+      <c r="DB66" t="inlineStr">
+        <is>
+          <t>Giovana Isabel Rosângela</t>
+        </is>
+      </c>
+      <c r="DC66" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="DD66" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="DE66" t="n">
+        <v>132546</v>
+      </c>
+      <c r="DF66" t="inlineStr"/>
+      <c r="DG66" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH66" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ66" t="n">
+        <v>480480916</v>
+      </c>
+      <c r="DK66" t="inlineStr">
+        <is>
+          <t>838.824.227-00</t>
+        </is>
+      </c>
+      <c r="DL66" t="inlineStr">
+        <is>
+          <t>raulaugustodepaula@vinax.com.br</t>
+        </is>
+      </c>
+      <c r="DM66" t="n">
+        <v>13234567</v>
+      </c>
+      <c r="DN66" t="inlineStr"/>
+      <c r="DO66" t="inlineStr">
+        <is>
+          <t>Bradesco</t>
+        </is>
+      </c>
+      <c r="DP66" t="inlineStr">
+        <is>
+          <t>Conta Poupança</t>
+        </is>
+      </c>
+      <c r="DQ66" t="inlineStr">
+        <is>
+          <t>Conta Poupança</t>
+        </is>
+      </c>
+      <c r="DR66" t="n">
+        <v>4675</v>
+      </c>
+      <c r="DS66" t="n">
+        <v>324401</v>
+      </c>
+      <c r="DT66" t="inlineStr">
+        <is>
+          <t>raulaugustodepaula@vinax.com.br</t>
+        </is>
+      </c>
+      <c r="DU66" t="inlineStr">
+        <is>
+          <t>wrw34</t>
+        </is>
+      </c>
+      <c r="DV66" t="inlineStr">
+        <is>
+          <t>Rua Joaquim da Rocha</t>
+        </is>
+      </c>
+      <c r="DW66" t="n">
+        <v>665</v>
+      </c>
+      <c r="DX66" t="inlineStr"/>
+      <c r="DY66" t="inlineStr">
+        <is>
+          <t>76811-348</t>
+        </is>
+      </c>
+      <c r="DZ66" t="inlineStr">
+        <is>
+          <t>Castanheira</t>
+        </is>
+      </c>
+      <c r="EA66" t="inlineStr">
+        <is>
+          <t>Porto Velho</t>
+        </is>
+      </c>
+      <c r="EB66" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC66" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED66" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="EE66" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF66" t="inlineStr"/>
+      <c r="EG66" t="inlineStr"/>
+      <c r="EH66" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:46:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Karolina Navarro - {{2026-07-01 09:46:27}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:46:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;sasas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:43:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;sasa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Karolina Navarro - {{2026-07-01 09:43:38}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;asas &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI66" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ66" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK66" t="inlineStr"/>
+      <c r="EL66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>01/07/2026, 10:14:49</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br//triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>131</v>
+      </c>
+      <c r="D67" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>22821</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>408</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>408</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>1782874800</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1782911574</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>01/07/2026 10:12</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:37</t>
+        </is>
+      </c>
+      <c r="W67" t="n">
+        <v>22821</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:42</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>02/07/2026 09:43</t>
+        </is>
+      </c>
+      <c r="Z67" t="n">
+        <v>131443</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>532</v>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>Luana Lidia</t>
+        </is>
+      </c>
+      <c r="AE67" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="inlineStr"/>
+      <c r="AK67" t="inlineStr"/>
+      <c r="AL67" t="inlineStr"/>
+      <c r="AM67" t="n">
+        <v>131443</v>
+      </c>
+      <c r="AN67" t="inlineStr">
+        <is>
+          <t>Luana Lidia</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>luana.lidia@genter.com.br</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>Genter</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr">
+        <is>
+          <t>Genter</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT67" t="n">
+        <v>8900</v>
+      </c>
+      <c r="AU67" t="inlineStr"/>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>Comercial</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Genter</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Genter</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Jeferson Arimura (Genter)</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>Jeferson Arimura (Genter)</t>
+        </is>
+      </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>jeferson.arimura@genter.com.br</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>jeferson.arimura@genter.com.br</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE67" t="inlineStr"/>
+      <c r="BF67" t="inlineStr">
+        <is>
+          <t>[x] Celular</t>
+        </is>
+      </c>
+      <c r="BG67" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BH67" t="inlineStr"/>
+      <c r="BI67" t="inlineStr">
+        <is>
+          <t>[x] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ67" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BK67" t="inlineStr"/>
+      <c r="BL67" t="inlineStr">
+        <is>
+          <t>[x] Mouse</t>
+        </is>
+      </c>
+      <c r="BM67" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN67" t="inlineStr"/>
+      <c r="BO67" t="inlineStr">
+        <is>
+          <t>[x] Fone</t>
+        </is>
+      </c>
+      <c r="BP67" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BQ67" t="inlineStr"/>
+      <c r="BR67" t="inlineStr">
+        <is>
+          <t>[x] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS67" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BT67" t="inlineStr"/>
+      <c r="BU67" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV67" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW67" t="inlineStr"/>
+      <c r="BX67" t="inlineStr">
+        <is>
+          <t>[ ] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY67" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ67" t="inlineStr"/>
+      <c r="CA67" t="inlineStr">
+        <is>
+          <t>[x] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB67" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="CC67" t="inlineStr"/>
+      <c r="CD67" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF67" t="inlineStr"/>
+      <c r="CG67" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI67" t="inlineStr"/>
+      <c r="CJ67" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL67" t="inlineStr"/>
+      <c r="CM67" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO67" t="inlineStr"/>
+      <c r="CP67" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR67" t="inlineStr"/>
+      <c r="CS67" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT67" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU67" t="inlineStr"/>
+      <c r="CV67" t="inlineStr">
+        <is>
+          <t>Brenda Tatiane Carolina da Rocha</t>
+        </is>
+      </c>
+      <c r="CW67" t="inlineStr">
+        <is>
+          <t>06/05/1951</t>
+        </is>
+      </c>
+      <c r="CX67" t="inlineStr">
+        <is>
+          <t>Casado</t>
+        </is>
+      </c>
+      <c r="CY67" t="inlineStr">
+        <is>
+          <t>Casado</t>
+        </is>
+      </c>
+      <c r="CZ67" t="inlineStr">
+        <is>
+          <t>Tiago Igor Thomas da Rocha</t>
+        </is>
+      </c>
+      <c r="DA67" t="inlineStr">
+        <is>
+          <t>Isabella Isabelle Sara</t>
+        </is>
+      </c>
+      <c r="DB67" t="inlineStr">
+        <is>
+          <t>tomas neves</t>
+        </is>
+      </c>
+      <c r="DC67" t="inlineStr">
+        <is>
+          <t>Esposo(a)</t>
+        </is>
+      </c>
+      <c r="DD67" t="inlineStr">
+        <is>
+          <t>Esposo(a)</t>
+        </is>
+      </c>
+      <c r="DE67" t="n">
+        <v>645645</v>
+      </c>
+      <c r="DF67" t="inlineStr"/>
+      <c r="DG67" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH67" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ67" t="n">
+        <v>314452163</v>
+      </c>
+      <c r="DK67" t="inlineStr">
+        <is>
+          <t>149.339.407-03</t>
+        </is>
+      </c>
+      <c r="DL67" t="inlineStr">
+        <is>
+          <t>brenda_darocha@mv1.com.br</t>
+        </is>
+      </c>
+      <c r="DM67" t="n">
+        <v>4655656</v>
+      </c>
+      <c r="DN67" t="inlineStr">
+        <is>
+          <t>59.988.037/0001-12</t>
+        </is>
+      </c>
+      <c r="DO67" t="inlineStr">
+        <is>
+          <t>Itau</t>
+        </is>
+      </c>
+      <c r="DP67" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ67" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR67" t="n">
+        <v>4257</v>
+      </c>
+      <c r="DS67" t="n">
+        <v>177347</v>
+      </c>
+      <c r="DT67" t="inlineStr">
+        <is>
+          <t>brenda_darocha@mv1.com.br</t>
+        </is>
+      </c>
+      <c r="DU67" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="DV67" t="inlineStr">
+        <is>
+          <t>Travessa Limoeiro</t>
+        </is>
+      </c>
+      <c r="DW67" t="inlineStr"/>
+      <c r="DX67" t="inlineStr"/>
+      <c r="DY67" t="inlineStr">
+        <is>
+          <t>42801-100</t>
+        </is>
+      </c>
+      <c r="DZ67" t="inlineStr">
+        <is>
+          <t>Ponto Certo</t>
+        </is>
+      </c>
+      <c r="EA67" t="inlineStr">
+        <is>
+          <t>Camaçari</t>
+        </is>
+      </c>
+      <c r="EB67" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC67" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED67" t="inlineStr">
+        <is>
+          <t>relacoes publicas</t>
+        </is>
+      </c>
+      <c r="EE67" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF67" t="inlineStr"/>
+      <c r="EG67" t="inlineStr"/>
+      <c r="EH67" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:42:31}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Luana Lidia - {{2026-07-01 09:42:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;sas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:41:56}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;sasas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:38:40}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Luana Lidia - {{2026-07-01 09:38:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI67" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ67" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK67" t="inlineStr"/>
+      <c r="EL67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>01/07/2026, 10:22:25</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>125</v>
+      </c>
+      <c r="D68" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>408</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>408</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>1782874800</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1782912030</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>01/07/2026 10:20</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W68" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:36</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>02/07/2026 09:37</t>
+        </is>
+      </c>
+      <c r="Z68" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE68" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="inlineStr"/>
+      <c r="AK68" t="inlineStr"/>
+      <c r="AL68" t="inlineStr"/>
+      <c r="AM68" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AN68" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT68" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU68" t="inlineStr"/>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE68" t="inlineStr"/>
+      <c r="BF68" t="inlineStr">
+        <is>
+          <t>[ ] Celular</t>
+        </is>
+      </c>
+      <c r="BG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH68" t="inlineStr"/>
+      <c r="BI68" t="inlineStr">
+        <is>
+          <t>[x] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ68" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BK68" t="inlineStr"/>
+      <c r="BL68" t="inlineStr">
+        <is>
+          <t>[x] Mouse</t>
+        </is>
+      </c>
+      <c r="BM68" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN68" t="inlineStr"/>
+      <c r="BO68" t="inlineStr">
+        <is>
+          <t>[ ] Fone</t>
+        </is>
+      </c>
+      <c r="BP68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ68" t="inlineStr"/>
+      <c r="BR68" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT68" t="inlineStr"/>
+      <c r="BU68" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV68" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW68" t="inlineStr"/>
+      <c r="BX68" t="inlineStr">
+        <is>
+          <t>[ ] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY68" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ68" t="inlineStr"/>
+      <c r="CA68" t="inlineStr">
+        <is>
+          <t>[ ] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB68" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC68" t="inlineStr"/>
+      <c r="CD68" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF68" t="inlineStr"/>
+      <c r="CG68" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI68" t="inlineStr"/>
+      <c r="CJ68" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL68" t="inlineStr"/>
+      <c r="CM68" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO68" t="inlineStr"/>
+      <c r="CP68" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR68" t="inlineStr"/>
+      <c r="CS68" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU68" t="inlineStr"/>
+      <c r="CV68" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW68" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX68" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY68" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ68" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA68" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB68" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC68" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD68" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE68" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF68" t="inlineStr"/>
+      <c r="DG68" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH68" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI68" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ68" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK68" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL68" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM68" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN68" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO68" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP68" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ68" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR68" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS68" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT68" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU68" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV68" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW68" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX68" t="inlineStr"/>
+      <c r="DY68" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ68" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA68" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB68" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC68" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED68" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE68" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF68" t="inlineStr"/>
+      <c r="EG68" t="inlineStr"/>
+      <c r="EH68" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI68" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ68" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK68" t="inlineStr"/>
+      <c r="EL68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>01/07/2026, 10:23:49</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>137</v>
+      </c>
+      <c r="D69" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>22823</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>408</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>408</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>1782874800</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1782912114</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>01/07/2026 10:21</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:42</t>
+        </is>
+      </c>
+      <c r="W69" t="n">
+        <v>22823</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:46</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>02/07/2026 09:47</t>
+        </is>
+      </c>
+      <c r="Z69" t="n">
+        <v>131450</v>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>363</v>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>Karolina Navarro</t>
+        </is>
+      </c>
+      <c r="AE69" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="inlineStr"/>
+      <c r="AK69" t="inlineStr"/>
+      <c r="AL69" t="inlineStr"/>
+      <c r="AM69" t="n">
+        <v>131450</v>
+      </c>
+      <c r="AN69" t="inlineStr">
+        <is>
+          <t>Karolina Navarro</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>karolina.navarro@arantesarimura.adv.br</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>Arantes Arimura Advocacia</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>Arantes Arimura Advocacia</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT69" t="n">
+        <v>5600</v>
+      </c>
+      <c r="AU69" t="inlineStr"/>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Arantes Arimura Advocacia</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Arantes Arimura Advocacia</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Raphaella Arantes (Arantes)</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>Raphaella Arantes  (Arantes)</t>
+        </is>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>raphaella@arantesarimura.adv.br</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>raphaella@arantesarimura.adv.br</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE69" t="inlineStr"/>
+      <c r="BF69" t="inlineStr">
+        <is>
+          <t>[x] Celular</t>
+        </is>
+      </c>
+      <c r="BG69" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BH69" t="inlineStr"/>
+      <c r="BI69" t="inlineStr">
+        <is>
+          <t>[x] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ69" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BK69" t="inlineStr"/>
+      <c r="BL69" t="inlineStr">
+        <is>
+          <t>[x] Mouse</t>
+        </is>
+      </c>
+      <c r="BM69" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN69" t="inlineStr"/>
+      <c r="BO69" t="inlineStr">
+        <is>
+          <t>[ ] Fone</t>
+        </is>
+      </c>
+      <c r="BP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ69" t="inlineStr"/>
+      <c r="BR69" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT69" t="inlineStr"/>
+      <c r="BU69" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV69" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW69" t="inlineStr"/>
+      <c r="BX69" t="inlineStr">
+        <is>
+          <t>[x] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY69" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BZ69" t="inlineStr"/>
+      <c r="CA69" t="inlineStr">
+        <is>
+          <t>[x] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB69" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="CC69" t="inlineStr"/>
+      <c r="CD69" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF69" t="inlineStr"/>
+      <c r="CG69" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI69" t="inlineStr"/>
+      <c r="CJ69" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL69" t="inlineStr"/>
+      <c r="CM69" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO69" t="inlineStr"/>
+      <c r="CP69" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR69" t="inlineStr"/>
+      <c r="CS69" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU69" t="inlineStr"/>
+      <c r="CV69" t="inlineStr">
+        <is>
+          <t>Raul Augusto de Paula</t>
+        </is>
+      </c>
+      <c r="CW69" t="inlineStr">
+        <is>
+          <t>21/06/1984</t>
+        </is>
+      </c>
+      <c r="CX69" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY69" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ69" t="inlineStr">
+        <is>
+          <t>Diego Ian Sérgio de Paula</t>
+        </is>
+      </c>
+      <c r="DA69" t="inlineStr">
+        <is>
+          <t>Giovana Isabel Rosângela</t>
+        </is>
+      </c>
+      <c r="DB69" t="inlineStr">
+        <is>
+          <t>Giovana Isabel Rosângela</t>
+        </is>
+      </c>
+      <c r="DC69" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="DD69" t="inlineStr">
+        <is>
+          <t>Mãe</t>
+        </is>
+      </c>
+      <c r="DE69" t="n">
+        <v>132546</v>
+      </c>
+      <c r="DF69" t="inlineStr"/>
+      <c r="DG69" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH69" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ69" t="n">
+        <v>480480916</v>
+      </c>
+      <c r="DK69" t="inlineStr">
+        <is>
+          <t>838.824.227-00</t>
+        </is>
+      </c>
+      <c r="DL69" t="inlineStr">
+        <is>
+          <t>raulaugustodepaula@vinax.com.br</t>
+        </is>
+      </c>
+      <c r="DM69" t="n">
+        <v>13234567</v>
+      </c>
+      <c r="DN69" t="inlineStr"/>
+      <c r="DO69" t="inlineStr">
+        <is>
+          <t>Bradesco</t>
+        </is>
+      </c>
+      <c r="DP69" t="inlineStr">
+        <is>
+          <t>Conta Poupança</t>
+        </is>
+      </c>
+      <c r="DQ69" t="inlineStr">
+        <is>
+          <t>Conta Poupança</t>
+        </is>
+      </c>
+      <c r="DR69" t="n">
+        <v>4675</v>
+      </c>
+      <c r="DS69" t="n">
+        <v>324401</v>
+      </c>
+      <c r="DT69" t="inlineStr">
+        <is>
+          <t>raulaugustodepaula@vinax.com.br</t>
+        </is>
+      </c>
+      <c r="DU69" t="inlineStr">
+        <is>
+          <t>wrw34</t>
+        </is>
+      </c>
+      <c r="DV69" t="inlineStr">
+        <is>
+          <t>Rua Joaquim da Rocha</t>
+        </is>
+      </c>
+      <c r="DW69" t="n">
+        <v>665</v>
+      </c>
+      <c r="DX69" t="inlineStr"/>
+      <c r="DY69" t="inlineStr">
+        <is>
+          <t>76811-348</t>
+        </is>
+      </c>
+      <c r="DZ69" t="inlineStr">
+        <is>
+          <t>Castanheira</t>
+        </is>
+      </c>
+      <c r="EA69" t="inlineStr">
+        <is>
+          <t>Porto Velho</t>
+        </is>
+      </c>
+      <c r="EB69" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC69" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED69" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="EE69" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF69" t="inlineStr"/>
+      <c r="EG69" t="inlineStr"/>
+      <c r="EH69" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:46:48}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Karolina Navarro - {{2026-07-01 09:46:27}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:46:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;sasas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:43:57}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;sasa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Karolina Navarro - {{2026-07-01 09:43:38}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;asas &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI69" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ69" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK69" t="inlineStr"/>
+      <c r="EL69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>01/07/2026, 10:23:58</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br//triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>131</v>
+      </c>
+      <c r="D70" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>22821</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>408</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>408</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>1782874800</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1782912123</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>01/07/2026 10:22</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:37</t>
+        </is>
+      </c>
+      <c r="W70" t="n">
+        <v>22821</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:42</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>02/07/2026 09:43</t>
+        </is>
+      </c>
+      <c r="Z70" t="n">
+        <v>131443</v>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>532</v>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>Luana Lidia</t>
+        </is>
+      </c>
+      <c r="AE70" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="inlineStr"/>
+      <c r="AK70" t="inlineStr"/>
+      <c r="AL70" t="inlineStr"/>
+      <c r="AM70" t="n">
+        <v>131443</v>
+      </c>
+      <c r="AN70" t="inlineStr">
+        <is>
+          <t>Luana Lidia</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>luana.lidia@genter.com.br</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>Genter</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>Genter</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT70" t="n">
+        <v>8900</v>
+      </c>
+      <c r="AU70" t="inlineStr"/>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>Comercial</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Genter</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Genter</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Jeferson Arimura (Genter)</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>Jeferson Arimura (Genter)</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>jeferson.arimura@genter.com.br</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>jeferson.arimura@genter.com.br</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE70" t="inlineStr"/>
+      <c r="BF70" t="inlineStr">
+        <is>
+          <t>[x] Celular</t>
+        </is>
+      </c>
+      <c r="BG70" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BH70" t="inlineStr"/>
+      <c r="BI70" t="inlineStr">
+        <is>
+          <t>[x] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ70" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BK70" t="inlineStr"/>
+      <c r="BL70" t="inlineStr">
+        <is>
+          <t>[x] Mouse</t>
+        </is>
+      </c>
+      <c r="BM70" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN70" t="inlineStr"/>
+      <c r="BO70" t="inlineStr">
+        <is>
+          <t>[x] Fone</t>
+        </is>
+      </c>
+      <c r="BP70" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BQ70" t="inlineStr"/>
+      <c r="BR70" t="inlineStr">
+        <is>
+          <t>[x] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS70" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BT70" t="inlineStr"/>
+      <c r="BU70" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV70" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW70" t="inlineStr"/>
+      <c r="BX70" t="inlineStr">
+        <is>
+          <t>[ ] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY70" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ70" t="inlineStr"/>
+      <c r="CA70" t="inlineStr">
+        <is>
+          <t>[x] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB70" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="CC70" t="inlineStr"/>
+      <c r="CD70" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF70" t="inlineStr"/>
+      <c r="CG70" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI70" t="inlineStr"/>
+      <c r="CJ70" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL70" t="inlineStr"/>
+      <c r="CM70" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO70" t="inlineStr"/>
+      <c r="CP70" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR70" t="inlineStr"/>
+      <c r="CS70" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU70" t="inlineStr"/>
+      <c r="CV70" t="inlineStr">
+        <is>
+          <t>Brenda Tatiane Carolina da Rocha</t>
+        </is>
+      </c>
+      <c r="CW70" t="inlineStr">
+        <is>
+          <t>06/05/1951</t>
+        </is>
+      </c>
+      <c r="CX70" t="inlineStr">
+        <is>
+          <t>Casado</t>
+        </is>
+      </c>
+      <c r="CY70" t="inlineStr">
+        <is>
+          <t>Casado</t>
+        </is>
+      </c>
+      <c r="CZ70" t="inlineStr">
+        <is>
+          <t>Tiago Igor Thomas da Rocha</t>
+        </is>
+      </c>
+      <c r="DA70" t="inlineStr">
+        <is>
+          <t>Isabella Isabelle Sara</t>
+        </is>
+      </c>
+      <c r="DB70" t="inlineStr">
+        <is>
+          <t>tomas neves</t>
+        </is>
+      </c>
+      <c r="DC70" t="inlineStr">
+        <is>
+          <t>Esposo(a)</t>
+        </is>
+      </c>
+      <c r="DD70" t="inlineStr">
+        <is>
+          <t>Esposo(a)</t>
+        </is>
+      </c>
+      <c r="DE70" t="n">
+        <v>645645</v>
+      </c>
+      <c r="DF70" t="inlineStr"/>
+      <c r="DG70" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH70" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ70" t="n">
+        <v>314452163</v>
+      </c>
+      <c r="DK70" t="inlineStr">
+        <is>
+          <t>149.339.407-03</t>
+        </is>
+      </c>
+      <c r="DL70" t="inlineStr">
+        <is>
+          <t>brenda_darocha@mv1.com.br</t>
+        </is>
+      </c>
+      <c r="DM70" t="n">
+        <v>4655656</v>
+      </c>
+      <c r="DN70" t="inlineStr">
+        <is>
+          <t>59.988.037/0001-12</t>
+        </is>
+      </c>
+      <c r="DO70" t="inlineStr">
+        <is>
+          <t>Itau</t>
+        </is>
+      </c>
+      <c r="DP70" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ70" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR70" t="n">
+        <v>4257</v>
+      </c>
+      <c r="DS70" t="n">
+        <v>177347</v>
+      </c>
+      <c r="DT70" t="inlineStr">
+        <is>
+          <t>brenda_darocha@mv1.com.br</t>
+        </is>
+      </c>
+      <c r="DU70" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="DV70" t="inlineStr">
+        <is>
+          <t>Travessa Limoeiro</t>
+        </is>
+      </c>
+      <c r="DW70" t="inlineStr"/>
+      <c r="DX70" t="inlineStr"/>
+      <c r="DY70" t="inlineStr">
+        <is>
+          <t>42801-100</t>
+        </is>
+      </c>
+      <c r="DZ70" t="inlineStr">
+        <is>
+          <t>Ponto Certo</t>
+        </is>
+      </c>
+      <c r="EA70" t="inlineStr">
+        <is>
+          <t>Camaçari</t>
+        </is>
+      </c>
+      <c r="EB70" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC70" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED70" t="inlineStr">
+        <is>
+          <t>relacoes publicas</t>
+        </is>
+      </c>
+      <c r="EE70" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF70" t="inlineStr"/>
+      <c r="EG70" t="inlineStr"/>
+      <c r="EH70" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:42:31}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;Luana Lidia - {{2026-07-01 09:42:13}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;sas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:41:56}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;sasas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:38:40}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;Luana Lidia - {{2026-07-01 09:38:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI70" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ70" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK70" t="inlineStr"/>
+      <c r="EL70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>01/07/2026, 10:25:10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>125</v>
+      </c>
+      <c r="D71" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>408</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>408</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>1782874800</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1782912195</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>01/07/2026 10:23</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W71" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:36</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>02/07/2026 09:37</t>
+        </is>
+      </c>
+      <c r="Z71" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE71" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="inlineStr"/>
+      <c r="AK71" t="inlineStr"/>
+      <c r="AL71" t="inlineStr"/>
+      <c r="AM71" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AN71" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT71" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU71" t="inlineStr"/>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE71" t="inlineStr"/>
+      <c r="BF71" t="inlineStr">
+        <is>
+          <t>[ ] Celular</t>
+        </is>
+      </c>
+      <c r="BG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH71" t="inlineStr"/>
+      <c r="BI71" t="inlineStr">
+        <is>
+          <t>[x] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ71" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BK71" t="inlineStr"/>
+      <c r="BL71" t="inlineStr">
+        <is>
+          <t>[x] Mouse</t>
+        </is>
+      </c>
+      <c r="BM71" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN71" t="inlineStr"/>
+      <c r="BO71" t="inlineStr">
+        <is>
+          <t>[ ] Fone</t>
+        </is>
+      </c>
+      <c r="BP71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ71" t="inlineStr"/>
+      <c r="BR71" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT71" t="inlineStr"/>
+      <c r="BU71" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV71" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW71" t="inlineStr"/>
+      <c r="BX71" t="inlineStr">
+        <is>
+          <t>[ ] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY71" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ71" t="inlineStr"/>
+      <c r="CA71" t="inlineStr">
+        <is>
+          <t>[ ] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB71" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC71" t="inlineStr"/>
+      <c r="CD71" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF71" t="inlineStr"/>
+      <c r="CG71" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI71" t="inlineStr"/>
+      <c r="CJ71" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL71" t="inlineStr"/>
+      <c r="CM71" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO71" t="inlineStr"/>
+      <c r="CP71" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR71" t="inlineStr"/>
+      <c r="CS71" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU71" t="inlineStr"/>
+      <c r="CV71" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW71" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX71" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY71" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ71" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA71" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB71" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC71" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD71" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE71" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF71" t="inlineStr"/>
+      <c r="DG71" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH71" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ71" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK71" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL71" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM71" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN71" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO71" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP71" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ71" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR71" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS71" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT71" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU71" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV71" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW71" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX71" t="inlineStr"/>
+      <c r="DY71" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ71" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA71" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB71" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC71" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED71" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE71" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF71" t="inlineStr"/>
+      <c r="EG71" t="inlineStr"/>
+      <c r="EH71" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI71" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ71" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK71" t="inlineStr"/>
+      <c r="EL71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>01/07/2026, 10:29:38</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>125</v>
+      </c>
+      <c r="D72" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>408</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>408</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>1782874800</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1782912463</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>01/07/2026 10:27</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W72" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:36</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>02/07/2026 09:37</t>
+        </is>
+      </c>
+      <c r="Z72" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE72" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="inlineStr"/>
+      <c r="AK72" t="inlineStr"/>
+      <c r="AL72" t="inlineStr"/>
+      <c r="AM72" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AN72" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT72" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU72" t="inlineStr"/>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE72" t="inlineStr"/>
+      <c r="BF72" t="inlineStr">
+        <is>
+          <t>[ ] Celular</t>
+        </is>
+      </c>
+      <c r="BG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH72" t="inlineStr"/>
+      <c r="BI72" t="inlineStr">
+        <is>
+          <t>[x] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ72" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BK72" t="inlineStr"/>
+      <c r="BL72" t="inlineStr">
+        <is>
+          <t>[x] Mouse</t>
+        </is>
+      </c>
+      <c r="BM72" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN72" t="inlineStr"/>
+      <c r="BO72" t="inlineStr">
+        <is>
+          <t>[ ] Fone</t>
+        </is>
+      </c>
+      <c r="BP72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ72" t="inlineStr"/>
+      <c r="BR72" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT72" t="inlineStr"/>
+      <c r="BU72" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV72" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW72" t="inlineStr"/>
+      <c r="BX72" t="inlineStr">
+        <is>
+          <t>[ ] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY72" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ72" t="inlineStr"/>
+      <c r="CA72" t="inlineStr">
+        <is>
+          <t>[ ] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB72" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC72" t="inlineStr"/>
+      <c r="CD72" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF72" t="inlineStr"/>
+      <c r="CG72" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI72" t="inlineStr"/>
+      <c r="CJ72" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL72" t="inlineStr"/>
+      <c r="CM72" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO72" t="inlineStr"/>
+      <c r="CP72" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR72" t="inlineStr"/>
+      <c r="CS72" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU72" t="inlineStr"/>
+      <c r="CV72" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW72" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX72" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY72" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ72" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA72" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB72" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC72" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD72" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE72" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF72" t="inlineStr"/>
+      <c r="DG72" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH72" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ72" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK72" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL72" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM72" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN72" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO72" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP72" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ72" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR72" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS72" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT72" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU72" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV72" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW72" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX72" t="inlineStr"/>
+      <c r="DY72" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ72" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA72" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB72" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC72" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED72" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE72" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF72" t="inlineStr"/>
+      <c r="EG72" t="inlineStr"/>
+      <c r="EH72" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI72" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ72" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK72" t="inlineStr"/>
+      <c r="EL72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>01/07/2026, 10:30:59</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>125</v>
+      </c>
+      <c r="D73" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>408</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>408</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>1782874800</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1782912544</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>01/07/2026 10:29</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W73" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:36</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>02/07/2026 09:37</t>
+        </is>
+      </c>
+      <c r="Z73" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE73" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AN73" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT73" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU73" t="inlineStr"/>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE73" t="inlineStr"/>
+      <c r="BF73" t="inlineStr">
+        <is>
+          <t>[ ] Celular</t>
+        </is>
+      </c>
+      <c r="BG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH73" t="inlineStr"/>
+      <c r="BI73" t="inlineStr">
+        <is>
+          <t>[x] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ73" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BK73" t="inlineStr"/>
+      <c r="BL73" t="inlineStr">
+        <is>
+          <t>[x] Mouse</t>
+        </is>
+      </c>
+      <c r="BM73" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN73" t="inlineStr"/>
+      <c r="BO73" t="inlineStr">
+        <is>
+          <t>[ ] Fone</t>
+        </is>
+      </c>
+      <c r="BP73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ73" t="inlineStr"/>
+      <c r="BR73" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT73" t="inlineStr"/>
+      <c r="BU73" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV73" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW73" t="inlineStr"/>
+      <c r="BX73" t="inlineStr">
+        <is>
+          <t>[ ] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY73" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ73" t="inlineStr"/>
+      <c r="CA73" t="inlineStr">
+        <is>
+          <t>[ ] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB73" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC73" t="inlineStr"/>
+      <c r="CD73" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF73" t="inlineStr"/>
+      <c r="CG73" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI73" t="inlineStr"/>
+      <c r="CJ73" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL73" t="inlineStr"/>
+      <c r="CM73" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO73" t="inlineStr"/>
+      <c r="CP73" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR73" t="inlineStr"/>
+      <c r="CS73" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT73" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU73" t="inlineStr"/>
+      <c r="CV73" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW73" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX73" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY73" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ73" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA73" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB73" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC73" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD73" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE73" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF73" t="inlineStr"/>
+      <c r="DG73" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH73" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI73" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ73" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK73" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL73" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM73" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN73" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO73" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP73" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ73" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR73" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS73" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT73" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU73" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV73" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW73" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX73" t="inlineStr"/>
+      <c r="DY73" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ73" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA73" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB73" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC73" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED73" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE73" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF73" t="inlineStr"/>
+      <c r="EG73" t="inlineStr"/>
+      <c r="EH73" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI73" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ73" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK73" t="inlineStr"/>
+      <c r="EL73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>01/07/2026, 10:47:07</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>125</v>
+      </c>
+      <c r="D74" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>408</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
+        <v>408</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>1782874800</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1782913512</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>01/07/2026 10:45</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W74" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:36</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>02/07/2026 09:37</t>
+        </is>
+      </c>
+      <c r="Z74" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE74" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr"/>
+      <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AN74" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT74" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU74" t="inlineStr"/>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE74" t="inlineStr"/>
+      <c r="BF74" t="inlineStr">
+        <is>
+          <t>[ ] Celular</t>
+        </is>
+      </c>
+      <c r="BG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH74" t="inlineStr"/>
+      <c r="BI74" t="inlineStr">
+        <is>
+          <t>[x] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ74" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BK74" t="inlineStr"/>
+      <c r="BL74" t="inlineStr">
+        <is>
+          <t>[x] Mouse</t>
+        </is>
+      </c>
+      <c r="BM74" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN74" t="inlineStr"/>
+      <c r="BO74" t="inlineStr">
+        <is>
+          <t>[ ] Fone</t>
+        </is>
+      </c>
+      <c r="BP74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ74" t="inlineStr"/>
+      <c r="BR74" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT74" t="inlineStr"/>
+      <c r="BU74" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV74" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW74" t="inlineStr"/>
+      <c r="BX74" t="inlineStr">
+        <is>
+          <t>[ ] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY74" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ74" t="inlineStr"/>
+      <c r="CA74" t="inlineStr">
+        <is>
+          <t>[ ] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB74" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC74" t="inlineStr"/>
+      <c r="CD74" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF74" t="inlineStr"/>
+      <c r="CG74" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI74" t="inlineStr"/>
+      <c r="CJ74" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL74" t="inlineStr"/>
+      <c r="CM74" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO74" t="inlineStr"/>
+      <c r="CP74" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR74" t="inlineStr"/>
+      <c r="CS74" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT74" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU74" t="inlineStr"/>
+      <c r="CV74" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW74" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX74" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY74" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ74" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA74" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB74" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC74" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD74" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE74" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF74" t="inlineStr"/>
+      <c r="DG74" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH74" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI74" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ74" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK74" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL74" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM74" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN74" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO74" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP74" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ74" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR74" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS74" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT74" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU74" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV74" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW74" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX74" t="inlineStr"/>
+      <c r="DY74" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ74" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA74" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB74" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC74" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED74" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE74" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF74" t="inlineStr"/>
+      <c r="EG74" t="inlineStr"/>
+      <c r="EH74" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI74" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ74" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK74" t="inlineStr"/>
+      <c r="EL74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>01/07/2026, 11:00:51</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>125</v>
+      </c>
+      <c r="D75" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>408</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>408</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>1782874800</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1782914335</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>01/07/2026 10:58</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W75" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:36</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>02/07/2026 09:37</t>
+        </is>
+      </c>
+      <c r="Z75" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE75" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr"/>
+      <c r="AL75" t="inlineStr"/>
+      <c r="AM75" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AN75" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT75" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU75" t="inlineStr"/>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE75" t="inlineStr"/>
+      <c r="BF75" t="inlineStr">
+        <is>
+          <t>[ ] Celular</t>
+        </is>
+      </c>
+      <c r="BG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH75" t="inlineStr"/>
+      <c r="BI75" t="inlineStr">
+        <is>
+          <t>[x] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ75" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BK75" t="inlineStr"/>
+      <c r="BL75" t="inlineStr">
+        <is>
+          <t>[x] Mouse</t>
+        </is>
+      </c>
+      <c r="BM75" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN75" t="inlineStr"/>
+      <c r="BO75" t="inlineStr">
+        <is>
+          <t>[ ] Fone</t>
+        </is>
+      </c>
+      <c r="BP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ75" t="inlineStr"/>
+      <c r="BR75" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT75" t="inlineStr"/>
+      <c r="BU75" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV75" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW75" t="inlineStr"/>
+      <c r="BX75" t="inlineStr">
+        <is>
+          <t>[ ] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY75" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ75" t="inlineStr"/>
+      <c r="CA75" t="inlineStr">
+        <is>
+          <t>[ ] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB75" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC75" t="inlineStr"/>
+      <c r="CD75" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF75" t="inlineStr"/>
+      <c r="CG75" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI75" t="inlineStr"/>
+      <c r="CJ75" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL75" t="inlineStr"/>
+      <c r="CM75" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO75" t="inlineStr"/>
+      <c r="CP75" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR75" t="inlineStr"/>
+      <c r="CS75" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU75" t="inlineStr"/>
+      <c r="CV75" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW75" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX75" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY75" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ75" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA75" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB75" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC75" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD75" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE75" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF75" t="inlineStr"/>
+      <c r="DG75" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH75" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ75" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK75" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL75" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM75" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN75" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO75" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP75" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ75" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR75" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS75" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT75" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU75" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV75" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW75" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX75" t="inlineStr"/>
+      <c r="DY75" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ75" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA75" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB75" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC75" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED75" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE75" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF75" t="inlineStr"/>
+      <c r="EG75" t="inlineStr"/>
+      <c r="EH75" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI75" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ75" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK75" t="inlineStr"/>
+      <c r="EL75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>01/07/2026, 11:08:02</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>125</v>
+      </c>
+      <c r="D76" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>408</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
+        <v>408</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>1782874800</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1782914767</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>01/07/2026 11:06</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W76" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:36</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>02/07/2026 09:37</t>
+        </is>
+      </c>
+      <c r="Z76" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE76" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr"/>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AN76" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP76" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ76" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT76" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU76" t="inlineStr"/>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE76" t="inlineStr"/>
+      <c r="BF76" t="inlineStr">
+        <is>
+          <t>[ ] Celular</t>
+        </is>
+      </c>
+      <c r="BG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH76" t="inlineStr"/>
+      <c r="BI76" t="inlineStr">
+        <is>
+          <t>[x] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ76" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BK76" t="inlineStr"/>
+      <c r="BL76" t="inlineStr">
+        <is>
+          <t>[x] Mouse</t>
+        </is>
+      </c>
+      <c r="BM76" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN76" t="inlineStr"/>
+      <c r="BO76" t="inlineStr">
+        <is>
+          <t>[ ] Fone</t>
+        </is>
+      </c>
+      <c r="BP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ76" t="inlineStr"/>
+      <c r="BR76" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT76" t="inlineStr"/>
+      <c r="BU76" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV76" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW76" t="inlineStr"/>
+      <c r="BX76" t="inlineStr">
+        <is>
+          <t>[ ] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY76" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ76" t="inlineStr"/>
+      <c r="CA76" t="inlineStr">
+        <is>
+          <t>[ ] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB76" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC76" t="inlineStr"/>
+      <c r="CD76" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF76" t="inlineStr"/>
+      <c r="CG76" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI76" t="inlineStr"/>
+      <c r="CJ76" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL76" t="inlineStr"/>
+      <c r="CM76" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO76" t="inlineStr"/>
+      <c r="CP76" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR76" t="inlineStr"/>
+      <c r="CS76" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU76" t="inlineStr"/>
+      <c r="CV76" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW76" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX76" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY76" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ76" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA76" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB76" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC76" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD76" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE76" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF76" t="inlineStr"/>
+      <c r="DG76" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH76" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI76" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ76" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK76" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL76" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM76" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN76" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO76" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP76" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ76" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR76" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS76" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT76" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU76" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV76" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW76" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX76" t="inlineStr"/>
+      <c r="DY76" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ76" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA76" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB76" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC76" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED76" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE76" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF76" t="inlineStr"/>
+      <c r="EG76" t="inlineStr"/>
+      <c r="EH76" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI76" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ76" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK76" t="inlineStr"/>
+      <c r="EL76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>01/07/2026, 11:28:21</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>125</v>
+      </c>
+      <c r="D77" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>408</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O77" t="n">
+        <v>408</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>1782874800</v>
+      </c>
+      <c r="R77" t="n">
+        <v>1782915986</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>01/07/2026 11:26</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W77" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:36</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>02/07/2026 09:37</t>
+        </is>
+      </c>
+      <c r="Z77" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE77" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr"/>
+      <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AN77" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT77" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU77" t="inlineStr"/>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE77" t="inlineStr"/>
+      <c r="BF77" t="inlineStr">
+        <is>
+          <t>[ ] Celular</t>
+        </is>
+      </c>
+      <c r="BG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH77" t="inlineStr"/>
+      <c r="BI77" t="inlineStr">
+        <is>
+          <t>[x] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ77" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BK77" t="inlineStr"/>
+      <c r="BL77" t="inlineStr">
+        <is>
+          <t>[x] Mouse</t>
+        </is>
+      </c>
+      <c r="BM77" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN77" t="inlineStr"/>
+      <c r="BO77" t="inlineStr">
+        <is>
+          <t>[ ] Fone</t>
+        </is>
+      </c>
+      <c r="BP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ77" t="inlineStr"/>
+      <c r="BR77" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT77" t="inlineStr"/>
+      <c r="BU77" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV77" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW77" t="inlineStr"/>
+      <c r="BX77" t="inlineStr">
+        <is>
+          <t>[ ] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY77" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ77" t="inlineStr"/>
+      <c r="CA77" t="inlineStr">
+        <is>
+          <t>[ ] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB77" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC77" t="inlineStr"/>
+      <c r="CD77" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF77" t="inlineStr"/>
+      <c r="CG77" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI77" t="inlineStr"/>
+      <c r="CJ77" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL77" t="inlineStr"/>
+      <c r="CM77" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO77" t="inlineStr"/>
+      <c r="CP77" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR77" t="inlineStr"/>
+      <c r="CS77" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU77" t="inlineStr"/>
+      <c r="CV77" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW77" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX77" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY77" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ77" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA77" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB77" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC77" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD77" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE77" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF77" t="inlineStr"/>
+      <c r="DG77" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH77" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI77" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ77" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK77" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL77" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM77" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN77" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO77" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP77" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ77" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR77" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS77" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT77" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU77" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV77" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW77" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX77" t="inlineStr"/>
+      <c r="DY77" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ77" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA77" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB77" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC77" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED77" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE77" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF77" t="inlineStr"/>
+      <c r="EG77" t="inlineStr"/>
+      <c r="EH77" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI77" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ77" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK77" t="inlineStr"/>
+      <c r="EL77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>01/07/2026, 11:43:34</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>125</v>
+      </c>
+      <c r="D78" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>408</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O78" t="n">
+        <v>408</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>1782874800</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1782916898</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>01/07/2026 11:41</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W78" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:36</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>02/07/2026 09:37</t>
+        </is>
+      </c>
+      <c r="Z78" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE78" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG78" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr"/>
+      <c r="AM78" t="n">
+        <v>131436</v>
+      </c>
+      <c r="AN78" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ78" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU78" t="inlineStr"/>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE78" t="inlineStr"/>
+      <c r="BF78" t="inlineStr">
+        <is>
+          <t>[ ] Celular</t>
+        </is>
+      </c>
+      <c r="BG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="BH78" t="inlineStr"/>
+      <c r="BI78" t="inlineStr">
+        <is>
+          <t>[x] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ78" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BK78" t="inlineStr"/>
+      <c r="BL78" t="inlineStr">
+        <is>
+          <t>[x] Mouse</t>
+        </is>
+      </c>
+      <c r="BM78" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BN78" t="inlineStr"/>
+      <c r="BO78" t="inlineStr">
+        <is>
+          <t>[ ] Fone</t>
+        </is>
+      </c>
+      <c r="BP78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ78" t="inlineStr"/>
+      <c r="BR78" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT78" t="inlineStr"/>
+      <c r="BU78" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV78" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW78" t="inlineStr"/>
+      <c r="BX78" t="inlineStr">
+        <is>
+          <t>[ ] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY78" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ78" t="inlineStr"/>
+      <c r="CA78" t="inlineStr">
+        <is>
+          <t>[ ] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB78" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC78" t="inlineStr"/>
+      <c r="CD78" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF78" t="inlineStr"/>
+      <c r="CG78" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI78" t="inlineStr"/>
+      <c r="CJ78" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL78" t="inlineStr"/>
+      <c r="CM78" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO78" t="inlineStr"/>
+      <c r="CP78" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR78" t="inlineStr"/>
+      <c r="CS78" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU78" t="inlineStr"/>
+      <c r="CV78" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW78" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX78" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY78" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ78" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA78" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB78" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC78" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD78" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE78" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF78" t="inlineStr"/>
+      <c r="DG78" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH78" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI78" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ78" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK78" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL78" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM78" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN78" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO78" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP78" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ78" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR78" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS78" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT78" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU78" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV78" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW78" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX78" t="inlineStr"/>
+      <c r="DY78" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ78" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA78" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB78" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC78" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED78" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE78" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF78" t="inlineStr"/>
+      <c r="EG78" t="inlineStr"/>
+      <c r="EH78" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI78" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ78" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK78" t="inlineStr"/>
+      <c r="EL78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>01/07/2026, 12:02:38</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>144</v>
+      </c>
+      <c r="D79" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>22837</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>408</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O79" t="n">
+        <v>408</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>1782874800</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1782918042</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>01/07/2026 12:00</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>01/07/2026 11:52</t>
+        </is>
+      </c>
+      <c r="W79" t="n">
+        <v>22837</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>01/07/2026 11:56</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:57</t>
+        </is>
+      </c>
+      <c r="Z79" t="n">
+        <v>131521</v>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE79" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG79" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr"/>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="n">
+        <v>131521</v>
+      </c>
+      <c r="AN79" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ79" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT79" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AU79" t="inlineStr"/>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB79" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC79" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE79" t="inlineStr"/>
+      <c r="BF79" t="inlineStr">
+        <is>
+          <t>[x] Celular</t>
+        </is>
+      </c>
+      <c r="BG79" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BH79" t="inlineStr"/>
+      <c r="BI79" t="inlineStr">
+        <is>
+          <t>[ ] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ79" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK79" t="inlineStr"/>
+      <c r="BL79" t="inlineStr">
+        <is>
+          <t>[ ] Mouse</t>
+        </is>
+      </c>
+      <c r="BM79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN79" t="inlineStr"/>
+      <c r="BO79" t="inlineStr">
+        <is>
+          <t>[ ] Fone</t>
+        </is>
+      </c>
+      <c r="BP79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ79" t="inlineStr"/>
+      <c r="BR79" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT79" t="inlineStr"/>
+      <c r="BU79" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV79" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW79" t="inlineStr"/>
+      <c r="BX79" t="inlineStr">
+        <is>
+          <t>[ ] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY79" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ79" t="inlineStr"/>
+      <c r="CA79" t="inlineStr">
+        <is>
+          <t>[ ] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB79" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC79" t="inlineStr"/>
+      <c r="CD79" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF79" t="inlineStr"/>
+      <c r="CG79" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI79" t="inlineStr"/>
+      <c r="CJ79" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL79" t="inlineStr"/>
+      <c r="CM79" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO79" t="inlineStr"/>
+      <c r="CP79" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR79" t="inlineStr"/>
+      <c r="CS79" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU79" t="inlineStr"/>
+      <c r="CV79" t="inlineStr">
+        <is>
+          <t>jaoa tomas</t>
+        </is>
+      </c>
+      <c r="CW79" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX79" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY79" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ79" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="DA79" t="inlineStr">
+        <is>
+          <t>maria santana</t>
+        </is>
+      </c>
+      <c r="DB79" t="inlineStr">
+        <is>
+          <t>kaka</t>
+        </is>
+      </c>
+      <c r="DC79" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD79" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE79" t="n">
+        <v>222124</v>
+      </c>
+      <c r="DF79" t="inlineStr"/>
+      <c r="DG79" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH79" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI79" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ79" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK79" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL79" t="inlineStr">
+        <is>
+          <t>nicolas.ryan.rezende@murosterrae.com.br</t>
+        </is>
+      </c>
+      <c r="DM79" t="n">
+        <v>323424</v>
+      </c>
+      <c r="DN79" t="inlineStr"/>
+      <c r="DO79" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP79" t="inlineStr">
+        <is>
+          <t>Conta Internacional</t>
+        </is>
+      </c>
+      <c r="DQ79" t="inlineStr">
+        <is>
+          <t>Conta Internacional</t>
+        </is>
+      </c>
+      <c r="DR79" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS79" t="n">
+        <v>324401</v>
+      </c>
+      <c r="DT79" t="inlineStr">
+        <is>
+          <t>nicolas.ryan.rezende@murosterrae.com.br</t>
+        </is>
+      </c>
+      <c r="DU79" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV79" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW79" t="inlineStr"/>
+      <c r="DX79" t="inlineStr"/>
+      <c r="DY79" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ79" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA79" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB79" t="inlineStr">
+        <is>
+          <t>Pós graduado(a)</t>
+        </is>
+      </c>
+      <c r="EC79" t="inlineStr">
+        <is>
+          <t>Pós graduado(a)</t>
+        </is>
+      </c>
+      <c r="ED79" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE79" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr"/>
+      <c r="EG79" t="inlineStr"/>
+      <c r="EH79" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 11:56:41}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;asas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 11:55:55}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 11:55:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;sasasa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 11:53:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;sassas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 11:52:53}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;a &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI79" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ79" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK79" t="inlineStr"/>
+      <c r="EL79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>01/07/2026, 12:06:37</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>0121000</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>01210000013</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>22837</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1782874800</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1782918281</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>01/07/2026 12:04</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>01/07/2026 11:52</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>22837</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>01/07/2026 11:56</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:57</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>131521</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG80" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>131521</t>
+        </is>
+      </c>
+      <c r="AN80" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP80" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr">
+        <is>
+          <t>1200.00</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr"/>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB80" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC80" t="inlineStr">
+        <is>
+          <t>[x] Notebook</t>
+        </is>
+      </c>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BE80" t="inlineStr"/>
+      <c r="BF80" t="inlineStr">
+        <is>
+          <t>[x] Celular</t>
+        </is>
+      </c>
+      <c r="BG80" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BH80" t="inlineStr"/>
+      <c r="BI80" t="inlineStr">
+        <is>
+          <t>[ ] Teclado</t>
+        </is>
+      </c>
+      <c r="BJ80" t="b">
+        <v>0</v>
+      </c>
+      <c r="BK80" t="inlineStr"/>
+      <c r="BL80" t="inlineStr">
+        <is>
+          <t>[ ] Mouse</t>
+        </is>
+      </c>
+      <c r="BM80" t="b">
+        <v>0</v>
+      </c>
+      <c r="BN80" t="inlineStr"/>
+      <c r="BO80" t="inlineStr">
+        <is>
+          <t>[ ] Fone</t>
+        </is>
+      </c>
+      <c r="BP80" t="b">
+        <v>0</v>
+      </c>
+      <c r="BQ80" t="inlineStr"/>
+      <c r="BR80" t="inlineStr">
+        <is>
+          <t>[ ] Linha móvel</t>
+        </is>
+      </c>
+      <c r="BS80" t="b">
+        <v>0</v>
+      </c>
+      <c r="BT80" t="inlineStr"/>
+      <c r="BU80" t="inlineStr">
+        <is>
+          <t>[x] 365</t>
+        </is>
+      </c>
+      <c r="BV80" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="BW80" t="inlineStr"/>
+      <c r="BX80" t="inlineStr">
+        <is>
+          <t>[ ] LegalOne</t>
+        </is>
+      </c>
+      <c r="BY80" t="b">
+        <v>0</v>
+      </c>
+      <c r="BZ80" t="inlineStr"/>
+      <c r="CA80" t="inlineStr">
+        <is>
+          <t>[ ] MKTZap</t>
+        </is>
+      </c>
+      <c r="CB80" t="b">
+        <v>0</v>
+      </c>
+      <c r="CC80" t="inlineStr"/>
+      <c r="CD80" t="inlineStr">
+        <is>
+          <t>[ ] WorkFlow</t>
+        </is>
+      </c>
+      <c r="CE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF80" t="inlineStr"/>
+      <c r="CG80" t="inlineStr">
+        <is>
+          <t>[ ] Doc9/Whom</t>
+        </is>
+      </c>
+      <c r="CH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI80" t="inlineStr"/>
+      <c r="CJ80" t="inlineStr">
+        <is>
+          <t>[ ] Dominio</t>
+        </is>
+      </c>
+      <c r="CK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL80" t="inlineStr"/>
+      <c r="CM80" t="inlineStr">
+        <is>
+          <t>[ ] RD Station</t>
+        </is>
+      </c>
+      <c r="CN80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO80" t="inlineStr"/>
+      <c r="CP80" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - PowerBI</t>
+        </is>
+      </c>
+      <c r="CQ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR80" t="inlineStr"/>
+      <c r="CS80" t="inlineStr">
+        <is>
+          <t>[ ] Adicional - Power Automate</t>
+        </is>
+      </c>
+      <c r="CT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU80" t="inlineStr"/>
+      <c r="CV80" t="inlineStr">
+        <is>
+          <t>jaoa tomas</t>
+        </is>
+      </c>
+      <c r="CW80" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX80" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY80" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ80" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="DA80" t="inlineStr">
+        <is>
+          <t>maria santana</t>
+        </is>
+      </c>
+      <c r="DB80" t="inlineStr">
+        <is>
+          <t>kaka</t>
+        </is>
+      </c>
+      <c r="DC80" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD80" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE80" t="inlineStr">
+        <is>
+          <t>222124</t>
+        </is>
+      </c>
+      <c r="DF80" t="inlineStr"/>
+      <c r="DG80" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH80" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DJ80" t="inlineStr">
+        <is>
+          <t>12344</t>
+        </is>
+      </c>
+      <c r="DK80" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL80" t="inlineStr">
+        <is>
+          <t>nicolas.ryan.rezende@murosterrae.com.br</t>
+        </is>
+      </c>
+      <c r="DM80" t="inlineStr">
+        <is>
+          <t>323424</t>
+        </is>
+      </c>
+      <c r="DN80" t="inlineStr"/>
+      <c r="DO80" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP80" t="inlineStr">
+        <is>
+          <t>Conta Internacional</t>
+        </is>
+      </c>
+      <c r="DQ80" t="inlineStr">
+        <is>
+          <t>Conta Internacional</t>
+        </is>
+      </c>
+      <c r="DR80" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+      <c r="DS80" t="inlineStr">
+        <is>
+          <t>324401</t>
+        </is>
+      </c>
+      <c r="DT80" t="inlineStr">
+        <is>
+          <t>nicolas.ryan.rezende@murosterrae.com.br</t>
+        </is>
+      </c>
+      <c r="DU80" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV80" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW80" t="inlineStr"/>
+      <c r="DX80" t="inlineStr"/>
+      <c r="DY80" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ80" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA80" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB80" t="inlineStr">
+        <is>
+          <t>Pós graduado(a)</t>
+        </is>
+      </c>
+      <c r="EC80" t="inlineStr">
+        <is>
+          <t>Pós graduado(a)</t>
+        </is>
+      </c>
+      <c r="ED80" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE80" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF80" t="inlineStr"/>
+      <c r="EG80" t="inlineStr"/>
+      <c r="EH80" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 11:56:41}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;asas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 11:55:55}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 11:55:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;sasasa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 11:53:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;sassas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 11:52:53}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;a &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI80" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ80" t="inlineStr">
+        <is>
+          <t>05.1 - Confecção Proposta</t>
+        </is>
+      </c>
+      <c r="EK80" t="inlineStr"/>
+      <c r="EL80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados_formularios.xlsx
+++ b/dados_formularios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL80"/>
+  <dimension ref="A1:EQ93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1125,6 +1125,31 @@
       <c r="EL1" t="inlineStr">
         <is>
           <t>contrato_prestador</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>contrato_prestador_temporario</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>data_atual</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>endereco_formatado</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>cidade_estado</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>valor_remuneracao</t>
         </is>
       </c>
     </row>
@@ -1655,6 +1680,11 @@
       </c>
       <c r="EK2" t="inlineStr"/>
       <c r="EL2" t="inlineStr"/>
+      <c r="EM2" t="inlineStr"/>
+      <c r="EN2" t="inlineStr"/>
+      <c r="EO2" t="inlineStr"/>
+      <c r="EP2" t="inlineStr"/>
+      <c r="EQ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2183,6 +2213,11 @@
       </c>
       <c r="EK3" t="inlineStr"/>
       <c r="EL3" t="inlineStr"/>
+      <c r="EM3" t="inlineStr"/>
+      <c r="EN3" t="inlineStr"/>
+      <c r="EO3" t="inlineStr"/>
+      <c r="EP3" t="inlineStr"/>
+      <c r="EQ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2619,6 +2654,11 @@
         </is>
       </c>
       <c r="EL4" t="inlineStr"/>
+      <c r="EM4" t="inlineStr"/>
+      <c r="EN4" t="inlineStr"/>
+      <c r="EO4" t="inlineStr"/>
+      <c r="EP4" t="inlineStr"/>
+      <c r="EQ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3055,6 +3095,11 @@
         </is>
       </c>
       <c r="EL5" t="inlineStr"/>
+      <c r="EM5" t="inlineStr"/>
+      <c r="EN5" t="inlineStr"/>
+      <c r="EO5" t="inlineStr"/>
+      <c r="EP5" t="inlineStr"/>
+      <c r="EQ5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3491,6 +3536,11 @@
         </is>
       </c>
       <c r="EL6" t="inlineStr"/>
+      <c r="EM6" t="inlineStr"/>
+      <c r="EN6" t="inlineStr"/>
+      <c r="EO6" t="inlineStr"/>
+      <c r="EP6" t="inlineStr"/>
+      <c r="EQ6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3927,6 +3977,11 @@
         </is>
       </c>
       <c r="EL7" t="inlineStr"/>
+      <c r="EM7" t="inlineStr"/>
+      <c r="EN7" t="inlineStr"/>
+      <c r="EO7" t="inlineStr"/>
+      <c r="EP7" t="inlineStr"/>
+      <c r="EQ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4363,6 +4418,11 @@
         </is>
       </c>
       <c r="EL8" t="inlineStr"/>
+      <c r="EM8" t="inlineStr"/>
+      <c r="EN8" t="inlineStr"/>
+      <c r="EO8" t="inlineStr"/>
+      <c r="EP8" t="inlineStr"/>
+      <c r="EQ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4799,6 +4859,11 @@
         </is>
       </c>
       <c r="EL9" t="inlineStr"/>
+      <c r="EM9" t="inlineStr"/>
+      <c r="EN9" t="inlineStr"/>
+      <c r="EO9" t="inlineStr"/>
+      <c r="EP9" t="inlineStr"/>
+      <c r="EQ9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5235,6 +5300,11 @@
         </is>
       </c>
       <c r="EL10" t="inlineStr"/>
+      <c r="EM10" t="inlineStr"/>
+      <c r="EN10" t="inlineStr"/>
+      <c r="EO10" t="inlineStr"/>
+      <c r="EP10" t="inlineStr"/>
+      <c r="EQ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5671,6 +5741,11 @@
         </is>
       </c>
       <c r="EL11" t="inlineStr"/>
+      <c r="EM11" t="inlineStr"/>
+      <c r="EN11" t="inlineStr"/>
+      <c r="EO11" t="inlineStr"/>
+      <c r="EP11" t="inlineStr"/>
+      <c r="EQ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6107,6 +6182,11 @@
         </is>
       </c>
       <c r="EL12" t="inlineStr"/>
+      <c r="EM12" t="inlineStr"/>
+      <c r="EN12" t="inlineStr"/>
+      <c r="EO12" t="inlineStr"/>
+      <c r="EP12" t="inlineStr"/>
+      <c r="EQ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6543,6 +6623,11 @@
         </is>
       </c>
       <c r="EL13" t="inlineStr"/>
+      <c r="EM13" t="inlineStr"/>
+      <c r="EN13" t="inlineStr"/>
+      <c r="EO13" t="inlineStr"/>
+      <c r="EP13" t="inlineStr"/>
+      <c r="EQ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6979,6 +7064,11 @@
         </is>
       </c>
       <c r="EL14" t="inlineStr"/>
+      <c r="EM14" t="inlineStr"/>
+      <c r="EN14" t="inlineStr"/>
+      <c r="EO14" t="inlineStr"/>
+      <c r="EP14" t="inlineStr"/>
+      <c r="EQ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7415,6 +7505,11 @@
         </is>
       </c>
       <c r="EL15" t="inlineStr"/>
+      <c r="EM15" t="inlineStr"/>
+      <c r="EN15" t="inlineStr"/>
+      <c r="EO15" t="inlineStr"/>
+      <c r="EP15" t="inlineStr"/>
+      <c r="EQ15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7851,6 +7946,11 @@
         </is>
       </c>
       <c r="EL16" t="inlineStr"/>
+      <c r="EM16" t="inlineStr"/>
+      <c r="EN16" t="inlineStr"/>
+      <c r="EO16" t="inlineStr"/>
+      <c r="EP16" t="inlineStr"/>
+      <c r="EQ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8287,6 +8387,11 @@
         </is>
       </c>
       <c r="EL17" t="inlineStr"/>
+      <c r="EM17" t="inlineStr"/>
+      <c r="EN17" t="inlineStr"/>
+      <c r="EO17" t="inlineStr"/>
+      <c r="EP17" t="inlineStr"/>
+      <c r="EQ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8723,6 +8828,11 @@
         </is>
       </c>
       <c r="EL18" t="inlineStr"/>
+      <c r="EM18" t="inlineStr"/>
+      <c r="EN18" t="inlineStr"/>
+      <c r="EO18" t="inlineStr"/>
+      <c r="EP18" t="inlineStr"/>
+      <c r="EQ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9159,6 +9269,11 @@
         </is>
       </c>
       <c r="EL19" t="inlineStr"/>
+      <c r="EM19" t="inlineStr"/>
+      <c r="EN19" t="inlineStr"/>
+      <c r="EO19" t="inlineStr"/>
+      <c r="EP19" t="inlineStr"/>
+      <c r="EQ19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9595,6 +9710,11 @@
         </is>
       </c>
       <c r="EL20" t="inlineStr"/>
+      <c r="EM20" t="inlineStr"/>
+      <c r="EN20" t="inlineStr"/>
+      <c r="EO20" t="inlineStr"/>
+      <c r="EP20" t="inlineStr"/>
+      <c r="EQ20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10031,6 +10151,11 @@
         </is>
       </c>
       <c r="EL21" t="inlineStr"/>
+      <c r="EM21" t="inlineStr"/>
+      <c r="EN21" t="inlineStr"/>
+      <c r="EO21" t="inlineStr"/>
+      <c r="EP21" t="inlineStr"/>
+      <c r="EQ21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10467,6 +10592,11 @@
         </is>
       </c>
       <c r="EL22" t="inlineStr"/>
+      <c r="EM22" t="inlineStr"/>
+      <c r="EN22" t="inlineStr"/>
+      <c r="EO22" t="inlineStr"/>
+      <c r="EP22" t="inlineStr"/>
+      <c r="EQ22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10903,6 +11033,11 @@
         </is>
       </c>
       <c r="EL23" t="inlineStr"/>
+      <c r="EM23" t="inlineStr"/>
+      <c r="EN23" t="inlineStr"/>
+      <c r="EO23" t="inlineStr"/>
+      <c r="EP23" t="inlineStr"/>
+      <c r="EQ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11339,6 +11474,11 @@
         </is>
       </c>
       <c r="EL24" t="inlineStr"/>
+      <c r="EM24" t="inlineStr"/>
+      <c r="EN24" t="inlineStr"/>
+      <c r="EO24" t="inlineStr"/>
+      <c r="EP24" t="inlineStr"/>
+      <c r="EQ24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11775,6 +11915,11 @@
         </is>
       </c>
       <c r="EL25" t="inlineStr"/>
+      <c r="EM25" t="inlineStr"/>
+      <c r="EN25" t="inlineStr"/>
+      <c r="EO25" t="inlineStr"/>
+      <c r="EP25" t="inlineStr"/>
+      <c r="EQ25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -12211,6 +12356,11 @@
         </is>
       </c>
       <c r="EL26" t="inlineStr"/>
+      <c r="EM26" t="inlineStr"/>
+      <c r="EN26" t="inlineStr"/>
+      <c r="EO26" t="inlineStr"/>
+      <c r="EP26" t="inlineStr"/>
+      <c r="EQ26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -12647,6 +12797,11 @@
         </is>
       </c>
       <c r="EL27" t="inlineStr"/>
+      <c r="EM27" t="inlineStr"/>
+      <c r="EN27" t="inlineStr"/>
+      <c r="EO27" t="inlineStr"/>
+      <c r="EP27" t="inlineStr"/>
+      <c r="EQ27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -13083,6 +13238,11 @@
         </is>
       </c>
       <c r="EL28" t="inlineStr"/>
+      <c r="EM28" t="inlineStr"/>
+      <c r="EN28" t="inlineStr"/>
+      <c r="EO28" t="inlineStr"/>
+      <c r="EP28" t="inlineStr"/>
+      <c r="EQ28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -13519,6 +13679,11 @@
         </is>
       </c>
       <c r="EL29" t="inlineStr"/>
+      <c r="EM29" t="inlineStr"/>
+      <c r="EN29" t="inlineStr"/>
+      <c r="EO29" t="inlineStr"/>
+      <c r="EP29" t="inlineStr"/>
+      <c r="EQ29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -13955,6 +14120,11 @@
         </is>
       </c>
       <c r="EL30" t="inlineStr"/>
+      <c r="EM30" t="inlineStr"/>
+      <c r="EN30" t="inlineStr"/>
+      <c r="EO30" t="inlineStr"/>
+      <c r="EP30" t="inlineStr"/>
+      <c r="EQ30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -14391,6 +14561,11 @@
         </is>
       </c>
       <c r="EL31" t="inlineStr"/>
+      <c r="EM31" t="inlineStr"/>
+      <c r="EN31" t="inlineStr"/>
+      <c r="EO31" t="inlineStr"/>
+      <c r="EP31" t="inlineStr"/>
+      <c r="EQ31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -14827,6 +15002,11 @@
         </is>
       </c>
       <c r="EL32" t="inlineStr"/>
+      <c r="EM32" t="inlineStr"/>
+      <c r="EN32" t="inlineStr"/>
+      <c r="EO32" t="inlineStr"/>
+      <c r="EP32" t="inlineStr"/>
+      <c r="EQ32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15263,6 +15443,11 @@
         </is>
       </c>
       <c r="EL33" t="inlineStr"/>
+      <c r="EM33" t="inlineStr"/>
+      <c r="EN33" t="inlineStr"/>
+      <c r="EO33" t="inlineStr"/>
+      <c r="EP33" t="inlineStr"/>
+      <c r="EQ33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -15699,6 +15884,11 @@
         </is>
       </c>
       <c r="EL34" t="inlineStr"/>
+      <c r="EM34" t="inlineStr"/>
+      <c r="EN34" t="inlineStr"/>
+      <c r="EO34" t="inlineStr"/>
+      <c r="EP34" t="inlineStr"/>
+      <c r="EQ34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16135,6 +16325,11 @@
         </is>
       </c>
       <c r="EL35" t="inlineStr"/>
+      <c r="EM35" t="inlineStr"/>
+      <c r="EN35" t="inlineStr"/>
+      <c r="EO35" t="inlineStr"/>
+      <c r="EP35" t="inlineStr"/>
+      <c r="EQ35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -16571,6 +16766,11 @@
         </is>
       </c>
       <c r="EL36" t="inlineStr"/>
+      <c r="EM36" t="inlineStr"/>
+      <c r="EN36" t="inlineStr"/>
+      <c r="EO36" t="inlineStr"/>
+      <c r="EP36" t="inlineStr"/>
+      <c r="EQ36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -17007,6 +17207,11 @@
         </is>
       </c>
       <c r="EL37" t="inlineStr"/>
+      <c r="EM37" t="inlineStr"/>
+      <c r="EN37" t="inlineStr"/>
+      <c r="EO37" t="inlineStr"/>
+      <c r="EP37" t="inlineStr"/>
+      <c r="EQ37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -17443,6 +17648,11 @@
         </is>
       </c>
       <c r="EL38" t="inlineStr"/>
+      <c r="EM38" t="inlineStr"/>
+      <c r="EN38" t="inlineStr"/>
+      <c r="EO38" t="inlineStr"/>
+      <c r="EP38" t="inlineStr"/>
+      <c r="EQ38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -17879,6 +18089,11 @@
         </is>
       </c>
       <c r="EL39" t="inlineStr"/>
+      <c r="EM39" t="inlineStr"/>
+      <c r="EN39" t="inlineStr"/>
+      <c r="EO39" t="inlineStr"/>
+      <c r="EP39" t="inlineStr"/>
+      <c r="EQ39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -18315,6 +18530,11 @@
         </is>
       </c>
       <c r="EL40" t="inlineStr"/>
+      <c r="EM40" t="inlineStr"/>
+      <c r="EN40" t="inlineStr"/>
+      <c r="EO40" t="inlineStr"/>
+      <c r="EP40" t="inlineStr"/>
+      <c r="EQ40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -18751,6 +18971,11 @@
         </is>
       </c>
       <c r="EL41" t="inlineStr"/>
+      <c r="EM41" t="inlineStr"/>
+      <c r="EN41" t="inlineStr"/>
+      <c r="EO41" t="inlineStr"/>
+      <c r="EP41" t="inlineStr"/>
+      <c r="EQ41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -19187,6 +19412,11 @@
         </is>
       </c>
       <c r="EL42" t="inlineStr"/>
+      <c r="EM42" t="inlineStr"/>
+      <c r="EN42" t="inlineStr"/>
+      <c r="EO42" t="inlineStr"/>
+      <c r="EP42" t="inlineStr"/>
+      <c r="EQ42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -19623,6 +19853,11 @@
         </is>
       </c>
       <c r="EL43" t="inlineStr"/>
+      <c r="EM43" t="inlineStr"/>
+      <c r="EN43" t="inlineStr"/>
+      <c r="EO43" t="inlineStr"/>
+      <c r="EP43" t="inlineStr"/>
+      <c r="EQ43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -20059,6 +20294,11 @@
         </is>
       </c>
       <c r="EL44" t="inlineStr"/>
+      <c r="EM44" t="inlineStr"/>
+      <c r="EN44" t="inlineStr"/>
+      <c r="EO44" t="inlineStr"/>
+      <c r="EP44" t="inlineStr"/>
+      <c r="EQ44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -20495,6 +20735,11 @@
         </is>
       </c>
       <c r="EL45" t="inlineStr"/>
+      <c r="EM45" t="inlineStr"/>
+      <c r="EN45" t="inlineStr"/>
+      <c r="EO45" t="inlineStr"/>
+      <c r="EP45" t="inlineStr"/>
+      <c r="EQ45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -20931,6 +21176,11 @@
         </is>
       </c>
       <c r="EL46" t="inlineStr"/>
+      <c r="EM46" t="inlineStr"/>
+      <c r="EN46" t="inlineStr"/>
+      <c r="EO46" t="inlineStr"/>
+      <c r="EP46" t="inlineStr"/>
+      <c r="EQ46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -21367,6 +21617,11 @@
         </is>
       </c>
       <c r="EL47" t="inlineStr"/>
+      <c r="EM47" t="inlineStr"/>
+      <c r="EN47" t="inlineStr"/>
+      <c r="EO47" t="inlineStr"/>
+      <c r="EP47" t="inlineStr"/>
+      <c r="EQ47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -21803,6 +22058,11 @@
         </is>
       </c>
       <c r="EL48" t="inlineStr"/>
+      <c r="EM48" t="inlineStr"/>
+      <c r="EN48" t="inlineStr"/>
+      <c r="EO48" t="inlineStr"/>
+      <c r="EP48" t="inlineStr"/>
+      <c r="EQ48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -22239,6 +22499,11 @@
         </is>
       </c>
       <c r="EL49" t="inlineStr"/>
+      <c r="EM49" t="inlineStr"/>
+      <c r="EN49" t="inlineStr"/>
+      <c r="EO49" t="inlineStr"/>
+      <c r="EP49" t="inlineStr"/>
+      <c r="EQ49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -22675,6 +22940,11 @@
         </is>
       </c>
       <c r="EL50" t="inlineStr"/>
+      <c r="EM50" t="inlineStr"/>
+      <c r="EN50" t="inlineStr"/>
+      <c r="EO50" t="inlineStr"/>
+      <c r="EP50" t="inlineStr"/>
+      <c r="EQ50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -23111,6 +23381,11 @@
         </is>
       </c>
       <c r="EL51" t="inlineStr"/>
+      <c r="EM51" t="inlineStr"/>
+      <c r="EN51" t="inlineStr"/>
+      <c r="EO51" t="inlineStr"/>
+      <c r="EP51" t="inlineStr"/>
+      <c r="EQ51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -23547,6 +23822,11 @@
         </is>
       </c>
       <c r="EL52" t="inlineStr"/>
+      <c r="EM52" t="inlineStr"/>
+      <c r="EN52" t="inlineStr"/>
+      <c r="EO52" t="inlineStr"/>
+      <c r="EP52" t="inlineStr"/>
+      <c r="EQ52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -23983,6 +24263,11 @@
         </is>
       </c>
       <c r="EL53" t="inlineStr"/>
+      <c r="EM53" t="inlineStr"/>
+      <c r="EN53" t="inlineStr"/>
+      <c r="EO53" t="inlineStr"/>
+      <c r="EP53" t="inlineStr"/>
+      <c r="EQ53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -24419,6 +24704,11 @@
         </is>
       </c>
       <c r="EL54" t="inlineStr"/>
+      <c r="EM54" t="inlineStr"/>
+      <c r="EN54" t="inlineStr"/>
+      <c r="EO54" t="inlineStr"/>
+      <c r="EP54" t="inlineStr"/>
+      <c r="EQ54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -24855,6 +25145,11 @@
         </is>
       </c>
       <c r="EL55" t="inlineStr"/>
+      <c r="EM55" t="inlineStr"/>
+      <c r="EN55" t="inlineStr"/>
+      <c r="EO55" t="inlineStr"/>
+      <c r="EP55" t="inlineStr"/>
+      <c r="EQ55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -25291,6 +25586,11 @@
         </is>
       </c>
       <c r="EL56" t="inlineStr"/>
+      <c r="EM56" t="inlineStr"/>
+      <c r="EN56" t="inlineStr"/>
+      <c r="EO56" t="inlineStr"/>
+      <c r="EP56" t="inlineStr"/>
+      <c r="EQ56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -25727,6 +26027,11 @@
         </is>
       </c>
       <c r="EL57" t="inlineStr"/>
+      <c r="EM57" t="inlineStr"/>
+      <c r="EN57" t="inlineStr"/>
+      <c r="EO57" t="inlineStr"/>
+      <c r="EP57" t="inlineStr"/>
+      <c r="EQ57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -26163,6 +26468,11 @@
         </is>
       </c>
       <c r="EL58" t="inlineStr"/>
+      <c r="EM58" t="inlineStr"/>
+      <c r="EN58" t="inlineStr"/>
+      <c r="EO58" t="inlineStr"/>
+      <c r="EP58" t="inlineStr"/>
+      <c r="EQ58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -26599,6 +26909,11 @@
         </is>
       </c>
       <c r="EL59" t="inlineStr"/>
+      <c r="EM59" t="inlineStr"/>
+      <c r="EN59" t="inlineStr"/>
+      <c r="EO59" t="inlineStr"/>
+      <c r="EP59" t="inlineStr"/>
+      <c r="EQ59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -27035,6 +27350,11 @@
         </is>
       </c>
       <c r="EL60" t="inlineStr"/>
+      <c r="EM60" t="inlineStr"/>
+      <c r="EN60" t="inlineStr"/>
+      <c r="EO60" t="inlineStr"/>
+      <c r="EP60" t="inlineStr"/>
+      <c r="EQ60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -27563,6 +27883,11 @@
       </c>
       <c r="EK61" t="inlineStr"/>
       <c r="EL61" t="inlineStr"/>
+      <c r="EM61" t="inlineStr"/>
+      <c r="EN61" t="inlineStr"/>
+      <c r="EO61" t="inlineStr"/>
+      <c r="EP61" t="inlineStr"/>
+      <c r="EQ61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -28091,6 +28416,11 @@
       </c>
       <c r="EK62" t="inlineStr"/>
       <c r="EL62" t="inlineStr"/>
+      <c r="EM62" t="inlineStr"/>
+      <c r="EN62" t="inlineStr"/>
+      <c r="EO62" t="inlineStr"/>
+      <c r="EP62" t="inlineStr"/>
+      <c r="EQ62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -28621,6 +28951,11 @@
       </c>
       <c r="EK63" t="inlineStr"/>
       <c r="EL63" t="inlineStr"/>
+      <c r="EM63" t="inlineStr"/>
+      <c r="EN63" t="inlineStr"/>
+      <c r="EO63" t="inlineStr"/>
+      <c r="EP63" t="inlineStr"/>
+      <c r="EQ63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -29151,6 +29486,11 @@
       </c>
       <c r="EK64" t="inlineStr"/>
       <c r="EL64" t="inlineStr"/>
+      <c r="EM64" t="inlineStr"/>
+      <c r="EN64" t="inlineStr"/>
+      <c r="EO64" t="inlineStr"/>
+      <c r="EP64" t="inlineStr"/>
+      <c r="EQ64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -29681,6 +30021,11 @@
       </c>
       <c r="EK65" t="inlineStr"/>
       <c r="EL65" t="inlineStr"/>
+      <c r="EM65" t="inlineStr"/>
+      <c r="EN65" t="inlineStr"/>
+      <c r="EO65" t="inlineStr"/>
+      <c r="EP65" t="inlineStr"/>
+      <c r="EQ65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -30209,6 +30554,11 @@
       </c>
       <c r="EK66" t="inlineStr"/>
       <c r="EL66" t="inlineStr"/>
+      <c r="EM66" t="inlineStr"/>
+      <c r="EN66" t="inlineStr"/>
+      <c r="EO66" t="inlineStr"/>
+      <c r="EP66" t="inlineStr"/>
+      <c r="EQ66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -30741,6 +31091,11 @@
       </c>
       <c r="EK67" t="inlineStr"/>
       <c r="EL67" t="inlineStr"/>
+      <c r="EM67" t="inlineStr"/>
+      <c r="EN67" t="inlineStr"/>
+      <c r="EO67" t="inlineStr"/>
+      <c r="EP67" t="inlineStr"/>
+      <c r="EQ67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -31267,6 +31622,11 @@
       </c>
       <c r="EK68" t="inlineStr"/>
       <c r="EL68" t="inlineStr"/>
+      <c r="EM68" t="inlineStr"/>
+      <c r="EN68" t="inlineStr"/>
+      <c r="EO68" t="inlineStr"/>
+      <c r="EP68" t="inlineStr"/>
+      <c r="EQ68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -31795,6 +32155,11 @@
       </c>
       <c r="EK69" t="inlineStr"/>
       <c r="EL69" t="inlineStr"/>
+      <c r="EM69" t="inlineStr"/>
+      <c r="EN69" t="inlineStr"/>
+      <c r="EO69" t="inlineStr"/>
+      <c r="EP69" t="inlineStr"/>
+      <c r="EQ69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -32327,6 +32692,11 @@
       </c>
       <c r="EK70" t="inlineStr"/>
       <c r="EL70" t="inlineStr"/>
+      <c r="EM70" t="inlineStr"/>
+      <c r="EN70" t="inlineStr"/>
+      <c r="EO70" t="inlineStr"/>
+      <c r="EP70" t="inlineStr"/>
+      <c r="EQ70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -32853,6 +33223,11 @@
       </c>
       <c r="EK71" t="inlineStr"/>
       <c r="EL71" t="inlineStr"/>
+      <c r="EM71" t="inlineStr"/>
+      <c r="EN71" t="inlineStr"/>
+      <c r="EO71" t="inlineStr"/>
+      <c r="EP71" t="inlineStr"/>
+      <c r="EQ71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -33379,6 +33754,11 @@
       </c>
       <c r="EK72" t="inlineStr"/>
       <c r="EL72" t="inlineStr"/>
+      <c r="EM72" t="inlineStr"/>
+      <c r="EN72" t="inlineStr"/>
+      <c r="EO72" t="inlineStr"/>
+      <c r="EP72" t="inlineStr"/>
+      <c r="EQ72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -33905,6 +34285,11 @@
       </c>
       <c r="EK73" t="inlineStr"/>
       <c r="EL73" t="inlineStr"/>
+      <c r="EM73" t="inlineStr"/>
+      <c r="EN73" t="inlineStr"/>
+      <c r="EO73" t="inlineStr"/>
+      <c r="EP73" t="inlineStr"/>
+      <c r="EQ73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -34431,6 +34816,11 @@
       </c>
       <c r="EK74" t="inlineStr"/>
       <c r="EL74" t="inlineStr"/>
+      <c r="EM74" t="inlineStr"/>
+      <c r="EN74" t="inlineStr"/>
+      <c r="EO74" t="inlineStr"/>
+      <c r="EP74" t="inlineStr"/>
+      <c r="EQ74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -34957,6 +35347,11 @@
       </c>
       <c r="EK75" t="inlineStr"/>
       <c r="EL75" t="inlineStr"/>
+      <c r="EM75" t="inlineStr"/>
+      <c r="EN75" t="inlineStr"/>
+      <c r="EO75" t="inlineStr"/>
+      <c r="EP75" t="inlineStr"/>
+      <c r="EQ75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -35483,6 +35878,11 @@
       </c>
       <c r="EK76" t="inlineStr"/>
       <c r="EL76" t="inlineStr"/>
+      <c r="EM76" t="inlineStr"/>
+      <c r="EN76" t="inlineStr"/>
+      <c r="EO76" t="inlineStr"/>
+      <c r="EP76" t="inlineStr"/>
+      <c r="EQ76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -36009,6 +36409,11 @@
       </c>
       <c r="EK77" t="inlineStr"/>
       <c r="EL77" t="inlineStr"/>
+      <c r="EM77" t="inlineStr"/>
+      <c r="EN77" t="inlineStr"/>
+      <c r="EO77" t="inlineStr"/>
+      <c r="EP77" t="inlineStr"/>
+      <c r="EQ77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -36535,6 +36940,11 @@
       </c>
       <c r="EK78" t="inlineStr"/>
       <c r="EL78" t="inlineStr"/>
+      <c r="EM78" t="inlineStr"/>
+      <c r="EN78" t="inlineStr"/>
+      <c r="EO78" t="inlineStr"/>
+      <c r="EP78" t="inlineStr"/>
+      <c r="EQ78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -37053,6 +37463,11 @@
       </c>
       <c r="EK79" t="inlineStr"/>
       <c r="EL79" t="inlineStr"/>
+      <c r="EM79" t="inlineStr"/>
+      <c r="EN79" t="inlineStr"/>
+      <c r="EO79" t="inlineStr"/>
+      <c r="EP79" t="inlineStr"/>
+      <c r="EQ79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -37065,47 +37480,33 @@
           <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>0121000</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>01210000013</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C80" t="n">
+        <v>144</v>
+      </c>
+      <c r="D80" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1210000013</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>22837</t>
-        </is>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>22837</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="L80" t="n">
+        <v>408</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -37117,25 +37518,19 @@
           <t>robo.relatorio@folhatech.com.br</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="O80" t="n">
+        <v>408</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Robo Cadastro Cliente</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>1782874800</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>1782918281</t>
-        </is>
+      <c r="Q80" t="n">
+        <v>1782874800</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1782918281</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -37157,10 +37552,8 @@
           <t>01/07/2026 11:52</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>22837</t>
-        </is>
+      <c r="W80" t="n">
+        <v>22837</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -37172,35 +37565,27 @@
           <t>02/07/2026 11:57</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>131521</t>
-        </is>
+      <c r="Z80" t="n">
+        <v>131521</v>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>05.1 - Confecção Proposta</t>
         </is>
       </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
+      <c r="AB80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>427</v>
       </c>
       <c r="AD80" t="inlineStr">
         <is>
           <t>tiago izaias</t>
         </is>
       </c>
-      <c r="AE80" t="inlineStr">
-        <is>
-          <t>0121</t>
-        </is>
+      <c r="AE80" t="n">
+        <v>121</v>
       </c>
       <c r="AF80" t="inlineStr">
         <is>
@@ -37217,10 +37602,8 @@
       <c r="AJ80" t="inlineStr"/>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>131521</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>131521</v>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
@@ -37252,10 +37635,8 @@
           <t>Aumento de quadro</t>
         </is>
       </c>
-      <c r="AT80" t="inlineStr">
-        <is>
-          <t>1200.00</t>
-        </is>
+      <c r="AT80" t="n">
+        <v>1200</v>
       </c>
       <c r="AU80" t="inlineStr"/>
       <c r="AV80" t="inlineStr">
@@ -37329,7 +37710,7 @@
           <t>[ ] Mouse</t>
         </is>
       </c>
-      <c r="BM80" t="b">
+      <c r="BM80" t="n">
         <v>0</v>
       </c>
       <c r="BN80" t="inlineStr"/>
@@ -37338,7 +37719,7 @@
           <t>[ ] Fone</t>
         </is>
       </c>
-      <c r="BP80" t="b">
+      <c r="BP80" t="n">
         <v>0</v>
       </c>
       <c r="BQ80" t="inlineStr"/>
@@ -37347,7 +37728,7 @@
           <t>[ ] Linha móvel</t>
         </is>
       </c>
-      <c r="BS80" t="b">
+      <c r="BS80" t="n">
         <v>0</v>
       </c>
       <c r="BT80" t="inlineStr"/>
@@ -37479,10 +37860,8 @@
           <t>Pai</t>
         </is>
       </c>
-      <c r="DE80" t="inlineStr">
-        <is>
-          <t>222124</t>
-        </is>
+      <c r="DE80" t="n">
+        <v>222124</v>
       </c>
       <c r="DF80" t="inlineStr"/>
       <c r="DG80" t="inlineStr">
@@ -37495,15 +37874,11 @@
           <t>- Selecione algo -</t>
         </is>
       </c>
-      <c r="DI80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DJ80" t="inlineStr">
-        <is>
-          <t>12344</t>
-        </is>
+      <c r="DI80" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ80" t="n">
+        <v>12344</v>
       </c>
       <c r="DK80" t="inlineStr">
         <is>
@@ -37515,10 +37890,8 @@
           <t>nicolas.ryan.rezende@murosterrae.com.br</t>
         </is>
       </c>
-      <c r="DM80" t="inlineStr">
-        <is>
-          <t>323424</t>
-        </is>
+      <c r="DM80" t="n">
+        <v>323424</v>
       </c>
       <c r="DN80" t="inlineStr"/>
       <c r="DO80" t="inlineStr">
@@ -37536,15 +37909,11 @@
           <t>Conta Internacional</t>
         </is>
       </c>
-      <c r="DR80" t="inlineStr">
-        <is>
-          <t>12121</t>
-        </is>
-      </c>
-      <c r="DS80" t="inlineStr">
-        <is>
-          <t>324401</t>
-        </is>
+      <c r="DR80" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS80" t="n">
+        <v>324401</v>
       </c>
       <c r="DT80" t="inlineStr">
         <is>
@@ -37617,6 +37986,5912 @@
       </c>
       <c r="EK80" t="inlineStr"/>
       <c r="EL80" t="inlineStr"/>
+      <c r="EM80" t="inlineStr"/>
+      <c r="EN80" t="inlineStr"/>
+      <c r="EO80" t="inlineStr"/>
+      <c r="EP80" t="inlineStr"/>
+      <c r="EQ80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>02/07/2026, 11:47:51</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>147</v>
+      </c>
+      <c r="D81" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>408</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O81" t="n">
+        <v>408</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>1782961200</v>
+      </c>
+      <c r="R81" t="n">
+        <v>1783003547</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>02/07/2026 11:45</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W81" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:17</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:18</t>
+        </is>
+      </c>
+      <c r="Z81" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE81" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AN81" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT81" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU81" t="inlineStr"/>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB81" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC81" t="inlineStr"/>
+      <c r="BD81" t="inlineStr"/>
+      <c r="BE81" t="inlineStr"/>
+      <c r="BF81" t="inlineStr"/>
+      <c r="BG81" t="inlineStr"/>
+      <c r="BH81" t="inlineStr"/>
+      <c r="BI81" t="inlineStr"/>
+      <c r="BJ81" t="inlineStr"/>
+      <c r="BK81" t="inlineStr"/>
+      <c r="BL81" t="inlineStr"/>
+      <c r="BM81" t="inlineStr"/>
+      <c r="BN81" t="inlineStr"/>
+      <c r="BO81" t="inlineStr"/>
+      <c r="BP81" t="inlineStr"/>
+      <c r="BQ81" t="inlineStr"/>
+      <c r="BR81" t="inlineStr"/>
+      <c r="BS81" t="inlineStr"/>
+      <c r="BT81" t="inlineStr"/>
+      <c r="BU81" t="inlineStr"/>
+      <c r="BV81" t="inlineStr"/>
+      <c r="BW81" t="inlineStr"/>
+      <c r="BX81" t="inlineStr"/>
+      <c r="BY81" t="inlineStr"/>
+      <c r="BZ81" t="inlineStr"/>
+      <c r="CA81" t="inlineStr"/>
+      <c r="CB81" t="inlineStr"/>
+      <c r="CC81" t="inlineStr"/>
+      <c r="CD81" t="inlineStr"/>
+      <c r="CE81" t="inlineStr"/>
+      <c r="CF81" t="inlineStr"/>
+      <c r="CG81" t="inlineStr"/>
+      <c r="CH81" t="inlineStr"/>
+      <c r="CI81" t="inlineStr"/>
+      <c r="CJ81" t="inlineStr"/>
+      <c r="CK81" t="inlineStr"/>
+      <c r="CL81" t="inlineStr"/>
+      <c r="CM81" t="inlineStr"/>
+      <c r="CN81" t="inlineStr"/>
+      <c r="CO81" t="inlineStr"/>
+      <c r="CP81" t="inlineStr"/>
+      <c r="CQ81" t="inlineStr"/>
+      <c r="CR81" t="inlineStr"/>
+      <c r="CS81" t="inlineStr"/>
+      <c r="CT81" t="inlineStr"/>
+      <c r="CU81" t="inlineStr"/>
+      <c r="CV81" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW81" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX81" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY81" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ81" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA81" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB81" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC81" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD81" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE81" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF81" t="inlineStr"/>
+      <c r="DG81" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH81" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI81" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ81" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK81" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL81" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM81" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN81" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO81" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP81" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ81" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR81" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS81" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT81" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU81" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV81" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW81" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX81" t="inlineStr"/>
+      <c r="DY81" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ81" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA81" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB81" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC81" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED81" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE81" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF81" t="inlineStr"/>
+      <c r="EG81" t="inlineStr"/>
+      <c r="EH81" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:17:12}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:16:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 11:44:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI81" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ81" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK81" t="inlineStr">
+        <is>
+          <t>Mirella Manicure</t>
+        </is>
+      </c>
+      <c r="EL81" t="inlineStr"/>
+      <c r="EM81" t="inlineStr"/>
+      <c r="EN81" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="EO81" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28, 762  - Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EP81" t="inlineStr">
+        <is>
+          <t>Mata de São João/SP</t>
+        </is>
+      </c>
+      <c r="EQ81" t="inlineStr">
+        <is>
+          <t>R$ 12.700,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>02/07/2026, 13:49:29</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>149</v>
+      </c>
+      <c r="D82" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>22837</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>408</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O82" t="n">
+        <v>408</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>1782961200</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1783010845</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>02/07/2026 13:47</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>01/07/2026 11:52</t>
+        </is>
+      </c>
+      <c r="W82" t="n">
+        <v>22837</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:20</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:21</t>
+        </is>
+      </c>
+      <c r="Z82" t="n">
+        <v>131610</v>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE82" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG82" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr"/>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="n">
+        <v>131610</v>
+      </c>
+      <c r="AN82" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP82" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ82" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT82" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AU82" t="inlineStr"/>
+      <c r="AV82" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB82" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC82" t="inlineStr"/>
+      <c r="BD82" t="inlineStr"/>
+      <c r="BE82" t="inlineStr"/>
+      <c r="BF82" t="inlineStr"/>
+      <c r="BG82" t="inlineStr"/>
+      <c r="BH82" t="inlineStr"/>
+      <c r="BI82" t="inlineStr"/>
+      <c r="BJ82" t="inlineStr"/>
+      <c r="BK82" t="inlineStr"/>
+      <c r="BL82" t="inlineStr"/>
+      <c r="BM82" t="inlineStr"/>
+      <c r="BN82" t="inlineStr"/>
+      <c r="BO82" t="inlineStr"/>
+      <c r="BP82" t="inlineStr"/>
+      <c r="BQ82" t="inlineStr"/>
+      <c r="BR82" t="inlineStr"/>
+      <c r="BS82" t="inlineStr"/>
+      <c r="BT82" t="inlineStr"/>
+      <c r="BU82" t="inlineStr"/>
+      <c r="BV82" t="inlineStr"/>
+      <c r="BW82" t="inlineStr"/>
+      <c r="BX82" t="inlineStr"/>
+      <c r="BY82" t="inlineStr"/>
+      <c r="BZ82" t="inlineStr"/>
+      <c r="CA82" t="inlineStr"/>
+      <c r="CB82" t="inlineStr"/>
+      <c r="CC82" t="inlineStr"/>
+      <c r="CD82" t="inlineStr"/>
+      <c r="CE82" t="inlineStr"/>
+      <c r="CF82" t="inlineStr"/>
+      <c r="CG82" t="inlineStr"/>
+      <c r="CH82" t="inlineStr"/>
+      <c r="CI82" t="inlineStr"/>
+      <c r="CJ82" t="inlineStr"/>
+      <c r="CK82" t="inlineStr"/>
+      <c r="CL82" t="inlineStr"/>
+      <c r="CM82" t="inlineStr"/>
+      <c r="CN82" t="inlineStr"/>
+      <c r="CO82" t="inlineStr"/>
+      <c r="CP82" t="inlineStr"/>
+      <c r="CQ82" t="inlineStr"/>
+      <c r="CR82" t="inlineStr"/>
+      <c r="CS82" t="inlineStr"/>
+      <c r="CT82" t="inlineStr"/>
+      <c r="CU82" t="inlineStr"/>
+      <c r="CV82" t="inlineStr">
+        <is>
+          <t>jaoa tomas</t>
+        </is>
+      </c>
+      <c r="CW82" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX82" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY82" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ82" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="DA82" t="inlineStr">
+        <is>
+          <t>maria santana</t>
+        </is>
+      </c>
+      <c r="DB82" t="inlineStr">
+        <is>
+          <t>kaka</t>
+        </is>
+      </c>
+      <c r="DC82" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD82" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE82" t="n">
+        <v>222124</v>
+      </c>
+      <c r="DF82" t="inlineStr"/>
+      <c r="DG82" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH82" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI82" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ82" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK82" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL82" t="inlineStr">
+        <is>
+          <t>nicolas.ryan.rezende@murosterrae.com.br</t>
+        </is>
+      </c>
+      <c r="DM82" t="n">
+        <v>323424</v>
+      </c>
+      <c r="DN82" t="inlineStr"/>
+      <c r="DO82" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP82" t="inlineStr">
+        <is>
+          <t>Conta Internacional</t>
+        </is>
+      </c>
+      <c r="DQ82" t="inlineStr">
+        <is>
+          <t>Conta Internacional</t>
+        </is>
+      </c>
+      <c r="DR82" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS82" t="n">
+        <v>324401</v>
+      </c>
+      <c r="DT82" t="inlineStr">
+        <is>
+          <t>nicolas.ryan.rezende@murosterrae.com.br</t>
+        </is>
+      </c>
+      <c r="DU82" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV82" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW82" t="inlineStr"/>
+      <c r="DX82" t="inlineStr"/>
+      <c r="DY82" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ82" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA82" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB82" t="inlineStr">
+        <is>
+          <t>Pós graduado(a)</t>
+        </is>
+      </c>
+      <c r="EC82" t="inlineStr">
+        <is>
+          <t>Pós graduado(a)</t>
+        </is>
+      </c>
+      <c r="ED82" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE82" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF82" t="inlineStr"/>
+      <c r="EG82" t="inlineStr"/>
+      <c r="EH82" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:20:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:19:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 12:07:20}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 11:56:41}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;asas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 11:55:55}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 11:55:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;sasasa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 11:53:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;sassas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 11:52:53}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;a &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI82" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ82" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK82" t="inlineStr">
+        <is>
+          <t>jaoa e maria pe de feijao</t>
+        </is>
+      </c>
+      <c r="EL82" t="inlineStr"/>
+      <c r="EM82" t="inlineStr"/>
+      <c r="EN82" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="EO82" t="inlineStr">
+        <is>
+          <t>etetetet,   - wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EP82" t="inlineStr">
+        <is>
+          <t>são paulo/SP</t>
+        </is>
+      </c>
+      <c r="EQ82" t="inlineStr">
+        <is>
+          <t>R$ 1.200,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>02/07/2026, 13:49:38</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br//triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>147</v>
+      </c>
+      <c r="D83" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>408</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O83" t="n">
+        <v>408</v>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>1782961200</v>
+      </c>
+      <c r="R83" t="n">
+        <v>1783010854</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>02/07/2026 13:47</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W83" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:17</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:18</t>
+        </is>
+      </c>
+      <c r="Z83" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD83" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE83" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG83" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr"/>
+      <c r="AJ83" t="inlineStr"/>
+      <c r="AK83" t="inlineStr"/>
+      <c r="AL83" t="inlineStr"/>
+      <c r="AM83" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AN83" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT83" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU83" t="inlineStr"/>
+      <c r="AV83" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB83" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC83" t="inlineStr"/>
+      <c r="BD83" t="inlineStr"/>
+      <c r="BE83" t="inlineStr"/>
+      <c r="BF83" t="inlineStr"/>
+      <c r="BG83" t="inlineStr"/>
+      <c r="BH83" t="inlineStr"/>
+      <c r="BI83" t="inlineStr"/>
+      <c r="BJ83" t="inlineStr"/>
+      <c r="BK83" t="inlineStr"/>
+      <c r="BL83" t="inlineStr"/>
+      <c r="BM83" t="inlineStr"/>
+      <c r="BN83" t="inlineStr"/>
+      <c r="BO83" t="inlineStr"/>
+      <c r="BP83" t="inlineStr"/>
+      <c r="BQ83" t="inlineStr"/>
+      <c r="BR83" t="inlineStr"/>
+      <c r="BS83" t="inlineStr"/>
+      <c r="BT83" t="inlineStr"/>
+      <c r="BU83" t="inlineStr"/>
+      <c r="BV83" t="inlineStr"/>
+      <c r="BW83" t="inlineStr"/>
+      <c r="BX83" t="inlineStr"/>
+      <c r="BY83" t="inlineStr"/>
+      <c r="BZ83" t="inlineStr"/>
+      <c r="CA83" t="inlineStr"/>
+      <c r="CB83" t="inlineStr"/>
+      <c r="CC83" t="inlineStr"/>
+      <c r="CD83" t="inlineStr"/>
+      <c r="CE83" t="inlineStr"/>
+      <c r="CF83" t="inlineStr"/>
+      <c r="CG83" t="inlineStr"/>
+      <c r="CH83" t="inlineStr"/>
+      <c r="CI83" t="inlineStr"/>
+      <c r="CJ83" t="inlineStr"/>
+      <c r="CK83" t="inlineStr"/>
+      <c r="CL83" t="inlineStr"/>
+      <c r="CM83" t="inlineStr"/>
+      <c r="CN83" t="inlineStr"/>
+      <c r="CO83" t="inlineStr"/>
+      <c r="CP83" t="inlineStr"/>
+      <c r="CQ83" t="inlineStr"/>
+      <c r="CR83" t="inlineStr"/>
+      <c r="CS83" t="inlineStr"/>
+      <c r="CT83" t="inlineStr"/>
+      <c r="CU83" t="inlineStr"/>
+      <c r="CV83" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW83" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX83" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY83" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ83" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA83" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB83" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC83" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD83" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE83" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF83" t="inlineStr"/>
+      <c r="DG83" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH83" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI83" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ83" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK83" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL83" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM83" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN83" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO83" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP83" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ83" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR83" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS83" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT83" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU83" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV83" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW83" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX83" t="inlineStr"/>
+      <c r="DY83" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ83" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA83" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB83" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC83" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED83" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE83" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF83" t="inlineStr"/>
+      <c r="EG83" t="inlineStr"/>
+      <c r="EH83" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:17:12}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:16:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 11:44:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI83" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ83" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK83" t="inlineStr">
+        <is>
+          <t>Mirella Manicure</t>
+        </is>
+      </c>
+      <c r="EL83" t="inlineStr"/>
+      <c r="EM83" t="inlineStr"/>
+      <c r="EN83" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="EO83" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28, 762  - Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EP83" t="inlineStr">
+        <is>
+          <t>Mata de São João/SP</t>
+        </is>
+      </c>
+      <c r="EQ83" t="inlineStr">
+        <is>
+          <t>R$ 12.700,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>02/07/2026, 15:51:04</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>149</v>
+      </c>
+      <c r="D84" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>22837</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>408</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O84" t="n">
+        <v>408</v>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>1782961200</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1783018139</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>02/07/2026 15:48</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>01/07/2026 11:52</t>
+        </is>
+      </c>
+      <c r="W84" t="n">
+        <v>22837</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:20</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:21</t>
+        </is>
+      </c>
+      <c r="Z84" t="n">
+        <v>131610</v>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB84" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE84" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr"/>
+      <c r="AJ84" t="inlineStr"/>
+      <c r="AK84" t="inlineStr"/>
+      <c r="AL84" t="inlineStr"/>
+      <c r="AM84" t="n">
+        <v>131610</v>
+      </c>
+      <c r="AN84" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP84" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT84" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AU84" t="inlineStr"/>
+      <c r="AV84" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB84" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC84" t="inlineStr"/>
+      <c r="BD84" t="inlineStr"/>
+      <c r="BE84" t="inlineStr"/>
+      <c r="BF84" t="inlineStr"/>
+      <c r="BG84" t="inlineStr"/>
+      <c r="BH84" t="inlineStr"/>
+      <c r="BI84" t="inlineStr"/>
+      <c r="BJ84" t="inlineStr"/>
+      <c r="BK84" t="inlineStr"/>
+      <c r="BL84" t="inlineStr"/>
+      <c r="BM84" t="inlineStr"/>
+      <c r="BN84" t="inlineStr"/>
+      <c r="BO84" t="inlineStr"/>
+      <c r="BP84" t="inlineStr"/>
+      <c r="BQ84" t="inlineStr"/>
+      <c r="BR84" t="inlineStr"/>
+      <c r="BS84" t="inlineStr"/>
+      <c r="BT84" t="inlineStr"/>
+      <c r="BU84" t="inlineStr"/>
+      <c r="BV84" t="inlineStr"/>
+      <c r="BW84" t="inlineStr"/>
+      <c r="BX84" t="inlineStr"/>
+      <c r="BY84" t="inlineStr"/>
+      <c r="BZ84" t="inlineStr"/>
+      <c r="CA84" t="inlineStr"/>
+      <c r="CB84" t="inlineStr"/>
+      <c r="CC84" t="inlineStr"/>
+      <c r="CD84" t="inlineStr"/>
+      <c r="CE84" t="inlineStr"/>
+      <c r="CF84" t="inlineStr"/>
+      <c r="CG84" t="inlineStr"/>
+      <c r="CH84" t="inlineStr"/>
+      <c r="CI84" t="inlineStr"/>
+      <c r="CJ84" t="inlineStr"/>
+      <c r="CK84" t="inlineStr"/>
+      <c r="CL84" t="inlineStr"/>
+      <c r="CM84" t="inlineStr"/>
+      <c r="CN84" t="inlineStr"/>
+      <c r="CO84" t="inlineStr"/>
+      <c r="CP84" t="inlineStr"/>
+      <c r="CQ84" t="inlineStr"/>
+      <c r="CR84" t="inlineStr"/>
+      <c r="CS84" t="inlineStr"/>
+      <c r="CT84" t="inlineStr"/>
+      <c r="CU84" t="inlineStr"/>
+      <c r="CV84" t="inlineStr">
+        <is>
+          <t>jaoa tomas</t>
+        </is>
+      </c>
+      <c r="CW84" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX84" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY84" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ84" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="DA84" t="inlineStr">
+        <is>
+          <t>maria santana</t>
+        </is>
+      </c>
+      <c r="DB84" t="inlineStr">
+        <is>
+          <t>kaka</t>
+        </is>
+      </c>
+      <c r="DC84" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD84" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE84" t="n">
+        <v>222124</v>
+      </c>
+      <c r="DF84" t="inlineStr"/>
+      <c r="DG84" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH84" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI84" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ84" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK84" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL84" t="inlineStr">
+        <is>
+          <t>nicolas.ryan.rezende@murosterrae.com.br</t>
+        </is>
+      </c>
+      <c r="DM84" t="n">
+        <v>323424</v>
+      </c>
+      <c r="DN84" t="inlineStr"/>
+      <c r="DO84" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP84" t="inlineStr">
+        <is>
+          <t>Conta Internacional</t>
+        </is>
+      </c>
+      <c r="DQ84" t="inlineStr">
+        <is>
+          <t>Conta Internacional</t>
+        </is>
+      </c>
+      <c r="DR84" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS84" t="n">
+        <v>324401</v>
+      </c>
+      <c r="DT84" t="inlineStr">
+        <is>
+          <t>nicolas.ryan.rezende@murosterrae.com.br</t>
+        </is>
+      </c>
+      <c r="DU84" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV84" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW84" t="inlineStr"/>
+      <c r="DX84" t="inlineStr"/>
+      <c r="DY84" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ84" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA84" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB84" t="inlineStr">
+        <is>
+          <t>Pós graduado(a)</t>
+        </is>
+      </c>
+      <c r="EC84" t="inlineStr">
+        <is>
+          <t>Pós graduado(a)</t>
+        </is>
+      </c>
+      <c r="ED84" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE84" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF84" t="inlineStr"/>
+      <c r="EG84" t="inlineStr"/>
+      <c r="EH84" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:20:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:19:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 12:07:20}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 11:56:41}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;asas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 11:55:55}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 11:55:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;sasasa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 11:53:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;sassas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 11:52:53}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;a &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI84" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ84" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK84" t="inlineStr">
+        <is>
+          <t>jaoa e maria pe de feijao</t>
+        </is>
+      </c>
+      <c r="EL84" t="inlineStr"/>
+      <c r="EM84" t="inlineStr"/>
+      <c r="EN84" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="EO84" t="inlineStr">
+        <is>
+          <t>etetetet,   - wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EP84" t="inlineStr">
+        <is>
+          <t>são paulo/SP</t>
+        </is>
+      </c>
+      <c r="EQ84" t="inlineStr">
+        <is>
+          <t>R$ 1.200,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>02/07/2026, 15:51:13</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br//triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>147</v>
+      </c>
+      <c r="D85" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>408</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O85" t="n">
+        <v>408</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>1782961200</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1783018148</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>02/07/2026 15:49</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W85" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:17</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:18</t>
+        </is>
+      </c>
+      <c r="Z85" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB85" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE85" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr"/>
+      <c r="AI85" t="inlineStr"/>
+      <c r="AJ85" t="inlineStr"/>
+      <c r="AK85" t="inlineStr"/>
+      <c r="AL85" t="inlineStr"/>
+      <c r="AM85" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AN85" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP85" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT85" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU85" t="inlineStr"/>
+      <c r="AV85" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB85" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC85" t="inlineStr"/>
+      <c r="BD85" t="inlineStr"/>
+      <c r="BE85" t="inlineStr"/>
+      <c r="BF85" t="inlineStr"/>
+      <c r="BG85" t="inlineStr"/>
+      <c r="BH85" t="inlineStr"/>
+      <c r="BI85" t="inlineStr"/>
+      <c r="BJ85" t="inlineStr"/>
+      <c r="BK85" t="inlineStr"/>
+      <c r="BL85" t="inlineStr"/>
+      <c r="BM85" t="inlineStr"/>
+      <c r="BN85" t="inlineStr"/>
+      <c r="BO85" t="inlineStr"/>
+      <c r="BP85" t="inlineStr"/>
+      <c r="BQ85" t="inlineStr"/>
+      <c r="BR85" t="inlineStr"/>
+      <c r="BS85" t="inlineStr"/>
+      <c r="BT85" t="inlineStr"/>
+      <c r="BU85" t="inlineStr"/>
+      <c r="BV85" t="inlineStr"/>
+      <c r="BW85" t="inlineStr"/>
+      <c r="BX85" t="inlineStr"/>
+      <c r="BY85" t="inlineStr"/>
+      <c r="BZ85" t="inlineStr"/>
+      <c r="CA85" t="inlineStr"/>
+      <c r="CB85" t="inlineStr"/>
+      <c r="CC85" t="inlineStr"/>
+      <c r="CD85" t="inlineStr"/>
+      <c r="CE85" t="inlineStr"/>
+      <c r="CF85" t="inlineStr"/>
+      <c r="CG85" t="inlineStr"/>
+      <c r="CH85" t="inlineStr"/>
+      <c r="CI85" t="inlineStr"/>
+      <c r="CJ85" t="inlineStr"/>
+      <c r="CK85" t="inlineStr"/>
+      <c r="CL85" t="inlineStr"/>
+      <c r="CM85" t="inlineStr"/>
+      <c r="CN85" t="inlineStr"/>
+      <c r="CO85" t="inlineStr"/>
+      <c r="CP85" t="inlineStr"/>
+      <c r="CQ85" t="inlineStr"/>
+      <c r="CR85" t="inlineStr"/>
+      <c r="CS85" t="inlineStr"/>
+      <c r="CT85" t="inlineStr"/>
+      <c r="CU85" t="inlineStr"/>
+      <c r="CV85" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW85" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX85" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY85" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ85" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA85" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB85" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC85" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD85" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE85" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF85" t="inlineStr"/>
+      <c r="DG85" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH85" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI85" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ85" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK85" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL85" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM85" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN85" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO85" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP85" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ85" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR85" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS85" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT85" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU85" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV85" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW85" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX85" t="inlineStr"/>
+      <c r="DY85" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ85" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA85" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB85" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC85" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED85" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE85" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF85" t="inlineStr"/>
+      <c r="EG85" t="inlineStr"/>
+      <c r="EH85" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:17:12}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:16:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 11:44:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI85" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ85" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK85" t="inlineStr">
+        <is>
+          <t>Mirella Manicure</t>
+        </is>
+      </c>
+      <c r="EL85" t="inlineStr"/>
+      <c r="EM85" t="inlineStr"/>
+      <c r="EN85" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="EO85" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28, 762  - Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EP85" t="inlineStr">
+        <is>
+          <t>Mata de São João/SP</t>
+        </is>
+      </c>
+      <c r="EQ85" t="inlineStr">
+        <is>
+          <t>R$ 12.700,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>02/07/2026, 15:56:36</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>149</v>
+      </c>
+      <c r="D86" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>22837</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>408</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O86" t="n">
+        <v>408</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>1782961200</v>
+      </c>
+      <c r="R86" t="n">
+        <v>1783018472</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>02/07/2026 15:54</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>01/07/2026 11:52</t>
+        </is>
+      </c>
+      <c r="W86" t="n">
+        <v>22837</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:20</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:21</t>
+        </is>
+      </c>
+      <c r="Z86" t="n">
+        <v>131610</v>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE86" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr"/>
+      <c r="AI86" t="inlineStr"/>
+      <c r="AJ86" t="inlineStr"/>
+      <c r="AK86" t="inlineStr"/>
+      <c r="AL86" t="inlineStr"/>
+      <c r="AM86" t="n">
+        <v>131610</v>
+      </c>
+      <c r="AN86" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT86" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AU86" t="inlineStr"/>
+      <c r="AV86" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB86" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC86" t="inlineStr"/>
+      <c r="BD86" t="inlineStr"/>
+      <c r="BE86" t="inlineStr"/>
+      <c r="BF86" t="inlineStr"/>
+      <c r="BG86" t="inlineStr"/>
+      <c r="BH86" t="inlineStr"/>
+      <c r="BI86" t="inlineStr"/>
+      <c r="BJ86" t="inlineStr"/>
+      <c r="BK86" t="inlineStr"/>
+      <c r="BL86" t="inlineStr"/>
+      <c r="BM86" t="inlineStr"/>
+      <c r="BN86" t="inlineStr"/>
+      <c r="BO86" t="inlineStr"/>
+      <c r="BP86" t="inlineStr"/>
+      <c r="BQ86" t="inlineStr"/>
+      <c r="BR86" t="inlineStr"/>
+      <c r="BS86" t="inlineStr"/>
+      <c r="BT86" t="inlineStr"/>
+      <c r="BU86" t="inlineStr"/>
+      <c r="BV86" t="inlineStr"/>
+      <c r="BW86" t="inlineStr"/>
+      <c r="BX86" t="inlineStr"/>
+      <c r="BY86" t="inlineStr"/>
+      <c r="BZ86" t="inlineStr"/>
+      <c r="CA86" t="inlineStr"/>
+      <c r="CB86" t="inlineStr"/>
+      <c r="CC86" t="inlineStr"/>
+      <c r="CD86" t="inlineStr"/>
+      <c r="CE86" t="inlineStr"/>
+      <c r="CF86" t="inlineStr"/>
+      <c r="CG86" t="inlineStr"/>
+      <c r="CH86" t="inlineStr"/>
+      <c r="CI86" t="inlineStr"/>
+      <c r="CJ86" t="inlineStr"/>
+      <c r="CK86" t="inlineStr"/>
+      <c r="CL86" t="inlineStr"/>
+      <c r="CM86" t="inlineStr"/>
+      <c r="CN86" t="inlineStr"/>
+      <c r="CO86" t="inlineStr"/>
+      <c r="CP86" t="inlineStr"/>
+      <c r="CQ86" t="inlineStr"/>
+      <c r="CR86" t="inlineStr"/>
+      <c r="CS86" t="inlineStr"/>
+      <c r="CT86" t="inlineStr"/>
+      <c r="CU86" t="inlineStr"/>
+      <c r="CV86" t="inlineStr">
+        <is>
+          <t>jaoa tomas</t>
+        </is>
+      </c>
+      <c r="CW86" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX86" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY86" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ86" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="DA86" t="inlineStr">
+        <is>
+          <t>maria santana</t>
+        </is>
+      </c>
+      <c r="DB86" t="inlineStr">
+        <is>
+          <t>kaka</t>
+        </is>
+      </c>
+      <c r="DC86" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD86" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE86" t="n">
+        <v>222124</v>
+      </c>
+      <c r="DF86" t="inlineStr"/>
+      <c r="DG86" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH86" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI86" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ86" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK86" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL86" t="inlineStr">
+        <is>
+          <t>nicolas.ryan.rezende@murosterrae.com.br</t>
+        </is>
+      </c>
+      <c r="DM86" t="n">
+        <v>323424</v>
+      </c>
+      <c r="DN86" t="inlineStr"/>
+      <c r="DO86" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP86" t="inlineStr">
+        <is>
+          <t>Conta Internacional</t>
+        </is>
+      </c>
+      <c r="DQ86" t="inlineStr">
+        <is>
+          <t>Conta Internacional</t>
+        </is>
+      </c>
+      <c r="DR86" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS86" t="n">
+        <v>324401</v>
+      </c>
+      <c r="DT86" t="inlineStr">
+        <is>
+          <t>nicolas.ryan.rezende@murosterrae.com.br</t>
+        </is>
+      </c>
+      <c r="DU86" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV86" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW86" t="inlineStr"/>
+      <c r="DX86" t="inlineStr"/>
+      <c r="DY86" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ86" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA86" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB86" t="inlineStr">
+        <is>
+          <t>Pós graduado(a)</t>
+        </is>
+      </c>
+      <c r="EC86" t="inlineStr">
+        <is>
+          <t>Pós graduado(a)</t>
+        </is>
+      </c>
+      <c r="ED86" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE86" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF86" t="inlineStr"/>
+      <c r="EG86" t="inlineStr"/>
+      <c r="EH86" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:20:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:19:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 12:07:20}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 11:56:41}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;asas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 11:55:55}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 11:55:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;sasasa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 11:53:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;sassas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 11:52:53}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;a &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI86" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ86" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK86" t="inlineStr">
+        <is>
+          <t>jaoa e maria pe de feijao</t>
+        </is>
+      </c>
+      <c r="EL86" t="inlineStr"/>
+      <c r="EM86" t="inlineStr"/>
+      <c r="EN86" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="EO86" t="inlineStr">
+        <is>
+          <t>etetetet,   - wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EP86" t="inlineStr">
+        <is>
+          <t>são paulo/SP</t>
+        </is>
+      </c>
+      <c r="EQ86" t="inlineStr">
+        <is>
+          <t>R$ 1.200,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>02/07/2026, 15:56:46</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br//triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>147</v>
+      </c>
+      <c r="D87" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>408</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O87" t="n">
+        <v>408</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>1782961200</v>
+      </c>
+      <c r="R87" t="n">
+        <v>1783018481</v>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>02/07/2026 15:54</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W87" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:17</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:18</t>
+        </is>
+      </c>
+      <c r="Z87" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB87" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE87" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr"/>
+      <c r="AI87" t="inlineStr"/>
+      <c r="AJ87" t="inlineStr"/>
+      <c r="AK87" t="inlineStr"/>
+      <c r="AL87" t="inlineStr"/>
+      <c r="AM87" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AN87" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP87" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT87" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU87" t="inlineStr"/>
+      <c r="AV87" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB87" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC87" t="inlineStr"/>
+      <c r="BD87" t="inlineStr"/>
+      <c r="BE87" t="inlineStr"/>
+      <c r="BF87" t="inlineStr"/>
+      <c r="BG87" t="inlineStr"/>
+      <c r="BH87" t="inlineStr"/>
+      <c r="BI87" t="inlineStr"/>
+      <c r="BJ87" t="inlineStr"/>
+      <c r="BK87" t="inlineStr"/>
+      <c r="BL87" t="inlineStr"/>
+      <c r="BM87" t="inlineStr"/>
+      <c r="BN87" t="inlineStr"/>
+      <c r="BO87" t="inlineStr"/>
+      <c r="BP87" t="inlineStr"/>
+      <c r="BQ87" t="inlineStr"/>
+      <c r="BR87" t="inlineStr"/>
+      <c r="BS87" t="inlineStr"/>
+      <c r="BT87" t="inlineStr"/>
+      <c r="BU87" t="inlineStr"/>
+      <c r="BV87" t="inlineStr"/>
+      <c r="BW87" t="inlineStr"/>
+      <c r="BX87" t="inlineStr"/>
+      <c r="BY87" t="inlineStr"/>
+      <c r="BZ87" t="inlineStr"/>
+      <c r="CA87" t="inlineStr"/>
+      <c r="CB87" t="inlineStr"/>
+      <c r="CC87" t="inlineStr"/>
+      <c r="CD87" t="inlineStr"/>
+      <c r="CE87" t="inlineStr"/>
+      <c r="CF87" t="inlineStr"/>
+      <c r="CG87" t="inlineStr"/>
+      <c r="CH87" t="inlineStr"/>
+      <c r="CI87" t="inlineStr"/>
+      <c r="CJ87" t="inlineStr"/>
+      <c r="CK87" t="inlineStr"/>
+      <c r="CL87" t="inlineStr"/>
+      <c r="CM87" t="inlineStr"/>
+      <c r="CN87" t="inlineStr"/>
+      <c r="CO87" t="inlineStr"/>
+      <c r="CP87" t="inlineStr"/>
+      <c r="CQ87" t="inlineStr"/>
+      <c r="CR87" t="inlineStr"/>
+      <c r="CS87" t="inlineStr"/>
+      <c r="CT87" t="inlineStr"/>
+      <c r="CU87" t="inlineStr"/>
+      <c r="CV87" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW87" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX87" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY87" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ87" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA87" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB87" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC87" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD87" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE87" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF87" t="inlineStr"/>
+      <c r="DG87" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH87" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI87" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ87" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK87" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL87" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM87" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN87" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO87" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP87" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ87" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR87" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS87" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT87" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU87" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV87" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW87" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX87" t="inlineStr"/>
+      <c r="DY87" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ87" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA87" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB87" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC87" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED87" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE87" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF87" t="inlineStr"/>
+      <c r="EG87" t="inlineStr"/>
+      <c r="EH87" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:17:12}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:16:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 11:44:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI87" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ87" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK87" t="inlineStr">
+        <is>
+          <t>Mirella Manicure</t>
+        </is>
+      </c>
+      <c r="EL87" t="inlineStr"/>
+      <c r="EM87" t="inlineStr"/>
+      <c r="EN87" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="EO87" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28, 762  - Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EP87" t="inlineStr">
+        <is>
+          <t>Mata de São João/SP</t>
+        </is>
+      </c>
+      <c r="EQ87" t="inlineStr">
+        <is>
+          <t>R$ 12.700,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>02/07/2026, 16:10:37</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>149</v>
+      </c>
+      <c r="D88" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>22837</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>408</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O88" t="n">
+        <v>408</v>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>1782961200</v>
+      </c>
+      <c r="R88" t="n">
+        <v>1783019312</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:08</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>01/07/2026 11:52</t>
+        </is>
+      </c>
+      <c r="W88" t="n">
+        <v>22837</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:20</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:21</t>
+        </is>
+      </c>
+      <c r="Z88" t="n">
+        <v>131610</v>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD88" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE88" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG88" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr"/>
+      <c r="AJ88" t="inlineStr"/>
+      <c r="AK88" t="inlineStr"/>
+      <c r="AL88" t="inlineStr"/>
+      <c r="AM88" t="n">
+        <v>131610</v>
+      </c>
+      <c r="AN88" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP88" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT88" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AU88" t="inlineStr"/>
+      <c r="AV88" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB88" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC88" t="inlineStr"/>
+      <c r="BD88" t="inlineStr"/>
+      <c r="BE88" t="inlineStr"/>
+      <c r="BF88" t="inlineStr"/>
+      <c r="BG88" t="inlineStr"/>
+      <c r="BH88" t="inlineStr"/>
+      <c r="BI88" t="inlineStr"/>
+      <c r="BJ88" t="inlineStr"/>
+      <c r="BK88" t="inlineStr"/>
+      <c r="BL88" t="inlineStr"/>
+      <c r="BM88" t="inlineStr"/>
+      <c r="BN88" t="inlineStr"/>
+      <c r="BO88" t="inlineStr"/>
+      <c r="BP88" t="inlineStr"/>
+      <c r="BQ88" t="inlineStr"/>
+      <c r="BR88" t="inlineStr"/>
+      <c r="BS88" t="inlineStr"/>
+      <c r="BT88" t="inlineStr"/>
+      <c r="BU88" t="inlineStr"/>
+      <c r="BV88" t="inlineStr"/>
+      <c r="BW88" t="inlineStr"/>
+      <c r="BX88" t="inlineStr"/>
+      <c r="BY88" t="inlineStr"/>
+      <c r="BZ88" t="inlineStr"/>
+      <c r="CA88" t="inlineStr"/>
+      <c r="CB88" t="inlineStr"/>
+      <c r="CC88" t="inlineStr"/>
+      <c r="CD88" t="inlineStr"/>
+      <c r="CE88" t="inlineStr"/>
+      <c r="CF88" t="inlineStr"/>
+      <c r="CG88" t="inlineStr"/>
+      <c r="CH88" t="inlineStr"/>
+      <c r="CI88" t="inlineStr"/>
+      <c r="CJ88" t="inlineStr"/>
+      <c r="CK88" t="inlineStr"/>
+      <c r="CL88" t="inlineStr"/>
+      <c r="CM88" t="inlineStr"/>
+      <c r="CN88" t="inlineStr"/>
+      <c r="CO88" t="inlineStr"/>
+      <c r="CP88" t="inlineStr"/>
+      <c r="CQ88" t="inlineStr"/>
+      <c r="CR88" t="inlineStr"/>
+      <c r="CS88" t="inlineStr"/>
+      <c r="CT88" t="inlineStr"/>
+      <c r="CU88" t="inlineStr"/>
+      <c r="CV88" t="inlineStr">
+        <is>
+          <t>jaoa tomas</t>
+        </is>
+      </c>
+      <c r="CW88" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX88" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY88" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ88" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="DA88" t="inlineStr">
+        <is>
+          <t>maria santana</t>
+        </is>
+      </c>
+      <c r="DB88" t="inlineStr">
+        <is>
+          <t>kaka</t>
+        </is>
+      </c>
+      <c r="DC88" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD88" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE88" t="n">
+        <v>222124</v>
+      </c>
+      <c r="DF88" t="inlineStr"/>
+      <c r="DG88" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH88" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI88" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ88" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK88" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL88" t="inlineStr">
+        <is>
+          <t>nicolas.ryan.rezende@murosterrae.com.br</t>
+        </is>
+      </c>
+      <c r="DM88" t="n">
+        <v>323424</v>
+      </c>
+      <c r="DN88" t="inlineStr"/>
+      <c r="DO88" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP88" t="inlineStr">
+        <is>
+          <t>Conta Internacional</t>
+        </is>
+      </c>
+      <c r="DQ88" t="inlineStr">
+        <is>
+          <t>Conta Internacional</t>
+        </is>
+      </c>
+      <c r="DR88" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS88" t="n">
+        <v>324401</v>
+      </c>
+      <c r="DT88" t="inlineStr">
+        <is>
+          <t>nicolas.ryan.rezende@murosterrae.com.br</t>
+        </is>
+      </c>
+      <c r="DU88" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV88" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW88" t="inlineStr"/>
+      <c r="DX88" t="inlineStr"/>
+      <c r="DY88" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ88" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA88" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB88" t="inlineStr">
+        <is>
+          <t>Pós graduado(a)</t>
+        </is>
+      </c>
+      <c r="EC88" t="inlineStr">
+        <is>
+          <t>Pós graduado(a)</t>
+        </is>
+      </c>
+      <c r="ED88" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE88" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF88" t="inlineStr"/>
+      <c r="EG88" t="inlineStr"/>
+      <c r="EH88" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:20:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:19:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 12:07:20}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 11:56:41}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;asas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 11:55:55}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 11:55:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;sasasa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 11:53:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;sassas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 11:52:53}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;a &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI88" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ88" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK88" t="inlineStr">
+        <is>
+          <t>jaoa e maria pe de feijao</t>
+        </is>
+      </c>
+      <c r="EL88" t="inlineStr"/>
+      <c r="EM88" t="inlineStr"/>
+      <c r="EN88" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="EO88" t="inlineStr">
+        <is>
+          <t>etetetet,   - wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EP88" t="inlineStr">
+        <is>
+          <t>são paulo/SP</t>
+        </is>
+      </c>
+      <c r="EQ88" t="inlineStr">
+        <is>
+          <t>R$ 1.200,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>02/07/2026, 16:10:46</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br//triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>147</v>
+      </c>
+      <c r="D89" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>408</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O89" t="n">
+        <v>408</v>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>1782961200</v>
+      </c>
+      <c r="R89" t="n">
+        <v>1783019321</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:08</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W89" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:17</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:18</t>
+        </is>
+      </c>
+      <c r="Z89" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE89" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr"/>
+      <c r="AJ89" t="inlineStr"/>
+      <c r="AK89" t="inlineStr"/>
+      <c r="AL89" t="inlineStr"/>
+      <c r="AM89" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AN89" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP89" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT89" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU89" t="inlineStr"/>
+      <c r="AV89" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB89" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC89" t="inlineStr"/>
+      <c r="BD89" t="inlineStr"/>
+      <c r="BE89" t="inlineStr"/>
+      <c r="BF89" t="inlineStr"/>
+      <c r="BG89" t="inlineStr"/>
+      <c r="BH89" t="inlineStr"/>
+      <c r="BI89" t="inlineStr"/>
+      <c r="BJ89" t="inlineStr"/>
+      <c r="BK89" t="inlineStr"/>
+      <c r="BL89" t="inlineStr"/>
+      <c r="BM89" t="inlineStr"/>
+      <c r="BN89" t="inlineStr"/>
+      <c r="BO89" t="inlineStr"/>
+      <c r="BP89" t="inlineStr"/>
+      <c r="BQ89" t="inlineStr"/>
+      <c r="BR89" t="inlineStr"/>
+      <c r="BS89" t="inlineStr"/>
+      <c r="BT89" t="inlineStr"/>
+      <c r="BU89" t="inlineStr"/>
+      <c r="BV89" t="inlineStr"/>
+      <c r="BW89" t="inlineStr"/>
+      <c r="BX89" t="inlineStr"/>
+      <c r="BY89" t="inlineStr"/>
+      <c r="BZ89" t="inlineStr"/>
+      <c r="CA89" t="inlineStr"/>
+      <c r="CB89" t="inlineStr"/>
+      <c r="CC89" t="inlineStr"/>
+      <c r="CD89" t="inlineStr"/>
+      <c r="CE89" t="inlineStr"/>
+      <c r="CF89" t="inlineStr"/>
+      <c r="CG89" t="inlineStr"/>
+      <c r="CH89" t="inlineStr"/>
+      <c r="CI89" t="inlineStr"/>
+      <c r="CJ89" t="inlineStr"/>
+      <c r="CK89" t="inlineStr"/>
+      <c r="CL89" t="inlineStr"/>
+      <c r="CM89" t="inlineStr"/>
+      <c r="CN89" t="inlineStr"/>
+      <c r="CO89" t="inlineStr"/>
+      <c r="CP89" t="inlineStr"/>
+      <c r="CQ89" t="inlineStr"/>
+      <c r="CR89" t="inlineStr"/>
+      <c r="CS89" t="inlineStr"/>
+      <c r="CT89" t="inlineStr"/>
+      <c r="CU89" t="inlineStr"/>
+      <c r="CV89" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW89" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX89" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY89" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ89" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA89" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB89" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC89" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD89" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE89" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF89" t="inlineStr"/>
+      <c r="DG89" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH89" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI89" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ89" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK89" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL89" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM89" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN89" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO89" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP89" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ89" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR89" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS89" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT89" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU89" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV89" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW89" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX89" t="inlineStr"/>
+      <c r="DY89" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ89" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA89" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB89" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC89" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED89" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE89" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF89" t="inlineStr"/>
+      <c r="EG89" t="inlineStr"/>
+      <c r="EH89" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:17:12}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:16:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 11:44:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI89" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ89" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK89" t="inlineStr">
+        <is>
+          <t>Mirella Manicure</t>
+        </is>
+      </c>
+      <c r="EL89" t="inlineStr"/>
+      <c r="EM89" t="inlineStr"/>
+      <c r="EN89" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="EO89" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28, 762  - Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EP89" t="inlineStr">
+        <is>
+          <t>Mata de São João/SP</t>
+        </is>
+      </c>
+      <c r="EQ89" t="inlineStr">
+        <is>
+          <t>R$ 12.700,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>02/07/2026, 16:23:28</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>149</v>
+      </c>
+      <c r="D90" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>22837</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>408</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O90" t="n">
+        <v>408</v>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>1782961200</v>
+      </c>
+      <c r="R90" t="n">
+        <v>1783020084</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:21</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>01/07/2026 11:52</t>
+        </is>
+      </c>
+      <c r="W90" t="n">
+        <v>22837</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:20</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:21</t>
+        </is>
+      </c>
+      <c r="Z90" t="n">
+        <v>131610</v>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE90" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr"/>
+      <c r="AI90" t="inlineStr"/>
+      <c r="AJ90" t="inlineStr"/>
+      <c r="AK90" t="inlineStr"/>
+      <c r="AL90" t="inlineStr"/>
+      <c r="AM90" t="n">
+        <v>131610</v>
+      </c>
+      <c r="AN90" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT90" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AU90" t="inlineStr"/>
+      <c r="AV90" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB90" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC90" t="inlineStr"/>
+      <c r="BD90" t="inlineStr"/>
+      <c r="BE90" t="inlineStr"/>
+      <c r="BF90" t="inlineStr"/>
+      <c r="BG90" t="inlineStr"/>
+      <c r="BH90" t="inlineStr"/>
+      <c r="BI90" t="inlineStr"/>
+      <c r="BJ90" t="inlineStr"/>
+      <c r="BK90" t="inlineStr"/>
+      <c r="BL90" t="inlineStr"/>
+      <c r="BM90" t="inlineStr"/>
+      <c r="BN90" t="inlineStr"/>
+      <c r="BO90" t="inlineStr"/>
+      <c r="BP90" t="inlineStr"/>
+      <c r="BQ90" t="inlineStr"/>
+      <c r="BR90" t="inlineStr"/>
+      <c r="BS90" t="inlineStr"/>
+      <c r="BT90" t="inlineStr"/>
+      <c r="BU90" t="inlineStr"/>
+      <c r="BV90" t="inlineStr"/>
+      <c r="BW90" t="inlineStr"/>
+      <c r="BX90" t="inlineStr"/>
+      <c r="BY90" t="inlineStr"/>
+      <c r="BZ90" t="inlineStr"/>
+      <c r="CA90" t="inlineStr"/>
+      <c r="CB90" t="inlineStr"/>
+      <c r="CC90" t="inlineStr"/>
+      <c r="CD90" t="inlineStr"/>
+      <c r="CE90" t="inlineStr"/>
+      <c r="CF90" t="inlineStr"/>
+      <c r="CG90" t="inlineStr"/>
+      <c r="CH90" t="inlineStr"/>
+      <c r="CI90" t="inlineStr"/>
+      <c r="CJ90" t="inlineStr"/>
+      <c r="CK90" t="inlineStr"/>
+      <c r="CL90" t="inlineStr"/>
+      <c r="CM90" t="inlineStr"/>
+      <c r="CN90" t="inlineStr"/>
+      <c r="CO90" t="inlineStr"/>
+      <c r="CP90" t="inlineStr"/>
+      <c r="CQ90" t="inlineStr"/>
+      <c r="CR90" t="inlineStr"/>
+      <c r="CS90" t="inlineStr"/>
+      <c r="CT90" t="inlineStr"/>
+      <c r="CU90" t="inlineStr"/>
+      <c r="CV90" t="inlineStr">
+        <is>
+          <t>jaoa tomas</t>
+        </is>
+      </c>
+      <c r="CW90" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX90" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY90" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ90" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="DA90" t="inlineStr">
+        <is>
+          <t>maria santana</t>
+        </is>
+      </c>
+      <c r="DB90" t="inlineStr">
+        <is>
+          <t>kaka</t>
+        </is>
+      </c>
+      <c r="DC90" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD90" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE90" t="n">
+        <v>222124</v>
+      </c>
+      <c r="DF90" t="inlineStr"/>
+      <c r="DG90" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH90" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI90" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ90" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK90" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL90" t="inlineStr">
+        <is>
+          <t>nicolas.ryan.rezende@murosterrae.com.br</t>
+        </is>
+      </c>
+      <c r="DM90" t="n">
+        <v>323424</v>
+      </c>
+      <c r="DN90" t="inlineStr"/>
+      <c r="DO90" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP90" t="inlineStr">
+        <is>
+          <t>Conta Internacional</t>
+        </is>
+      </c>
+      <c r="DQ90" t="inlineStr">
+        <is>
+          <t>Conta Internacional</t>
+        </is>
+      </c>
+      <c r="DR90" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS90" t="n">
+        <v>324401</v>
+      </c>
+      <c r="DT90" t="inlineStr">
+        <is>
+          <t>nicolas.ryan.rezende@murosterrae.com.br</t>
+        </is>
+      </c>
+      <c r="DU90" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV90" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW90" t="inlineStr"/>
+      <c r="DX90" t="inlineStr"/>
+      <c r="DY90" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ90" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA90" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB90" t="inlineStr">
+        <is>
+          <t>Pós graduado(a)</t>
+        </is>
+      </c>
+      <c r="EC90" t="inlineStr">
+        <is>
+          <t>Pós graduado(a)</t>
+        </is>
+      </c>
+      <c r="ED90" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE90" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF90" t="inlineStr"/>
+      <c r="EG90" t="inlineStr"/>
+      <c r="EH90" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:20:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:19:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 12:07:20}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 11:56:41}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;asas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 11:55:55}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 11:55:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;sasasa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 11:53:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;sassas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 11:52:53}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;a &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI90" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ90" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK90" t="inlineStr">
+        <is>
+          <t>jaoa e maria pe de feijao</t>
+        </is>
+      </c>
+      <c r="EL90" t="inlineStr"/>
+      <c r="EM90" t="inlineStr"/>
+      <c r="EN90" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="EO90" t="inlineStr">
+        <is>
+          <t>etetetet,   - wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EP90" t="inlineStr">
+        <is>
+          <t>são paulo/SP</t>
+        </is>
+      </c>
+      <c r="EQ90" t="inlineStr">
+        <is>
+          <t>R$ 1.200,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>02/07/2026, 16:23:38</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br//triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>147</v>
+      </c>
+      <c r="D91" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>408</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O91" t="n">
+        <v>408</v>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>1782961200</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1783020093</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:21</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W91" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:17</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:18</t>
+        </is>
+      </c>
+      <c r="Z91" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE91" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr"/>
+      <c r="AI91" t="inlineStr"/>
+      <c r="AJ91" t="inlineStr"/>
+      <c r="AK91" t="inlineStr"/>
+      <c r="AL91" t="inlineStr"/>
+      <c r="AM91" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AN91" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT91" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU91" t="inlineStr"/>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr"/>
+      <c r="BD91" t="inlineStr"/>
+      <c r="BE91" t="inlineStr"/>
+      <c r="BF91" t="inlineStr"/>
+      <c r="BG91" t="inlineStr"/>
+      <c r="BH91" t="inlineStr"/>
+      <c r="BI91" t="inlineStr"/>
+      <c r="BJ91" t="inlineStr"/>
+      <c r="BK91" t="inlineStr"/>
+      <c r="BL91" t="inlineStr"/>
+      <c r="BM91" t="inlineStr"/>
+      <c r="BN91" t="inlineStr"/>
+      <c r="BO91" t="inlineStr"/>
+      <c r="BP91" t="inlineStr"/>
+      <c r="BQ91" t="inlineStr"/>
+      <c r="BR91" t="inlineStr"/>
+      <c r="BS91" t="inlineStr"/>
+      <c r="BT91" t="inlineStr"/>
+      <c r="BU91" t="inlineStr"/>
+      <c r="BV91" t="inlineStr"/>
+      <c r="BW91" t="inlineStr"/>
+      <c r="BX91" t="inlineStr"/>
+      <c r="BY91" t="inlineStr"/>
+      <c r="BZ91" t="inlineStr"/>
+      <c r="CA91" t="inlineStr"/>
+      <c r="CB91" t="inlineStr"/>
+      <c r="CC91" t="inlineStr"/>
+      <c r="CD91" t="inlineStr"/>
+      <c r="CE91" t="inlineStr"/>
+      <c r="CF91" t="inlineStr"/>
+      <c r="CG91" t="inlineStr"/>
+      <c r="CH91" t="inlineStr"/>
+      <c r="CI91" t="inlineStr"/>
+      <c r="CJ91" t="inlineStr"/>
+      <c r="CK91" t="inlineStr"/>
+      <c r="CL91" t="inlineStr"/>
+      <c r="CM91" t="inlineStr"/>
+      <c r="CN91" t="inlineStr"/>
+      <c r="CO91" t="inlineStr"/>
+      <c r="CP91" t="inlineStr"/>
+      <c r="CQ91" t="inlineStr"/>
+      <c r="CR91" t="inlineStr"/>
+      <c r="CS91" t="inlineStr"/>
+      <c r="CT91" t="inlineStr"/>
+      <c r="CU91" t="inlineStr"/>
+      <c r="CV91" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW91" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX91" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY91" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ91" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA91" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB91" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC91" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD91" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE91" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF91" t="inlineStr"/>
+      <c r="DG91" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH91" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI91" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ91" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK91" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL91" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM91" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN91" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO91" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP91" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ91" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR91" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS91" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT91" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU91" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV91" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW91" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX91" t="inlineStr"/>
+      <c r="DY91" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ91" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA91" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB91" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC91" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED91" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE91" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF91" t="inlineStr"/>
+      <c r="EG91" t="inlineStr"/>
+      <c r="EH91" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:17:12}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:16:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 11:44:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI91" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ91" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK91" t="inlineStr">
+        <is>
+          <t>Mirella Manicure</t>
+        </is>
+      </c>
+      <c r="EL91" t="inlineStr"/>
+      <c r="EM91" t="inlineStr"/>
+      <c r="EN91" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="EO91" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28, 762  - Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EP91" t="inlineStr">
+        <is>
+          <t>Mata de São João/SP</t>
+        </is>
+      </c>
+      <c r="EQ91" t="inlineStr">
+        <is>
+          <t>R$ 12.700,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>02/07/2026, 16:52:35</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>149</v>
+      </c>
+      <c r="D92" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>22837</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>408</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O92" t="n">
+        <v>408</v>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>1782961200</v>
+      </c>
+      <c r="R92" t="n">
+        <v>1783021830</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:50</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>01/07/2026 11:52</t>
+        </is>
+      </c>
+      <c r="W92" t="n">
+        <v>22837</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:20</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:21</t>
+        </is>
+      </c>
+      <c r="Z92" t="n">
+        <v>131610</v>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB92" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE92" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr"/>
+      <c r="AI92" t="inlineStr"/>
+      <c r="AJ92" t="inlineStr"/>
+      <c r="AK92" t="inlineStr"/>
+      <c r="AL92" t="inlineStr"/>
+      <c r="AM92" t="n">
+        <v>131610</v>
+      </c>
+      <c r="AN92" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT92" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AU92" t="inlineStr"/>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>Juridico</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr"/>
+      <c r="BD92" t="inlineStr"/>
+      <c r="BE92" t="inlineStr"/>
+      <c r="BF92" t="inlineStr"/>
+      <c r="BG92" t="inlineStr"/>
+      <c r="BH92" t="inlineStr"/>
+      <c r="BI92" t="inlineStr"/>
+      <c r="BJ92" t="inlineStr"/>
+      <c r="BK92" t="inlineStr"/>
+      <c r="BL92" t="inlineStr"/>
+      <c r="BM92" t="inlineStr"/>
+      <c r="BN92" t="inlineStr"/>
+      <c r="BO92" t="inlineStr"/>
+      <c r="BP92" t="inlineStr"/>
+      <c r="BQ92" t="inlineStr"/>
+      <c r="BR92" t="inlineStr"/>
+      <c r="BS92" t="inlineStr"/>
+      <c r="BT92" t="inlineStr"/>
+      <c r="BU92" t="inlineStr"/>
+      <c r="BV92" t="inlineStr"/>
+      <c r="BW92" t="inlineStr"/>
+      <c r="BX92" t="inlineStr"/>
+      <c r="BY92" t="inlineStr"/>
+      <c r="BZ92" t="inlineStr"/>
+      <c r="CA92" t="inlineStr"/>
+      <c r="CB92" t="inlineStr"/>
+      <c r="CC92" t="inlineStr"/>
+      <c r="CD92" t="inlineStr"/>
+      <c r="CE92" t="inlineStr"/>
+      <c r="CF92" t="inlineStr"/>
+      <c r="CG92" t="inlineStr"/>
+      <c r="CH92" t="inlineStr"/>
+      <c r="CI92" t="inlineStr"/>
+      <c r="CJ92" t="inlineStr"/>
+      <c r="CK92" t="inlineStr"/>
+      <c r="CL92" t="inlineStr"/>
+      <c r="CM92" t="inlineStr"/>
+      <c r="CN92" t="inlineStr"/>
+      <c r="CO92" t="inlineStr"/>
+      <c r="CP92" t="inlineStr"/>
+      <c r="CQ92" t="inlineStr"/>
+      <c r="CR92" t="inlineStr"/>
+      <c r="CS92" t="inlineStr"/>
+      <c r="CT92" t="inlineStr"/>
+      <c r="CU92" t="inlineStr"/>
+      <c r="CV92" t="inlineStr">
+        <is>
+          <t>jaoa tomas</t>
+        </is>
+      </c>
+      <c r="CW92" t="inlineStr">
+        <is>
+          <t>15/12/1985</t>
+        </is>
+      </c>
+      <c r="CX92" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY92" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ92" t="inlineStr">
+        <is>
+          <t>Pedro Santana</t>
+        </is>
+      </c>
+      <c r="DA92" t="inlineStr">
+        <is>
+          <t>maria santana</t>
+        </is>
+      </c>
+      <c r="DB92" t="inlineStr">
+        <is>
+          <t>kaka</t>
+        </is>
+      </c>
+      <c r="DC92" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD92" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE92" t="n">
+        <v>222124</v>
+      </c>
+      <c r="DF92" t="inlineStr"/>
+      <c r="DG92" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH92" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI92" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ92" t="n">
+        <v>12344</v>
+      </c>
+      <c r="DK92" t="inlineStr">
+        <is>
+          <t>042.815.546-45</t>
+        </is>
+      </c>
+      <c r="DL92" t="inlineStr">
+        <is>
+          <t>nicolas.ryan.rezende@murosterrae.com.br</t>
+        </is>
+      </c>
+      <c r="DM92" t="n">
+        <v>323424</v>
+      </c>
+      <c r="DN92" t="inlineStr"/>
+      <c r="DO92" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP92" t="inlineStr">
+        <is>
+          <t>Conta Internacional</t>
+        </is>
+      </c>
+      <c r="DQ92" t="inlineStr">
+        <is>
+          <t>Conta Internacional</t>
+        </is>
+      </c>
+      <c r="DR92" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS92" t="n">
+        <v>324401</v>
+      </c>
+      <c r="DT92" t="inlineStr">
+        <is>
+          <t>nicolas.ryan.rezende@murosterrae.com.br</t>
+        </is>
+      </c>
+      <c r="DU92" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV92" t="inlineStr">
+        <is>
+          <t>etetetet</t>
+        </is>
+      </c>
+      <c r="DW92" t="inlineStr"/>
+      <c r="DX92" t="inlineStr"/>
+      <c r="DY92" t="inlineStr">
+        <is>
+          <t>43242-523</t>
+        </is>
+      </c>
+      <c r="DZ92" t="inlineStr">
+        <is>
+          <t>wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EA92" t="inlineStr">
+        <is>
+          <t>são paulo</t>
+        </is>
+      </c>
+      <c r="EB92" t="inlineStr">
+        <is>
+          <t>Pós graduado(a)</t>
+        </is>
+      </c>
+      <c r="EC92" t="inlineStr">
+        <is>
+          <t>Pós graduado(a)</t>
+        </is>
+      </c>
+      <c r="ED92" t="inlineStr">
+        <is>
+          <t>aaa</t>
+        </is>
+      </c>
+      <c r="EE92" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF92" t="inlineStr"/>
+      <c r="EG92" t="inlineStr"/>
+      <c r="EH92" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:20:17}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:19:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 12:07:20}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 11:56:41}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;asas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 11:55:55}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 11:55:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;sasasa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 11:53:29}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;sassas &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 11:52:53}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;a &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI92" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ92" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK92" t="inlineStr">
+        <is>
+          <t>jaoa e maria pe de feijao</t>
+        </is>
+      </c>
+      <c r="EL92" t="inlineStr"/>
+      <c r="EM92" t="inlineStr"/>
+      <c r="EN92" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="EO92" t="inlineStr">
+        <is>
+          <t>etetetet,   - wrwrwrw</t>
+        </is>
+      </c>
+      <c r="EP92" t="inlineStr">
+        <is>
+          <t>são paulo/SP</t>
+        </is>
+      </c>
+      <c r="EQ92" t="inlineStr">
+        <is>
+          <t>R$ 1.200,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>02/07/2026, 16:52:44</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br//triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>0121000</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>01210000016</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>22820</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>1782961200</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>1783021839</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:50</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>22820</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:17</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:18</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>131607</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr"/>
+      <c r="AI93" t="inlineStr"/>
+      <c r="AJ93" t="inlineStr"/>
+      <c r="AK93" t="inlineStr"/>
+      <c r="AL93" t="inlineStr"/>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>131607</t>
+        </is>
+      </c>
+      <c r="AN93" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT93" t="inlineStr">
+        <is>
+          <t>12700.00</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr"/>
+      <c r="AV93" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB93" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC93" t="inlineStr"/>
+      <c r="BD93" t="inlineStr"/>
+      <c r="BE93" t="inlineStr"/>
+      <c r="BF93" t="inlineStr"/>
+      <c r="BG93" t="inlineStr"/>
+      <c r="BH93" t="inlineStr"/>
+      <c r="BI93" t="inlineStr"/>
+      <c r="BJ93" t="inlineStr"/>
+      <c r="BK93" t="inlineStr"/>
+      <c r="BL93" t="inlineStr"/>
+      <c r="BM93" t="inlineStr"/>
+      <c r="BN93" t="inlineStr"/>
+      <c r="BO93" t="inlineStr"/>
+      <c r="BP93" t="inlineStr"/>
+      <c r="BQ93" t="inlineStr"/>
+      <c r="BR93" t="inlineStr"/>
+      <c r="BS93" t="inlineStr"/>
+      <c r="BT93" t="inlineStr"/>
+      <c r="BU93" t="inlineStr"/>
+      <c r="BV93" t="inlineStr"/>
+      <c r="BW93" t="inlineStr"/>
+      <c r="BX93" t="inlineStr"/>
+      <c r="BY93" t="inlineStr"/>
+      <c r="BZ93" t="inlineStr"/>
+      <c r="CA93" t="inlineStr"/>
+      <c r="CB93" t="inlineStr"/>
+      <c r="CC93" t="inlineStr"/>
+      <c r="CD93" t="inlineStr"/>
+      <c r="CE93" t="inlineStr"/>
+      <c r="CF93" t="inlineStr"/>
+      <c r="CG93" t="inlineStr"/>
+      <c r="CH93" t="inlineStr"/>
+      <c r="CI93" t="inlineStr"/>
+      <c r="CJ93" t="inlineStr"/>
+      <c r="CK93" t="inlineStr"/>
+      <c r="CL93" t="inlineStr"/>
+      <c r="CM93" t="inlineStr"/>
+      <c r="CN93" t="inlineStr"/>
+      <c r="CO93" t="inlineStr"/>
+      <c r="CP93" t="inlineStr"/>
+      <c r="CQ93" t="inlineStr"/>
+      <c r="CR93" t="inlineStr"/>
+      <c r="CS93" t="inlineStr"/>
+      <c r="CT93" t="inlineStr"/>
+      <c r="CU93" t="inlineStr"/>
+      <c r="CV93" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW93" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX93" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY93" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ93" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA93" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB93" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC93" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD93" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE93" t="inlineStr">
+        <is>
+          <t>312423424</t>
+        </is>
+      </c>
+      <c r="DF93" t="inlineStr"/>
+      <c r="DG93" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH93" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DJ93" t="inlineStr">
+        <is>
+          <t>174280130</t>
+        </is>
+      </c>
+      <c r="DK93" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL93" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM93" t="inlineStr">
+        <is>
+          <t>1234242354</t>
+        </is>
+      </c>
+      <c r="DN93" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO93" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP93" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ93" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR93" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+      <c r="DS93" t="inlineStr">
+        <is>
+          <t>3144</t>
+        </is>
+      </c>
+      <c r="DT93" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU93" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV93" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW93" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="DX93" t="inlineStr"/>
+      <c r="DY93" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ93" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA93" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB93" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC93" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED93" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE93" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF93" t="inlineStr"/>
+      <c r="EG93" t="inlineStr"/>
+      <c r="EH93" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:17:12}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:16:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 11:44:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI93" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ93" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK93" t="inlineStr">
+        <is>
+          <t>Mirella Manicure</t>
+        </is>
+      </c>
+      <c r="EL93" t="inlineStr"/>
+      <c r="EM93" t="inlineStr"/>
+      <c r="EN93" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
+      </c>
+      <c r="EO93" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28, 762  - Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EP93" t="inlineStr">
+        <is>
+          <t>Mata de São João/SP</t>
+        </is>
+      </c>
+      <c r="EQ93" t="inlineStr">
+        <is>
+          <t>R$ 12.700,00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dados_formularios.xlsx
+++ b/dados_formularios.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EQ93"/>
+  <dimension ref="A1:EQ99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43403,47 +43403,33 @@
           <t>https://workflow.folhatech.com.br//triata/Sistema.php</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>0121000</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>01210000016</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="C93" t="n">
+        <v>147</v>
+      </c>
+      <c r="D93" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>22820</t>
-        </is>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>22820</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="L93" t="n">
+        <v>408</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -43455,25 +43441,19 @@
           <t>robo.relatorio@folhatech.com.br</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
+      <c r="O93" t="n">
+        <v>408</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Robo Cadastro Cliente</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>1782961200</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>1783021839</t>
-        </is>
+      <c r="Q93" t="n">
+        <v>1782961200</v>
+      </c>
+      <c r="R93" t="n">
+        <v>1783021839</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -43495,10 +43475,8 @@
           <t>01/07/2026 09:31</t>
         </is>
       </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>22820</t>
-        </is>
+      <c r="W93" t="n">
+        <v>22820</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -43510,35 +43488,27 @@
           <t>02/07/2026 16:18</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>131607</t>
-        </is>
+      <c r="Z93" t="n">
+        <v>131607</v>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>08 - Confecção 30 dias (Contrato)</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>427</t>
-        </is>
+      <c r="AB93" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>427</v>
       </c>
       <c r="AD93" t="inlineStr">
         <is>
           <t>tiago izaias</t>
         </is>
       </c>
-      <c r="AE93" t="inlineStr">
-        <is>
-          <t>0121</t>
-        </is>
+      <c r="AE93" t="n">
+        <v>121</v>
       </c>
       <c r="AF93" t="inlineStr">
         <is>
@@ -43555,10 +43525,8 @@
       <c r="AJ93" t="inlineStr"/>
       <c r="AK93" t="inlineStr"/>
       <c r="AL93" t="inlineStr"/>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>131607</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>131607</v>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
@@ -43590,10 +43558,8 @@
           <t>Aumento de quadro</t>
         </is>
       </c>
-      <c r="AT93" t="inlineStr">
-        <is>
-          <t>12700.00</t>
-        </is>
+      <c r="AT93" t="n">
+        <v>12700</v>
       </c>
       <c r="AU93" t="inlineStr"/>
       <c r="AV93" t="inlineStr">
@@ -43721,10 +43687,8 @@
           <t>Pai</t>
         </is>
       </c>
-      <c r="DE93" t="inlineStr">
-        <is>
-          <t>312423424</t>
-        </is>
+      <c r="DE93" t="n">
+        <v>312423424</v>
       </c>
       <c r="DF93" t="inlineStr"/>
       <c r="DG93" t="inlineStr">
@@ -43737,15 +43701,11 @@
           <t>- Selecione algo -</t>
         </is>
       </c>
-      <c r="DI93" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="DJ93" t="inlineStr">
-        <is>
-          <t>174280130</t>
-        </is>
+      <c r="DI93" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ93" t="n">
+        <v>174280130</v>
       </c>
       <c r="DK93" t="inlineStr">
         <is>
@@ -43757,10 +43717,8 @@
           <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
         </is>
       </c>
-      <c r="DM93" t="inlineStr">
-        <is>
-          <t>1234242354</t>
-        </is>
+      <c r="DM93" t="n">
+        <v>1234242354</v>
       </c>
       <c r="DN93" t="inlineStr">
         <is>
@@ -43782,15 +43740,11 @@
           <t>Conta Corrente</t>
         </is>
       </c>
-      <c r="DR93" t="inlineStr">
-        <is>
-          <t>12121</t>
-        </is>
-      </c>
-      <c r="DS93" t="inlineStr">
-        <is>
-          <t>3144</t>
-        </is>
+      <c r="DR93" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS93" t="n">
+        <v>3144</v>
       </c>
       <c r="DT93" t="inlineStr">
         <is>
@@ -43807,10 +43761,8 @@
           <t>Alameda dos Pescadores 202 Loja 28</t>
         </is>
       </c>
-      <c r="DW93" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
+      <c r="DW93" t="n">
+        <v>762</v>
       </c>
       <c r="DX93" t="inlineStr"/>
       <c r="DY93" t="inlineStr">
@@ -43888,6 +43840,2772 @@
         </is>
       </c>
       <c r="EQ93" t="inlineStr">
+        <is>
+          <t>R$ 12.700,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>03/07/2026, 15:24:44</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>147</v>
+      </c>
+      <c r="D94" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>408</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O94" t="n">
+        <v>408</v>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>1783047600</v>
+      </c>
+      <c r="R94" t="n">
+        <v>1783102953</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>03/07/2026 15:22</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W94" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:17</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:18</t>
+        </is>
+      </c>
+      <c r="Z94" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD94" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE94" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG94" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH94" t="inlineStr"/>
+      <c r="AI94" t="inlineStr"/>
+      <c r="AJ94" t="inlineStr"/>
+      <c r="AK94" t="inlineStr"/>
+      <c r="AL94" t="inlineStr"/>
+      <c r="AM94" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AN94" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT94" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU94" t="inlineStr"/>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr"/>
+      <c r="BD94" t="inlineStr"/>
+      <c r="BE94" t="inlineStr"/>
+      <c r="BF94" t="inlineStr"/>
+      <c r="BG94" t="inlineStr"/>
+      <c r="BH94" t="inlineStr"/>
+      <c r="BI94" t="inlineStr"/>
+      <c r="BJ94" t="inlineStr"/>
+      <c r="BK94" t="inlineStr"/>
+      <c r="BL94" t="inlineStr"/>
+      <c r="BM94" t="inlineStr"/>
+      <c r="BN94" t="inlineStr"/>
+      <c r="BO94" t="inlineStr"/>
+      <c r="BP94" t="inlineStr"/>
+      <c r="BQ94" t="inlineStr"/>
+      <c r="BR94" t="inlineStr"/>
+      <c r="BS94" t="inlineStr"/>
+      <c r="BT94" t="inlineStr"/>
+      <c r="BU94" t="inlineStr"/>
+      <c r="BV94" t="inlineStr"/>
+      <c r="BW94" t="inlineStr"/>
+      <c r="BX94" t="inlineStr"/>
+      <c r="BY94" t="inlineStr"/>
+      <c r="BZ94" t="inlineStr"/>
+      <c r="CA94" t="inlineStr"/>
+      <c r="CB94" t="inlineStr"/>
+      <c r="CC94" t="inlineStr"/>
+      <c r="CD94" t="inlineStr"/>
+      <c r="CE94" t="inlineStr"/>
+      <c r="CF94" t="inlineStr"/>
+      <c r="CG94" t="inlineStr"/>
+      <c r="CH94" t="inlineStr"/>
+      <c r="CI94" t="inlineStr"/>
+      <c r="CJ94" t="inlineStr"/>
+      <c r="CK94" t="inlineStr"/>
+      <c r="CL94" t="inlineStr"/>
+      <c r="CM94" t="inlineStr"/>
+      <c r="CN94" t="inlineStr"/>
+      <c r="CO94" t="inlineStr"/>
+      <c r="CP94" t="inlineStr"/>
+      <c r="CQ94" t="inlineStr"/>
+      <c r="CR94" t="inlineStr"/>
+      <c r="CS94" t="inlineStr"/>
+      <c r="CT94" t="inlineStr"/>
+      <c r="CU94" t="inlineStr"/>
+      <c r="CV94" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW94" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX94" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY94" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ94" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA94" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB94" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC94" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD94" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE94" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF94" t="inlineStr"/>
+      <c r="DG94" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH94" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI94" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ94" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK94" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL94" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM94" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN94" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO94" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP94" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ94" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR94" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS94" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT94" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU94" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV94" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW94" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX94" t="inlineStr"/>
+      <c r="DY94" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ94" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA94" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB94" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC94" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED94" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE94" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF94" t="inlineStr"/>
+      <c r="EG94" t="inlineStr"/>
+      <c r="EH94" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:17:12}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:16:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 11:44:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI94" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ94" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK94" t="inlineStr">
+        <is>
+          <t>Mirella Manicure</t>
+        </is>
+      </c>
+      <c r="EL94" t="inlineStr"/>
+      <c r="EM94" t="inlineStr"/>
+      <c r="EN94" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="EO94" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28, 762  - Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EP94" t="inlineStr">
+        <is>
+          <t>Mata de São João/SP</t>
+        </is>
+      </c>
+      <c r="EQ94" t="inlineStr">
+        <is>
+          <t>R$ 12.700,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>03/07/2026, 15:56:16</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>147</v>
+      </c>
+      <c r="D95" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>408</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O95" t="n">
+        <v>408</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>1783047600</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1783104845</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>03/07/2026 15:54</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W95" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:17</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:18</t>
+        </is>
+      </c>
+      <c r="Z95" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB95" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE95" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr"/>
+      <c r="AI95" t="inlineStr"/>
+      <c r="AJ95" t="inlineStr"/>
+      <c r="AK95" t="inlineStr"/>
+      <c r="AL95" t="inlineStr"/>
+      <c r="AM95" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AN95" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT95" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU95" t="inlineStr"/>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr"/>
+      <c r="BD95" t="inlineStr"/>
+      <c r="BE95" t="inlineStr"/>
+      <c r="BF95" t="inlineStr"/>
+      <c r="BG95" t="inlineStr"/>
+      <c r="BH95" t="inlineStr"/>
+      <c r="BI95" t="inlineStr"/>
+      <c r="BJ95" t="inlineStr"/>
+      <c r="BK95" t="inlineStr"/>
+      <c r="BL95" t="inlineStr"/>
+      <c r="BM95" t="inlineStr"/>
+      <c r="BN95" t="inlineStr"/>
+      <c r="BO95" t="inlineStr"/>
+      <c r="BP95" t="inlineStr"/>
+      <c r="BQ95" t="inlineStr"/>
+      <c r="BR95" t="inlineStr"/>
+      <c r="BS95" t="inlineStr"/>
+      <c r="BT95" t="inlineStr"/>
+      <c r="BU95" t="inlineStr"/>
+      <c r="BV95" t="inlineStr"/>
+      <c r="BW95" t="inlineStr"/>
+      <c r="BX95" t="inlineStr"/>
+      <c r="BY95" t="inlineStr"/>
+      <c r="BZ95" t="inlineStr"/>
+      <c r="CA95" t="inlineStr"/>
+      <c r="CB95" t="inlineStr"/>
+      <c r="CC95" t="inlineStr"/>
+      <c r="CD95" t="inlineStr"/>
+      <c r="CE95" t="inlineStr"/>
+      <c r="CF95" t="inlineStr"/>
+      <c r="CG95" t="inlineStr"/>
+      <c r="CH95" t="inlineStr"/>
+      <c r="CI95" t="inlineStr"/>
+      <c r="CJ95" t="inlineStr"/>
+      <c r="CK95" t="inlineStr"/>
+      <c r="CL95" t="inlineStr"/>
+      <c r="CM95" t="inlineStr"/>
+      <c r="CN95" t="inlineStr"/>
+      <c r="CO95" t="inlineStr"/>
+      <c r="CP95" t="inlineStr"/>
+      <c r="CQ95" t="inlineStr"/>
+      <c r="CR95" t="inlineStr"/>
+      <c r="CS95" t="inlineStr"/>
+      <c r="CT95" t="inlineStr"/>
+      <c r="CU95" t="inlineStr"/>
+      <c r="CV95" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW95" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX95" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY95" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ95" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA95" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB95" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC95" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD95" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE95" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF95" t="inlineStr"/>
+      <c r="DG95" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH95" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI95" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ95" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK95" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL95" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM95" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN95" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO95" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP95" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ95" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR95" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS95" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT95" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU95" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV95" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW95" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX95" t="inlineStr"/>
+      <c r="DY95" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ95" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA95" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB95" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC95" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED95" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE95" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF95" t="inlineStr"/>
+      <c r="EG95" t="inlineStr"/>
+      <c r="EH95" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:17:12}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:16:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 11:44:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI95" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ95" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK95" t="inlineStr">
+        <is>
+          <t>Mirella Manicure</t>
+        </is>
+      </c>
+      <c r="EL95" t="inlineStr"/>
+      <c r="EM95" t="inlineStr"/>
+      <c r="EN95" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="EO95" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28, 762  - Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EP95" t="inlineStr">
+        <is>
+          <t>Mata de São João/SP</t>
+        </is>
+      </c>
+      <c r="EQ95" t="inlineStr">
+        <is>
+          <t>R$ 12.700,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>03/07/2026, 16:10:33</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>147</v>
+      </c>
+      <c r="D96" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>408</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O96" t="n">
+        <v>408</v>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>1783047600</v>
+      </c>
+      <c r="R96" t="n">
+        <v>1783105702</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>03/07/2026 16:08</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W96" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:17</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:18</t>
+        </is>
+      </c>
+      <c r="Z96" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB96" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE96" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr"/>
+      <c r="AI96" t="inlineStr"/>
+      <c r="AJ96" t="inlineStr"/>
+      <c r="AK96" t="inlineStr"/>
+      <c r="AL96" t="inlineStr"/>
+      <c r="AM96" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AN96" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT96" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU96" t="inlineStr"/>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr"/>
+      <c r="BD96" t="inlineStr"/>
+      <c r="BE96" t="inlineStr"/>
+      <c r="BF96" t="inlineStr"/>
+      <c r="BG96" t="inlineStr"/>
+      <c r="BH96" t="inlineStr"/>
+      <c r="BI96" t="inlineStr"/>
+      <c r="BJ96" t="inlineStr"/>
+      <c r="BK96" t="inlineStr"/>
+      <c r="BL96" t="inlineStr"/>
+      <c r="BM96" t="inlineStr"/>
+      <c r="BN96" t="inlineStr"/>
+      <c r="BO96" t="inlineStr"/>
+      <c r="BP96" t="inlineStr"/>
+      <c r="BQ96" t="inlineStr"/>
+      <c r="BR96" t="inlineStr"/>
+      <c r="BS96" t="inlineStr"/>
+      <c r="BT96" t="inlineStr"/>
+      <c r="BU96" t="inlineStr"/>
+      <c r="BV96" t="inlineStr"/>
+      <c r="BW96" t="inlineStr"/>
+      <c r="BX96" t="inlineStr"/>
+      <c r="BY96" t="inlineStr"/>
+      <c r="BZ96" t="inlineStr"/>
+      <c r="CA96" t="inlineStr"/>
+      <c r="CB96" t="inlineStr"/>
+      <c r="CC96" t="inlineStr"/>
+      <c r="CD96" t="inlineStr"/>
+      <c r="CE96" t="inlineStr"/>
+      <c r="CF96" t="inlineStr"/>
+      <c r="CG96" t="inlineStr"/>
+      <c r="CH96" t="inlineStr"/>
+      <c r="CI96" t="inlineStr"/>
+      <c r="CJ96" t="inlineStr"/>
+      <c r="CK96" t="inlineStr"/>
+      <c r="CL96" t="inlineStr"/>
+      <c r="CM96" t="inlineStr"/>
+      <c r="CN96" t="inlineStr"/>
+      <c r="CO96" t="inlineStr"/>
+      <c r="CP96" t="inlineStr"/>
+      <c r="CQ96" t="inlineStr"/>
+      <c r="CR96" t="inlineStr"/>
+      <c r="CS96" t="inlineStr"/>
+      <c r="CT96" t="inlineStr"/>
+      <c r="CU96" t="inlineStr"/>
+      <c r="CV96" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW96" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX96" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY96" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ96" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA96" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB96" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC96" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD96" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE96" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF96" t="inlineStr"/>
+      <c r="DG96" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH96" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI96" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ96" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK96" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL96" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM96" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN96" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO96" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP96" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ96" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR96" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS96" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT96" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU96" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV96" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW96" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX96" t="inlineStr"/>
+      <c r="DY96" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ96" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA96" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB96" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC96" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED96" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE96" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF96" t="inlineStr"/>
+      <c r="EG96" t="inlineStr"/>
+      <c r="EH96" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:17:12}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:16:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 11:44:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI96" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ96" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK96" t="inlineStr">
+        <is>
+          <t>Mirella Manicure</t>
+        </is>
+      </c>
+      <c r="EL96" t="inlineStr"/>
+      <c r="EM96" t="inlineStr"/>
+      <c r="EN96" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="EO96" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28, 762  - Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EP96" t="inlineStr">
+        <is>
+          <t>Mata de São João/SP</t>
+        </is>
+      </c>
+      <c r="EQ96" t="inlineStr">
+        <is>
+          <t>R$ 12.700,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>03/07/2026, 16:14:35</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>147</v>
+      </c>
+      <c r="D97" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>408</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O97" t="n">
+        <v>408</v>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>1783047600</v>
+      </c>
+      <c r="R97" t="n">
+        <v>1783105943</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>03/07/2026 16:12</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W97" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:17</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:18</t>
+        </is>
+      </c>
+      <c r="Z97" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE97" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr"/>
+      <c r="AI97" t="inlineStr"/>
+      <c r="AJ97" t="inlineStr"/>
+      <c r="AK97" t="inlineStr"/>
+      <c r="AL97" t="inlineStr"/>
+      <c r="AM97" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AN97" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT97" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU97" t="inlineStr"/>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr"/>
+      <c r="BD97" t="inlineStr"/>
+      <c r="BE97" t="inlineStr"/>
+      <c r="BF97" t="inlineStr"/>
+      <c r="BG97" t="inlineStr"/>
+      <c r="BH97" t="inlineStr"/>
+      <c r="BI97" t="inlineStr"/>
+      <c r="BJ97" t="inlineStr"/>
+      <c r="BK97" t="inlineStr"/>
+      <c r="BL97" t="inlineStr"/>
+      <c r="BM97" t="inlineStr"/>
+      <c r="BN97" t="inlineStr"/>
+      <c r="BO97" t="inlineStr"/>
+      <c r="BP97" t="inlineStr"/>
+      <c r="BQ97" t="inlineStr"/>
+      <c r="BR97" t="inlineStr"/>
+      <c r="BS97" t="inlineStr"/>
+      <c r="BT97" t="inlineStr"/>
+      <c r="BU97" t="inlineStr"/>
+      <c r="BV97" t="inlineStr"/>
+      <c r="BW97" t="inlineStr"/>
+      <c r="BX97" t="inlineStr"/>
+      <c r="BY97" t="inlineStr"/>
+      <c r="BZ97" t="inlineStr"/>
+      <c r="CA97" t="inlineStr"/>
+      <c r="CB97" t="inlineStr"/>
+      <c r="CC97" t="inlineStr"/>
+      <c r="CD97" t="inlineStr"/>
+      <c r="CE97" t="inlineStr"/>
+      <c r="CF97" t="inlineStr"/>
+      <c r="CG97" t="inlineStr"/>
+      <c r="CH97" t="inlineStr"/>
+      <c r="CI97" t="inlineStr"/>
+      <c r="CJ97" t="inlineStr"/>
+      <c r="CK97" t="inlineStr"/>
+      <c r="CL97" t="inlineStr"/>
+      <c r="CM97" t="inlineStr"/>
+      <c r="CN97" t="inlineStr"/>
+      <c r="CO97" t="inlineStr"/>
+      <c r="CP97" t="inlineStr"/>
+      <c r="CQ97" t="inlineStr"/>
+      <c r="CR97" t="inlineStr"/>
+      <c r="CS97" t="inlineStr"/>
+      <c r="CT97" t="inlineStr"/>
+      <c r="CU97" t="inlineStr"/>
+      <c r="CV97" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW97" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX97" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY97" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ97" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA97" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB97" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC97" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD97" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE97" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF97" t="inlineStr"/>
+      <c r="DG97" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH97" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI97" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ97" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK97" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL97" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM97" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN97" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO97" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP97" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ97" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR97" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS97" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT97" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU97" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV97" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW97" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX97" t="inlineStr"/>
+      <c r="DY97" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ97" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA97" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB97" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC97" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED97" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE97" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF97" t="inlineStr"/>
+      <c r="EG97" t="inlineStr"/>
+      <c r="EH97" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:17:12}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:16:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 11:44:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI97" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ97" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK97" t="inlineStr">
+        <is>
+          <t>Mirella Manicure</t>
+        </is>
+      </c>
+      <c r="EL97" t="inlineStr"/>
+      <c r="EM97" t="inlineStr"/>
+      <c r="EN97" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="EO97" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28, 762  - Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EP97" t="inlineStr">
+        <is>
+          <t>Mata de São João/SP</t>
+        </is>
+      </c>
+      <c r="EQ97" t="inlineStr">
+        <is>
+          <t>R$ 12.700,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>03/07/2026, 16:44:16</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>147</v>
+      </c>
+      <c r="D98" t="n">
+        <v>121000</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1210000016</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>22820</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>408</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O98" t="n">
+        <v>408</v>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>1783047600</v>
+      </c>
+      <c r="R98" t="n">
+        <v>1783107724</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>03/07/2026 16:42</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W98" t="n">
+        <v>22820</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:17</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:18</t>
+        </is>
+      </c>
+      <c r="Z98" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE98" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr"/>
+      <c r="AI98" t="inlineStr"/>
+      <c r="AJ98" t="inlineStr"/>
+      <c r="AK98" t="inlineStr"/>
+      <c r="AL98" t="inlineStr"/>
+      <c r="AM98" t="n">
+        <v>131607</v>
+      </c>
+      <c r="AN98" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT98" t="n">
+        <v>12700</v>
+      </c>
+      <c r="AU98" t="inlineStr"/>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr"/>
+      <c r="BD98" t="inlineStr"/>
+      <c r="BE98" t="inlineStr"/>
+      <c r="BF98" t="inlineStr"/>
+      <c r="BG98" t="inlineStr"/>
+      <c r="BH98" t="inlineStr"/>
+      <c r="BI98" t="inlineStr"/>
+      <c r="BJ98" t="inlineStr"/>
+      <c r="BK98" t="inlineStr"/>
+      <c r="BL98" t="inlineStr"/>
+      <c r="BM98" t="inlineStr"/>
+      <c r="BN98" t="inlineStr"/>
+      <c r="BO98" t="inlineStr"/>
+      <c r="BP98" t="inlineStr"/>
+      <c r="BQ98" t="inlineStr"/>
+      <c r="BR98" t="inlineStr"/>
+      <c r="BS98" t="inlineStr"/>
+      <c r="BT98" t="inlineStr"/>
+      <c r="BU98" t="inlineStr"/>
+      <c r="BV98" t="inlineStr"/>
+      <c r="BW98" t="inlineStr"/>
+      <c r="BX98" t="inlineStr"/>
+      <c r="BY98" t="inlineStr"/>
+      <c r="BZ98" t="inlineStr"/>
+      <c r="CA98" t="inlineStr"/>
+      <c r="CB98" t="inlineStr"/>
+      <c r="CC98" t="inlineStr"/>
+      <c r="CD98" t="inlineStr"/>
+      <c r="CE98" t="inlineStr"/>
+      <c r="CF98" t="inlineStr"/>
+      <c r="CG98" t="inlineStr"/>
+      <c r="CH98" t="inlineStr"/>
+      <c r="CI98" t="inlineStr"/>
+      <c r="CJ98" t="inlineStr"/>
+      <c r="CK98" t="inlineStr"/>
+      <c r="CL98" t="inlineStr"/>
+      <c r="CM98" t="inlineStr"/>
+      <c r="CN98" t="inlineStr"/>
+      <c r="CO98" t="inlineStr"/>
+      <c r="CP98" t="inlineStr"/>
+      <c r="CQ98" t="inlineStr"/>
+      <c r="CR98" t="inlineStr"/>
+      <c r="CS98" t="inlineStr"/>
+      <c r="CT98" t="inlineStr"/>
+      <c r="CU98" t="inlineStr"/>
+      <c r="CV98" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW98" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX98" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY98" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ98" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA98" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB98" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC98" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD98" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE98" t="n">
+        <v>312423424</v>
+      </c>
+      <c r="DF98" t="inlineStr"/>
+      <c r="DG98" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH98" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI98" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ98" t="n">
+        <v>174280130</v>
+      </c>
+      <c r="DK98" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL98" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM98" t="n">
+        <v>1234242354</v>
+      </c>
+      <c r="DN98" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO98" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP98" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ98" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR98" t="n">
+        <v>12121</v>
+      </c>
+      <c r="DS98" t="n">
+        <v>3144</v>
+      </c>
+      <c r="DT98" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU98" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV98" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW98" t="n">
+        <v>762</v>
+      </c>
+      <c r="DX98" t="inlineStr"/>
+      <c r="DY98" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ98" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA98" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB98" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC98" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED98" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE98" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF98" t="inlineStr"/>
+      <c r="EG98" t="inlineStr"/>
+      <c r="EH98" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:17:12}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:16:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 11:44:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI98" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ98" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK98" t="inlineStr">
+        <is>
+          <t>Mirella Manicure</t>
+        </is>
+      </c>
+      <c r="EL98" t="inlineStr"/>
+      <c r="EM98" t="inlineStr"/>
+      <c r="EN98" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="EO98" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28, 762  - Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EP98" t="inlineStr">
+        <is>
+          <t>Mata de São João/SP</t>
+        </is>
+      </c>
+      <c r="EQ98" t="inlineStr">
+        <is>
+          <t>R$ 12.700,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>03/07/2026, 17:06:56</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/triata/Sistema.php</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>0121000</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>01210000016</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>22820</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>robo.relatorio@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Robo Cadastro Cliente</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>1783047600</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>1783109084</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>03/07/2026 17:04</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>01/07/2026 09:31</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>22820</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>01/07/2026 16:17</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>02/07/2026 16:18</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>131607</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>0121</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>Arantes - Contratação PJ</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>https://workflow.folhatech.com.br/</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr"/>
+      <c r="AJ99" t="inlineStr"/>
+      <c r="AK99" t="inlineStr"/>
+      <c r="AL99" t="inlineStr"/>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>131607</t>
+        </is>
+      </c>
+      <c r="AN99" t="inlineStr">
+        <is>
+          <t>tiago izaias</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>tiago.izaias@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>Aumento de quadro</t>
+        </is>
+      </c>
+      <c r="AT99" t="inlineStr">
+        <is>
+          <t>12700.00</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr"/>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Folha Tech</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>Fernando Andrade (Folha Tech)</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>fernando.andrade@folhatech.com.br</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr"/>
+      <c r="BD99" t="inlineStr"/>
+      <c r="BE99" t="inlineStr"/>
+      <c r="BF99" t="inlineStr"/>
+      <c r="BG99" t="inlineStr"/>
+      <c r="BH99" t="inlineStr"/>
+      <c r="BI99" t="inlineStr"/>
+      <c r="BJ99" t="inlineStr"/>
+      <c r="BK99" t="inlineStr"/>
+      <c r="BL99" t="inlineStr"/>
+      <c r="BM99" t="inlineStr"/>
+      <c r="BN99" t="inlineStr"/>
+      <c r="BO99" t="inlineStr"/>
+      <c r="BP99" t="inlineStr"/>
+      <c r="BQ99" t="inlineStr"/>
+      <c r="BR99" t="inlineStr"/>
+      <c r="BS99" t="inlineStr"/>
+      <c r="BT99" t="inlineStr"/>
+      <c r="BU99" t="inlineStr"/>
+      <c r="BV99" t="inlineStr"/>
+      <c r="BW99" t="inlineStr"/>
+      <c r="BX99" t="inlineStr"/>
+      <c r="BY99" t="inlineStr"/>
+      <c r="BZ99" t="inlineStr"/>
+      <c r="CA99" t="inlineStr"/>
+      <c r="CB99" t="inlineStr"/>
+      <c r="CC99" t="inlineStr"/>
+      <c r="CD99" t="inlineStr"/>
+      <c r="CE99" t="inlineStr"/>
+      <c r="CF99" t="inlineStr"/>
+      <c r="CG99" t="inlineStr"/>
+      <c r="CH99" t="inlineStr"/>
+      <c r="CI99" t="inlineStr"/>
+      <c r="CJ99" t="inlineStr"/>
+      <c r="CK99" t="inlineStr"/>
+      <c r="CL99" t="inlineStr"/>
+      <c r="CM99" t="inlineStr"/>
+      <c r="CN99" t="inlineStr"/>
+      <c r="CO99" t="inlineStr"/>
+      <c r="CP99" t="inlineStr"/>
+      <c r="CQ99" t="inlineStr"/>
+      <c r="CR99" t="inlineStr"/>
+      <c r="CS99" t="inlineStr"/>
+      <c r="CT99" t="inlineStr"/>
+      <c r="CU99" t="inlineStr"/>
+      <c r="CV99" t="inlineStr">
+        <is>
+          <t>Mirella Daiane Stella Lima</t>
+        </is>
+      </c>
+      <c r="CW99" t="inlineStr">
+        <is>
+          <t>24/06/2004</t>
+        </is>
+      </c>
+      <c r="CX99" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CY99" t="inlineStr">
+        <is>
+          <t>Solteiro</t>
+        </is>
+      </c>
+      <c r="CZ99" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DA99" t="inlineStr">
+        <is>
+          <t>Betina Sara Carla</t>
+        </is>
+      </c>
+      <c r="DB99" t="inlineStr">
+        <is>
+          <t>Fernando Osvaldo Raul Lima</t>
+        </is>
+      </c>
+      <c r="DC99" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DD99" t="inlineStr">
+        <is>
+          <t>Pai</t>
+        </is>
+      </c>
+      <c r="DE99" t="inlineStr">
+        <is>
+          <t>312423424</t>
+        </is>
+      </c>
+      <c r="DF99" t="inlineStr"/>
+      <c r="DG99" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DH99" t="inlineStr">
+        <is>
+          <t>- Selecione algo -</t>
+        </is>
+      </c>
+      <c r="DI99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="DJ99" t="inlineStr">
+        <is>
+          <t>174280130</t>
+        </is>
+      </c>
+      <c r="DK99" t="inlineStr">
+        <is>
+          <t>579.445.157-26</t>
+        </is>
+      </c>
+      <c r="DL99" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.br</t>
+        </is>
+      </c>
+      <c r="DM99" t="inlineStr">
+        <is>
+          <t>1234242354</t>
+        </is>
+      </c>
+      <c r="DN99" t="inlineStr">
+        <is>
+          <t>98.923.964/0001-06</t>
+        </is>
+      </c>
+      <c r="DO99" t="inlineStr">
+        <is>
+          <t>Nubank</t>
+        </is>
+      </c>
+      <c r="DP99" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DQ99" t="inlineStr">
+        <is>
+          <t>Conta Corrente</t>
+        </is>
+      </c>
+      <c r="DR99" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+      <c r="DS99" t="inlineStr">
+        <is>
+          <t>3144</t>
+        </is>
+      </c>
+      <c r="DT99" t="inlineStr">
+        <is>
+          <t>mirella_daiane_lima@a-qualitybrasil.com.</t>
+        </is>
+      </c>
+      <c r="DU99" t="inlineStr">
+        <is>
+          <t>tetwetete</t>
+        </is>
+      </c>
+      <c r="DV99" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28</t>
+        </is>
+      </c>
+      <c r="DW99" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="DX99" t="inlineStr"/>
+      <c r="DY99" t="inlineStr">
+        <is>
+          <t>42880-971</t>
+        </is>
+      </c>
+      <c r="DZ99" t="inlineStr">
+        <is>
+          <t>Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EA99" t="inlineStr">
+        <is>
+          <t>Mata de São João</t>
+        </is>
+      </c>
+      <c r="EB99" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="EC99" t="inlineStr">
+        <is>
+          <t>Ensino superior completo</t>
+        </is>
+      </c>
+      <c r="ED99" t="inlineStr">
+        <is>
+          <t>adm</t>
+        </is>
+      </c>
+      <c r="EE99" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="EF99" t="inlineStr"/>
+      <c r="EG99" t="inlineStr"/>
+      <c r="EH99" t="inlineStr">
+        <is>
+          <t>_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 07 - Sistema / Equipamento TI&lt;br&gt;Pedro Santana - {{2026-07-01 16:17:12}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 06 - Proposta&lt;br&gt;Adrielly Santana - {{2026-07-01 16:16:28}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;segue &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 05.1 - Confecção Proposta&lt;br&gt;Robo Cadastro Cliente - {{2026-07-01 11:44:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;concluido pelo robo &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 05 - Validação jurídico&lt;br&gt;Leonardo Toledo - {{2026-07-01 09:36:50}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;ok &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 04 - Aprovação gestor&lt;br&gt;tiago izaias - {{2026-07-01 09:36:34}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 03 - Recrutamento&lt;br&gt;Luana Lidia - {{2026-07-01 09:36:14}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_1"&gt;{{TAREFA}}: 02 - Aprovação Financeiro&lt;br&gt;Jefferson Silva - {{2026-07-01 09:32:24}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_1"&gt;aaa &lt;/div&gt;_BR_TRIATA_&lt;div class="hist_autor hist_cor_2"&gt;{{TAREFA}}: 01 - Requisição&lt;br&gt;tiago izaias - {{2026-07-01 09:32:02}}&lt;/div&gt;&lt;div class="hist_texto hist_cor_2"&gt;aaa &lt;/div&gt;</t>
+        </is>
+      </c>
+      <c r="EI99" t="inlineStr">
+        <is>
+          <t>{{TAREFA}}: 08 - Confecção 30 dias (Contrato)&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="EJ99" t="inlineStr">
+        <is>
+          <t>08 - Confecção 30 dias (Contrato)</t>
+        </is>
+      </c>
+      <c r="EK99" t="inlineStr">
+        <is>
+          <t>Mirella Manicure</t>
+        </is>
+      </c>
+      <c r="EL99" t="inlineStr"/>
+      <c r="EM99" t="inlineStr"/>
+      <c r="EN99" t="inlineStr">
+        <is>
+          <t>03/07/2026</t>
+        </is>
+      </c>
+      <c r="EO99" t="inlineStr">
+        <is>
+          <t>Alameda dos Pescadores 202 Loja 28, 762  - Praia do Forte</t>
+        </is>
+      </c>
+      <c r="EP99" t="inlineStr">
+        <is>
+          <t>Mata de São João/SP</t>
+        </is>
+      </c>
+      <c r="EQ99" t="inlineStr">
         <is>
           <t>R$ 12.700,00</t>
         </is>
